--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -45,6 +45,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -61,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -79,6 +84,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -65219,6 +65230,5186 @@
         <v>143.31</v>
       </c>
     </row>
+    <row r="5903">
+      <c r="A5903" s="6">
+        <v>46098.0</v>
+      </c>
+      <c r="B5903" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5903" s="7">
+        <v>142.9603</v>
+      </c>
+    </row>
+    <row r="5904">
+      <c r="A5904" s="6">
+        <v>46099.0</v>
+      </c>
+      <c r="B5904" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5904" s="7">
+        <v>149.868039</v>
+      </c>
+    </row>
+    <row r="5905">
+      <c r="A5905" s="6">
+        <v>46100.0</v>
+      </c>
+      <c r="B5905" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5905" s="7">
+        <v>139.21633</v>
+      </c>
+    </row>
+    <row r="5906">
+      <c r="A5906" s="6">
+        <v>46101.0</v>
+      </c>
+      <c r="B5906" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5906" s="7">
+        <v>157.454769</v>
+      </c>
+    </row>
+    <row r="5907">
+      <c r="A5907" s="6">
+        <v>46102.0</v>
+      </c>
+      <c r="B5907" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5907" s="7">
+        <v>148.551728</v>
+      </c>
+    </row>
+    <row r="5908">
+      <c r="A5908" s="6">
+        <v>46103.0</v>
+      </c>
+      <c r="B5908" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5908" s="7">
+        <v>161.892417</v>
+      </c>
+    </row>
+    <row r="5909">
+      <c r="A5909" s="6">
+        <v>46104.0</v>
+      </c>
+      <c r="B5909" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5909" s="7">
+        <v>165.243774</v>
+      </c>
+    </row>
+    <row r="5910">
+      <c r="A5910" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="B5910" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5910" s="7">
+        <v>139.877856</v>
+      </c>
+    </row>
+    <row r="5911">
+      <c r="A5911" s="6">
+        <v>46106.0</v>
+      </c>
+      <c r="B5911" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5911" s="7">
+        <v>138.051181</v>
+      </c>
+    </row>
+    <row r="5912">
+      <c r="A5912" s="6">
+        <v>46107.0</v>
+      </c>
+      <c r="B5912" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5912" s="7">
+        <v>144.048499</v>
+      </c>
+    </row>
+    <row r="5913">
+      <c r="A5913" s="6">
+        <v>46108.0</v>
+      </c>
+      <c r="B5913" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5913" s="7">
+        <v>148.349492</v>
+      </c>
+    </row>
+    <row r="5914">
+      <c r="A5914" s="6">
+        <v>46109.0</v>
+      </c>
+      <c r="B5914" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5914" s="7">
+        <v>114.544443</v>
+      </c>
+    </row>
+    <row r="5915">
+      <c r="A5915" s="6">
+        <v>46110.0</v>
+      </c>
+      <c r="B5915" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5915" s="7">
+        <v>116.933452</v>
+      </c>
+    </row>
+    <row r="5916">
+      <c r="A5916" s="6">
+        <v>46111.0</v>
+      </c>
+      <c r="B5916" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5916" s="7">
+        <v>151.025505</v>
+      </c>
+    </row>
+    <row r="5917">
+      <c r="A5917" s="6">
+        <v>46112.0</v>
+      </c>
+      <c r="B5917" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5917" s="7">
+        <v>156.020675</v>
+      </c>
+    </row>
+    <row r="5918">
+      <c r="A5918" s="6">
+        <v>46113.0</v>
+      </c>
+      <c r="B5918" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5918" s="7">
+        <v>159.990538</v>
+      </c>
+    </row>
+    <row r="5919">
+      <c r="A5919" s="6">
+        <v>46114.0</v>
+      </c>
+      <c r="B5919" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5919" s="7">
+        <v>148.5102</v>
+      </c>
+    </row>
+    <row r="5920">
+      <c r="A5920" s="6">
+        <v>46115.0</v>
+      </c>
+      <c r="B5920" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5920" s="7">
+        <v>122.767547</v>
+      </c>
+    </row>
+    <row r="5921">
+      <c r="A5921" s="6">
+        <v>46116.0</v>
+      </c>
+      <c r="B5921" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5921" s="7">
+        <v>113.457711</v>
+      </c>
+    </row>
+    <row r="5922">
+      <c r="A5922" s="6">
+        <v>46117.0</v>
+      </c>
+      <c r="B5922" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5922" s="7">
+        <v>101.259583</v>
+      </c>
+    </row>
+    <row r="5923">
+      <c r="A5923" s="6">
+        <v>46118.0</v>
+      </c>
+      <c r="B5923" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5923" s="7">
+        <v>108.845358</v>
+      </c>
+    </row>
+    <row r="5924">
+      <c r="A5924" s="6">
+        <v>46119.0</v>
+      </c>
+      <c r="B5924" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5924" s="7">
+        <v>127.924371</v>
+      </c>
+    </row>
+    <row r="5925">
+      <c r="A5925" s="6">
+        <v>46120.0</v>
+      </c>
+      <c r="B5925" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5925" s="7">
+        <v>127.976949</v>
+      </c>
+    </row>
+    <row r="5926">
+      <c r="A5926" s="6">
+        <v>46121.0</v>
+      </c>
+      <c r="B5926" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5926" s="7">
+        <v>122.681112</v>
+      </c>
+    </row>
+    <row r="5927">
+      <c r="A5927" s="6">
+        <v>46122.0</v>
+      </c>
+      <c r="B5927" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5927" s="7">
+        <v>129.670221</v>
+      </c>
+    </row>
+    <row r="5928">
+      <c r="A5928" s="6">
+        <v>46123.0</v>
+      </c>
+      <c r="B5928" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5928" s="7">
+        <v>120.948904</v>
+      </c>
+    </row>
+    <row r="5929">
+      <c r="A5929" s="6">
+        <v>46124.0</v>
+      </c>
+      <c r="B5929" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5929" s="7">
+        <v>101.194572</v>
+      </c>
+    </row>
+    <row r="5930">
+      <c r="A5930" s="6">
+        <v>46125.0</v>
+      </c>
+      <c r="B5930" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5930" s="7">
+        <v>141.857965</v>
+      </c>
+    </row>
+    <row r="5931">
+      <c r="A5931" s="6">
+        <v>46126.0</v>
+      </c>
+      <c r="B5931" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5931" s="7">
+        <v>150.624876</v>
+      </c>
+    </row>
+    <row r="5932">
+      <c r="A5932" s="6">
+        <v>46127.0</v>
+      </c>
+      <c r="B5932" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5932" s="7">
+        <v>140.194363</v>
+      </c>
+    </row>
+    <row r="5933">
+      <c r="A5933" s="2"/>
+      <c r="B5933" s="5"/>
+      <c r="C5933" s="3"/>
+    </row>
+    <row r="5934">
+      <c r="A5934" s="2"/>
+      <c r="B5934" s="5"/>
+      <c r="C5934" s="3"/>
+    </row>
+    <row r="5935">
+      <c r="A5935" s="2"/>
+      <c r="B5935" s="5"/>
+      <c r="C5935" s="3"/>
+    </row>
+    <row r="5936">
+      <c r="A5936" s="2"/>
+      <c r="B5936" s="5"/>
+      <c r="C5936" s="3"/>
+    </row>
+    <row r="5937">
+      <c r="A5937" s="2"/>
+      <c r="B5937" s="5"/>
+      <c r="C5937" s="3"/>
+    </row>
+    <row r="5938">
+      <c r="A5938" s="2"/>
+      <c r="B5938" s="5"/>
+      <c r="C5938" s="3"/>
+    </row>
+    <row r="5939">
+      <c r="A5939" s="2"/>
+      <c r="B5939" s="5"/>
+      <c r="C5939" s="3"/>
+    </row>
+    <row r="5940">
+      <c r="A5940" s="2"/>
+      <c r="B5940" s="5"/>
+      <c r="C5940" s="3"/>
+    </row>
+    <row r="5941">
+      <c r="A5941" s="2"/>
+      <c r="B5941" s="5"/>
+      <c r="C5941" s="3"/>
+    </row>
+    <row r="5942">
+      <c r="A5942" s="2"/>
+      <c r="B5942" s="5"/>
+      <c r="C5942" s="3"/>
+    </row>
+    <row r="5943">
+      <c r="A5943" s="2"/>
+      <c r="B5943" s="5"/>
+      <c r="C5943" s="3"/>
+    </row>
+    <row r="5944">
+      <c r="A5944" s="2"/>
+      <c r="B5944" s="5"/>
+      <c r="C5944" s="3"/>
+    </row>
+    <row r="5945">
+      <c r="A5945" s="2"/>
+      <c r="B5945" s="5"/>
+      <c r="C5945" s="3"/>
+    </row>
+    <row r="5946">
+      <c r="A5946" s="2"/>
+      <c r="B5946" s="5"/>
+      <c r="C5946" s="3"/>
+    </row>
+    <row r="5947">
+      <c r="A5947" s="2"/>
+      <c r="B5947" s="5"/>
+      <c r="C5947" s="3"/>
+    </row>
+    <row r="5948">
+      <c r="A5948" s="2"/>
+      <c r="B5948" s="5"/>
+      <c r="C5948" s="3"/>
+    </row>
+    <row r="5949">
+      <c r="A5949" s="2"/>
+      <c r="B5949" s="5"/>
+      <c r="C5949" s="3"/>
+    </row>
+    <row r="5950">
+      <c r="A5950" s="2"/>
+      <c r="B5950" s="5"/>
+      <c r="C5950" s="3"/>
+    </row>
+    <row r="5951">
+      <c r="A5951" s="2"/>
+      <c r="B5951" s="5"/>
+      <c r="C5951" s="3"/>
+    </row>
+    <row r="5952">
+      <c r="A5952" s="2"/>
+      <c r="B5952" s="5"/>
+      <c r="C5952" s="3"/>
+    </row>
+    <row r="5953">
+      <c r="A5953" s="2"/>
+      <c r="B5953" s="5"/>
+      <c r="C5953" s="3"/>
+    </row>
+    <row r="5954">
+      <c r="A5954" s="2"/>
+      <c r="B5954" s="5"/>
+      <c r="C5954" s="3"/>
+    </row>
+    <row r="5955">
+      <c r="A5955" s="2"/>
+      <c r="B5955" s="5"/>
+      <c r="C5955" s="3"/>
+    </row>
+    <row r="5956">
+      <c r="A5956" s="2"/>
+      <c r="B5956" s="5"/>
+      <c r="C5956" s="3"/>
+    </row>
+    <row r="5957">
+      <c r="A5957" s="2"/>
+      <c r="B5957" s="5"/>
+      <c r="C5957" s="3"/>
+    </row>
+    <row r="5958">
+      <c r="A5958" s="2"/>
+      <c r="B5958" s="5"/>
+      <c r="C5958" s="3"/>
+    </row>
+    <row r="5959">
+      <c r="A5959" s="2"/>
+      <c r="B5959" s="5"/>
+      <c r="C5959" s="3"/>
+    </row>
+    <row r="5960">
+      <c r="A5960" s="2"/>
+      <c r="B5960" s="5"/>
+      <c r="C5960" s="3"/>
+    </row>
+    <row r="5961">
+      <c r="A5961" s="2"/>
+      <c r="B5961" s="5"/>
+      <c r="C5961" s="3"/>
+    </row>
+    <row r="5962">
+      <c r="A5962" s="2"/>
+      <c r="B5962" s="5"/>
+      <c r="C5962" s="3"/>
+    </row>
+    <row r="5963">
+      <c r="A5963" s="2"/>
+      <c r="B5963" s="5"/>
+      <c r="C5963" s="3"/>
+    </row>
+    <row r="5964">
+      <c r="A5964" s="2"/>
+      <c r="B5964" s="5"/>
+      <c r="C5964" s="3"/>
+    </row>
+    <row r="5965">
+      <c r="A5965" s="2"/>
+      <c r="B5965" s="5"/>
+      <c r="C5965" s="3"/>
+    </row>
+    <row r="5966">
+      <c r="A5966" s="2"/>
+      <c r="B5966" s="5"/>
+      <c r="C5966" s="3"/>
+    </row>
+    <row r="5967">
+      <c r="A5967" s="2"/>
+      <c r="B5967" s="5"/>
+      <c r="C5967" s="3"/>
+    </row>
+    <row r="5968">
+      <c r="A5968" s="2"/>
+      <c r="B5968" s="5"/>
+      <c r="C5968" s="3"/>
+    </row>
+    <row r="5969">
+      <c r="A5969" s="2"/>
+      <c r="B5969" s="5"/>
+      <c r="C5969" s="3"/>
+    </row>
+    <row r="5970">
+      <c r="A5970" s="2"/>
+      <c r="B5970" s="5"/>
+      <c r="C5970" s="3"/>
+    </row>
+    <row r="5971">
+      <c r="A5971" s="2"/>
+      <c r="B5971" s="5"/>
+      <c r="C5971" s="3"/>
+    </row>
+    <row r="5972">
+      <c r="A5972" s="2"/>
+      <c r="B5972" s="5"/>
+      <c r="C5972" s="3"/>
+    </row>
+    <row r="5973">
+      <c r="A5973" s="2"/>
+      <c r="B5973" s="5"/>
+      <c r="C5973" s="3"/>
+    </row>
+    <row r="5974">
+      <c r="A5974" s="2"/>
+      <c r="B5974" s="5"/>
+      <c r="C5974" s="3"/>
+    </row>
+    <row r="5975">
+      <c r="A5975" s="2"/>
+      <c r="B5975" s="5"/>
+      <c r="C5975" s="3"/>
+    </row>
+    <row r="5976">
+      <c r="A5976" s="2"/>
+      <c r="B5976" s="5"/>
+      <c r="C5976" s="3"/>
+    </row>
+    <row r="5977">
+      <c r="A5977" s="2"/>
+      <c r="B5977" s="5"/>
+      <c r="C5977" s="3"/>
+    </row>
+    <row r="5978">
+      <c r="A5978" s="2"/>
+      <c r="B5978" s="5"/>
+      <c r="C5978" s="3"/>
+    </row>
+    <row r="5979">
+      <c r="A5979" s="2"/>
+      <c r="B5979" s="5"/>
+      <c r="C5979" s="3"/>
+    </row>
+    <row r="5980">
+      <c r="A5980" s="2"/>
+      <c r="B5980" s="5"/>
+      <c r="C5980" s="3"/>
+    </row>
+    <row r="5981">
+      <c r="A5981" s="2"/>
+      <c r="B5981" s="5"/>
+      <c r="C5981" s="3"/>
+    </row>
+    <row r="5982">
+      <c r="A5982" s="2"/>
+      <c r="B5982" s="5"/>
+      <c r="C5982" s="3"/>
+    </row>
+    <row r="5983">
+      <c r="A5983" s="2"/>
+      <c r="B5983" s="5"/>
+      <c r="C5983" s="3"/>
+    </row>
+    <row r="5984">
+      <c r="A5984" s="2"/>
+      <c r="B5984" s="5"/>
+      <c r="C5984" s="3"/>
+    </row>
+    <row r="5985">
+      <c r="A5985" s="2"/>
+      <c r="B5985" s="5"/>
+      <c r="C5985" s="3"/>
+    </row>
+    <row r="5986">
+      <c r="A5986" s="2"/>
+      <c r="B5986" s="5"/>
+      <c r="C5986" s="3"/>
+    </row>
+    <row r="5987">
+      <c r="A5987" s="2"/>
+      <c r="B5987" s="5"/>
+      <c r="C5987" s="3"/>
+    </row>
+    <row r="5988">
+      <c r="A5988" s="2"/>
+      <c r="B5988" s="5"/>
+      <c r="C5988" s="3"/>
+    </row>
+    <row r="5989">
+      <c r="A5989" s="2"/>
+      <c r="B5989" s="5"/>
+      <c r="C5989" s="3"/>
+    </row>
+    <row r="5990">
+      <c r="A5990" s="2"/>
+      <c r="B5990" s="5"/>
+      <c r="C5990" s="3"/>
+    </row>
+    <row r="5991">
+      <c r="A5991" s="2"/>
+      <c r="B5991" s="5"/>
+      <c r="C5991" s="3"/>
+    </row>
+    <row r="5992">
+      <c r="A5992" s="2"/>
+      <c r="B5992" s="5"/>
+      <c r="C5992" s="3"/>
+    </row>
+    <row r="5993">
+      <c r="A5993" s="2"/>
+      <c r="B5993" s="5"/>
+      <c r="C5993" s="3"/>
+    </row>
+    <row r="5994">
+      <c r="A5994" s="2"/>
+      <c r="B5994" s="5"/>
+      <c r="C5994" s="3"/>
+    </row>
+    <row r="5995">
+      <c r="A5995" s="2"/>
+      <c r="B5995" s="5"/>
+      <c r="C5995" s="3"/>
+    </row>
+    <row r="5996">
+      <c r="A5996" s="2"/>
+      <c r="B5996" s="5"/>
+      <c r="C5996" s="3"/>
+    </row>
+    <row r="5997">
+      <c r="A5997" s="2"/>
+      <c r="B5997" s="5"/>
+      <c r="C5997" s="3"/>
+    </row>
+    <row r="5998">
+      <c r="A5998" s="2"/>
+      <c r="B5998" s="5"/>
+      <c r="C5998" s="3"/>
+    </row>
+    <row r="5999">
+      <c r="A5999" s="2"/>
+      <c r="B5999" s="5"/>
+      <c r="C5999" s="3"/>
+    </row>
+    <row r="6000">
+      <c r="A6000" s="2"/>
+      <c r="B6000" s="5"/>
+      <c r="C6000" s="3"/>
+    </row>
+    <row r="6001">
+      <c r="A6001" s="2"/>
+      <c r="B6001" s="5"/>
+      <c r="C6001" s="3"/>
+    </row>
+    <row r="6002">
+      <c r="A6002" s="2"/>
+      <c r="B6002" s="5"/>
+      <c r="C6002" s="3"/>
+    </row>
+    <row r="6003">
+      <c r="A6003" s="2"/>
+      <c r="B6003" s="5"/>
+      <c r="C6003" s="3"/>
+    </row>
+    <row r="6004">
+      <c r="A6004" s="2"/>
+      <c r="B6004" s="5"/>
+      <c r="C6004" s="3"/>
+    </row>
+    <row r="6005">
+      <c r="A6005" s="2"/>
+      <c r="B6005" s="5"/>
+      <c r="C6005" s="3"/>
+    </row>
+    <row r="6006">
+      <c r="A6006" s="2"/>
+      <c r="B6006" s="5"/>
+      <c r="C6006" s="3"/>
+    </row>
+    <row r="6007">
+      <c r="A6007" s="2"/>
+      <c r="B6007" s="5"/>
+      <c r="C6007" s="3"/>
+    </row>
+    <row r="6008">
+      <c r="A6008" s="2"/>
+      <c r="B6008" s="5"/>
+      <c r="C6008" s="3"/>
+    </row>
+    <row r="6009">
+      <c r="A6009" s="2"/>
+      <c r="B6009" s="5"/>
+      <c r="C6009" s="3"/>
+    </row>
+    <row r="6010">
+      <c r="A6010" s="2"/>
+      <c r="B6010" s="5"/>
+      <c r="C6010" s="3"/>
+    </row>
+    <row r="6011">
+      <c r="A6011" s="2"/>
+      <c r="B6011" s="5"/>
+      <c r="C6011" s="3"/>
+    </row>
+    <row r="6012">
+      <c r="A6012" s="2"/>
+      <c r="B6012" s="5"/>
+      <c r="C6012" s="3"/>
+    </row>
+    <row r="6013">
+      <c r="A6013" s="2"/>
+      <c r="B6013" s="5"/>
+      <c r="C6013" s="3"/>
+    </row>
+    <row r="6014">
+      <c r="A6014" s="2"/>
+      <c r="B6014" s="5"/>
+      <c r="C6014" s="3"/>
+    </row>
+    <row r="6015">
+      <c r="A6015" s="2"/>
+      <c r="B6015" s="5"/>
+      <c r="C6015" s="3"/>
+    </row>
+    <row r="6016">
+      <c r="A6016" s="2"/>
+      <c r="B6016" s="5"/>
+      <c r="C6016" s="3"/>
+    </row>
+    <row r="6017">
+      <c r="A6017" s="2"/>
+      <c r="B6017" s="5"/>
+      <c r="C6017" s="3"/>
+    </row>
+    <row r="6018">
+      <c r="A6018" s="2"/>
+      <c r="B6018" s="5"/>
+      <c r="C6018" s="3"/>
+    </row>
+    <row r="6019">
+      <c r="A6019" s="2"/>
+      <c r="B6019" s="5"/>
+      <c r="C6019" s="3"/>
+    </row>
+    <row r="6020">
+      <c r="A6020" s="2"/>
+      <c r="B6020" s="5"/>
+      <c r="C6020" s="3"/>
+    </row>
+    <row r="6021">
+      <c r="A6021" s="2"/>
+      <c r="B6021" s="5"/>
+      <c r="C6021" s="3"/>
+    </row>
+    <row r="6022">
+      <c r="A6022" s="2"/>
+      <c r="B6022" s="5"/>
+      <c r="C6022" s="3"/>
+    </row>
+    <row r="6023">
+      <c r="A6023" s="2"/>
+      <c r="B6023" s="5"/>
+      <c r="C6023" s="3"/>
+    </row>
+    <row r="6024">
+      <c r="A6024" s="2"/>
+      <c r="B6024" s="5"/>
+      <c r="C6024" s="3"/>
+    </row>
+    <row r="6025">
+      <c r="A6025" s="2"/>
+      <c r="B6025" s="5"/>
+      <c r="C6025" s="3"/>
+    </row>
+    <row r="6026">
+      <c r="A6026" s="2"/>
+      <c r="B6026" s="5"/>
+      <c r="C6026" s="3"/>
+    </row>
+    <row r="6027">
+      <c r="A6027" s="2"/>
+      <c r="B6027" s="5"/>
+      <c r="C6027" s="3"/>
+    </row>
+    <row r="6028">
+      <c r="A6028" s="2"/>
+      <c r="B6028" s="5"/>
+      <c r="C6028" s="3"/>
+    </row>
+    <row r="6029">
+      <c r="A6029" s="2"/>
+      <c r="B6029" s="5"/>
+      <c r="C6029" s="3"/>
+    </row>
+    <row r="6030">
+      <c r="A6030" s="2"/>
+      <c r="B6030" s="5"/>
+      <c r="C6030" s="3"/>
+    </row>
+    <row r="6031">
+      <c r="A6031" s="2"/>
+      <c r="B6031" s="5"/>
+      <c r="C6031" s="3"/>
+    </row>
+    <row r="6032">
+      <c r="A6032" s="2"/>
+      <c r="B6032" s="5"/>
+      <c r="C6032" s="3"/>
+    </row>
+    <row r="6033">
+      <c r="A6033" s="2"/>
+      <c r="B6033" s="5"/>
+      <c r="C6033" s="3"/>
+    </row>
+    <row r="6034">
+      <c r="A6034" s="2"/>
+      <c r="B6034" s="5"/>
+      <c r="C6034" s="3"/>
+    </row>
+    <row r="6035">
+      <c r="A6035" s="2"/>
+      <c r="B6035" s="5"/>
+      <c r="C6035" s="3"/>
+    </row>
+    <row r="6036">
+      <c r="A6036" s="2"/>
+      <c r="B6036" s="5"/>
+      <c r="C6036" s="3"/>
+    </row>
+    <row r="6037">
+      <c r="A6037" s="2"/>
+      <c r="B6037" s="5"/>
+      <c r="C6037" s="3"/>
+    </row>
+    <row r="6038">
+      <c r="A6038" s="2"/>
+      <c r="B6038" s="5"/>
+      <c r="C6038" s="3"/>
+    </row>
+    <row r="6039">
+      <c r="A6039" s="2"/>
+      <c r="B6039" s="5"/>
+      <c r="C6039" s="3"/>
+    </row>
+    <row r="6040">
+      <c r="A6040" s="2"/>
+      <c r="B6040" s="5"/>
+      <c r="C6040" s="3"/>
+    </row>
+    <row r="6041">
+      <c r="A6041" s="2"/>
+      <c r="B6041" s="5"/>
+      <c r="C6041" s="3"/>
+    </row>
+    <row r="6042">
+      <c r="A6042" s="2"/>
+      <c r="B6042" s="5"/>
+      <c r="C6042" s="3"/>
+    </row>
+    <row r="6043">
+      <c r="A6043" s="2"/>
+      <c r="B6043" s="5"/>
+      <c r="C6043" s="3"/>
+    </row>
+    <row r="6044">
+      <c r="A6044" s="2"/>
+      <c r="B6044" s="5"/>
+      <c r="C6044" s="3"/>
+    </row>
+    <row r="6045">
+      <c r="A6045" s="2"/>
+      <c r="B6045" s="5"/>
+      <c r="C6045" s="3"/>
+    </row>
+    <row r="6046">
+      <c r="A6046" s="2"/>
+      <c r="B6046" s="5"/>
+      <c r="C6046" s="3"/>
+    </row>
+    <row r="6047">
+      <c r="A6047" s="2"/>
+      <c r="B6047" s="5"/>
+      <c r="C6047" s="3"/>
+    </row>
+    <row r="6048">
+      <c r="A6048" s="2"/>
+      <c r="B6048" s="5"/>
+      <c r="C6048" s="3"/>
+    </row>
+    <row r="6049">
+      <c r="A6049" s="2"/>
+      <c r="B6049" s="5"/>
+      <c r="C6049" s="3"/>
+    </row>
+    <row r="6050">
+      <c r="A6050" s="2"/>
+      <c r="B6050" s="5"/>
+      <c r="C6050" s="3"/>
+    </row>
+    <row r="6051">
+      <c r="A6051" s="2"/>
+      <c r="B6051" s="5"/>
+      <c r="C6051" s="3"/>
+    </row>
+    <row r="6052">
+      <c r="A6052" s="2"/>
+      <c r="B6052" s="5"/>
+      <c r="C6052" s="3"/>
+    </row>
+    <row r="6053">
+      <c r="A6053" s="2"/>
+      <c r="B6053" s="5"/>
+      <c r="C6053" s="3"/>
+    </row>
+    <row r="6054">
+      <c r="A6054" s="2"/>
+      <c r="B6054" s="5"/>
+      <c r="C6054" s="3"/>
+    </row>
+    <row r="6055">
+      <c r="A6055" s="2"/>
+      <c r="B6055" s="5"/>
+      <c r="C6055" s="3"/>
+    </row>
+    <row r="6056">
+      <c r="A6056" s="2"/>
+      <c r="B6056" s="5"/>
+      <c r="C6056" s="3"/>
+    </row>
+    <row r="6057">
+      <c r="A6057" s="2"/>
+      <c r="B6057" s="5"/>
+      <c r="C6057" s="3"/>
+    </row>
+    <row r="6058">
+      <c r="A6058" s="2"/>
+      <c r="B6058" s="5"/>
+      <c r="C6058" s="3"/>
+    </row>
+    <row r="6059">
+      <c r="A6059" s="2"/>
+      <c r="B6059" s="5"/>
+      <c r="C6059" s="3"/>
+    </row>
+    <row r="6060">
+      <c r="A6060" s="2"/>
+      <c r="B6060" s="5"/>
+      <c r="C6060" s="3"/>
+    </row>
+    <row r="6061">
+      <c r="A6061" s="2"/>
+      <c r="B6061" s="5"/>
+      <c r="C6061" s="3"/>
+    </row>
+    <row r="6062">
+      <c r="A6062" s="2"/>
+      <c r="B6062" s="5"/>
+      <c r="C6062" s="3"/>
+    </row>
+    <row r="6063">
+      <c r="A6063" s="2"/>
+      <c r="B6063" s="5"/>
+      <c r="C6063" s="3"/>
+    </row>
+    <row r="6064">
+      <c r="A6064" s="2"/>
+      <c r="B6064" s="5"/>
+      <c r="C6064" s="3"/>
+    </row>
+    <row r="6065">
+      <c r="A6065" s="2"/>
+      <c r="B6065" s="5"/>
+      <c r="C6065" s="3"/>
+    </row>
+    <row r="6066">
+      <c r="A6066" s="2"/>
+      <c r="B6066" s="5"/>
+      <c r="C6066" s="3"/>
+    </row>
+    <row r="6067">
+      <c r="A6067" s="2"/>
+      <c r="B6067" s="5"/>
+      <c r="C6067" s="3"/>
+    </row>
+    <row r="6068">
+      <c r="A6068" s="2"/>
+      <c r="B6068" s="5"/>
+      <c r="C6068" s="3"/>
+    </row>
+    <row r="6069">
+      <c r="A6069" s="2"/>
+      <c r="B6069" s="5"/>
+      <c r="C6069" s="3"/>
+    </row>
+    <row r="6070">
+      <c r="A6070" s="2"/>
+      <c r="B6070" s="5"/>
+      <c r="C6070" s="3"/>
+    </row>
+    <row r="6071">
+      <c r="A6071" s="2"/>
+      <c r="B6071" s="5"/>
+      <c r="C6071" s="3"/>
+    </row>
+    <row r="6072">
+      <c r="A6072" s="2"/>
+      <c r="B6072" s="5"/>
+      <c r="C6072" s="3"/>
+    </row>
+    <row r="6073">
+      <c r="A6073" s="2"/>
+      <c r="B6073" s="5"/>
+      <c r="C6073" s="3"/>
+    </row>
+    <row r="6074">
+      <c r="A6074" s="2"/>
+      <c r="B6074" s="5"/>
+      <c r="C6074" s="3"/>
+    </row>
+    <row r="6075">
+      <c r="A6075" s="2"/>
+      <c r="B6075" s="5"/>
+      <c r="C6075" s="3"/>
+    </row>
+    <row r="6076">
+      <c r="A6076" s="2"/>
+      <c r="B6076" s="5"/>
+      <c r="C6076" s="3"/>
+    </row>
+    <row r="6077">
+      <c r="A6077" s="2"/>
+      <c r="B6077" s="5"/>
+      <c r="C6077" s="3"/>
+    </row>
+    <row r="6078">
+      <c r="A6078" s="2"/>
+      <c r="B6078" s="5"/>
+      <c r="C6078" s="3"/>
+    </row>
+    <row r="6079">
+      <c r="A6079" s="2"/>
+      <c r="B6079" s="5"/>
+      <c r="C6079" s="3"/>
+    </row>
+    <row r="6080">
+      <c r="A6080" s="2"/>
+      <c r="B6080" s="5"/>
+      <c r="C6080" s="3"/>
+    </row>
+    <row r="6081">
+      <c r="A6081" s="2"/>
+      <c r="B6081" s="5"/>
+      <c r="C6081" s="3"/>
+    </row>
+    <row r="6082">
+      <c r="A6082" s="2"/>
+      <c r="B6082" s="5"/>
+      <c r="C6082" s="3"/>
+    </row>
+    <row r="6083">
+      <c r="A6083" s="2"/>
+      <c r="B6083" s="5"/>
+      <c r="C6083" s="3"/>
+    </row>
+    <row r="6084">
+      <c r="A6084" s="2"/>
+      <c r="B6084" s="5"/>
+      <c r="C6084" s="3"/>
+    </row>
+    <row r="6085">
+      <c r="A6085" s="2"/>
+      <c r="B6085" s="5"/>
+      <c r="C6085" s="3"/>
+    </row>
+    <row r="6086">
+      <c r="A6086" s="2"/>
+      <c r="B6086" s="5"/>
+      <c r="C6086" s="3"/>
+    </row>
+    <row r="6087">
+      <c r="A6087" s="2"/>
+      <c r="B6087" s="5"/>
+      <c r="C6087" s="3"/>
+    </row>
+    <row r="6088">
+      <c r="A6088" s="2"/>
+      <c r="B6088" s="5"/>
+      <c r="C6088" s="3"/>
+    </row>
+    <row r="6089">
+      <c r="A6089" s="2"/>
+      <c r="B6089" s="5"/>
+      <c r="C6089" s="3"/>
+    </row>
+    <row r="6090">
+      <c r="A6090" s="2"/>
+      <c r="B6090" s="5"/>
+      <c r="C6090" s="3"/>
+    </row>
+    <row r="6091">
+      <c r="A6091" s="2"/>
+      <c r="B6091" s="5"/>
+      <c r="C6091" s="3"/>
+    </row>
+    <row r="6092">
+      <c r="A6092" s="2"/>
+      <c r="B6092" s="5"/>
+      <c r="C6092" s="3"/>
+    </row>
+    <row r="6093">
+      <c r="A6093" s="2"/>
+      <c r="B6093" s="5"/>
+      <c r="C6093" s="3"/>
+    </row>
+    <row r="6094">
+      <c r="A6094" s="2"/>
+      <c r="B6094" s="5"/>
+      <c r="C6094" s="3"/>
+    </row>
+    <row r="6095">
+      <c r="A6095" s="2"/>
+      <c r="B6095" s="5"/>
+      <c r="C6095" s="3"/>
+    </row>
+    <row r="6096">
+      <c r="A6096" s="2"/>
+      <c r="B6096" s="5"/>
+      <c r="C6096" s="3"/>
+    </row>
+    <row r="6097">
+      <c r="A6097" s="2"/>
+      <c r="B6097" s="5"/>
+      <c r="C6097" s="3"/>
+    </row>
+    <row r="6098">
+      <c r="A6098" s="2"/>
+      <c r="B6098" s="5"/>
+      <c r="C6098" s="3"/>
+    </row>
+    <row r="6099">
+      <c r="A6099" s="2"/>
+      <c r="B6099" s="5"/>
+      <c r="C6099" s="3"/>
+    </row>
+    <row r="6100">
+      <c r="A6100" s="2"/>
+      <c r="B6100" s="5"/>
+      <c r="C6100" s="3"/>
+    </row>
+    <row r="6101">
+      <c r="A6101" s="2"/>
+      <c r="B6101" s="5"/>
+      <c r="C6101" s="3"/>
+    </row>
+    <row r="6102">
+      <c r="A6102" s="2"/>
+      <c r="B6102" s="5"/>
+      <c r="C6102" s="3"/>
+    </row>
+    <row r="6103">
+      <c r="A6103" s="2"/>
+      <c r="B6103" s="5"/>
+      <c r="C6103" s="3"/>
+    </row>
+    <row r="6104">
+      <c r="A6104" s="2"/>
+      <c r="B6104" s="5"/>
+      <c r="C6104" s="3"/>
+    </row>
+    <row r="6105">
+      <c r="A6105" s="2"/>
+      <c r="B6105" s="5"/>
+      <c r="C6105" s="3"/>
+    </row>
+    <row r="6106">
+      <c r="A6106" s="2"/>
+      <c r="B6106" s="5"/>
+      <c r="C6106" s="3"/>
+    </row>
+    <row r="6107">
+      <c r="A6107" s="2"/>
+      <c r="B6107" s="5"/>
+      <c r="C6107" s="3"/>
+    </row>
+    <row r="6108">
+      <c r="A6108" s="2"/>
+      <c r="B6108" s="5"/>
+      <c r="C6108" s="3"/>
+    </row>
+    <row r="6109">
+      <c r="A6109" s="2"/>
+      <c r="B6109" s="5"/>
+      <c r="C6109" s="3"/>
+    </row>
+    <row r="6110">
+      <c r="A6110" s="2"/>
+      <c r="B6110" s="5"/>
+      <c r="C6110" s="3"/>
+    </row>
+    <row r="6111">
+      <c r="A6111" s="2"/>
+      <c r="B6111" s="5"/>
+      <c r="C6111" s="3"/>
+    </row>
+    <row r="6112">
+      <c r="A6112" s="2"/>
+      <c r="B6112" s="5"/>
+      <c r="C6112" s="3"/>
+    </row>
+    <row r="6113">
+      <c r="A6113" s="2"/>
+      <c r="B6113" s="5"/>
+      <c r="C6113" s="3"/>
+    </row>
+    <row r="6114">
+      <c r="A6114" s="2"/>
+      <c r="B6114" s="5"/>
+      <c r="C6114" s="3"/>
+    </row>
+    <row r="6115">
+      <c r="A6115" s="2"/>
+      <c r="B6115" s="5"/>
+      <c r="C6115" s="3"/>
+    </row>
+    <row r="6116">
+      <c r="A6116" s="2"/>
+      <c r="B6116" s="5"/>
+      <c r="C6116" s="3"/>
+    </row>
+    <row r="6117">
+      <c r="A6117" s="2"/>
+      <c r="B6117" s="5"/>
+      <c r="C6117" s="3"/>
+    </row>
+    <row r="6118">
+      <c r="A6118" s="2"/>
+      <c r="B6118" s="5"/>
+      <c r="C6118" s="3"/>
+    </row>
+    <row r="6119">
+      <c r="A6119" s="2"/>
+      <c r="B6119" s="5"/>
+      <c r="C6119" s="3"/>
+    </row>
+    <row r="6120">
+      <c r="A6120" s="2"/>
+      <c r="B6120" s="5"/>
+      <c r="C6120" s="3"/>
+    </row>
+    <row r="6121">
+      <c r="A6121" s="2"/>
+      <c r="B6121" s="5"/>
+      <c r="C6121" s="3"/>
+    </row>
+    <row r="6122">
+      <c r="A6122" s="2"/>
+      <c r="B6122" s="5"/>
+      <c r="C6122" s="3"/>
+    </row>
+    <row r="6123">
+      <c r="A6123" s="2"/>
+      <c r="B6123" s="5"/>
+      <c r="C6123" s="3"/>
+    </row>
+    <row r="6124">
+      <c r="A6124" s="2"/>
+      <c r="B6124" s="5"/>
+      <c r="C6124" s="3"/>
+    </row>
+    <row r="6125">
+      <c r="A6125" s="2"/>
+      <c r="B6125" s="5"/>
+      <c r="C6125" s="3"/>
+    </row>
+    <row r="6126">
+      <c r="A6126" s="2"/>
+      <c r="B6126" s="5"/>
+      <c r="C6126" s="3"/>
+    </row>
+    <row r="6127">
+      <c r="A6127" s="2"/>
+      <c r="B6127" s="5"/>
+      <c r="C6127" s="3"/>
+    </row>
+    <row r="6128">
+      <c r="A6128" s="2"/>
+      <c r="B6128" s="5"/>
+      <c r="C6128" s="3"/>
+    </row>
+    <row r="6129">
+      <c r="A6129" s="2"/>
+      <c r="B6129" s="5"/>
+      <c r="C6129" s="3"/>
+    </row>
+    <row r="6130">
+      <c r="A6130" s="2"/>
+      <c r="B6130" s="5"/>
+      <c r="C6130" s="3"/>
+    </row>
+    <row r="6131">
+      <c r="A6131" s="2"/>
+      <c r="B6131" s="5"/>
+      <c r="C6131" s="3"/>
+    </row>
+    <row r="6132">
+      <c r="A6132" s="2"/>
+      <c r="B6132" s="5"/>
+      <c r="C6132" s="3"/>
+    </row>
+    <row r="6133">
+      <c r="A6133" s="2"/>
+      <c r="B6133" s="5"/>
+      <c r="C6133" s="3"/>
+    </row>
+    <row r="6134">
+      <c r="A6134" s="2"/>
+      <c r="B6134" s="5"/>
+      <c r="C6134" s="3"/>
+    </row>
+    <row r="6135">
+      <c r="A6135" s="2"/>
+      <c r="B6135" s="5"/>
+      <c r="C6135" s="3"/>
+    </row>
+    <row r="6136">
+      <c r="A6136" s="2"/>
+      <c r="B6136" s="5"/>
+      <c r="C6136" s="3"/>
+    </row>
+    <row r="6137">
+      <c r="A6137" s="2"/>
+      <c r="B6137" s="5"/>
+      <c r="C6137" s="3"/>
+    </row>
+    <row r="6138">
+      <c r="A6138" s="2"/>
+      <c r="B6138" s="5"/>
+      <c r="C6138" s="3"/>
+    </row>
+    <row r="6139">
+      <c r="A6139" s="2"/>
+      <c r="B6139" s="5"/>
+      <c r="C6139" s="3"/>
+    </row>
+    <row r="6140">
+      <c r="A6140" s="2"/>
+      <c r="B6140" s="5"/>
+      <c r="C6140" s="3"/>
+    </row>
+    <row r="6141">
+      <c r="A6141" s="2"/>
+      <c r="B6141" s="5"/>
+      <c r="C6141" s="3"/>
+    </row>
+    <row r="6142">
+      <c r="A6142" s="2"/>
+      <c r="B6142" s="5"/>
+      <c r="C6142" s="3"/>
+    </row>
+    <row r="6143">
+      <c r="A6143" s="2"/>
+      <c r="B6143" s="5"/>
+      <c r="C6143" s="3"/>
+    </row>
+    <row r="6144">
+      <c r="A6144" s="2"/>
+      <c r="B6144" s="5"/>
+      <c r="C6144" s="3"/>
+    </row>
+    <row r="6145">
+      <c r="A6145" s="2"/>
+      <c r="B6145" s="5"/>
+      <c r="C6145" s="3"/>
+    </row>
+    <row r="6146">
+      <c r="A6146" s="2"/>
+      <c r="B6146" s="5"/>
+      <c r="C6146" s="3"/>
+    </row>
+    <row r="6147">
+      <c r="A6147" s="2"/>
+      <c r="B6147" s="5"/>
+      <c r="C6147" s="3"/>
+    </row>
+    <row r="6148">
+      <c r="A6148" s="2"/>
+      <c r="B6148" s="5"/>
+      <c r="C6148" s="3"/>
+    </row>
+    <row r="6149">
+      <c r="A6149" s="2"/>
+      <c r="B6149" s="5"/>
+      <c r="C6149" s="3"/>
+    </row>
+    <row r="6150">
+      <c r="A6150" s="2"/>
+      <c r="B6150" s="5"/>
+      <c r="C6150" s="3"/>
+    </row>
+    <row r="6151">
+      <c r="A6151" s="2"/>
+      <c r="B6151" s="5"/>
+      <c r="C6151" s="3"/>
+    </row>
+    <row r="6152">
+      <c r="A6152" s="2"/>
+      <c r="B6152" s="5"/>
+      <c r="C6152" s="3"/>
+    </row>
+    <row r="6153">
+      <c r="A6153" s="2"/>
+      <c r="B6153" s="5"/>
+      <c r="C6153" s="3"/>
+    </row>
+    <row r="6154">
+      <c r="A6154" s="2"/>
+      <c r="B6154" s="5"/>
+      <c r="C6154" s="3"/>
+    </row>
+    <row r="6155">
+      <c r="A6155" s="2"/>
+      <c r="B6155" s="5"/>
+      <c r="C6155" s="3"/>
+    </row>
+    <row r="6156">
+      <c r="A6156" s="2"/>
+      <c r="B6156" s="5"/>
+      <c r="C6156" s="3"/>
+    </row>
+    <row r="6157">
+      <c r="A6157" s="2"/>
+      <c r="B6157" s="5"/>
+      <c r="C6157" s="3"/>
+    </row>
+    <row r="6158">
+      <c r="A6158" s="2"/>
+      <c r="B6158" s="5"/>
+      <c r="C6158" s="3"/>
+    </row>
+    <row r="6159">
+      <c r="A6159" s="2"/>
+      <c r="B6159" s="5"/>
+      <c r="C6159" s="3"/>
+    </row>
+    <row r="6160">
+      <c r="A6160" s="2"/>
+      <c r="B6160" s="5"/>
+      <c r="C6160" s="3"/>
+    </row>
+    <row r="6161">
+      <c r="A6161" s="2"/>
+      <c r="B6161" s="5"/>
+      <c r="C6161" s="3"/>
+    </row>
+    <row r="6162">
+      <c r="A6162" s="2"/>
+      <c r="B6162" s="5"/>
+      <c r="C6162" s="3"/>
+    </row>
+    <row r="6163">
+      <c r="A6163" s="2"/>
+      <c r="B6163" s="5"/>
+      <c r="C6163" s="3"/>
+    </row>
+    <row r="6164">
+      <c r="A6164" s="2"/>
+      <c r="B6164" s="5"/>
+      <c r="C6164" s="3"/>
+    </row>
+    <row r="6165">
+      <c r="A6165" s="2"/>
+      <c r="B6165" s="5"/>
+      <c r="C6165" s="3"/>
+    </row>
+    <row r="6166">
+      <c r="A6166" s="2"/>
+      <c r="B6166" s="5"/>
+      <c r="C6166" s="3"/>
+    </row>
+    <row r="6167">
+      <c r="A6167" s="2"/>
+      <c r="B6167" s="5"/>
+      <c r="C6167" s="3"/>
+    </row>
+    <row r="6168">
+      <c r="A6168" s="2"/>
+      <c r="B6168" s="5"/>
+      <c r="C6168" s="3"/>
+    </row>
+    <row r="6169">
+      <c r="A6169" s="2"/>
+      <c r="B6169" s="5"/>
+      <c r="C6169" s="3"/>
+    </row>
+    <row r="6170">
+      <c r="A6170" s="2"/>
+      <c r="B6170" s="5"/>
+      <c r="C6170" s="3"/>
+    </row>
+    <row r="6171">
+      <c r="A6171" s="2"/>
+      <c r="B6171" s="5"/>
+      <c r="C6171" s="3"/>
+    </row>
+    <row r="6172">
+      <c r="A6172" s="2"/>
+      <c r="B6172" s="5"/>
+      <c r="C6172" s="3"/>
+    </row>
+    <row r="6173">
+      <c r="A6173" s="2"/>
+      <c r="B6173" s="5"/>
+      <c r="C6173" s="3"/>
+    </row>
+    <row r="6174">
+      <c r="A6174" s="2"/>
+      <c r="B6174" s="5"/>
+      <c r="C6174" s="3"/>
+    </row>
+    <row r="6175">
+      <c r="A6175" s="2"/>
+      <c r="B6175" s="5"/>
+      <c r="C6175" s="3"/>
+    </row>
+    <row r="6176">
+      <c r="A6176" s="2"/>
+      <c r="B6176" s="5"/>
+      <c r="C6176" s="3"/>
+    </row>
+    <row r="6177">
+      <c r="A6177" s="2"/>
+      <c r="B6177" s="5"/>
+      <c r="C6177" s="3"/>
+    </row>
+    <row r="6178">
+      <c r="A6178" s="2"/>
+      <c r="B6178" s="5"/>
+      <c r="C6178" s="3"/>
+    </row>
+    <row r="6179">
+      <c r="A6179" s="2"/>
+      <c r="B6179" s="5"/>
+      <c r="C6179" s="3"/>
+    </row>
+    <row r="6180">
+      <c r="A6180" s="2"/>
+      <c r="B6180" s="5"/>
+      <c r="C6180" s="3"/>
+    </row>
+    <row r="6181">
+      <c r="A6181" s="2"/>
+      <c r="B6181" s="5"/>
+      <c r="C6181" s="3"/>
+    </row>
+    <row r="6182">
+      <c r="A6182" s="2"/>
+      <c r="B6182" s="5"/>
+      <c r="C6182" s="3"/>
+    </row>
+    <row r="6183">
+      <c r="A6183" s="2"/>
+      <c r="B6183" s="5"/>
+      <c r="C6183" s="3"/>
+    </row>
+    <row r="6184">
+      <c r="A6184" s="2"/>
+      <c r="B6184" s="5"/>
+      <c r="C6184" s="3"/>
+    </row>
+    <row r="6185">
+      <c r="A6185" s="2"/>
+      <c r="B6185" s="5"/>
+      <c r="C6185" s="3"/>
+    </row>
+    <row r="6186">
+      <c r="A6186" s="2"/>
+      <c r="B6186" s="5"/>
+      <c r="C6186" s="3"/>
+    </row>
+    <row r="6187">
+      <c r="A6187" s="2"/>
+      <c r="B6187" s="5"/>
+      <c r="C6187" s="3"/>
+    </row>
+    <row r="6188">
+      <c r="A6188" s="2"/>
+      <c r="B6188" s="5"/>
+      <c r="C6188" s="3"/>
+    </row>
+    <row r="6189">
+      <c r="A6189" s="2"/>
+      <c r="B6189" s="5"/>
+      <c r="C6189" s="3"/>
+    </row>
+    <row r="6190">
+      <c r="A6190" s="2"/>
+      <c r="B6190" s="5"/>
+      <c r="C6190" s="3"/>
+    </row>
+    <row r="6191">
+      <c r="A6191" s="2"/>
+      <c r="B6191" s="5"/>
+      <c r="C6191" s="3"/>
+    </row>
+    <row r="6192">
+      <c r="A6192" s="2"/>
+      <c r="B6192" s="5"/>
+      <c r="C6192" s="3"/>
+    </row>
+    <row r="6193">
+      <c r="A6193" s="2"/>
+      <c r="B6193" s="5"/>
+      <c r="C6193" s="3"/>
+    </row>
+    <row r="6194">
+      <c r="A6194" s="2"/>
+      <c r="B6194" s="5"/>
+      <c r="C6194" s="3"/>
+    </row>
+    <row r="6195">
+      <c r="A6195" s="2"/>
+      <c r="B6195" s="5"/>
+      <c r="C6195" s="3"/>
+    </row>
+    <row r="6196">
+      <c r="A6196" s="2"/>
+      <c r="B6196" s="5"/>
+      <c r="C6196" s="3"/>
+    </row>
+    <row r="6197">
+      <c r="A6197" s="2"/>
+      <c r="B6197" s="5"/>
+      <c r="C6197" s="3"/>
+    </row>
+    <row r="6198">
+      <c r="A6198" s="2"/>
+      <c r="B6198" s="5"/>
+      <c r="C6198" s="3"/>
+    </row>
+    <row r="6199">
+      <c r="A6199" s="2"/>
+      <c r="B6199" s="5"/>
+      <c r="C6199" s="3"/>
+    </row>
+    <row r="6200">
+      <c r="A6200" s="2"/>
+      <c r="B6200" s="5"/>
+      <c r="C6200" s="3"/>
+    </row>
+    <row r="6201">
+      <c r="A6201" s="2"/>
+      <c r="B6201" s="5"/>
+      <c r="C6201" s="3"/>
+    </row>
+    <row r="6202">
+      <c r="A6202" s="2"/>
+      <c r="B6202" s="5"/>
+      <c r="C6202" s="3"/>
+    </row>
+    <row r="6203">
+      <c r="A6203" s="2"/>
+      <c r="B6203" s="5"/>
+      <c r="C6203" s="3"/>
+    </row>
+    <row r="6204">
+      <c r="A6204" s="2"/>
+      <c r="B6204" s="5"/>
+      <c r="C6204" s="3"/>
+    </row>
+    <row r="6205">
+      <c r="A6205" s="2"/>
+      <c r="B6205" s="5"/>
+      <c r="C6205" s="3"/>
+    </row>
+    <row r="6206">
+      <c r="A6206" s="2"/>
+      <c r="B6206" s="5"/>
+      <c r="C6206" s="3"/>
+    </row>
+    <row r="6207">
+      <c r="A6207" s="2"/>
+      <c r="B6207" s="5"/>
+      <c r="C6207" s="3"/>
+    </row>
+    <row r="6208">
+      <c r="A6208" s="2"/>
+      <c r="B6208" s="5"/>
+      <c r="C6208" s="3"/>
+    </row>
+    <row r="6209">
+      <c r="A6209" s="2"/>
+      <c r="B6209" s="5"/>
+      <c r="C6209" s="3"/>
+    </row>
+    <row r="6210">
+      <c r="A6210" s="2"/>
+      <c r="B6210" s="5"/>
+      <c r="C6210" s="3"/>
+    </row>
+    <row r="6211">
+      <c r="A6211" s="2"/>
+      <c r="B6211" s="5"/>
+      <c r="C6211" s="3"/>
+    </row>
+    <row r="6212">
+      <c r="A6212" s="2"/>
+      <c r="B6212" s="5"/>
+      <c r="C6212" s="3"/>
+    </row>
+    <row r="6213">
+      <c r="A6213" s="2"/>
+      <c r="B6213" s="5"/>
+      <c r="C6213" s="3"/>
+    </row>
+    <row r="6214">
+      <c r="A6214" s="2"/>
+      <c r="B6214" s="5"/>
+      <c r="C6214" s="3"/>
+    </row>
+    <row r="6215">
+      <c r="A6215" s="2"/>
+      <c r="B6215" s="5"/>
+      <c r="C6215" s="3"/>
+    </row>
+    <row r="6216">
+      <c r="A6216" s="2"/>
+      <c r="B6216" s="5"/>
+      <c r="C6216" s="3"/>
+    </row>
+    <row r="6217">
+      <c r="A6217" s="2"/>
+      <c r="B6217" s="5"/>
+      <c r="C6217" s="3"/>
+    </row>
+    <row r="6218">
+      <c r="A6218" s="2"/>
+      <c r="B6218" s="5"/>
+      <c r="C6218" s="3"/>
+    </row>
+    <row r="6219">
+      <c r="A6219" s="2"/>
+      <c r="B6219" s="5"/>
+      <c r="C6219" s="3"/>
+    </row>
+    <row r="6220">
+      <c r="A6220" s="2"/>
+      <c r="B6220" s="5"/>
+      <c r="C6220" s="3"/>
+    </row>
+    <row r="6221">
+      <c r="A6221" s="2"/>
+      <c r="B6221" s="5"/>
+      <c r="C6221" s="3"/>
+    </row>
+    <row r="6222">
+      <c r="A6222" s="2"/>
+      <c r="B6222" s="5"/>
+      <c r="C6222" s="3"/>
+    </row>
+    <row r="6223">
+      <c r="A6223" s="2"/>
+      <c r="B6223" s="5"/>
+      <c r="C6223" s="3"/>
+    </row>
+    <row r="6224">
+      <c r="A6224" s="2"/>
+      <c r="B6224" s="5"/>
+      <c r="C6224" s="3"/>
+    </row>
+    <row r="6225">
+      <c r="A6225" s="2"/>
+      <c r="B6225" s="5"/>
+      <c r="C6225" s="3"/>
+    </row>
+    <row r="6226">
+      <c r="A6226" s="2"/>
+      <c r="B6226" s="5"/>
+      <c r="C6226" s="3"/>
+    </row>
+    <row r="6227">
+      <c r="A6227" s="2"/>
+      <c r="B6227" s="5"/>
+      <c r="C6227" s="3"/>
+    </row>
+    <row r="6228">
+      <c r="A6228" s="2"/>
+      <c r="B6228" s="5"/>
+      <c r="C6228" s="3"/>
+    </row>
+    <row r="6229">
+      <c r="A6229" s="2"/>
+      <c r="B6229" s="5"/>
+      <c r="C6229" s="3"/>
+    </row>
+    <row r="6230">
+      <c r="A6230" s="2"/>
+      <c r="B6230" s="5"/>
+      <c r="C6230" s="3"/>
+    </row>
+    <row r="6231">
+      <c r="A6231" s="2"/>
+      <c r="B6231" s="5"/>
+      <c r="C6231" s="3"/>
+    </row>
+    <row r="6232">
+      <c r="A6232" s="2"/>
+      <c r="B6232" s="5"/>
+      <c r="C6232" s="3"/>
+    </row>
+    <row r="6233">
+      <c r="A6233" s="2"/>
+      <c r="B6233" s="5"/>
+      <c r="C6233" s="3"/>
+    </row>
+    <row r="6234">
+      <c r="A6234" s="2"/>
+      <c r="B6234" s="5"/>
+      <c r="C6234" s="3"/>
+    </row>
+    <row r="6235">
+      <c r="A6235" s="2"/>
+      <c r="B6235" s="5"/>
+      <c r="C6235" s="3"/>
+    </row>
+    <row r="6236">
+      <c r="A6236" s="2"/>
+      <c r="B6236" s="5"/>
+      <c r="C6236" s="3"/>
+    </row>
+    <row r="6237">
+      <c r="A6237" s="2"/>
+      <c r="B6237" s="5"/>
+      <c r="C6237" s="3"/>
+    </row>
+    <row r="6238">
+      <c r="A6238" s="2"/>
+      <c r="B6238" s="5"/>
+      <c r="C6238" s="3"/>
+    </row>
+    <row r="6239">
+      <c r="A6239" s="2"/>
+      <c r="B6239" s="5"/>
+      <c r="C6239" s="3"/>
+    </row>
+    <row r="6240">
+      <c r="A6240" s="2"/>
+      <c r="B6240" s="5"/>
+      <c r="C6240" s="3"/>
+    </row>
+    <row r="6241">
+      <c r="A6241" s="2"/>
+      <c r="B6241" s="5"/>
+      <c r="C6241" s="3"/>
+    </row>
+    <row r="6242">
+      <c r="A6242" s="2"/>
+      <c r="B6242" s="5"/>
+      <c r="C6242" s="3"/>
+    </row>
+    <row r="6243">
+      <c r="A6243" s="2"/>
+      <c r="B6243" s="5"/>
+      <c r="C6243" s="3"/>
+    </row>
+    <row r="6244">
+      <c r="A6244" s="2"/>
+      <c r="B6244" s="5"/>
+      <c r="C6244" s="3"/>
+    </row>
+    <row r="6245">
+      <c r="A6245" s="2"/>
+      <c r="B6245" s="5"/>
+      <c r="C6245" s="3"/>
+    </row>
+    <row r="6246">
+      <c r="A6246" s="2"/>
+      <c r="B6246" s="5"/>
+      <c r="C6246" s="3"/>
+    </row>
+    <row r="6247">
+      <c r="A6247" s="2"/>
+      <c r="B6247" s="5"/>
+      <c r="C6247" s="3"/>
+    </row>
+    <row r="6248">
+      <c r="A6248" s="2"/>
+      <c r="B6248" s="5"/>
+      <c r="C6248" s="3"/>
+    </row>
+    <row r="6249">
+      <c r="A6249" s="2"/>
+      <c r="B6249" s="5"/>
+      <c r="C6249" s="3"/>
+    </row>
+    <row r="6250">
+      <c r="A6250" s="2"/>
+      <c r="B6250" s="5"/>
+      <c r="C6250" s="3"/>
+    </row>
+    <row r="6251">
+      <c r="A6251" s="2"/>
+      <c r="B6251" s="5"/>
+      <c r="C6251" s="3"/>
+    </row>
+    <row r="6252">
+      <c r="A6252" s="2"/>
+      <c r="B6252" s="5"/>
+      <c r="C6252" s="3"/>
+    </row>
+    <row r="6253">
+      <c r="A6253" s="2"/>
+      <c r="B6253" s="5"/>
+      <c r="C6253" s="3"/>
+    </row>
+    <row r="6254">
+      <c r="A6254" s="2"/>
+      <c r="B6254" s="5"/>
+      <c r="C6254" s="3"/>
+    </row>
+    <row r="6255">
+      <c r="A6255" s="2"/>
+      <c r="B6255" s="5"/>
+      <c r="C6255" s="3"/>
+    </row>
+    <row r="6256">
+      <c r="A6256" s="2"/>
+      <c r="B6256" s="5"/>
+      <c r="C6256" s="3"/>
+    </row>
+    <row r="6257">
+      <c r="A6257" s="2"/>
+      <c r="B6257" s="5"/>
+      <c r="C6257" s="3"/>
+    </row>
+    <row r="6258">
+      <c r="A6258" s="2"/>
+      <c r="B6258" s="5"/>
+      <c r="C6258" s="3"/>
+    </row>
+    <row r="6259">
+      <c r="A6259" s="2"/>
+      <c r="B6259" s="5"/>
+      <c r="C6259" s="3"/>
+    </row>
+    <row r="6260">
+      <c r="A6260" s="2"/>
+      <c r="B6260" s="5"/>
+      <c r="C6260" s="3"/>
+    </row>
+    <row r="6261">
+      <c r="A6261" s="2"/>
+      <c r="B6261" s="5"/>
+      <c r="C6261" s="3"/>
+    </row>
+    <row r="6262">
+      <c r="A6262" s="2"/>
+      <c r="B6262" s="5"/>
+      <c r="C6262" s="3"/>
+    </row>
+    <row r="6263">
+      <c r="A6263" s="2"/>
+      <c r="B6263" s="5"/>
+      <c r="C6263" s="3"/>
+    </row>
+    <row r="6264">
+      <c r="A6264" s="2"/>
+      <c r="B6264" s="5"/>
+      <c r="C6264" s="3"/>
+    </row>
+    <row r="6265">
+      <c r="A6265" s="2"/>
+      <c r="B6265" s="5"/>
+      <c r="C6265" s="3"/>
+    </row>
+    <row r="6266">
+      <c r="A6266" s="2"/>
+      <c r="B6266" s="5"/>
+      <c r="C6266" s="3"/>
+    </row>
+    <row r="6267">
+      <c r="A6267" s="2"/>
+      <c r="B6267" s="5"/>
+      <c r="C6267" s="3"/>
+    </row>
+    <row r="6268">
+      <c r="A6268" s="2"/>
+      <c r="B6268" s="5"/>
+      <c r="C6268" s="3"/>
+    </row>
+    <row r="6269">
+      <c r="A6269" s="2"/>
+      <c r="B6269" s="5"/>
+      <c r="C6269" s="3"/>
+    </row>
+    <row r="6270">
+      <c r="A6270" s="2"/>
+      <c r="B6270" s="5"/>
+      <c r="C6270" s="3"/>
+    </row>
+    <row r="6271">
+      <c r="A6271" s="2"/>
+      <c r="B6271" s="5"/>
+      <c r="C6271" s="3"/>
+    </row>
+    <row r="6272">
+      <c r="A6272" s="2"/>
+      <c r="B6272" s="5"/>
+      <c r="C6272" s="3"/>
+    </row>
+    <row r="6273">
+      <c r="A6273" s="2"/>
+      <c r="B6273" s="5"/>
+      <c r="C6273" s="3"/>
+    </row>
+    <row r="6274">
+      <c r="A6274" s="2"/>
+      <c r="B6274" s="5"/>
+      <c r="C6274" s="3"/>
+    </row>
+    <row r="6275">
+      <c r="A6275" s="2"/>
+      <c r="B6275" s="5"/>
+      <c r="C6275" s="3"/>
+    </row>
+    <row r="6276">
+      <c r="A6276" s="2"/>
+      <c r="B6276" s="5"/>
+      <c r="C6276" s="3"/>
+    </row>
+    <row r="6277">
+      <c r="A6277" s="2"/>
+      <c r="B6277" s="5"/>
+      <c r="C6277" s="3"/>
+    </row>
+    <row r="6278">
+      <c r="A6278" s="2"/>
+      <c r="B6278" s="5"/>
+      <c r="C6278" s="3"/>
+    </row>
+    <row r="6279">
+      <c r="A6279" s="2"/>
+      <c r="B6279" s="5"/>
+      <c r="C6279" s="3"/>
+    </row>
+    <row r="6280">
+      <c r="A6280" s="2"/>
+      <c r="B6280" s="5"/>
+      <c r="C6280" s="3"/>
+    </row>
+    <row r="6281">
+      <c r="A6281" s="2"/>
+      <c r="B6281" s="5"/>
+      <c r="C6281" s="3"/>
+    </row>
+    <row r="6282">
+      <c r="A6282" s="2"/>
+      <c r="B6282" s="5"/>
+      <c r="C6282" s="3"/>
+    </row>
+    <row r="6283">
+      <c r="A6283" s="2"/>
+      <c r="B6283" s="5"/>
+      <c r="C6283" s="3"/>
+    </row>
+    <row r="6284">
+      <c r="A6284" s="2"/>
+      <c r="B6284" s="5"/>
+      <c r="C6284" s="3"/>
+    </row>
+    <row r="6285">
+      <c r="A6285" s="2"/>
+      <c r="B6285" s="5"/>
+      <c r="C6285" s="3"/>
+    </row>
+    <row r="6286">
+      <c r="A6286" s="2"/>
+      <c r="B6286" s="5"/>
+      <c r="C6286" s="3"/>
+    </row>
+    <row r="6287">
+      <c r="A6287" s="2"/>
+      <c r="B6287" s="5"/>
+      <c r="C6287" s="3"/>
+    </row>
+    <row r="6288">
+      <c r="A6288" s="2"/>
+      <c r="B6288" s="5"/>
+      <c r="C6288" s="3"/>
+    </row>
+    <row r="6289">
+      <c r="A6289" s="2"/>
+      <c r="B6289" s="5"/>
+      <c r="C6289" s="3"/>
+    </row>
+    <row r="6290">
+      <c r="A6290" s="2"/>
+      <c r="B6290" s="5"/>
+      <c r="C6290" s="3"/>
+    </row>
+    <row r="6291">
+      <c r="A6291" s="2"/>
+      <c r="B6291" s="5"/>
+      <c r="C6291" s="3"/>
+    </row>
+    <row r="6292">
+      <c r="A6292" s="2"/>
+      <c r="B6292" s="5"/>
+      <c r="C6292" s="3"/>
+    </row>
+    <row r="6293">
+      <c r="A6293" s="2"/>
+      <c r="B6293" s="5"/>
+      <c r="C6293" s="3"/>
+    </row>
+    <row r="6294">
+      <c r="A6294" s="2"/>
+      <c r="B6294" s="5"/>
+      <c r="C6294" s="3"/>
+    </row>
+    <row r="6295">
+      <c r="A6295" s="2"/>
+      <c r="B6295" s="5"/>
+      <c r="C6295" s="3"/>
+    </row>
+    <row r="6296">
+      <c r="A6296" s="2"/>
+      <c r="B6296" s="5"/>
+      <c r="C6296" s="3"/>
+    </row>
+    <row r="6297">
+      <c r="A6297" s="2"/>
+      <c r="B6297" s="5"/>
+      <c r="C6297" s="3"/>
+    </row>
+    <row r="6298">
+      <c r="A6298" s="2"/>
+      <c r="B6298" s="5"/>
+      <c r="C6298" s="3"/>
+    </row>
+    <row r="6299">
+      <c r="A6299" s="2"/>
+      <c r="B6299" s="5"/>
+      <c r="C6299" s="3"/>
+    </row>
+    <row r="6300">
+      <c r="A6300" s="2"/>
+      <c r="B6300" s="5"/>
+      <c r="C6300" s="3"/>
+    </row>
+    <row r="6301">
+      <c r="A6301" s="2"/>
+      <c r="B6301" s="5"/>
+      <c r="C6301" s="3"/>
+    </row>
+    <row r="6302">
+      <c r="A6302" s="2"/>
+      <c r="B6302" s="5"/>
+      <c r="C6302" s="3"/>
+    </row>
+    <row r="6303">
+      <c r="A6303" s="2"/>
+      <c r="B6303" s="5"/>
+      <c r="C6303" s="3"/>
+    </row>
+    <row r="6304">
+      <c r="A6304" s="2"/>
+      <c r="B6304" s="5"/>
+      <c r="C6304" s="3"/>
+    </row>
+    <row r="6305">
+      <c r="A6305" s="2"/>
+      <c r="B6305" s="5"/>
+      <c r="C6305" s="3"/>
+    </row>
+    <row r="6306">
+      <c r="A6306" s="2"/>
+      <c r="B6306" s="5"/>
+      <c r="C6306" s="3"/>
+    </row>
+    <row r="6307">
+      <c r="A6307" s="2"/>
+      <c r="B6307" s="5"/>
+      <c r="C6307" s="3"/>
+    </row>
+    <row r="6308">
+      <c r="A6308" s="2"/>
+      <c r="B6308" s="5"/>
+      <c r="C6308" s="3"/>
+    </row>
+    <row r="6309">
+      <c r="A6309" s="2"/>
+      <c r="B6309" s="5"/>
+      <c r="C6309" s="3"/>
+    </row>
+    <row r="6310">
+      <c r="A6310" s="2"/>
+      <c r="B6310" s="5"/>
+      <c r="C6310" s="3"/>
+    </row>
+    <row r="6311">
+      <c r="A6311" s="2"/>
+      <c r="B6311" s="5"/>
+      <c r="C6311" s="3"/>
+    </row>
+    <row r="6312">
+      <c r="A6312" s="2"/>
+      <c r="B6312" s="5"/>
+      <c r="C6312" s="3"/>
+    </row>
+    <row r="6313">
+      <c r="A6313" s="2"/>
+      <c r="B6313" s="5"/>
+      <c r="C6313" s="3"/>
+    </row>
+    <row r="6314">
+      <c r="A6314" s="2"/>
+      <c r="B6314" s="5"/>
+      <c r="C6314" s="3"/>
+    </row>
+    <row r="6315">
+      <c r="A6315" s="2"/>
+      <c r="B6315" s="5"/>
+      <c r="C6315" s="3"/>
+    </row>
+    <row r="6316">
+      <c r="A6316" s="2"/>
+      <c r="B6316" s="5"/>
+      <c r="C6316" s="3"/>
+    </row>
+    <row r="6317">
+      <c r="A6317" s="2"/>
+      <c r="B6317" s="5"/>
+      <c r="C6317" s="3"/>
+    </row>
+    <row r="6318">
+      <c r="A6318" s="2"/>
+      <c r="B6318" s="5"/>
+      <c r="C6318" s="3"/>
+    </row>
+    <row r="6319">
+      <c r="A6319" s="2"/>
+      <c r="B6319" s="5"/>
+      <c r="C6319" s="3"/>
+    </row>
+    <row r="6320">
+      <c r="A6320" s="2"/>
+      <c r="B6320" s="5"/>
+      <c r="C6320" s="3"/>
+    </row>
+    <row r="6321">
+      <c r="A6321" s="2"/>
+      <c r="B6321" s="5"/>
+      <c r="C6321" s="3"/>
+    </row>
+    <row r="6322">
+      <c r="A6322" s="2"/>
+      <c r="B6322" s="5"/>
+      <c r="C6322" s="3"/>
+    </row>
+    <row r="6323">
+      <c r="A6323" s="2"/>
+      <c r="B6323" s="5"/>
+      <c r="C6323" s="3"/>
+    </row>
+    <row r="6324">
+      <c r="A6324" s="2"/>
+      <c r="B6324" s="5"/>
+      <c r="C6324" s="3"/>
+    </row>
+    <row r="6325">
+      <c r="A6325" s="2"/>
+      <c r="B6325" s="5"/>
+      <c r="C6325" s="3"/>
+    </row>
+    <row r="6326">
+      <c r="A6326" s="2"/>
+      <c r="B6326" s="5"/>
+      <c r="C6326" s="3"/>
+    </row>
+    <row r="6327">
+      <c r="A6327" s="2"/>
+      <c r="B6327" s="5"/>
+      <c r="C6327" s="3"/>
+    </row>
+    <row r="6328">
+      <c r="A6328" s="2"/>
+      <c r="B6328" s="5"/>
+      <c r="C6328" s="3"/>
+    </row>
+    <row r="6329">
+      <c r="A6329" s="2"/>
+      <c r="B6329" s="5"/>
+      <c r="C6329" s="3"/>
+    </row>
+    <row r="6330">
+      <c r="A6330" s="2"/>
+      <c r="B6330" s="5"/>
+      <c r="C6330" s="3"/>
+    </row>
+    <row r="6331">
+      <c r="A6331" s="2"/>
+      <c r="B6331" s="5"/>
+      <c r="C6331" s="3"/>
+    </row>
+    <row r="6332">
+      <c r="A6332" s="2"/>
+      <c r="B6332" s="5"/>
+      <c r="C6332" s="3"/>
+    </row>
+    <row r="6333">
+      <c r="A6333" s="2"/>
+      <c r="B6333" s="5"/>
+      <c r="C6333" s="3"/>
+    </row>
+    <row r="6334">
+      <c r="A6334" s="2"/>
+      <c r="B6334" s="5"/>
+      <c r="C6334" s="3"/>
+    </row>
+    <row r="6335">
+      <c r="A6335" s="2"/>
+      <c r="B6335" s="5"/>
+      <c r="C6335" s="3"/>
+    </row>
+    <row r="6336">
+      <c r="A6336" s="2"/>
+      <c r="B6336" s="5"/>
+      <c r="C6336" s="3"/>
+    </row>
+    <row r="6337">
+      <c r="A6337" s="2"/>
+      <c r="B6337" s="5"/>
+      <c r="C6337" s="3"/>
+    </row>
+    <row r="6338">
+      <c r="A6338" s="2"/>
+      <c r="B6338" s="5"/>
+      <c r="C6338" s="3"/>
+    </row>
+    <row r="6339">
+      <c r="A6339" s="2"/>
+      <c r="B6339" s="5"/>
+      <c r="C6339" s="3"/>
+    </row>
+    <row r="6340">
+      <c r="A6340" s="2"/>
+      <c r="B6340" s="5"/>
+      <c r="C6340" s="3"/>
+    </row>
+    <row r="6341">
+      <c r="A6341" s="2"/>
+      <c r="B6341" s="5"/>
+      <c r="C6341" s="3"/>
+    </row>
+    <row r="6342">
+      <c r="A6342" s="2"/>
+      <c r="B6342" s="5"/>
+      <c r="C6342" s="3"/>
+    </row>
+    <row r="6343">
+      <c r="A6343" s="2"/>
+      <c r="B6343" s="5"/>
+      <c r="C6343" s="3"/>
+    </row>
+    <row r="6344">
+      <c r="A6344" s="2"/>
+      <c r="B6344" s="5"/>
+      <c r="C6344" s="3"/>
+    </row>
+    <row r="6345">
+      <c r="A6345" s="2"/>
+      <c r="B6345" s="5"/>
+      <c r="C6345" s="3"/>
+    </row>
+    <row r="6346">
+      <c r="A6346" s="2"/>
+      <c r="B6346" s="5"/>
+      <c r="C6346" s="3"/>
+    </row>
+    <row r="6347">
+      <c r="A6347" s="2"/>
+      <c r="B6347" s="5"/>
+      <c r="C6347" s="3"/>
+    </row>
+    <row r="6348">
+      <c r="A6348" s="2"/>
+      <c r="B6348" s="5"/>
+      <c r="C6348" s="3"/>
+    </row>
+    <row r="6349">
+      <c r="A6349" s="2"/>
+      <c r="B6349" s="5"/>
+      <c r="C6349" s="3"/>
+    </row>
+    <row r="6350">
+      <c r="A6350" s="2"/>
+      <c r="B6350" s="5"/>
+      <c r="C6350" s="3"/>
+    </row>
+    <row r="6351">
+      <c r="A6351" s="2"/>
+      <c r="B6351" s="5"/>
+      <c r="C6351" s="3"/>
+    </row>
+    <row r="6352">
+      <c r="A6352" s="2"/>
+      <c r="B6352" s="5"/>
+      <c r="C6352" s="3"/>
+    </row>
+    <row r="6353">
+      <c r="A6353" s="2"/>
+      <c r="B6353" s="5"/>
+      <c r="C6353" s="3"/>
+    </row>
+    <row r="6354">
+      <c r="A6354" s="2"/>
+      <c r="B6354" s="5"/>
+      <c r="C6354" s="3"/>
+    </row>
+    <row r="6355">
+      <c r="A6355" s="2"/>
+      <c r="B6355" s="5"/>
+      <c r="C6355" s="3"/>
+    </row>
+    <row r="6356">
+      <c r="A6356" s="2"/>
+      <c r="B6356" s="5"/>
+      <c r="C6356" s="3"/>
+    </row>
+    <row r="6357">
+      <c r="A6357" s="2"/>
+      <c r="B6357" s="5"/>
+      <c r="C6357" s="3"/>
+    </row>
+    <row r="6358">
+      <c r="A6358" s="2"/>
+      <c r="B6358" s="5"/>
+      <c r="C6358" s="3"/>
+    </row>
+    <row r="6359">
+      <c r="A6359" s="2"/>
+      <c r="B6359" s="5"/>
+      <c r="C6359" s="3"/>
+    </row>
+    <row r="6360">
+      <c r="A6360" s="2"/>
+      <c r="B6360" s="5"/>
+      <c r="C6360" s="3"/>
+    </row>
+    <row r="6361">
+      <c r="A6361" s="2"/>
+      <c r="B6361" s="5"/>
+      <c r="C6361" s="3"/>
+    </row>
+    <row r="6362">
+      <c r="A6362" s="2"/>
+      <c r="B6362" s="5"/>
+      <c r="C6362" s="3"/>
+    </row>
+    <row r="6363">
+      <c r="A6363" s="2"/>
+      <c r="B6363" s="5"/>
+      <c r="C6363" s="3"/>
+    </row>
+    <row r="6364">
+      <c r="A6364" s="2"/>
+      <c r="B6364" s="5"/>
+      <c r="C6364" s="3"/>
+    </row>
+    <row r="6365">
+      <c r="A6365" s="2"/>
+      <c r="B6365" s="5"/>
+      <c r="C6365" s="3"/>
+    </row>
+    <row r="6366">
+      <c r="A6366" s="2"/>
+      <c r="B6366" s="5"/>
+      <c r="C6366" s="3"/>
+    </row>
+    <row r="6367">
+      <c r="A6367" s="2"/>
+      <c r="B6367" s="5"/>
+      <c r="C6367" s="3"/>
+    </row>
+    <row r="6368">
+      <c r="A6368" s="2"/>
+      <c r="B6368" s="5"/>
+      <c r="C6368" s="3"/>
+    </row>
+    <row r="6369">
+      <c r="A6369" s="2"/>
+      <c r="B6369" s="5"/>
+      <c r="C6369" s="3"/>
+    </row>
+    <row r="6370">
+      <c r="A6370" s="2"/>
+      <c r="B6370" s="5"/>
+      <c r="C6370" s="3"/>
+    </row>
+    <row r="6371">
+      <c r="A6371" s="2"/>
+      <c r="B6371" s="5"/>
+      <c r="C6371" s="3"/>
+    </row>
+    <row r="6372">
+      <c r="A6372" s="2"/>
+      <c r="B6372" s="5"/>
+      <c r="C6372" s="3"/>
+    </row>
+    <row r="6373">
+      <c r="A6373" s="2"/>
+      <c r="B6373" s="5"/>
+      <c r="C6373" s="3"/>
+    </row>
+    <row r="6374">
+      <c r="A6374" s="2"/>
+      <c r="B6374" s="5"/>
+      <c r="C6374" s="3"/>
+    </row>
+    <row r="6375">
+      <c r="A6375" s="2"/>
+      <c r="B6375" s="5"/>
+      <c r="C6375" s="3"/>
+    </row>
+    <row r="6376">
+      <c r="A6376" s="2"/>
+      <c r="B6376" s="5"/>
+      <c r="C6376" s="3"/>
+    </row>
+    <row r="6377">
+      <c r="A6377" s="2"/>
+      <c r="B6377" s="5"/>
+      <c r="C6377" s="3"/>
+    </row>
+    <row r="6378">
+      <c r="A6378" s="2"/>
+      <c r="B6378" s="5"/>
+      <c r="C6378" s="3"/>
+    </row>
+    <row r="6379">
+      <c r="A6379" s="2"/>
+      <c r="B6379" s="5"/>
+      <c r="C6379" s="3"/>
+    </row>
+    <row r="6380">
+      <c r="A6380" s="2"/>
+      <c r="B6380" s="5"/>
+      <c r="C6380" s="3"/>
+    </row>
+    <row r="6381">
+      <c r="A6381" s="2"/>
+      <c r="B6381" s="5"/>
+      <c r="C6381" s="3"/>
+    </row>
+    <row r="6382">
+      <c r="A6382" s="2"/>
+      <c r="B6382" s="5"/>
+      <c r="C6382" s="3"/>
+    </row>
+    <row r="6383">
+      <c r="A6383" s="2"/>
+      <c r="B6383" s="5"/>
+      <c r="C6383" s="3"/>
+    </row>
+    <row r="6384">
+      <c r="A6384" s="2"/>
+      <c r="B6384" s="5"/>
+      <c r="C6384" s="3"/>
+    </row>
+    <row r="6385">
+      <c r="A6385" s="2"/>
+      <c r="B6385" s="5"/>
+      <c r="C6385" s="3"/>
+    </row>
+    <row r="6386">
+      <c r="A6386" s="2"/>
+      <c r="B6386" s="5"/>
+      <c r="C6386" s="3"/>
+    </row>
+    <row r="6387">
+      <c r="A6387" s="2"/>
+      <c r="B6387" s="5"/>
+      <c r="C6387" s="3"/>
+    </row>
+    <row r="6388">
+      <c r="A6388" s="2"/>
+      <c r="B6388" s="5"/>
+      <c r="C6388" s="3"/>
+    </row>
+    <row r="6389">
+      <c r="A6389" s="2"/>
+      <c r="B6389" s="5"/>
+      <c r="C6389" s="3"/>
+    </row>
+    <row r="6390">
+      <c r="A6390" s="2"/>
+      <c r="B6390" s="5"/>
+      <c r="C6390" s="3"/>
+    </row>
+    <row r="6391">
+      <c r="A6391" s="2"/>
+      <c r="B6391" s="5"/>
+      <c r="C6391" s="3"/>
+    </row>
+    <row r="6392">
+      <c r="A6392" s="2"/>
+      <c r="B6392" s="5"/>
+      <c r="C6392" s="3"/>
+    </row>
+    <row r="6393">
+      <c r="A6393" s="2"/>
+      <c r="B6393" s="5"/>
+      <c r="C6393" s="3"/>
+    </row>
+    <row r="6394">
+      <c r="A6394" s="2"/>
+      <c r="B6394" s="5"/>
+      <c r="C6394" s="3"/>
+    </row>
+    <row r="6395">
+      <c r="A6395" s="2"/>
+      <c r="B6395" s="5"/>
+      <c r="C6395" s="3"/>
+    </row>
+    <row r="6396">
+      <c r="A6396" s="2"/>
+      <c r="B6396" s="5"/>
+      <c r="C6396" s="3"/>
+    </row>
+    <row r="6397">
+      <c r="A6397" s="2"/>
+      <c r="B6397" s="5"/>
+      <c r="C6397" s="3"/>
+    </row>
+    <row r="6398">
+      <c r="A6398" s="2"/>
+      <c r="B6398" s="5"/>
+      <c r="C6398" s="3"/>
+    </row>
+    <row r="6399">
+      <c r="A6399" s="2"/>
+      <c r="B6399" s="5"/>
+      <c r="C6399" s="3"/>
+    </row>
+    <row r="6400">
+      <c r="A6400" s="2"/>
+      <c r="B6400" s="5"/>
+      <c r="C6400" s="3"/>
+    </row>
+    <row r="6401">
+      <c r="A6401" s="2"/>
+      <c r="B6401" s="5"/>
+      <c r="C6401" s="3"/>
+    </row>
+    <row r="6402">
+      <c r="A6402" s="2"/>
+      <c r="B6402" s="5"/>
+      <c r="C6402" s="3"/>
+    </row>
+    <row r="6403">
+      <c r="A6403" s="2"/>
+      <c r="B6403" s="5"/>
+      <c r="C6403" s="3"/>
+    </row>
+    <row r="6404">
+      <c r="A6404" s="2"/>
+      <c r="B6404" s="5"/>
+      <c r="C6404" s="3"/>
+    </row>
+    <row r="6405">
+      <c r="A6405" s="2"/>
+      <c r="B6405" s="5"/>
+      <c r="C6405" s="3"/>
+    </row>
+    <row r="6406">
+      <c r="A6406" s="2"/>
+      <c r="B6406" s="5"/>
+      <c r="C6406" s="3"/>
+    </row>
+    <row r="6407">
+      <c r="A6407" s="2"/>
+      <c r="B6407" s="5"/>
+      <c r="C6407" s="3"/>
+    </row>
+    <row r="6408">
+      <c r="A6408" s="2"/>
+      <c r="B6408" s="5"/>
+      <c r="C6408" s="3"/>
+    </row>
+    <row r="6409">
+      <c r="A6409" s="2"/>
+      <c r="B6409" s="5"/>
+      <c r="C6409" s="3"/>
+    </row>
+    <row r="6410">
+      <c r="A6410" s="2"/>
+      <c r="B6410" s="5"/>
+      <c r="C6410" s="3"/>
+    </row>
+    <row r="6411">
+      <c r="A6411" s="2"/>
+      <c r="B6411" s="5"/>
+      <c r="C6411" s="3"/>
+    </row>
+    <row r="6412">
+      <c r="A6412" s="2"/>
+      <c r="B6412" s="5"/>
+      <c r="C6412" s="3"/>
+    </row>
+    <row r="6413">
+      <c r="A6413" s="2"/>
+      <c r="B6413" s="5"/>
+      <c r="C6413" s="3"/>
+    </row>
+    <row r="6414">
+      <c r="A6414" s="2"/>
+      <c r="B6414" s="5"/>
+      <c r="C6414" s="3"/>
+    </row>
+    <row r="6415">
+      <c r="A6415" s="2"/>
+      <c r="B6415" s="5"/>
+      <c r="C6415" s="3"/>
+    </row>
+    <row r="6416">
+      <c r="A6416" s="2"/>
+      <c r="B6416" s="5"/>
+      <c r="C6416" s="3"/>
+    </row>
+    <row r="6417">
+      <c r="A6417" s="2"/>
+      <c r="B6417" s="5"/>
+      <c r="C6417" s="3"/>
+    </row>
+    <row r="6418">
+      <c r="A6418" s="2"/>
+      <c r="B6418" s="5"/>
+      <c r="C6418" s="3"/>
+    </row>
+    <row r="6419">
+      <c r="A6419" s="2"/>
+      <c r="B6419" s="5"/>
+      <c r="C6419" s="3"/>
+    </row>
+    <row r="6420">
+      <c r="A6420" s="2"/>
+      <c r="B6420" s="5"/>
+      <c r="C6420" s="3"/>
+    </row>
+    <row r="6421">
+      <c r="A6421" s="2"/>
+      <c r="B6421" s="5"/>
+      <c r="C6421" s="3"/>
+    </row>
+    <row r="6422">
+      <c r="A6422" s="2"/>
+      <c r="B6422" s="5"/>
+      <c r="C6422" s="3"/>
+    </row>
+    <row r="6423">
+      <c r="A6423" s="2"/>
+      <c r="B6423" s="5"/>
+      <c r="C6423" s="3"/>
+    </row>
+    <row r="6424">
+      <c r="A6424" s="2"/>
+      <c r="B6424" s="5"/>
+      <c r="C6424" s="3"/>
+    </row>
+    <row r="6425">
+      <c r="A6425" s="2"/>
+      <c r="B6425" s="5"/>
+      <c r="C6425" s="3"/>
+    </row>
+    <row r="6426">
+      <c r="A6426" s="2"/>
+      <c r="B6426" s="5"/>
+      <c r="C6426" s="3"/>
+    </row>
+    <row r="6427">
+      <c r="A6427" s="2"/>
+      <c r="B6427" s="5"/>
+      <c r="C6427" s="3"/>
+    </row>
+    <row r="6428">
+      <c r="A6428" s="2"/>
+      <c r="B6428" s="5"/>
+      <c r="C6428" s="3"/>
+    </row>
+    <row r="6429">
+      <c r="A6429" s="2"/>
+      <c r="B6429" s="5"/>
+      <c r="C6429" s="3"/>
+    </row>
+    <row r="6430">
+      <c r="A6430" s="2"/>
+      <c r="B6430" s="5"/>
+      <c r="C6430" s="3"/>
+    </row>
+    <row r="6431">
+      <c r="A6431" s="2"/>
+      <c r="B6431" s="5"/>
+      <c r="C6431" s="3"/>
+    </row>
+    <row r="6432">
+      <c r="A6432" s="2"/>
+      <c r="B6432" s="5"/>
+      <c r="C6432" s="3"/>
+    </row>
+    <row r="6433">
+      <c r="A6433" s="2"/>
+      <c r="B6433" s="5"/>
+      <c r="C6433" s="3"/>
+    </row>
+    <row r="6434">
+      <c r="A6434" s="2"/>
+      <c r="B6434" s="5"/>
+      <c r="C6434" s="3"/>
+    </row>
+    <row r="6435">
+      <c r="A6435" s="2"/>
+      <c r="B6435" s="5"/>
+      <c r="C6435" s="3"/>
+    </row>
+    <row r="6436">
+      <c r="A6436" s="2"/>
+      <c r="B6436" s="5"/>
+      <c r="C6436" s="3"/>
+    </row>
+    <row r="6437">
+      <c r="A6437" s="2"/>
+      <c r="B6437" s="5"/>
+      <c r="C6437" s="3"/>
+    </row>
+    <row r="6438">
+      <c r="A6438" s="2"/>
+      <c r="B6438" s="5"/>
+      <c r="C6438" s="3"/>
+    </row>
+    <row r="6439">
+      <c r="A6439" s="2"/>
+      <c r="B6439" s="5"/>
+      <c r="C6439" s="3"/>
+    </row>
+    <row r="6440">
+      <c r="A6440" s="2"/>
+      <c r="B6440" s="5"/>
+      <c r="C6440" s="3"/>
+    </row>
+    <row r="6441">
+      <c r="A6441" s="2"/>
+      <c r="B6441" s="5"/>
+      <c r="C6441" s="3"/>
+    </row>
+    <row r="6442">
+      <c r="A6442" s="2"/>
+      <c r="B6442" s="5"/>
+      <c r="C6442" s="3"/>
+    </row>
+    <row r="6443">
+      <c r="A6443" s="2"/>
+      <c r="B6443" s="5"/>
+      <c r="C6443" s="3"/>
+    </row>
+    <row r="6444">
+      <c r="A6444" s="2"/>
+      <c r="B6444" s="5"/>
+      <c r="C6444" s="3"/>
+    </row>
+    <row r="6445">
+      <c r="A6445" s="2"/>
+      <c r="B6445" s="5"/>
+      <c r="C6445" s="3"/>
+    </row>
+    <row r="6446">
+      <c r="A6446" s="2"/>
+      <c r="B6446" s="5"/>
+      <c r="C6446" s="3"/>
+    </row>
+    <row r="6447">
+      <c r="A6447" s="2"/>
+      <c r="B6447" s="5"/>
+      <c r="C6447" s="3"/>
+    </row>
+    <row r="6448">
+      <c r="A6448" s="2"/>
+      <c r="B6448" s="5"/>
+      <c r="C6448" s="3"/>
+    </row>
+    <row r="6449">
+      <c r="A6449" s="2"/>
+      <c r="B6449" s="5"/>
+      <c r="C6449" s="3"/>
+    </row>
+    <row r="6450">
+      <c r="A6450" s="2"/>
+      <c r="B6450" s="5"/>
+      <c r="C6450" s="3"/>
+    </row>
+    <row r="6451">
+      <c r="A6451" s="2"/>
+      <c r="B6451" s="5"/>
+      <c r="C6451" s="3"/>
+    </row>
+    <row r="6452">
+      <c r="A6452" s="2"/>
+      <c r="B6452" s="5"/>
+      <c r="C6452" s="3"/>
+    </row>
+    <row r="6453">
+      <c r="A6453" s="2"/>
+      <c r="B6453" s="5"/>
+      <c r="C6453" s="3"/>
+    </row>
+    <row r="6454">
+      <c r="A6454" s="2"/>
+      <c r="B6454" s="5"/>
+      <c r="C6454" s="3"/>
+    </row>
+    <row r="6455">
+      <c r="A6455" s="2"/>
+      <c r="B6455" s="5"/>
+      <c r="C6455" s="3"/>
+    </row>
+    <row r="6456">
+      <c r="A6456" s="2"/>
+      <c r="B6456" s="5"/>
+      <c r="C6456" s="3"/>
+    </row>
+    <row r="6457">
+      <c r="A6457" s="2"/>
+      <c r="B6457" s="5"/>
+      <c r="C6457" s="3"/>
+    </row>
+    <row r="6458">
+      <c r="A6458" s="2"/>
+      <c r="B6458" s="5"/>
+      <c r="C6458" s="3"/>
+    </row>
+    <row r="6459">
+      <c r="A6459" s="2"/>
+      <c r="B6459" s="5"/>
+      <c r="C6459" s="3"/>
+    </row>
+    <row r="6460">
+      <c r="A6460" s="2"/>
+      <c r="B6460" s="5"/>
+      <c r="C6460" s="3"/>
+    </row>
+    <row r="6461">
+      <c r="A6461" s="2"/>
+      <c r="B6461" s="5"/>
+      <c r="C6461" s="3"/>
+    </row>
+    <row r="6462">
+      <c r="A6462" s="2"/>
+      <c r="B6462" s="5"/>
+      <c r="C6462" s="3"/>
+    </row>
+    <row r="6463">
+      <c r="A6463" s="2"/>
+      <c r="B6463" s="5"/>
+      <c r="C6463" s="3"/>
+    </row>
+    <row r="6464">
+      <c r="A6464" s="2"/>
+      <c r="B6464" s="5"/>
+      <c r="C6464" s="3"/>
+    </row>
+    <row r="6465">
+      <c r="A6465" s="2"/>
+      <c r="B6465" s="5"/>
+      <c r="C6465" s="3"/>
+    </row>
+    <row r="6466">
+      <c r="A6466" s="2"/>
+      <c r="B6466" s="5"/>
+      <c r="C6466" s="3"/>
+    </row>
+    <row r="6467">
+      <c r="A6467" s="2"/>
+      <c r="B6467" s="5"/>
+      <c r="C6467" s="3"/>
+    </row>
+    <row r="6468">
+      <c r="A6468" s="2"/>
+      <c r="B6468" s="5"/>
+      <c r="C6468" s="3"/>
+    </row>
+    <row r="6469">
+      <c r="A6469" s="2"/>
+      <c r="B6469" s="5"/>
+      <c r="C6469" s="3"/>
+    </row>
+    <row r="6470">
+      <c r="A6470" s="2"/>
+      <c r="B6470" s="5"/>
+      <c r="C6470" s="3"/>
+    </row>
+    <row r="6471">
+      <c r="A6471" s="2"/>
+      <c r="B6471" s="5"/>
+      <c r="C6471" s="3"/>
+    </row>
+    <row r="6472">
+      <c r="A6472" s="2"/>
+      <c r="B6472" s="5"/>
+      <c r="C6472" s="3"/>
+    </row>
+    <row r="6473">
+      <c r="A6473" s="2"/>
+      <c r="B6473" s="5"/>
+      <c r="C6473" s="3"/>
+    </row>
+    <row r="6474">
+      <c r="A6474" s="2"/>
+      <c r="B6474" s="5"/>
+      <c r="C6474" s="3"/>
+    </row>
+    <row r="6475">
+      <c r="A6475" s="2"/>
+      <c r="B6475" s="5"/>
+      <c r="C6475" s="3"/>
+    </row>
+    <row r="6476">
+      <c r="A6476" s="2"/>
+      <c r="B6476" s="5"/>
+      <c r="C6476" s="3"/>
+    </row>
+    <row r="6477">
+      <c r="A6477" s="2"/>
+      <c r="B6477" s="5"/>
+      <c r="C6477" s="3"/>
+    </row>
+    <row r="6478">
+      <c r="A6478" s="2"/>
+      <c r="B6478" s="5"/>
+      <c r="C6478" s="3"/>
+    </row>
+    <row r="6479">
+      <c r="A6479" s="2"/>
+      <c r="B6479" s="5"/>
+      <c r="C6479" s="3"/>
+    </row>
+    <row r="6480">
+      <c r="A6480" s="2"/>
+      <c r="B6480" s="5"/>
+      <c r="C6480" s="3"/>
+    </row>
+    <row r="6481">
+      <c r="A6481" s="2"/>
+      <c r="B6481" s="5"/>
+      <c r="C6481" s="3"/>
+    </row>
+    <row r="6482">
+      <c r="A6482" s="2"/>
+      <c r="B6482" s="5"/>
+      <c r="C6482" s="3"/>
+    </row>
+    <row r="6483">
+      <c r="A6483" s="2"/>
+      <c r="B6483" s="5"/>
+      <c r="C6483" s="3"/>
+    </row>
+    <row r="6484">
+      <c r="A6484" s="2"/>
+      <c r="B6484" s="5"/>
+      <c r="C6484" s="3"/>
+    </row>
+    <row r="6485">
+      <c r="A6485" s="2"/>
+      <c r="B6485" s="5"/>
+      <c r="C6485" s="3"/>
+    </row>
+    <row r="6486">
+      <c r="A6486" s="2"/>
+      <c r="B6486" s="5"/>
+      <c r="C6486" s="3"/>
+    </row>
+    <row r="6487">
+      <c r="A6487" s="2"/>
+      <c r="B6487" s="5"/>
+      <c r="C6487" s="3"/>
+    </row>
+    <row r="6488">
+      <c r="A6488" s="2"/>
+      <c r="B6488" s="5"/>
+      <c r="C6488" s="3"/>
+    </row>
+    <row r="6489">
+      <c r="A6489" s="2"/>
+      <c r="B6489" s="5"/>
+      <c r="C6489" s="3"/>
+    </row>
+    <row r="6490">
+      <c r="A6490" s="2"/>
+      <c r="B6490" s="5"/>
+      <c r="C6490" s="3"/>
+    </row>
+    <row r="6491">
+      <c r="A6491" s="2"/>
+      <c r="B6491" s="5"/>
+      <c r="C6491" s="3"/>
+    </row>
+    <row r="6492">
+      <c r="A6492" s="2"/>
+      <c r="B6492" s="5"/>
+      <c r="C6492" s="3"/>
+    </row>
+    <row r="6493">
+      <c r="A6493" s="2"/>
+      <c r="B6493" s="5"/>
+      <c r="C6493" s="3"/>
+    </row>
+    <row r="6494">
+      <c r="A6494" s="2"/>
+      <c r="B6494" s="5"/>
+      <c r="C6494" s="3"/>
+    </row>
+    <row r="6495">
+      <c r="A6495" s="2"/>
+      <c r="B6495" s="5"/>
+      <c r="C6495" s="3"/>
+    </row>
+    <row r="6496">
+      <c r="A6496" s="2"/>
+      <c r="B6496" s="5"/>
+      <c r="C6496" s="3"/>
+    </row>
+    <row r="6497">
+      <c r="A6497" s="2"/>
+      <c r="B6497" s="5"/>
+      <c r="C6497" s="3"/>
+    </row>
+    <row r="6498">
+      <c r="A6498" s="2"/>
+      <c r="B6498" s="5"/>
+      <c r="C6498" s="3"/>
+    </row>
+    <row r="6499">
+      <c r="A6499" s="2"/>
+      <c r="B6499" s="5"/>
+      <c r="C6499" s="3"/>
+    </row>
+    <row r="6500">
+      <c r="A6500" s="2"/>
+      <c r="B6500" s="5"/>
+      <c r="C6500" s="3"/>
+    </row>
+    <row r="6501">
+      <c r="A6501" s="2"/>
+      <c r="B6501" s="5"/>
+      <c r="C6501" s="3"/>
+    </row>
+    <row r="6502">
+      <c r="A6502" s="2"/>
+      <c r="B6502" s="5"/>
+      <c r="C6502" s="3"/>
+    </row>
+    <row r="6503">
+      <c r="A6503" s="2"/>
+      <c r="B6503" s="5"/>
+      <c r="C6503" s="3"/>
+    </row>
+    <row r="6504">
+      <c r="A6504" s="2"/>
+      <c r="B6504" s="5"/>
+      <c r="C6504" s="3"/>
+    </row>
+    <row r="6505">
+      <c r="A6505" s="2"/>
+      <c r="B6505" s="5"/>
+      <c r="C6505" s="3"/>
+    </row>
+    <row r="6506">
+      <c r="A6506" s="2"/>
+      <c r="B6506" s="5"/>
+      <c r="C6506" s="3"/>
+    </row>
+    <row r="6507">
+      <c r="A6507" s="2"/>
+      <c r="B6507" s="5"/>
+      <c r="C6507" s="3"/>
+    </row>
+    <row r="6508">
+      <c r="A6508" s="2"/>
+      <c r="B6508" s="5"/>
+      <c r="C6508" s="3"/>
+    </row>
+    <row r="6509">
+      <c r="A6509" s="2"/>
+      <c r="B6509" s="5"/>
+      <c r="C6509" s="3"/>
+    </row>
+    <row r="6510">
+      <c r="A6510" s="2"/>
+      <c r="B6510" s="5"/>
+      <c r="C6510" s="3"/>
+    </row>
+    <row r="6511">
+      <c r="A6511" s="2"/>
+      <c r="B6511" s="5"/>
+      <c r="C6511" s="3"/>
+    </row>
+    <row r="6512">
+      <c r="A6512" s="2"/>
+      <c r="B6512" s="5"/>
+      <c r="C6512" s="3"/>
+    </row>
+    <row r="6513">
+      <c r="A6513" s="2"/>
+      <c r="B6513" s="5"/>
+      <c r="C6513" s="3"/>
+    </row>
+    <row r="6514">
+      <c r="A6514" s="2"/>
+      <c r="B6514" s="5"/>
+      <c r="C6514" s="3"/>
+    </row>
+    <row r="6515">
+      <c r="A6515" s="2"/>
+      <c r="B6515" s="5"/>
+      <c r="C6515" s="3"/>
+    </row>
+    <row r="6516">
+      <c r="A6516" s="2"/>
+      <c r="B6516" s="5"/>
+      <c r="C6516" s="3"/>
+    </row>
+    <row r="6517">
+      <c r="A6517" s="2"/>
+      <c r="B6517" s="5"/>
+      <c r="C6517" s="3"/>
+    </row>
+    <row r="6518">
+      <c r="A6518" s="2"/>
+      <c r="B6518" s="5"/>
+      <c r="C6518" s="3"/>
+    </row>
+    <row r="6519">
+      <c r="A6519" s="2"/>
+      <c r="B6519" s="5"/>
+      <c r="C6519" s="3"/>
+    </row>
+    <row r="6520">
+      <c r="A6520" s="2"/>
+      <c r="B6520" s="5"/>
+      <c r="C6520" s="3"/>
+    </row>
+    <row r="6521">
+      <c r="A6521" s="2"/>
+      <c r="B6521" s="5"/>
+      <c r="C6521" s="3"/>
+    </row>
+    <row r="6522">
+      <c r="A6522" s="2"/>
+      <c r="B6522" s="5"/>
+      <c r="C6522" s="3"/>
+    </row>
+    <row r="6523">
+      <c r="A6523" s="2"/>
+      <c r="B6523" s="5"/>
+      <c r="C6523" s="3"/>
+    </row>
+    <row r="6524">
+      <c r="A6524" s="2"/>
+      <c r="B6524" s="5"/>
+      <c r="C6524" s="3"/>
+    </row>
+    <row r="6525">
+      <c r="A6525" s="2"/>
+      <c r="B6525" s="5"/>
+      <c r="C6525" s="3"/>
+    </row>
+    <row r="6526">
+      <c r="A6526" s="2"/>
+      <c r="B6526" s="5"/>
+      <c r="C6526" s="3"/>
+    </row>
+    <row r="6527">
+      <c r="A6527" s="2"/>
+      <c r="B6527" s="5"/>
+      <c r="C6527" s="3"/>
+    </row>
+    <row r="6528">
+      <c r="A6528" s="2"/>
+      <c r="B6528" s="5"/>
+      <c r="C6528" s="3"/>
+    </row>
+    <row r="6529">
+      <c r="A6529" s="2"/>
+      <c r="B6529" s="5"/>
+      <c r="C6529" s="3"/>
+    </row>
+    <row r="6530">
+      <c r="A6530" s="2"/>
+      <c r="B6530" s="5"/>
+      <c r="C6530" s="3"/>
+    </row>
+    <row r="6531">
+      <c r="A6531" s="2"/>
+      <c r="B6531" s="5"/>
+      <c r="C6531" s="3"/>
+    </row>
+    <row r="6532">
+      <c r="A6532" s="2"/>
+      <c r="B6532" s="5"/>
+      <c r="C6532" s="3"/>
+    </row>
+    <row r="6533">
+      <c r="A6533" s="2"/>
+      <c r="B6533" s="5"/>
+      <c r="C6533" s="3"/>
+    </row>
+    <row r="6534">
+      <c r="A6534" s="2"/>
+      <c r="B6534" s="5"/>
+      <c r="C6534" s="3"/>
+    </row>
+    <row r="6535">
+      <c r="A6535" s="2"/>
+      <c r="B6535" s="5"/>
+      <c r="C6535" s="3"/>
+    </row>
+    <row r="6536">
+      <c r="A6536" s="2"/>
+      <c r="B6536" s="5"/>
+      <c r="C6536" s="3"/>
+    </row>
+    <row r="6537">
+      <c r="A6537" s="2"/>
+      <c r="B6537" s="5"/>
+      <c r="C6537" s="3"/>
+    </row>
+    <row r="6538">
+      <c r="A6538" s="2"/>
+      <c r="B6538" s="5"/>
+      <c r="C6538" s="3"/>
+    </row>
+    <row r="6539">
+      <c r="A6539" s="2"/>
+      <c r="B6539" s="5"/>
+      <c r="C6539" s="3"/>
+    </row>
+    <row r="6540">
+      <c r="A6540" s="2"/>
+      <c r="B6540" s="5"/>
+      <c r="C6540" s="3"/>
+    </row>
+    <row r="6541">
+      <c r="A6541" s="2"/>
+      <c r="B6541" s="5"/>
+      <c r="C6541" s="3"/>
+    </row>
+    <row r="6542">
+      <c r="A6542" s="2"/>
+      <c r="B6542" s="5"/>
+      <c r="C6542" s="3"/>
+    </row>
+    <row r="6543">
+      <c r="A6543" s="2"/>
+      <c r="B6543" s="5"/>
+      <c r="C6543" s="3"/>
+    </row>
+    <row r="6544">
+      <c r="A6544" s="2"/>
+      <c r="B6544" s="5"/>
+      <c r="C6544" s="3"/>
+    </row>
+    <row r="6545">
+      <c r="A6545" s="2"/>
+      <c r="B6545" s="5"/>
+      <c r="C6545" s="3"/>
+    </row>
+    <row r="6546">
+      <c r="A6546" s="2"/>
+      <c r="B6546" s="5"/>
+      <c r="C6546" s="3"/>
+    </row>
+    <row r="6547">
+      <c r="A6547" s="2"/>
+      <c r="B6547" s="5"/>
+      <c r="C6547" s="3"/>
+    </row>
+    <row r="6548">
+      <c r="A6548" s="2"/>
+      <c r="B6548" s="5"/>
+      <c r="C6548" s="3"/>
+    </row>
+    <row r="6549">
+      <c r="A6549" s="2"/>
+      <c r="B6549" s="5"/>
+      <c r="C6549" s="3"/>
+    </row>
+    <row r="6550">
+      <c r="A6550" s="2"/>
+      <c r="B6550" s="5"/>
+      <c r="C6550" s="3"/>
+    </row>
+    <row r="6551">
+      <c r="A6551" s="2"/>
+      <c r="B6551" s="5"/>
+      <c r="C6551" s="3"/>
+    </row>
+    <row r="6552">
+      <c r="A6552" s="2"/>
+      <c r="B6552" s="5"/>
+      <c r="C6552" s="3"/>
+    </row>
+    <row r="6553">
+      <c r="A6553" s="2"/>
+      <c r="B6553" s="5"/>
+      <c r="C6553" s="3"/>
+    </row>
+    <row r="6554">
+      <c r="A6554" s="2"/>
+      <c r="B6554" s="5"/>
+      <c r="C6554" s="3"/>
+    </row>
+    <row r="6555">
+      <c r="A6555" s="2"/>
+      <c r="B6555" s="5"/>
+      <c r="C6555" s="3"/>
+    </row>
+    <row r="6556">
+      <c r="A6556" s="2"/>
+      <c r="B6556" s="5"/>
+      <c r="C6556" s="3"/>
+    </row>
+    <row r="6557">
+      <c r="A6557" s="2"/>
+      <c r="B6557" s="5"/>
+      <c r="C6557" s="3"/>
+    </row>
+    <row r="6558">
+      <c r="A6558" s="2"/>
+      <c r="B6558" s="5"/>
+      <c r="C6558" s="3"/>
+    </row>
+    <row r="6559">
+      <c r="A6559" s="2"/>
+      <c r="B6559" s="5"/>
+      <c r="C6559" s="3"/>
+    </row>
+    <row r="6560">
+      <c r="A6560" s="2"/>
+      <c r="B6560" s="5"/>
+      <c r="C6560" s="3"/>
+    </row>
+    <row r="6561">
+      <c r="A6561" s="2"/>
+      <c r="B6561" s="5"/>
+      <c r="C6561" s="3"/>
+    </row>
+    <row r="6562">
+      <c r="A6562" s="2"/>
+      <c r="B6562" s="5"/>
+      <c r="C6562" s="3"/>
+    </row>
+    <row r="6563">
+      <c r="A6563" s="2"/>
+      <c r="B6563" s="5"/>
+      <c r="C6563" s="3"/>
+    </row>
+    <row r="6564">
+      <c r="A6564" s="2"/>
+      <c r="B6564" s="5"/>
+      <c r="C6564" s="3"/>
+    </row>
+    <row r="6565">
+      <c r="A6565" s="2"/>
+      <c r="B6565" s="5"/>
+      <c r="C6565" s="3"/>
+    </row>
+    <row r="6566">
+      <c r="A6566" s="2"/>
+      <c r="B6566" s="5"/>
+      <c r="C6566" s="3"/>
+    </row>
+    <row r="6567">
+      <c r="A6567" s="2"/>
+      <c r="B6567" s="5"/>
+      <c r="C6567" s="3"/>
+    </row>
+    <row r="6568">
+      <c r="A6568" s="2"/>
+      <c r="B6568" s="5"/>
+      <c r="C6568" s="3"/>
+    </row>
+    <row r="6569">
+      <c r="A6569" s="2"/>
+      <c r="B6569" s="5"/>
+      <c r="C6569" s="3"/>
+    </row>
+    <row r="6570">
+      <c r="A6570" s="2"/>
+      <c r="B6570" s="5"/>
+      <c r="C6570" s="3"/>
+    </row>
+    <row r="6571">
+      <c r="A6571" s="2"/>
+      <c r="B6571" s="5"/>
+      <c r="C6571" s="3"/>
+    </row>
+    <row r="6572">
+      <c r="A6572" s="2"/>
+      <c r="B6572" s="5"/>
+      <c r="C6572" s="3"/>
+    </row>
+    <row r="6573">
+      <c r="A6573" s="2"/>
+      <c r="B6573" s="5"/>
+      <c r="C6573" s="3"/>
+    </row>
+    <row r="6574">
+      <c r="A6574" s="2"/>
+      <c r="B6574" s="5"/>
+      <c r="C6574" s="3"/>
+    </row>
+    <row r="6575">
+      <c r="A6575" s="2"/>
+      <c r="B6575" s="5"/>
+      <c r="C6575" s="3"/>
+    </row>
+    <row r="6576">
+      <c r="A6576" s="2"/>
+      <c r="B6576" s="5"/>
+      <c r="C6576" s="3"/>
+    </row>
+    <row r="6577">
+      <c r="A6577" s="2"/>
+      <c r="B6577" s="5"/>
+      <c r="C6577" s="3"/>
+    </row>
+    <row r="6578">
+      <c r="A6578" s="2"/>
+      <c r="B6578" s="5"/>
+      <c r="C6578" s="3"/>
+    </row>
+    <row r="6579">
+      <c r="A6579" s="2"/>
+      <c r="B6579" s="5"/>
+      <c r="C6579" s="3"/>
+    </row>
+    <row r="6580">
+      <c r="A6580" s="2"/>
+      <c r="B6580" s="5"/>
+      <c r="C6580" s="3"/>
+    </row>
+    <row r="6581">
+      <c r="A6581" s="2"/>
+      <c r="B6581" s="5"/>
+      <c r="C6581" s="3"/>
+    </row>
+    <row r="6582">
+      <c r="A6582" s="2"/>
+      <c r="B6582" s="5"/>
+      <c r="C6582" s="3"/>
+    </row>
+    <row r="6583">
+      <c r="A6583" s="2"/>
+      <c r="B6583" s="5"/>
+      <c r="C6583" s="3"/>
+    </row>
+    <row r="6584">
+      <c r="A6584" s="2"/>
+      <c r="B6584" s="5"/>
+      <c r="C6584" s="3"/>
+    </row>
+    <row r="6585">
+      <c r="A6585" s="2"/>
+      <c r="B6585" s="5"/>
+      <c r="C6585" s="3"/>
+    </row>
+    <row r="6586">
+      <c r="A6586" s="2"/>
+      <c r="B6586" s="5"/>
+      <c r="C6586" s="3"/>
+    </row>
+    <row r="6587">
+      <c r="A6587" s="2"/>
+      <c r="B6587" s="5"/>
+      <c r="C6587" s="3"/>
+    </row>
+    <row r="6588">
+      <c r="A6588" s="2"/>
+      <c r="B6588" s="5"/>
+      <c r="C6588" s="3"/>
+    </row>
+    <row r="6589">
+      <c r="A6589" s="2"/>
+      <c r="B6589" s="5"/>
+      <c r="C6589" s="3"/>
+    </row>
+    <row r="6590">
+      <c r="A6590" s="2"/>
+      <c r="B6590" s="5"/>
+      <c r="C6590" s="3"/>
+    </row>
+    <row r="6591">
+      <c r="A6591" s="2"/>
+      <c r="B6591" s="5"/>
+      <c r="C6591" s="3"/>
+    </row>
+    <row r="6592">
+      <c r="A6592" s="2"/>
+      <c r="B6592" s="5"/>
+      <c r="C6592" s="3"/>
+    </row>
+    <row r="6593">
+      <c r="A6593" s="2"/>
+      <c r="B6593" s="5"/>
+      <c r="C6593" s="3"/>
+    </row>
+    <row r="6594">
+      <c r="A6594" s="2"/>
+      <c r="B6594" s="5"/>
+      <c r="C6594" s="3"/>
+    </row>
+    <row r="6595">
+      <c r="A6595" s="2"/>
+      <c r="B6595" s="5"/>
+      <c r="C6595" s="3"/>
+    </row>
+    <row r="6596">
+      <c r="A6596" s="2"/>
+      <c r="B6596" s="5"/>
+      <c r="C6596" s="3"/>
+    </row>
+    <row r="6597">
+      <c r="A6597" s="2"/>
+      <c r="B6597" s="5"/>
+      <c r="C6597" s="3"/>
+    </row>
+    <row r="6598">
+      <c r="A6598" s="2"/>
+      <c r="B6598" s="5"/>
+      <c r="C6598" s="3"/>
+    </row>
+    <row r="6599">
+      <c r="A6599" s="2"/>
+      <c r="B6599" s="5"/>
+      <c r="C6599" s="3"/>
+    </row>
+    <row r="6600">
+      <c r="A6600" s="2"/>
+      <c r="B6600" s="5"/>
+      <c r="C6600" s="3"/>
+    </row>
+    <row r="6601">
+      <c r="A6601" s="2"/>
+      <c r="B6601" s="5"/>
+      <c r="C6601" s="3"/>
+    </row>
+    <row r="6602">
+      <c r="A6602" s="2"/>
+      <c r="B6602" s="5"/>
+      <c r="C6602" s="3"/>
+    </row>
+    <row r="6603">
+      <c r="A6603" s="2"/>
+      <c r="B6603" s="5"/>
+      <c r="C6603" s="3"/>
+    </row>
+    <row r="6604">
+      <c r="A6604" s="2"/>
+      <c r="B6604" s="5"/>
+      <c r="C6604" s="3"/>
+    </row>
+    <row r="6605">
+      <c r="A6605" s="2"/>
+      <c r="B6605" s="5"/>
+      <c r="C6605" s="3"/>
+    </row>
+    <row r="6606">
+      <c r="A6606" s="2"/>
+      <c r="B6606" s="5"/>
+      <c r="C6606" s="3"/>
+    </row>
+    <row r="6607">
+      <c r="A6607" s="2"/>
+      <c r="B6607" s="5"/>
+      <c r="C6607" s="3"/>
+    </row>
+    <row r="6608">
+      <c r="A6608" s="2"/>
+      <c r="B6608" s="5"/>
+      <c r="C6608" s="3"/>
+    </row>
+    <row r="6609">
+      <c r="A6609" s="2"/>
+      <c r="B6609" s="5"/>
+      <c r="C6609" s="3"/>
+    </row>
+    <row r="6610">
+      <c r="A6610" s="2"/>
+      <c r="B6610" s="5"/>
+      <c r="C6610" s="3"/>
+    </row>
+    <row r="6611">
+      <c r="A6611" s="2"/>
+      <c r="B6611" s="5"/>
+      <c r="C6611" s="3"/>
+    </row>
+    <row r="6612">
+      <c r="A6612" s="2"/>
+      <c r="B6612" s="5"/>
+      <c r="C6612" s="3"/>
+    </row>
+    <row r="6613">
+      <c r="A6613" s="2"/>
+      <c r="B6613" s="5"/>
+      <c r="C6613" s="3"/>
+    </row>
+    <row r="6614">
+      <c r="A6614" s="2"/>
+      <c r="B6614" s="5"/>
+      <c r="C6614" s="3"/>
+    </row>
+    <row r="6615">
+      <c r="A6615" s="2"/>
+      <c r="B6615" s="5"/>
+      <c r="C6615" s="3"/>
+    </row>
+    <row r="6616">
+      <c r="A6616" s="2"/>
+      <c r="B6616" s="5"/>
+      <c r="C6616" s="3"/>
+    </row>
+    <row r="6617">
+      <c r="A6617" s="2"/>
+      <c r="B6617" s="5"/>
+      <c r="C6617" s="3"/>
+    </row>
+    <row r="6618">
+      <c r="A6618" s="2"/>
+      <c r="B6618" s="5"/>
+      <c r="C6618" s="3"/>
+    </row>
+    <row r="6619">
+      <c r="A6619" s="2"/>
+      <c r="B6619" s="5"/>
+      <c r="C6619" s="3"/>
+    </row>
+    <row r="6620">
+      <c r="A6620" s="2"/>
+      <c r="B6620" s="5"/>
+      <c r="C6620" s="3"/>
+    </row>
+    <row r="6621">
+      <c r="A6621" s="2"/>
+      <c r="B6621" s="5"/>
+      <c r="C6621" s="3"/>
+    </row>
+    <row r="6622">
+      <c r="A6622" s="2"/>
+      <c r="B6622" s="5"/>
+      <c r="C6622" s="3"/>
+    </row>
+    <row r="6623">
+      <c r="A6623" s="2"/>
+      <c r="B6623" s="5"/>
+      <c r="C6623" s="3"/>
+    </row>
+    <row r="6624">
+      <c r="A6624" s="2"/>
+      <c r="B6624" s="5"/>
+      <c r="C6624" s="3"/>
+    </row>
+    <row r="6625">
+      <c r="A6625" s="2"/>
+      <c r="B6625" s="5"/>
+      <c r="C6625" s="3"/>
+    </row>
+    <row r="6626">
+      <c r="A6626" s="2"/>
+      <c r="B6626" s="5"/>
+      <c r="C6626" s="3"/>
+    </row>
+    <row r="6627">
+      <c r="A6627" s="2"/>
+      <c r="B6627" s="5"/>
+      <c r="C6627" s="3"/>
+    </row>
+    <row r="6628">
+      <c r="A6628" s="2"/>
+      <c r="B6628" s="5"/>
+      <c r="C6628" s="3"/>
+    </row>
+    <row r="6629">
+      <c r="A6629" s="2"/>
+      <c r="B6629" s="5"/>
+      <c r="C6629" s="3"/>
+    </row>
+    <row r="6630">
+      <c r="A6630" s="2"/>
+      <c r="B6630" s="5"/>
+      <c r="C6630" s="3"/>
+    </row>
+    <row r="6631">
+      <c r="A6631" s="2"/>
+      <c r="B6631" s="5"/>
+      <c r="C6631" s="3"/>
+    </row>
+    <row r="6632">
+      <c r="A6632" s="2"/>
+      <c r="B6632" s="5"/>
+      <c r="C6632" s="3"/>
+    </row>
+    <row r="6633">
+      <c r="A6633" s="2"/>
+      <c r="B6633" s="5"/>
+      <c r="C6633" s="3"/>
+    </row>
+    <row r="6634">
+      <c r="A6634" s="2"/>
+      <c r="B6634" s="5"/>
+      <c r="C6634" s="3"/>
+    </row>
+    <row r="6635">
+      <c r="A6635" s="2"/>
+      <c r="B6635" s="5"/>
+      <c r="C6635" s="3"/>
+    </row>
+    <row r="6636">
+      <c r="A6636" s="2"/>
+      <c r="B6636" s="5"/>
+      <c r="C6636" s="3"/>
+    </row>
+    <row r="6637">
+      <c r="A6637" s="2"/>
+      <c r="B6637" s="5"/>
+      <c r="C6637" s="3"/>
+    </row>
+    <row r="6638">
+      <c r="A6638" s="2"/>
+      <c r="B6638" s="5"/>
+      <c r="C6638" s="3"/>
+    </row>
+    <row r="6639">
+      <c r="A6639" s="2"/>
+      <c r="B6639" s="5"/>
+      <c r="C6639" s="3"/>
+    </row>
+    <row r="6640">
+      <c r="A6640" s="2"/>
+      <c r="B6640" s="5"/>
+      <c r="C6640" s="3"/>
+    </row>
+    <row r="6641">
+      <c r="A6641" s="2"/>
+      <c r="B6641" s="5"/>
+      <c r="C6641" s="3"/>
+    </row>
+    <row r="6642">
+      <c r="A6642" s="2"/>
+      <c r="B6642" s="5"/>
+      <c r="C6642" s="3"/>
+    </row>
+    <row r="6643">
+      <c r="A6643" s="2"/>
+      <c r="B6643" s="5"/>
+      <c r="C6643" s="3"/>
+    </row>
+    <row r="6644">
+      <c r="A6644" s="2"/>
+      <c r="B6644" s="5"/>
+      <c r="C6644" s="3"/>
+    </row>
+    <row r="6645">
+      <c r="A6645" s="2"/>
+      <c r="B6645" s="5"/>
+      <c r="C6645" s="3"/>
+    </row>
+    <row r="6646">
+      <c r="A6646" s="2"/>
+      <c r="B6646" s="5"/>
+      <c r="C6646" s="3"/>
+    </row>
+    <row r="6647">
+      <c r="A6647" s="2"/>
+      <c r="B6647" s="5"/>
+      <c r="C6647" s="3"/>
+    </row>
+    <row r="6648">
+      <c r="A6648" s="2"/>
+      <c r="B6648" s="5"/>
+      <c r="C6648" s="3"/>
+    </row>
+    <row r="6649">
+      <c r="A6649" s="2"/>
+      <c r="B6649" s="5"/>
+      <c r="C6649" s="3"/>
+    </row>
+    <row r="6650">
+      <c r="A6650" s="2"/>
+      <c r="B6650" s="5"/>
+      <c r="C6650" s="3"/>
+    </row>
+    <row r="6651">
+      <c r="A6651" s="2"/>
+      <c r="B6651" s="5"/>
+      <c r="C6651" s="3"/>
+    </row>
+    <row r="6652">
+      <c r="A6652" s="2"/>
+      <c r="B6652" s="5"/>
+      <c r="C6652" s="3"/>
+    </row>
+    <row r="6653">
+      <c r="A6653" s="2"/>
+      <c r="B6653" s="5"/>
+      <c r="C6653" s="3"/>
+    </row>
+    <row r="6654">
+      <c r="A6654" s="2"/>
+      <c r="B6654" s="5"/>
+      <c r="C6654" s="3"/>
+    </row>
+    <row r="6655">
+      <c r="A6655" s="2"/>
+      <c r="B6655" s="5"/>
+      <c r="C6655" s="3"/>
+    </row>
+    <row r="6656">
+      <c r="A6656" s="2"/>
+      <c r="B6656" s="5"/>
+      <c r="C6656" s="3"/>
+    </row>
+    <row r="6657">
+      <c r="A6657" s="2"/>
+      <c r="B6657" s="5"/>
+      <c r="C6657" s="3"/>
+    </row>
+    <row r="6658">
+      <c r="A6658" s="2"/>
+      <c r="B6658" s="5"/>
+      <c r="C6658" s="3"/>
+    </row>
+    <row r="6659">
+      <c r="A6659" s="2"/>
+      <c r="B6659" s="5"/>
+      <c r="C6659" s="3"/>
+    </row>
+    <row r="6660">
+      <c r="A6660" s="2"/>
+      <c r="B6660" s="5"/>
+      <c r="C6660" s="3"/>
+    </row>
+    <row r="6661">
+      <c r="A6661" s="2"/>
+      <c r="B6661" s="5"/>
+      <c r="C6661" s="3"/>
+    </row>
+    <row r="6662">
+      <c r="A6662" s="2"/>
+      <c r="B6662" s="5"/>
+      <c r="C6662" s="3"/>
+    </row>
+    <row r="6663">
+      <c r="A6663" s="2"/>
+      <c r="B6663" s="5"/>
+      <c r="C6663" s="3"/>
+    </row>
+    <row r="6664">
+      <c r="A6664" s="2"/>
+      <c r="B6664" s="5"/>
+      <c r="C6664" s="3"/>
+    </row>
+    <row r="6665">
+      <c r="A6665" s="2"/>
+      <c r="B6665" s="5"/>
+      <c r="C6665" s="3"/>
+    </row>
+    <row r="6666">
+      <c r="A6666" s="2"/>
+      <c r="B6666" s="5"/>
+      <c r="C6666" s="3"/>
+    </row>
+    <row r="6667">
+      <c r="A6667" s="2"/>
+      <c r="B6667" s="5"/>
+      <c r="C6667" s="3"/>
+    </row>
+    <row r="6668">
+      <c r="A6668" s="2"/>
+      <c r="B6668" s="5"/>
+      <c r="C6668" s="3"/>
+    </row>
+    <row r="6669">
+      <c r="A6669" s="2"/>
+      <c r="B6669" s="5"/>
+      <c r="C6669" s="3"/>
+    </row>
+    <row r="6670">
+      <c r="A6670" s="2"/>
+      <c r="B6670" s="5"/>
+      <c r="C6670" s="3"/>
+    </row>
+    <row r="6671">
+      <c r="A6671" s="2"/>
+      <c r="B6671" s="5"/>
+      <c r="C6671" s="3"/>
+    </row>
+    <row r="6672">
+      <c r="A6672" s="2"/>
+      <c r="B6672" s="5"/>
+      <c r="C6672" s="3"/>
+    </row>
+    <row r="6673">
+      <c r="A6673" s="2"/>
+      <c r="B6673" s="5"/>
+      <c r="C6673" s="3"/>
+    </row>
+    <row r="6674">
+      <c r="A6674" s="2"/>
+      <c r="B6674" s="5"/>
+      <c r="C6674" s="3"/>
+    </row>
+    <row r="6675">
+      <c r="A6675" s="2"/>
+      <c r="B6675" s="5"/>
+      <c r="C6675" s="3"/>
+    </row>
+    <row r="6676">
+      <c r="A6676" s="2"/>
+      <c r="B6676" s="5"/>
+      <c r="C6676" s="3"/>
+    </row>
+    <row r="6677">
+      <c r="A6677" s="2"/>
+      <c r="B6677" s="5"/>
+      <c r="C6677" s="3"/>
+    </row>
+    <row r="6678">
+      <c r="A6678" s="2"/>
+      <c r="B6678" s="5"/>
+      <c r="C6678" s="3"/>
+    </row>
+    <row r="6679">
+      <c r="A6679" s="2"/>
+      <c r="B6679" s="5"/>
+      <c r="C6679" s="3"/>
+    </row>
+    <row r="6680">
+      <c r="A6680" s="2"/>
+      <c r="B6680" s="5"/>
+      <c r="C6680" s="3"/>
+    </row>
+    <row r="6681">
+      <c r="A6681" s="2"/>
+      <c r="B6681" s="5"/>
+      <c r="C6681" s="3"/>
+    </row>
+    <row r="6682">
+      <c r="A6682" s="2"/>
+      <c r="B6682" s="5"/>
+      <c r="C6682" s="3"/>
+    </row>
+    <row r="6683">
+      <c r="A6683" s="2"/>
+      <c r="B6683" s="5"/>
+      <c r="C6683" s="3"/>
+    </row>
+    <row r="6684">
+      <c r="A6684" s="2"/>
+      <c r="B6684" s="5"/>
+      <c r="C6684" s="3"/>
+    </row>
+    <row r="6685">
+      <c r="A6685" s="2"/>
+      <c r="B6685" s="5"/>
+      <c r="C6685" s="3"/>
+    </row>
+    <row r="6686">
+      <c r="A6686" s="2"/>
+      <c r="B6686" s="5"/>
+      <c r="C6686" s="3"/>
+    </row>
+    <row r="6687">
+      <c r="A6687" s="2"/>
+      <c r="B6687" s="5"/>
+      <c r="C6687" s="3"/>
+    </row>
+    <row r="6688">
+      <c r="A6688" s="2"/>
+      <c r="B6688" s="5"/>
+      <c r="C6688" s="3"/>
+    </row>
+    <row r="6689">
+      <c r="A6689" s="2"/>
+      <c r="B6689" s="5"/>
+      <c r="C6689" s="3"/>
+    </row>
+    <row r="6690">
+      <c r="A6690" s="2"/>
+      <c r="B6690" s="5"/>
+      <c r="C6690" s="3"/>
+    </row>
+    <row r="6691">
+      <c r="A6691" s="2"/>
+      <c r="B6691" s="5"/>
+      <c r="C6691" s="3"/>
+    </row>
+    <row r="6692">
+      <c r="A6692" s="2"/>
+      <c r="B6692" s="5"/>
+      <c r="C6692" s="3"/>
+    </row>
+    <row r="6693">
+      <c r="A6693" s="2"/>
+      <c r="B6693" s="5"/>
+      <c r="C6693" s="3"/>
+    </row>
+    <row r="6694">
+      <c r="A6694" s="2"/>
+      <c r="B6694" s="5"/>
+      <c r="C6694" s="3"/>
+    </row>
+    <row r="6695">
+      <c r="A6695" s="2"/>
+      <c r="B6695" s="5"/>
+      <c r="C6695" s="3"/>
+    </row>
+    <row r="6696">
+      <c r="A6696" s="2"/>
+      <c r="B6696" s="5"/>
+      <c r="C6696" s="3"/>
+    </row>
+    <row r="6697">
+      <c r="A6697" s="2"/>
+      <c r="B6697" s="5"/>
+      <c r="C6697" s="3"/>
+    </row>
+    <row r="6698">
+      <c r="A6698" s="2"/>
+      <c r="B6698" s="5"/>
+      <c r="C6698" s="3"/>
+    </row>
+    <row r="6699">
+      <c r="A6699" s="2"/>
+      <c r="B6699" s="5"/>
+      <c r="C6699" s="3"/>
+    </row>
+    <row r="6700">
+      <c r="A6700" s="2"/>
+      <c r="B6700" s="5"/>
+      <c r="C6700" s="3"/>
+    </row>
+    <row r="6701">
+      <c r="A6701" s="2"/>
+      <c r="B6701" s="5"/>
+      <c r="C6701" s="3"/>
+    </row>
+    <row r="6702">
+      <c r="A6702" s="2"/>
+      <c r="B6702" s="5"/>
+      <c r="C6702" s="3"/>
+    </row>
+    <row r="6703">
+      <c r="A6703" s="2"/>
+      <c r="B6703" s="5"/>
+      <c r="C6703" s="3"/>
+    </row>
+    <row r="6704">
+      <c r="A6704" s="2"/>
+      <c r="B6704" s="5"/>
+      <c r="C6704" s="3"/>
+    </row>
+    <row r="6705">
+      <c r="A6705" s="2"/>
+      <c r="B6705" s="5"/>
+      <c r="C6705" s="3"/>
+    </row>
+    <row r="6706">
+      <c r="A6706" s="2"/>
+      <c r="B6706" s="5"/>
+      <c r="C6706" s="3"/>
+    </row>
+    <row r="6707">
+      <c r="A6707" s="2"/>
+      <c r="B6707" s="5"/>
+      <c r="C6707" s="3"/>
+    </row>
+    <row r="6708">
+      <c r="A6708" s="2"/>
+      <c r="B6708" s="5"/>
+      <c r="C6708" s="3"/>
+    </row>
+    <row r="6709">
+      <c r="A6709" s="2"/>
+      <c r="B6709" s="5"/>
+      <c r="C6709" s="3"/>
+    </row>
+    <row r="6710">
+      <c r="A6710" s="2"/>
+      <c r="B6710" s="5"/>
+      <c r="C6710" s="3"/>
+    </row>
+    <row r="6711">
+      <c r="A6711" s="2"/>
+      <c r="B6711" s="5"/>
+      <c r="C6711" s="3"/>
+    </row>
+    <row r="6712">
+      <c r="A6712" s="2"/>
+      <c r="B6712" s="5"/>
+      <c r="C6712" s="3"/>
+    </row>
+    <row r="6713">
+      <c r="A6713" s="2"/>
+      <c r="B6713" s="5"/>
+      <c r="C6713" s="3"/>
+    </row>
+    <row r="6714">
+      <c r="A6714" s="2"/>
+      <c r="B6714" s="5"/>
+      <c r="C6714" s="3"/>
+    </row>
+    <row r="6715">
+      <c r="A6715" s="2"/>
+      <c r="B6715" s="5"/>
+      <c r="C6715" s="3"/>
+    </row>
+    <row r="6716">
+      <c r="A6716" s="2"/>
+      <c r="B6716" s="5"/>
+      <c r="C6716" s="3"/>
+    </row>
+    <row r="6717">
+      <c r="A6717" s="2"/>
+      <c r="B6717" s="5"/>
+      <c r="C6717" s="3"/>
+    </row>
+    <row r="6718">
+      <c r="A6718" s="2"/>
+      <c r="B6718" s="5"/>
+      <c r="C6718" s="3"/>
+    </row>
+    <row r="6719">
+      <c r="A6719" s="2"/>
+      <c r="B6719" s="5"/>
+      <c r="C6719" s="3"/>
+    </row>
+    <row r="6720">
+      <c r="A6720" s="2"/>
+      <c r="B6720" s="5"/>
+      <c r="C6720" s="3"/>
+    </row>
+    <row r="6721">
+      <c r="A6721" s="2"/>
+      <c r="B6721" s="5"/>
+      <c r="C6721" s="3"/>
+    </row>
+    <row r="6722">
+      <c r="A6722" s="2"/>
+      <c r="B6722" s="5"/>
+      <c r="C6722" s="3"/>
+    </row>
+    <row r="6723">
+      <c r="A6723" s="2"/>
+      <c r="B6723" s="5"/>
+      <c r="C6723" s="3"/>
+    </row>
+    <row r="6724">
+      <c r="A6724" s="2"/>
+      <c r="B6724" s="5"/>
+      <c r="C6724" s="3"/>
+    </row>
+    <row r="6725">
+      <c r="A6725" s="2"/>
+      <c r="B6725" s="5"/>
+      <c r="C6725" s="3"/>
+    </row>
+    <row r="6726">
+      <c r="A6726" s="2"/>
+      <c r="B6726" s="5"/>
+      <c r="C6726" s="3"/>
+    </row>
+    <row r="6727">
+      <c r="A6727" s="2"/>
+      <c r="B6727" s="5"/>
+      <c r="C6727" s="3"/>
+    </row>
+    <row r="6728">
+      <c r="A6728" s="2"/>
+      <c r="B6728" s="5"/>
+      <c r="C6728" s="3"/>
+    </row>
+    <row r="6729">
+      <c r="A6729" s="2"/>
+      <c r="B6729" s="5"/>
+      <c r="C6729" s="3"/>
+    </row>
+    <row r="6730">
+      <c r="A6730" s="2"/>
+      <c r="B6730" s="5"/>
+      <c r="C6730" s="3"/>
+    </row>
+    <row r="6731">
+      <c r="A6731" s="2"/>
+      <c r="B6731" s="5"/>
+      <c r="C6731" s="3"/>
+    </row>
+    <row r="6732">
+      <c r="A6732" s="2"/>
+      <c r="B6732" s="5"/>
+      <c r="C6732" s="3"/>
+    </row>
+    <row r="6733">
+      <c r="A6733" s="2"/>
+      <c r="B6733" s="5"/>
+      <c r="C6733" s="3"/>
+    </row>
+    <row r="6734">
+      <c r="A6734" s="2"/>
+      <c r="B6734" s="5"/>
+      <c r="C6734" s="3"/>
+    </row>
+    <row r="6735">
+      <c r="A6735" s="2"/>
+      <c r="B6735" s="5"/>
+      <c r="C6735" s="3"/>
+    </row>
+    <row r="6736">
+      <c r="A6736" s="2"/>
+      <c r="B6736" s="5"/>
+      <c r="C6736" s="3"/>
+    </row>
+    <row r="6737">
+      <c r="A6737" s="2"/>
+      <c r="B6737" s="5"/>
+      <c r="C6737" s="3"/>
+    </row>
+    <row r="6738">
+      <c r="A6738" s="2"/>
+      <c r="B6738" s="5"/>
+      <c r="C6738" s="3"/>
+    </row>
+    <row r="6739">
+      <c r="A6739" s="2"/>
+      <c r="B6739" s="5"/>
+      <c r="C6739" s="3"/>
+    </row>
+    <row r="6740">
+      <c r="A6740" s="2"/>
+      <c r="B6740" s="5"/>
+      <c r="C6740" s="3"/>
+    </row>
+    <row r="6741">
+      <c r="A6741" s="2"/>
+      <c r="B6741" s="5"/>
+      <c r="C6741" s="3"/>
+    </row>
+    <row r="6742">
+      <c r="A6742" s="2"/>
+      <c r="B6742" s="5"/>
+      <c r="C6742" s="3"/>
+    </row>
+    <row r="6743">
+      <c r="A6743" s="2"/>
+      <c r="B6743" s="5"/>
+      <c r="C6743" s="3"/>
+    </row>
+    <row r="6744">
+      <c r="A6744" s="2"/>
+      <c r="B6744" s="5"/>
+      <c r="C6744" s="3"/>
+    </row>
+    <row r="6745">
+      <c r="A6745" s="2"/>
+      <c r="B6745" s="5"/>
+      <c r="C6745" s="3"/>
+    </row>
+    <row r="6746">
+      <c r="A6746" s="2"/>
+      <c r="B6746" s="5"/>
+      <c r="C6746" s="3"/>
+    </row>
+    <row r="6747">
+      <c r="A6747" s="2"/>
+      <c r="B6747" s="5"/>
+      <c r="C6747" s="3"/>
+    </row>
+    <row r="6748">
+      <c r="A6748" s="2"/>
+      <c r="B6748" s="5"/>
+      <c r="C6748" s="3"/>
+    </row>
+    <row r="6749">
+      <c r="A6749" s="2"/>
+      <c r="B6749" s="5"/>
+      <c r="C6749" s="3"/>
+    </row>
+    <row r="6750">
+      <c r="A6750" s="2"/>
+      <c r="B6750" s="5"/>
+      <c r="C6750" s="3"/>
+    </row>
+    <row r="6751">
+      <c r="A6751" s="2"/>
+      <c r="B6751" s="5"/>
+      <c r="C6751" s="3"/>
+    </row>
+    <row r="6752">
+      <c r="A6752" s="2"/>
+      <c r="B6752" s="5"/>
+      <c r="C6752" s="3"/>
+    </row>
+    <row r="6753">
+      <c r="A6753" s="2"/>
+      <c r="B6753" s="5"/>
+      <c r="C6753" s="3"/>
+    </row>
+    <row r="6754">
+      <c r="A6754" s="2"/>
+      <c r="B6754" s="5"/>
+      <c r="C6754" s="3"/>
+    </row>
+    <row r="6755">
+      <c r="A6755" s="2"/>
+      <c r="B6755" s="5"/>
+      <c r="C6755" s="3"/>
+    </row>
+    <row r="6756">
+      <c r="A6756" s="2"/>
+      <c r="B6756" s="5"/>
+      <c r="C6756" s="3"/>
+    </row>
+    <row r="6757">
+      <c r="A6757" s="2"/>
+      <c r="B6757" s="5"/>
+      <c r="C6757" s="3"/>
+    </row>
+    <row r="6758">
+      <c r="A6758" s="2"/>
+      <c r="B6758" s="5"/>
+      <c r="C6758" s="3"/>
+    </row>
+    <row r="6759">
+      <c r="A6759" s="2"/>
+      <c r="B6759" s="5"/>
+      <c r="C6759" s="3"/>
+    </row>
+    <row r="6760">
+      <c r="A6760" s="2"/>
+      <c r="B6760" s="5"/>
+      <c r="C6760" s="3"/>
+    </row>
+    <row r="6761">
+      <c r="A6761" s="2"/>
+      <c r="B6761" s="5"/>
+      <c r="C6761" s="3"/>
+    </row>
+    <row r="6762">
+      <c r="A6762" s="2"/>
+      <c r="B6762" s="5"/>
+      <c r="C6762" s="3"/>
+    </row>
+    <row r="6763">
+      <c r="A6763" s="2"/>
+      <c r="B6763" s="5"/>
+      <c r="C6763" s="3"/>
+    </row>
+    <row r="6764">
+      <c r="A6764" s="2"/>
+      <c r="B6764" s="5"/>
+      <c r="C6764" s="3"/>
+    </row>
+    <row r="6765">
+      <c r="A6765" s="2"/>
+      <c r="B6765" s="5"/>
+      <c r="C6765" s="3"/>
+    </row>
+    <row r="6766">
+      <c r="A6766" s="2"/>
+      <c r="B6766" s="5"/>
+      <c r="C6766" s="3"/>
+    </row>
+    <row r="6767">
+      <c r="A6767" s="2"/>
+      <c r="B6767" s="5"/>
+      <c r="C6767" s="3"/>
+    </row>
+    <row r="6768">
+      <c r="A6768" s="2"/>
+      <c r="B6768" s="5"/>
+      <c r="C6768" s="3"/>
+    </row>
+    <row r="6769">
+      <c r="A6769" s="2"/>
+      <c r="B6769" s="5"/>
+      <c r="C6769" s="3"/>
+    </row>
+    <row r="6770">
+      <c r="A6770" s="2"/>
+      <c r="B6770" s="5"/>
+      <c r="C6770" s="3"/>
+    </row>
+    <row r="6771">
+      <c r="A6771" s="2"/>
+      <c r="B6771" s="5"/>
+      <c r="C6771" s="3"/>
+    </row>
+    <row r="6772">
+      <c r="A6772" s="2"/>
+      <c r="B6772" s="5"/>
+      <c r="C6772" s="3"/>
+    </row>
+    <row r="6773">
+      <c r="A6773" s="2"/>
+      <c r="B6773" s="5"/>
+      <c r="C6773" s="3"/>
+    </row>
+    <row r="6774">
+      <c r="A6774" s="2"/>
+      <c r="B6774" s="5"/>
+      <c r="C6774" s="3"/>
+    </row>
+    <row r="6775">
+      <c r="A6775" s="2"/>
+      <c r="B6775" s="5"/>
+      <c r="C6775" s="3"/>
+    </row>
+    <row r="6776">
+      <c r="A6776" s="2"/>
+      <c r="B6776" s="5"/>
+      <c r="C6776" s="3"/>
+    </row>
+    <row r="6777">
+      <c r="A6777" s="2"/>
+      <c r="B6777" s="5"/>
+      <c r="C6777" s="3"/>
+    </row>
+    <row r="6778">
+      <c r="A6778" s="2"/>
+      <c r="B6778" s="5"/>
+      <c r="C6778" s="3"/>
+    </row>
+    <row r="6779">
+      <c r="A6779" s="2"/>
+      <c r="B6779" s="5"/>
+      <c r="C6779" s="3"/>
+    </row>
+    <row r="6780">
+      <c r="A6780" s="2"/>
+      <c r="B6780" s="5"/>
+      <c r="C6780" s="3"/>
+    </row>
+    <row r="6781">
+      <c r="A6781" s="2"/>
+      <c r="B6781" s="5"/>
+      <c r="C6781" s="3"/>
+    </row>
+    <row r="6782">
+      <c r="A6782" s="2"/>
+      <c r="B6782" s="5"/>
+      <c r="C6782" s="3"/>
+    </row>
+    <row r="6783">
+      <c r="A6783" s="2"/>
+      <c r="B6783" s="5"/>
+      <c r="C6783" s="3"/>
+    </row>
+    <row r="6784">
+      <c r="A6784" s="2"/>
+      <c r="B6784" s="5"/>
+      <c r="C6784" s="3"/>
+    </row>
+    <row r="6785">
+      <c r="A6785" s="2"/>
+      <c r="B6785" s="5"/>
+      <c r="C6785" s="3"/>
+    </row>
+    <row r="6786">
+      <c r="A6786" s="2"/>
+      <c r="B6786" s="5"/>
+      <c r="C6786" s="3"/>
+    </row>
+    <row r="6787">
+      <c r="A6787" s="2"/>
+      <c r="B6787" s="5"/>
+      <c r="C6787" s="3"/>
+    </row>
+    <row r="6788">
+      <c r="A6788" s="2"/>
+      <c r="B6788" s="5"/>
+      <c r="C6788" s="3"/>
+    </row>
+    <row r="6789">
+      <c r="A6789" s="2"/>
+      <c r="B6789" s="5"/>
+      <c r="C6789" s="3"/>
+    </row>
+    <row r="6790">
+      <c r="A6790" s="2"/>
+      <c r="B6790" s="5"/>
+      <c r="C6790" s="3"/>
+    </row>
+    <row r="6791">
+      <c r="A6791" s="2"/>
+      <c r="B6791" s="5"/>
+      <c r="C6791" s="3"/>
+    </row>
+    <row r="6792">
+      <c r="A6792" s="2"/>
+      <c r="B6792" s="5"/>
+      <c r="C6792" s="3"/>
+    </row>
+    <row r="6793">
+      <c r="A6793" s="2"/>
+      <c r="B6793" s="5"/>
+      <c r="C6793" s="3"/>
+    </row>
+    <row r="6794">
+      <c r="A6794" s="2"/>
+      <c r="B6794" s="5"/>
+      <c r="C6794" s="3"/>
+    </row>
+    <row r="6795">
+      <c r="A6795" s="2"/>
+      <c r="B6795" s="5"/>
+      <c r="C6795" s="3"/>
+    </row>
+    <row r="6796">
+      <c r="A6796" s="2"/>
+      <c r="B6796" s="5"/>
+      <c r="C6796" s="3"/>
+    </row>
+    <row r="6797">
+      <c r="A6797" s="2"/>
+      <c r="B6797" s="5"/>
+      <c r="C6797" s="3"/>
+    </row>
+    <row r="6798">
+      <c r="A6798" s="2"/>
+      <c r="B6798" s="5"/>
+      <c r="C6798" s="3"/>
+    </row>
+    <row r="6799">
+      <c r="A6799" s="2"/>
+      <c r="B6799" s="5"/>
+      <c r="C6799" s="3"/>
+    </row>
+    <row r="6800">
+      <c r="A6800" s="2"/>
+      <c r="B6800" s="5"/>
+      <c r="C6800" s="3"/>
+    </row>
+    <row r="6801">
+      <c r="A6801" s="2"/>
+      <c r="B6801" s="5"/>
+      <c r="C6801" s="3"/>
+    </row>
+    <row r="6802">
+      <c r="A6802" s="2"/>
+      <c r="B6802" s="5"/>
+      <c r="C6802" s="3"/>
+    </row>
+    <row r="6803">
+      <c r="A6803" s="2"/>
+      <c r="B6803" s="5"/>
+      <c r="C6803" s="3"/>
+    </row>
+    <row r="6804">
+      <c r="A6804" s="2"/>
+      <c r="B6804" s="5"/>
+      <c r="C6804" s="3"/>
+    </row>
+    <row r="6805">
+      <c r="A6805" s="2"/>
+      <c r="B6805" s="5"/>
+      <c r="C6805" s="3"/>
+    </row>
+    <row r="6806">
+      <c r="A6806" s="2"/>
+      <c r="B6806" s="5"/>
+      <c r="C6806" s="3"/>
+    </row>
+    <row r="6807">
+      <c r="A6807" s="2"/>
+      <c r="B6807" s="5"/>
+      <c r="C6807" s="3"/>
+    </row>
+    <row r="6808">
+      <c r="A6808" s="2"/>
+      <c r="B6808" s="5"/>
+      <c r="C6808" s="3"/>
+    </row>
+    <row r="6809">
+      <c r="A6809" s="2"/>
+      <c r="B6809" s="5"/>
+      <c r="C6809" s="3"/>
+    </row>
+    <row r="6810">
+      <c r="A6810" s="2"/>
+      <c r="B6810" s="5"/>
+      <c r="C6810" s="3"/>
+    </row>
+    <row r="6811">
+      <c r="A6811" s="2"/>
+      <c r="B6811" s="5"/>
+      <c r="C6811" s="3"/>
+    </row>
+    <row r="6812">
+      <c r="A6812" s="2"/>
+      <c r="B6812" s="5"/>
+      <c r="C6812" s="3"/>
+    </row>
+    <row r="6813">
+      <c r="A6813" s="2"/>
+      <c r="B6813" s="5"/>
+      <c r="C6813" s="3"/>
+    </row>
+    <row r="6814">
+      <c r="A6814" s="2"/>
+      <c r="B6814" s="5"/>
+      <c r="C6814" s="3"/>
+    </row>
+    <row r="6815">
+      <c r="A6815" s="2"/>
+      <c r="B6815" s="5"/>
+      <c r="C6815" s="3"/>
+    </row>
+    <row r="6816">
+      <c r="A6816" s="2"/>
+      <c r="B6816" s="5"/>
+      <c r="C6816" s="3"/>
+    </row>
+    <row r="6817">
+      <c r="A6817" s="2"/>
+      <c r="B6817" s="5"/>
+      <c r="C6817" s="3"/>
+    </row>
+    <row r="6818">
+      <c r="A6818" s="2"/>
+      <c r="B6818" s="5"/>
+      <c r="C6818" s="3"/>
+    </row>
+    <row r="6819">
+      <c r="A6819" s="2"/>
+      <c r="B6819" s="5"/>
+      <c r="C6819" s="3"/>
+    </row>
+    <row r="6820">
+      <c r="A6820" s="2"/>
+      <c r="B6820" s="5"/>
+      <c r="C6820" s="3"/>
+    </row>
+    <row r="6821">
+      <c r="A6821" s="2"/>
+      <c r="B6821" s="5"/>
+      <c r="C6821" s="3"/>
+    </row>
+    <row r="6822">
+      <c r="A6822" s="2"/>
+      <c r="B6822" s="5"/>
+      <c r="C6822" s="3"/>
+    </row>
+    <row r="6823">
+      <c r="A6823" s="2"/>
+      <c r="B6823" s="5"/>
+      <c r="C6823" s="3"/>
+    </row>
+    <row r="6824">
+      <c r="A6824" s="2"/>
+      <c r="B6824" s="5"/>
+      <c r="C6824" s="3"/>
+    </row>
+    <row r="6825">
+      <c r="A6825" s="2"/>
+      <c r="B6825" s="5"/>
+      <c r="C6825" s="3"/>
+    </row>
+    <row r="6826">
+      <c r="A6826" s="2"/>
+      <c r="B6826" s="5"/>
+      <c r="C6826" s="3"/>
+    </row>
+    <row r="6827">
+      <c r="A6827" s="2"/>
+      <c r="B6827" s="5"/>
+      <c r="C6827" s="3"/>
+    </row>
+    <row r="6828">
+      <c r="A6828" s="2"/>
+      <c r="B6828" s="5"/>
+      <c r="C6828" s="3"/>
+    </row>
+    <row r="6829">
+      <c r="A6829" s="2"/>
+      <c r="B6829" s="5"/>
+      <c r="C6829" s="3"/>
+    </row>
+    <row r="6830">
+      <c r="A6830" s="2"/>
+      <c r="B6830" s="5"/>
+      <c r="C6830" s="3"/>
+    </row>
+    <row r="6831">
+      <c r="A6831" s="2"/>
+      <c r="B6831" s="5"/>
+      <c r="C6831" s="3"/>
+    </row>
+    <row r="6832">
+      <c r="A6832" s="2"/>
+      <c r="B6832" s="5"/>
+      <c r="C6832" s="3"/>
+    </row>
+    <row r="6833">
+      <c r="A6833" s="2"/>
+      <c r="B6833" s="5"/>
+      <c r="C6833" s="3"/>
+    </row>
+    <row r="6834">
+      <c r="A6834" s="2"/>
+      <c r="B6834" s="5"/>
+      <c r="C6834" s="3"/>
+    </row>
+    <row r="6835">
+      <c r="A6835" s="2"/>
+      <c r="B6835" s="5"/>
+      <c r="C6835" s="3"/>
+    </row>
+    <row r="6836">
+      <c r="A6836" s="2"/>
+      <c r="B6836" s="5"/>
+      <c r="C6836" s="3"/>
+    </row>
+    <row r="6837">
+      <c r="A6837" s="2"/>
+      <c r="B6837" s="5"/>
+      <c r="C6837" s="3"/>
+    </row>
+    <row r="6838">
+      <c r="A6838" s="2"/>
+      <c r="B6838" s="5"/>
+      <c r="C6838" s="3"/>
+    </row>
+    <row r="6839">
+      <c r="A6839" s="2"/>
+      <c r="B6839" s="5"/>
+      <c r="C6839" s="3"/>
+    </row>
+    <row r="6840">
+      <c r="A6840" s="2"/>
+      <c r="B6840" s="5"/>
+      <c r="C6840" s="3"/>
+    </row>
+    <row r="6841">
+      <c r="A6841" s="2"/>
+      <c r="B6841" s="5"/>
+      <c r="C6841" s="3"/>
+    </row>
+    <row r="6842">
+      <c r="A6842" s="2"/>
+      <c r="B6842" s="5"/>
+      <c r="C6842" s="3"/>
+    </row>
+    <row r="6843">
+      <c r="A6843" s="2"/>
+      <c r="B6843" s="5"/>
+      <c r="C6843" s="3"/>
+    </row>
+    <row r="6844">
+      <c r="A6844" s="2"/>
+      <c r="B6844" s="5"/>
+      <c r="C6844" s="3"/>
+    </row>
+    <row r="6845">
+      <c r="A6845" s="2"/>
+      <c r="B6845" s="5"/>
+      <c r="C6845" s="3"/>
+    </row>
+    <row r="6846">
+      <c r="A6846" s="2"/>
+      <c r="B6846" s="5"/>
+      <c r="C6846" s="3"/>
+    </row>
+    <row r="6847">
+      <c r="A6847" s="2"/>
+      <c r="B6847" s="5"/>
+      <c r="C6847" s="3"/>
+    </row>
+    <row r="6848">
+      <c r="A6848" s="2"/>
+      <c r="B6848" s="5"/>
+      <c r="C6848" s="3"/>
+    </row>
+    <row r="6849">
+      <c r="A6849" s="2"/>
+      <c r="B6849" s="5"/>
+      <c r="C6849" s="3"/>
+    </row>
+    <row r="6850">
+      <c r="A6850" s="2"/>
+      <c r="B6850" s="5"/>
+      <c r="C6850" s="3"/>
+    </row>
+    <row r="6851">
+      <c r="A6851" s="2"/>
+      <c r="B6851" s="5"/>
+      <c r="C6851" s="3"/>
+    </row>
+    <row r="6852">
+      <c r="A6852" s="2"/>
+      <c r="B6852" s="5"/>
+      <c r="C6852" s="3"/>
+    </row>
+    <row r="6853">
+      <c r="A6853" s="2"/>
+      <c r="B6853" s="5"/>
+      <c r="C6853" s="3"/>
+    </row>
+    <row r="6854">
+      <c r="A6854" s="2"/>
+      <c r="B6854" s="5"/>
+      <c r="C6854" s="3"/>
+    </row>
+    <row r="6855">
+      <c r="A6855" s="2"/>
+      <c r="B6855" s="5"/>
+      <c r="C6855" s="3"/>
+    </row>
+    <row r="6856">
+      <c r="A6856" s="2"/>
+      <c r="B6856" s="5"/>
+      <c r="C6856" s="3"/>
+    </row>
+    <row r="6857">
+      <c r="A6857" s="2"/>
+      <c r="B6857" s="5"/>
+      <c r="C6857" s="3"/>
+    </row>
+    <row r="6858">
+      <c r="A6858" s="2"/>
+      <c r="B6858" s="5"/>
+      <c r="C6858" s="3"/>
+    </row>
+    <row r="6859">
+      <c r="A6859" s="2"/>
+      <c r="B6859" s="5"/>
+      <c r="C6859" s="3"/>
+    </row>
+    <row r="6860">
+      <c r="A6860" s="2"/>
+      <c r="B6860" s="5"/>
+      <c r="C6860" s="3"/>
+    </row>
+    <row r="6861">
+      <c r="A6861" s="2"/>
+      <c r="B6861" s="5"/>
+      <c r="C6861" s="3"/>
+    </row>
+    <row r="6862">
+      <c r="A6862" s="2"/>
+      <c r="B6862" s="5"/>
+      <c r="C6862" s="3"/>
+    </row>
+    <row r="6863">
+      <c r="A6863" s="2"/>
+      <c r="B6863" s="5"/>
+      <c r="C6863" s="3"/>
+    </row>
+    <row r="6864">
+      <c r="A6864" s="2"/>
+      <c r="B6864" s="5"/>
+      <c r="C6864" s="3"/>
+    </row>
+    <row r="6865">
+      <c r="A6865" s="2"/>
+      <c r="B6865" s="5"/>
+      <c r="C6865" s="3"/>
+    </row>
+    <row r="6866">
+      <c r="A6866" s="2"/>
+      <c r="B6866" s="5"/>
+      <c r="C6866" s="3"/>
+    </row>
+    <row r="6867">
+      <c r="A6867" s="2"/>
+      <c r="B6867" s="5"/>
+      <c r="C6867" s="3"/>
+    </row>
+    <row r="6868">
+      <c r="A6868" s="2"/>
+      <c r="B6868" s="5"/>
+      <c r="C6868" s="3"/>
+    </row>
+    <row r="6869">
+      <c r="A6869" s="2"/>
+      <c r="B6869" s="5"/>
+      <c r="C6869" s="3"/>
+    </row>
+    <row r="6870">
+      <c r="A6870" s="2"/>
+      <c r="B6870" s="5"/>
+      <c r="C6870" s="3"/>
+    </row>
+    <row r="6871">
+      <c r="A6871" s="2"/>
+      <c r="B6871" s="5"/>
+      <c r="C6871" s="3"/>
+    </row>
+    <row r="6872">
+      <c r="A6872" s="2"/>
+      <c r="B6872" s="5"/>
+      <c r="C6872" s="3"/>
+    </row>
+    <row r="6873">
+      <c r="A6873" s="2"/>
+      <c r="B6873" s="5"/>
+      <c r="C6873" s="3"/>
+    </row>
+    <row r="6874">
+      <c r="A6874" s="2"/>
+      <c r="B6874" s="5"/>
+      <c r="C6874" s="3"/>
+    </row>
+    <row r="6875">
+      <c r="A6875" s="2"/>
+      <c r="B6875" s="5"/>
+      <c r="C6875" s="3"/>
+    </row>
+    <row r="6876">
+      <c r="A6876" s="2"/>
+      <c r="B6876" s="5"/>
+      <c r="C6876" s="3"/>
+    </row>
+    <row r="6877">
+      <c r="A6877" s="2"/>
+      <c r="B6877" s="5"/>
+      <c r="C6877" s="3"/>
+    </row>
+    <row r="6878">
+      <c r="A6878" s="2"/>
+      <c r="B6878" s="5"/>
+      <c r="C6878" s="3"/>
+    </row>
+    <row r="6879">
+      <c r="A6879" s="2"/>
+      <c r="B6879" s="5"/>
+      <c r="C6879" s="3"/>
+    </row>
+    <row r="6880">
+      <c r="A6880" s="2"/>
+      <c r="B6880" s="5"/>
+      <c r="C6880" s="3"/>
+    </row>
+    <row r="6881">
+      <c r="A6881" s="2"/>
+      <c r="B6881" s="5"/>
+      <c r="C6881" s="3"/>
+    </row>
+    <row r="6882">
+      <c r="A6882" s="2"/>
+      <c r="B6882" s="5"/>
+      <c r="C6882" s="3"/>
+    </row>
+    <row r="6883">
+      <c r="A6883" s="2"/>
+      <c r="B6883" s="5"/>
+      <c r="C6883" s="3"/>
+    </row>
+    <row r="6884">
+      <c r="A6884" s="2"/>
+      <c r="B6884" s="5"/>
+      <c r="C6884" s="3"/>
+    </row>
+    <row r="6885">
+      <c r="A6885" s="2"/>
+      <c r="B6885" s="5"/>
+      <c r="C6885" s="3"/>
+    </row>
+    <row r="6886">
+      <c r="A6886" s="2"/>
+      <c r="B6886" s="5"/>
+      <c r="C6886" s="3"/>
+    </row>
+    <row r="6887">
+      <c r="A6887" s="2"/>
+      <c r="B6887" s="5"/>
+      <c r="C6887" s="3"/>
+    </row>
+    <row r="6888">
+      <c r="A6888" s="2"/>
+      <c r="B6888" s="5"/>
+      <c r="C6888" s="3"/>
+    </row>
+    <row r="6889">
+      <c r="A6889" s="2"/>
+      <c r="B6889" s="5"/>
+      <c r="C6889" s="3"/>
+    </row>
+    <row r="6890">
+      <c r="A6890" s="2"/>
+      <c r="B6890" s="5"/>
+      <c r="C6890" s="3"/>
+    </row>
+    <row r="6891">
+      <c r="A6891" s="2"/>
+      <c r="B6891" s="5"/>
+      <c r="C6891" s="3"/>
+    </row>
+    <row r="6892">
+      <c r="A6892" s="2"/>
+      <c r="B6892" s="5"/>
+      <c r="C6892" s="3"/>
+    </row>
+    <row r="6893">
+      <c r="A6893" s="2"/>
+      <c r="B6893" s="5"/>
+      <c r="C6893" s="3"/>
+    </row>
+    <row r="6894">
+      <c r="A6894" s="2"/>
+      <c r="B6894" s="5"/>
+      <c r="C6894" s="3"/>
+    </row>
+    <row r="6895">
+      <c r="A6895" s="2"/>
+      <c r="B6895" s="5"/>
+      <c r="C6895" s="3"/>
+    </row>
+    <row r="6896">
+      <c r="A6896" s="2"/>
+      <c r="B6896" s="5"/>
+      <c r="C6896" s="3"/>
+    </row>
+    <row r="6897">
+      <c r="A6897" s="2"/>
+      <c r="B6897" s="5"/>
+      <c r="C6897" s="3"/>
+    </row>
+    <row r="6898">
+      <c r="A6898" s="2"/>
+      <c r="B6898" s="5"/>
+      <c r="C6898" s="3"/>
+    </row>
+    <row r="6899">
+      <c r="A6899" s="2"/>
+      <c r="B6899" s="5"/>
+      <c r="C6899" s="3"/>
+    </row>
+    <row r="6900">
+      <c r="A6900" s="2"/>
+      <c r="B6900" s="5"/>
+      <c r="C6900" s="3"/>
+    </row>
+    <row r="6901">
+      <c r="A6901" s="2"/>
+      <c r="B6901" s="5"/>
+      <c r="C6901" s="3"/>
+    </row>
+    <row r="6902">
+      <c r="A6902" s="2"/>
+      <c r="B6902" s="5"/>
+      <c r="C6902" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -65561,29 +65561,59 @@
       </c>
     </row>
     <row r="5933">
-      <c r="A5933" s="2"/>
-      <c r="B5933" s="5"/>
-      <c r="C5933" s="3"/>
+      <c r="A5933" s="6">
+        <v>46128.0</v>
+      </c>
+      <c r="B5933" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5933" s="7">
+        <v>130.187589</v>
+      </c>
     </row>
     <row r="5934">
-      <c r="A5934" s="2"/>
-      <c r="B5934" s="5"/>
-      <c r="C5934" s="3"/>
+      <c r="A5934" s="6">
+        <v>46129.0</v>
+      </c>
+      <c r="B5934" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5934" s="7">
+        <v>108.210714</v>
+      </c>
     </row>
     <row r="5935">
-      <c r="A5935" s="2"/>
-      <c r="B5935" s="5"/>
-      <c r="C5935" s="3"/>
+      <c r="A5935" s="6">
+        <v>46130.0</v>
+      </c>
+      <c r="B5935" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5935" s="7">
+        <v>89.390638</v>
+      </c>
     </row>
     <row r="5936">
-      <c r="A5936" s="2"/>
-      <c r="B5936" s="5"/>
-      <c r="C5936" s="3"/>
+      <c r="A5936" s="6">
+        <v>46131.0</v>
+      </c>
+      <c r="B5936" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5936" s="7">
+        <v>101.831701</v>
+      </c>
     </row>
     <row r="5937">
-      <c r="A5937" s="2"/>
-      <c r="B5937" s="5"/>
-      <c r="C5937" s="3"/>
+      <c r="A5937" s="6">
+        <v>46132.0</v>
+      </c>
+      <c r="B5937" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5937" s="7">
+        <v>110.845055</v>
+      </c>
     </row>
     <row r="5938">
       <c r="A5938" s="2"/>

--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -65616,57 +65616,105 @@
       </c>
     </row>
     <row r="5938">
-      <c r="A5938" s="2"/>
-      <c r="B5938" s="5"/>
-      <c r="C5938" s="3"/>
+      <c r="A5938" s="6">
+        <v>46133.0</v>
+      </c>
+      <c r="B5938" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5938" s="7">
+        <v>113.590683</v>
+      </c>
     </row>
     <row r="5939">
-      <c r="A5939" s="2"/>
-      <c r="B5939" s="5"/>
-      <c r="C5939" s="3"/>
+      <c r="A5939" s="6">
+        <v>46134.0</v>
+      </c>
+      <c r="B5939" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5939" s="7">
+        <v>120.065539</v>
+      </c>
     </row>
     <row r="5940">
-      <c r="A5940" s="2"/>
-      <c r="B5940" s="5"/>
-      <c r="C5940" s="3"/>
+      <c r="A5940" s="6">
+        <v>46135.0</v>
+      </c>
+      <c r="B5940" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5940" s="7">
+        <v>95.733503</v>
+      </c>
     </row>
     <row r="5941">
-      <c r="A5941" s="2"/>
-      <c r="B5941" s="5"/>
-      <c r="C5941" s="3"/>
+      <c r="A5941" s="6">
+        <v>46136.0</v>
+      </c>
+      <c r="B5941" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5941" s="7">
+        <v>111.57306</v>
+      </c>
     </row>
     <row r="5942">
-      <c r="A5942" s="2"/>
-      <c r="B5942" s="5"/>
-      <c r="C5942" s="3"/>
+      <c r="A5942" s="6">
+        <v>46137.0</v>
+      </c>
+      <c r="B5942" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5942" s="7">
+        <v>104.310104</v>
+      </c>
     </row>
     <row r="5943">
-      <c r="A5943" s="2"/>
-      <c r="B5943" s="5"/>
-      <c r="C5943" s="3"/>
+      <c r="A5943" s="6">
+        <v>46138.0</v>
+      </c>
+      <c r="B5943" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5943" s="7">
+        <v>107.731779</v>
+      </c>
     </row>
     <row r="5944">
-      <c r="A5944" s="2"/>
-      <c r="B5944" s="5"/>
-      <c r="C5944" s="3"/>
+      <c r="A5944" s="6">
+        <v>46139.0</v>
+      </c>
+      <c r="B5944" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5944" s="7">
+        <v>122.41275</v>
+      </c>
     </row>
     <row r="5945">
-      <c r="A5945" s="2"/>
-      <c r="B5945" s="5"/>
-      <c r="C5945" s="3"/>
+      <c r="A5945" s="6">
+        <v>46140.0</v>
+      </c>
+      <c r="B5945" s="5">
+        <v>2026.0</v>
+      </c>
+      <c r="C5945" s="7">
+        <v>128.587441</v>
+      </c>
     </row>
     <row r="5946">
-      <c r="A5946" s="2"/>
+      <c r="A5946" s="6"/>
       <c r="B5946" s="5"/>
-      <c r="C5946" s="3"/>
+      <c r="C5946" s="7"/>
     </row>
     <row r="5947">
-      <c r="A5947" s="2"/>
+      <c r="A5947" s="6"/>
       <c r="B5947" s="5"/>
       <c r="C5947" s="3"/>
     </row>
     <row r="5948">
-      <c r="A5948" s="2"/>
+      <c r="A5948" s="6"/>
       <c r="B5948" s="5"/>
       <c r="C5948" s="3"/>
     </row>

--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -66,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -85,10 +85,19 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -65858,4719 +65867,4803 @@
       </c>
     </row>
     <row r="5960">
-      <c r="A5960" s="6"/>
-      <c r="B5960" s="2"/>
-      <c r="C5960" s="7"/>
+      <c r="A5960" s="3">
+        <v>46155.0</v>
+      </c>
+      <c r="B5960" s="2">
+        <v>2026.0</v>
+      </c>
+      <c r="C5960" s="6">
+        <v>126.61</v>
+      </c>
     </row>
     <row r="5961">
-      <c r="A5961" s="6"/>
-      <c r="B5961" s="2"/>
-      <c r="C5961" s="7"/>
+      <c r="A5961" s="7">
+        <v>46156.0</v>
+      </c>
+      <c r="B5961" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5961" s="9">
+        <v>121.736692</v>
+      </c>
     </row>
     <row r="5962">
-      <c r="A5962" s="6"/>
-      <c r="B5962" s="2"/>
-      <c r="C5962" s="7"/>
+      <c r="A5962" s="7">
+        <v>46157.0</v>
+      </c>
+      <c r="B5962" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5962" s="9">
+        <v>136.363537</v>
+      </c>
     </row>
     <row r="5963">
-      <c r="A5963" s="6"/>
-      <c r="B5963" s="2"/>
-      <c r="C5963" s="7"/>
+      <c r="A5963" s="7">
+        <v>46158.0</v>
+      </c>
+      <c r="B5963" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5963" s="9">
+        <v>110.015278</v>
+      </c>
     </row>
     <row r="5964">
-      <c r="A5964" s="6"/>
-      <c r="B5964" s="2"/>
-      <c r="C5964" s="7"/>
+      <c r="A5964" s="7">
+        <v>46159.0</v>
+      </c>
+      <c r="B5964" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5964" s="9">
+        <v>100.758661</v>
+      </c>
     </row>
     <row r="5965">
-      <c r="A5965" s="6"/>
-      <c r="B5965" s="2"/>
-      <c r="C5965" s="7"/>
+      <c r="A5965" s="7">
+        <v>46160.0</v>
+      </c>
+      <c r="B5965" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5965" s="9">
+        <v>139.237325</v>
+      </c>
     </row>
     <row r="5966">
-      <c r="A5966" s="6"/>
-      <c r="B5966" s="2"/>
-      <c r="C5966" s="7"/>
+      <c r="A5966" s="7">
+        <v>46161.0</v>
+      </c>
+      <c r="B5966" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5966" s="9">
+        <v>133.018118</v>
+      </c>
     </row>
     <row r="5967">
-      <c r="A5967" s="6"/>
-      <c r="B5967" s="2"/>
-      <c r="C5967" s="7"/>
+      <c r="A5967" s="7">
+        <v>46162.0</v>
+      </c>
+      <c r="B5967" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5967" s="9">
+        <v>123.026191</v>
+      </c>
     </row>
     <row r="5968">
-      <c r="A5968" s="6"/>
-      <c r="B5968" s="2"/>
-      <c r="C5968" s="7"/>
+      <c r="A5968" s="7">
+        <v>46163.0</v>
+      </c>
+      <c r="B5968" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5968" s="9">
+        <v>115.370406</v>
+      </c>
     </row>
     <row r="5969">
-      <c r="A5969" s="6"/>
-      <c r="B5969" s="2"/>
-      <c r="C5969" s="7"/>
+      <c r="A5969" s="7">
+        <v>46164.0</v>
+      </c>
+      <c r="B5969" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5969" s="9">
+        <v>111.237184</v>
+      </c>
     </row>
     <row r="5970">
-      <c r="A5970" s="6"/>
-      <c r="B5970" s="2"/>
-      <c r="C5970" s="7"/>
+      <c r="A5970" s="7">
+        <v>46165.0</v>
+      </c>
+      <c r="B5970" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5970" s="9">
+        <v>100.015441</v>
+      </c>
     </row>
     <row r="5971">
-      <c r="A5971" s="6"/>
-      <c r="B5971" s="2"/>
-      <c r="C5971" s="7"/>
+      <c r="A5971" s="7">
+        <v>46166.0</v>
+      </c>
+      <c r="B5971" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5971" s="9">
+        <v>92.283061</v>
+      </c>
     </row>
     <row r="5972">
-      <c r="A5972" s="6"/>
-      <c r="B5972" s="2"/>
-      <c r="C5972" s="7"/>
+      <c r="A5972" s="7">
+        <v>46167.0</v>
+      </c>
+      <c r="B5972" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5972" s="9">
+        <v>116.418065</v>
+      </c>
     </row>
     <row r="5973">
-      <c r="A5973" s="6"/>
-      <c r="B5973" s="2"/>
-      <c r="C5973" s="7"/>
+      <c r="A5973" s="7">
+        <v>46168.0</v>
+      </c>
+      <c r="B5973" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5973" s="9">
+        <v>126.003893</v>
+      </c>
     </row>
     <row r="5974">
-      <c r="A5974" s="6"/>
+      <c r="A5974" s="10"/>
       <c r="B5974" s="2"/>
-      <c r="C5974" s="7"/>
+      <c r="C5974" s="6"/>
     </row>
     <row r="5975">
-      <c r="A5975" s="6"/>
+      <c r="A5975" s="10"/>
       <c r="B5975" s="2"/>
-      <c r="C5975" s="7"/>
+      <c r="C5975" s="6"/>
     </row>
     <row r="5976">
-      <c r="A5976" s="6"/>
+      <c r="A5976" s="10"/>
       <c r="B5976" s="2"/>
-      <c r="C5976" s="7"/>
+      <c r="C5976" s="6"/>
     </row>
     <row r="5977">
-      <c r="A5977" s="6"/>
+      <c r="A5977" s="10"/>
       <c r="B5977" s="2"/>
-      <c r="C5977" s="7"/>
+      <c r="C5977" s="6"/>
     </row>
     <row r="5978">
-      <c r="A5978" s="6"/>
+      <c r="A5978" s="10"/>
       <c r="B5978" s="2"/>
-      <c r="C5978" s="7"/>
+      <c r="C5978" s="6"/>
     </row>
     <row r="5979">
-      <c r="A5979" s="6"/>
+      <c r="A5979" s="10"/>
       <c r="B5979" s="2"/>
-      <c r="C5979" s="7"/>
+      <c r="C5979" s="6"/>
     </row>
     <row r="5980">
-      <c r="A5980" s="6"/>
+      <c r="A5980" s="10"/>
       <c r="B5980" s="2"/>
-      <c r="C5980" s="7"/>
+      <c r="C5980" s="6"/>
     </row>
     <row r="5981">
-      <c r="A5981" s="6"/>
+      <c r="A5981" s="10"/>
       <c r="B5981" s="2"/>
-      <c r="C5981" s="7"/>
+      <c r="C5981" s="6"/>
     </row>
     <row r="5982">
-      <c r="A5982" s="6"/>
+      <c r="A5982" s="10"/>
       <c r="B5982" s="2"/>
-      <c r="C5982" s="7"/>
+      <c r="C5982" s="6"/>
     </row>
     <row r="5983">
-      <c r="A5983" s="6"/>
+      <c r="A5983" s="10"/>
       <c r="B5983" s="2"/>
-      <c r="C5983" s="7"/>
+      <c r="C5983" s="6"/>
     </row>
     <row r="5984">
-      <c r="A5984" s="6"/>
+      <c r="A5984" s="10"/>
       <c r="B5984" s="2"/>
-      <c r="C5984" s="7"/>
+      <c r="C5984" s="6"/>
     </row>
     <row r="5985">
-      <c r="A5985" s="6"/>
+      <c r="A5985" s="10"/>
       <c r="B5985" s="2"/>
-      <c r="C5985" s="7"/>
+      <c r="C5985" s="6"/>
     </row>
     <row r="5986">
-      <c r="A5986" s="6"/>
+      <c r="A5986" s="10"/>
       <c r="B5986" s="2"/>
-      <c r="C5986" s="7"/>
+      <c r="C5986" s="6"/>
     </row>
     <row r="5987">
-      <c r="A5987" s="6"/>
+      <c r="A5987" s="10"/>
       <c r="B5987" s="2"/>
-      <c r="C5987" s="7"/>
+      <c r="C5987" s="6"/>
     </row>
     <row r="5988">
-      <c r="A5988" s="6"/>
+      <c r="A5988" s="10"/>
       <c r="B5988" s="2"/>
-      <c r="C5988" s="7"/>
+      <c r="C5988" s="6"/>
     </row>
     <row r="5989">
-      <c r="A5989" s="6"/>
+      <c r="A5989" s="10"/>
       <c r="B5989" s="2"/>
-      <c r="C5989" s="7"/>
+      <c r="C5989" s="6"/>
     </row>
     <row r="5990">
-      <c r="A5990" s="6"/>
+      <c r="A5990" s="10"/>
       <c r="B5990" s="2"/>
-      <c r="C5990" s="7"/>
+      <c r="C5990" s="6"/>
     </row>
     <row r="5991">
-      <c r="A5991" s="6"/>
+      <c r="A5991" s="10"/>
       <c r="B5991" s="2"/>
-      <c r="C5991" s="7"/>
+      <c r="C5991" s="6"/>
     </row>
     <row r="5992">
-      <c r="A5992" s="6"/>
+      <c r="A5992" s="10"/>
       <c r="B5992" s="2"/>
-      <c r="C5992" s="7"/>
+      <c r="C5992" s="6"/>
     </row>
     <row r="5993">
-      <c r="A5993" s="6"/>
+      <c r="A5993" s="10"/>
       <c r="B5993" s="2"/>
-      <c r="C5993" s="7"/>
+      <c r="C5993" s="6"/>
     </row>
     <row r="5994">
-      <c r="A5994" s="6"/>
+      <c r="A5994" s="10"/>
       <c r="B5994" s="2"/>
-      <c r="C5994" s="7"/>
+      <c r="C5994" s="6"/>
     </row>
     <row r="5995">
-      <c r="A5995" s="6"/>
+      <c r="A5995" s="10"/>
       <c r="B5995" s="2"/>
-      <c r="C5995" s="7"/>
+      <c r="C5995" s="6"/>
     </row>
     <row r="5996">
-      <c r="A5996" s="6"/>
+      <c r="A5996" s="10"/>
       <c r="B5996" s="2"/>
-      <c r="C5996" s="7"/>
+      <c r="C5996" s="6"/>
     </row>
     <row r="5997">
-      <c r="A5997" s="6"/>
+      <c r="A5997" s="10"/>
       <c r="B5997" s="2"/>
-      <c r="C5997" s="7"/>
+      <c r="C5997" s="6"/>
     </row>
     <row r="5998">
-      <c r="A5998" s="6"/>
+      <c r="A5998" s="10"/>
       <c r="B5998" s="2"/>
-      <c r="C5998" s="7"/>
+      <c r="C5998" s="6"/>
     </row>
     <row r="5999">
-      <c r="A5999" s="6"/>
+      <c r="A5999" s="10"/>
       <c r="B5999" s="2"/>
-      <c r="C5999" s="7"/>
+      <c r="C5999" s="6"/>
     </row>
     <row r="6000">
-      <c r="A6000" s="6"/>
+      <c r="A6000" s="10"/>
       <c r="B6000" s="2"/>
-      <c r="C6000" s="7"/>
+      <c r="C6000" s="6"/>
     </row>
     <row r="6001">
-      <c r="A6001" s="6"/>
+      <c r="A6001" s="10"/>
       <c r="B6001" s="2"/>
-      <c r="C6001" s="7"/>
+      <c r="C6001" s="6"/>
     </row>
     <row r="6002">
-      <c r="A6002" s="6"/>
+      <c r="A6002" s="10"/>
       <c r="B6002" s="2"/>
-      <c r="C6002" s="7"/>
+      <c r="C6002" s="6"/>
     </row>
     <row r="6003">
-      <c r="A6003" s="6"/>
+      <c r="A6003" s="10"/>
       <c r="B6003" s="2"/>
-      <c r="C6003" s="7"/>
+      <c r="C6003" s="6"/>
     </row>
     <row r="6004">
-      <c r="A6004" s="6"/>
+      <c r="A6004" s="10"/>
       <c r="B6004" s="2"/>
-      <c r="C6004" s="7"/>
+      <c r="C6004" s="6"/>
     </row>
     <row r="6005">
-      <c r="A6005" s="6"/>
+      <c r="A6005" s="10"/>
       <c r="B6005" s="2"/>
-      <c r="C6005" s="7"/>
+      <c r="C6005" s="6"/>
     </row>
     <row r="6006">
-      <c r="A6006" s="6"/>
+      <c r="A6006" s="10"/>
       <c r="B6006" s="2"/>
-      <c r="C6006" s="7"/>
+      <c r="C6006" s="6"/>
     </row>
     <row r="6007">
-      <c r="A6007" s="6"/>
+      <c r="A6007" s="10"/>
       <c r="B6007" s="2"/>
-      <c r="C6007" s="7"/>
+      <c r="C6007" s="6"/>
     </row>
     <row r="6008">
-      <c r="A6008" s="6"/>
+      <c r="A6008" s="10"/>
       <c r="B6008" s="2"/>
-      <c r="C6008" s="7"/>
+      <c r="C6008" s="6"/>
     </row>
     <row r="6009">
-      <c r="A6009" s="6"/>
+      <c r="A6009" s="10"/>
       <c r="B6009" s="2"/>
-      <c r="C6009" s="7"/>
+      <c r="C6009" s="6"/>
     </row>
     <row r="6010">
-      <c r="A6010" s="6"/>
+      <c r="A6010" s="10"/>
       <c r="B6010" s="2"/>
-      <c r="C6010" s="7"/>
+      <c r="C6010" s="6"/>
     </row>
     <row r="6011">
-      <c r="A6011" s="6"/>
+      <c r="A6011" s="10"/>
       <c r="B6011" s="2"/>
-      <c r="C6011" s="7"/>
+      <c r="C6011" s="6"/>
     </row>
     <row r="6012">
-      <c r="A6012" s="6"/>
+      <c r="A6012" s="10"/>
       <c r="B6012" s="2"/>
-      <c r="C6012" s="7"/>
+      <c r="C6012" s="6"/>
     </row>
     <row r="6013">
-      <c r="A6013" s="6"/>
+      <c r="A6013" s="10"/>
       <c r="B6013" s="2"/>
-      <c r="C6013" s="7"/>
+      <c r="C6013" s="6"/>
     </row>
     <row r="6014">
-      <c r="A6014" s="6"/>
+      <c r="A6014" s="10"/>
       <c r="B6014" s="2"/>
-      <c r="C6014" s="7"/>
+      <c r="C6014" s="6"/>
     </row>
     <row r="6015">
-      <c r="A6015" s="6"/>
+      <c r="A6015" s="10"/>
       <c r="B6015" s="2"/>
-      <c r="C6015" s="7"/>
+      <c r="C6015" s="6"/>
     </row>
     <row r="6016">
-      <c r="A6016" s="6"/>
+      <c r="A6016" s="10"/>
       <c r="B6016" s="2"/>
-      <c r="C6016" s="7"/>
+      <c r="C6016" s="6"/>
     </row>
     <row r="6017">
-      <c r="A6017" s="6"/>
+      <c r="A6017" s="10"/>
       <c r="B6017" s="2"/>
-      <c r="C6017" s="7"/>
+      <c r="C6017" s="6"/>
     </row>
     <row r="6018">
-      <c r="A6018" s="6"/>
+      <c r="A6018" s="10"/>
       <c r="B6018" s="2"/>
-      <c r="C6018" s="7"/>
+      <c r="C6018" s="6"/>
     </row>
     <row r="6019">
-      <c r="A6019" s="6"/>
+      <c r="A6019" s="10"/>
       <c r="B6019" s="2"/>
-      <c r="C6019" s="7"/>
+      <c r="C6019" s="6"/>
     </row>
     <row r="6020">
-      <c r="A6020" s="6"/>
+      <c r="A6020" s="10"/>
       <c r="B6020" s="2"/>
-      <c r="C6020" s="7"/>
+      <c r="C6020" s="6"/>
     </row>
     <row r="6021">
-      <c r="A6021" s="6"/>
+      <c r="A6021" s="10"/>
       <c r="B6021" s="2"/>
-      <c r="C6021" s="7"/>
+      <c r="C6021" s="6"/>
     </row>
     <row r="6022">
-      <c r="A6022" s="6"/>
+      <c r="A6022" s="10"/>
       <c r="B6022" s="2"/>
-      <c r="C6022" s="7"/>
+      <c r="C6022" s="6"/>
     </row>
     <row r="6023">
-      <c r="A6023" s="6"/>
+      <c r="A6023" s="10"/>
       <c r="B6023" s="2"/>
-      <c r="C6023" s="7"/>
+      <c r="C6023" s="6"/>
     </row>
     <row r="6024">
-      <c r="A6024" s="6"/>
+      <c r="A6024" s="10"/>
       <c r="B6024" s="2"/>
-      <c r="C6024" s="7"/>
+      <c r="C6024" s="6"/>
     </row>
     <row r="6025">
-      <c r="A6025" s="6"/>
+      <c r="A6025" s="10"/>
       <c r="B6025" s="2"/>
-      <c r="C6025" s="7"/>
+      <c r="C6025" s="6"/>
     </row>
     <row r="6026">
-      <c r="A6026" s="6"/>
+      <c r="A6026" s="10"/>
       <c r="B6026" s="2"/>
-      <c r="C6026" s="7"/>
+      <c r="C6026" s="6"/>
     </row>
     <row r="6027">
-      <c r="A6027" s="6"/>
+      <c r="A6027" s="10"/>
       <c r="B6027" s="2"/>
-      <c r="C6027" s="7"/>
+      <c r="C6027" s="6"/>
     </row>
     <row r="6028">
-      <c r="A6028" s="6"/>
+      <c r="A6028" s="10"/>
       <c r="B6028" s="2"/>
-      <c r="C6028" s="7"/>
+      <c r="C6028" s="6"/>
     </row>
     <row r="6029">
-      <c r="A6029" s="6"/>
+      <c r="A6029" s="10"/>
       <c r="B6029" s="2"/>
-      <c r="C6029" s="7"/>
+      <c r="C6029" s="6"/>
     </row>
     <row r="6030">
-      <c r="A6030" s="6"/>
+      <c r="A6030" s="10"/>
       <c r="B6030" s="2"/>
-      <c r="C6030" s="7"/>
+      <c r="C6030" s="6"/>
     </row>
     <row r="6031">
-      <c r="A6031" s="6"/>
+      <c r="A6031" s="10"/>
       <c r="B6031" s="2"/>
-      <c r="C6031" s="7"/>
+      <c r="C6031" s="6"/>
     </row>
     <row r="6032">
-      <c r="A6032" s="6"/>
+      <c r="A6032" s="10"/>
       <c r="B6032" s="2"/>
-      <c r="C6032" s="7"/>
+      <c r="C6032" s="6"/>
     </row>
     <row r="6033">
-      <c r="A6033" s="6"/>
+      <c r="A6033" s="10"/>
       <c r="B6033" s="2"/>
-      <c r="C6033" s="7"/>
+      <c r="C6033" s="6"/>
     </row>
     <row r="6034">
-      <c r="A6034" s="6"/>
+      <c r="A6034" s="10"/>
       <c r="B6034" s="2"/>
-      <c r="C6034" s="7"/>
+      <c r="C6034" s="6"/>
     </row>
     <row r="6035">
-      <c r="A6035" s="6"/>
+      <c r="A6035" s="10"/>
       <c r="B6035" s="2"/>
-      <c r="C6035" s="7"/>
+      <c r="C6035" s="6"/>
     </row>
     <row r="6036">
-      <c r="A6036" s="6"/>
+      <c r="A6036" s="10"/>
       <c r="B6036" s="2"/>
-      <c r="C6036" s="7"/>
+      <c r="C6036" s="6"/>
     </row>
     <row r="6037">
-      <c r="A6037" s="6"/>
+      <c r="A6037" s="10"/>
       <c r="B6037" s="2"/>
-      <c r="C6037" s="7"/>
+      <c r="C6037" s="6"/>
     </row>
     <row r="6038">
-      <c r="A6038" s="6"/>
+      <c r="A6038" s="10"/>
       <c r="B6038" s="2"/>
-      <c r="C6038" s="7"/>
+      <c r="C6038" s="6"/>
     </row>
     <row r="6039">
-      <c r="A6039" s="6"/>
+      <c r="A6039" s="10"/>
       <c r="B6039" s="2"/>
-      <c r="C6039" s="7"/>
+      <c r="C6039" s="6"/>
     </row>
     <row r="6040">
-      <c r="A6040" s="6"/>
+      <c r="A6040" s="10"/>
       <c r="B6040" s="2"/>
-      <c r="C6040" s="7"/>
+      <c r="C6040" s="6"/>
     </row>
     <row r="6041">
-      <c r="A6041" s="6"/>
+      <c r="A6041" s="10"/>
       <c r="B6041" s="2"/>
-      <c r="C6041" s="7"/>
+      <c r="C6041" s="6"/>
     </row>
     <row r="6042">
-      <c r="A6042" s="6"/>
+      <c r="A6042" s="10"/>
       <c r="B6042" s="2"/>
-      <c r="C6042" s="7"/>
+      <c r="C6042" s="6"/>
     </row>
     <row r="6043">
-      <c r="A6043" s="6"/>
+      <c r="A6043" s="10"/>
       <c r="B6043" s="2"/>
-      <c r="C6043" s="7"/>
+      <c r="C6043" s="6"/>
     </row>
     <row r="6044">
-      <c r="A6044" s="6"/>
+      <c r="A6044" s="10"/>
       <c r="B6044" s="2"/>
-      <c r="C6044" s="7"/>
+      <c r="C6044" s="6"/>
     </row>
     <row r="6045">
-      <c r="A6045" s="6"/>
+      <c r="A6045" s="10"/>
       <c r="B6045" s="2"/>
-      <c r="C6045" s="7"/>
+      <c r="C6045" s="6"/>
     </row>
     <row r="6046">
-      <c r="A6046" s="6"/>
+      <c r="A6046" s="10"/>
       <c r="B6046" s="2"/>
-      <c r="C6046" s="7"/>
+      <c r="C6046" s="6"/>
     </row>
     <row r="6047">
-      <c r="A6047" s="6"/>
+      <c r="A6047" s="10"/>
       <c r="B6047" s="2"/>
-      <c r="C6047" s="7"/>
+      <c r="C6047" s="6"/>
     </row>
     <row r="6048">
-      <c r="A6048" s="6"/>
+      <c r="A6048" s="10"/>
       <c r="B6048" s="2"/>
-      <c r="C6048" s="7"/>
+      <c r="C6048" s="6"/>
     </row>
     <row r="6049">
-      <c r="A6049" s="6"/>
+      <c r="A6049" s="10"/>
       <c r="B6049" s="2"/>
-      <c r="C6049" s="7"/>
+      <c r="C6049" s="6"/>
     </row>
     <row r="6050">
-      <c r="A6050" s="6"/>
+      <c r="A6050" s="10"/>
       <c r="B6050" s="2"/>
-      <c r="C6050" s="7"/>
+      <c r="C6050" s="6"/>
     </row>
     <row r="6051">
-      <c r="A6051" s="6"/>
+      <c r="A6051" s="10"/>
       <c r="B6051" s="2"/>
-      <c r="C6051" s="7"/>
+      <c r="C6051" s="6"/>
     </row>
     <row r="6052">
-      <c r="A6052" s="6"/>
+      <c r="A6052" s="10"/>
       <c r="B6052" s="2"/>
-      <c r="C6052" s="7"/>
+      <c r="C6052" s="6"/>
     </row>
     <row r="6053">
-      <c r="A6053" s="6"/>
+      <c r="A6053" s="10"/>
       <c r="B6053" s="2"/>
-      <c r="C6053" s="7"/>
+      <c r="C6053" s="6"/>
     </row>
     <row r="6054">
-      <c r="A6054" s="6"/>
+      <c r="A6054" s="10"/>
       <c r="B6054" s="2"/>
-      <c r="C6054" s="7"/>
+      <c r="C6054" s="6"/>
     </row>
     <row r="6055">
-      <c r="A6055" s="6"/>
+      <c r="A6055" s="10"/>
       <c r="B6055" s="2"/>
-      <c r="C6055" s="7"/>
+      <c r="C6055" s="6"/>
     </row>
     <row r="6056">
-      <c r="A6056" s="6"/>
+      <c r="A6056" s="10"/>
       <c r="B6056" s="2"/>
-      <c r="C6056" s="7"/>
+      <c r="C6056" s="6"/>
     </row>
     <row r="6057">
-      <c r="A6057" s="6"/>
+      <c r="A6057" s="10"/>
       <c r="B6057" s="2"/>
-      <c r="C6057" s="7"/>
+      <c r="C6057" s="6"/>
     </row>
     <row r="6058">
-      <c r="A6058" s="6"/>
+      <c r="A6058" s="10"/>
       <c r="B6058" s="2"/>
-      <c r="C6058" s="7"/>
+      <c r="C6058" s="6"/>
     </row>
     <row r="6059">
-      <c r="A6059" s="6"/>
+      <c r="A6059" s="10"/>
       <c r="B6059" s="2"/>
-      <c r="C6059" s="7"/>
+      <c r="C6059" s="6"/>
     </row>
     <row r="6060">
-      <c r="A6060" s="6"/>
+      <c r="A6060" s="10"/>
       <c r="B6060" s="2"/>
-      <c r="C6060" s="7"/>
+      <c r="C6060" s="6"/>
     </row>
     <row r="6061">
-      <c r="A6061" s="6"/>
+      <c r="A6061" s="10"/>
       <c r="B6061" s="2"/>
-      <c r="C6061" s="7"/>
+      <c r="C6061" s="6"/>
     </row>
     <row r="6062">
-      <c r="A6062" s="6"/>
+      <c r="A6062" s="10"/>
       <c r="B6062" s="2"/>
-      <c r="C6062" s="7"/>
+      <c r="C6062" s="6"/>
     </row>
     <row r="6063">
-      <c r="A6063" s="6"/>
+      <c r="A6063" s="10"/>
       <c r="B6063" s="2"/>
-      <c r="C6063" s="7"/>
+      <c r="C6063" s="6"/>
     </row>
     <row r="6064">
-      <c r="A6064" s="6"/>
+      <c r="A6064" s="10"/>
       <c r="B6064" s="2"/>
-      <c r="C6064" s="7"/>
+      <c r="C6064" s="6"/>
     </row>
     <row r="6065">
-      <c r="A6065" s="6"/>
+      <c r="A6065" s="10"/>
       <c r="B6065" s="2"/>
-      <c r="C6065" s="7"/>
+      <c r="C6065" s="6"/>
     </row>
     <row r="6066">
-      <c r="A6066" s="6"/>
+      <c r="A6066" s="10"/>
       <c r="B6066" s="2"/>
-      <c r="C6066" s="7"/>
+      <c r="C6066" s="6"/>
     </row>
     <row r="6067">
-      <c r="A6067" s="6"/>
+      <c r="A6067" s="10"/>
       <c r="B6067" s="2"/>
-      <c r="C6067" s="7"/>
+      <c r="C6067" s="6"/>
     </row>
     <row r="6068">
-      <c r="A6068" s="6"/>
+      <c r="A6068" s="10"/>
       <c r="B6068" s="2"/>
-      <c r="C6068" s="7"/>
+      <c r="C6068" s="6"/>
     </row>
     <row r="6069">
-      <c r="A6069" s="6"/>
+      <c r="A6069" s="10"/>
       <c r="B6069" s="2"/>
-      <c r="C6069" s="7"/>
+      <c r="C6069" s="6"/>
     </row>
     <row r="6070">
-      <c r="A6070" s="6"/>
+      <c r="A6070" s="10"/>
       <c r="B6070" s="2"/>
-      <c r="C6070" s="7"/>
+      <c r="C6070" s="6"/>
     </row>
     <row r="6071">
-      <c r="A6071" s="6"/>
+      <c r="A6071" s="10"/>
       <c r="B6071" s="2"/>
-      <c r="C6071" s="7"/>
+      <c r="C6071" s="6"/>
     </row>
     <row r="6072">
-      <c r="A6072" s="6"/>
+      <c r="A6072" s="10"/>
       <c r="B6072" s="2"/>
-      <c r="C6072" s="7"/>
+      <c r="C6072" s="6"/>
     </row>
     <row r="6073">
-      <c r="A6073" s="6"/>
+      <c r="A6073" s="10"/>
       <c r="B6073" s="2"/>
-      <c r="C6073" s="7"/>
+      <c r="C6073" s="6"/>
     </row>
     <row r="6074">
-      <c r="A6074" s="6"/>
+      <c r="A6074" s="10"/>
       <c r="B6074" s="2"/>
-      <c r="C6074" s="7"/>
+      <c r="C6074" s="6"/>
     </row>
     <row r="6075">
-      <c r="A6075" s="6"/>
+      <c r="A6075" s="10"/>
       <c r="B6075" s="2"/>
-      <c r="C6075" s="7"/>
+      <c r="C6075" s="6"/>
     </row>
     <row r="6076">
-      <c r="A6076" s="6"/>
+      <c r="A6076" s="10"/>
       <c r="B6076" s="2"/>
-      <c r="C6076" s="7"/>
+      <c r="C6076" s="6"/>
     </row>
     <row r="6077">
-      <c r="A6077" s="6"/>
+      <c r="A6077" s="10"/>
       <c r="B6077" s="2"/>
-      <c r="C6077" s="7"/>
+      <c r="C6077" s="6"/>
     </row>
     <row r="6078">
-      <c r="A6078" s="6"/>
+      <c r="A6078" s="10"/>
       <c r="B6078" s="2"/>
-      <c r="C6078" s="7"/>
+      <c r="C6078" s="6"/>
     </row>
     <row r="6079">
-      <c r="A6079" s="6"/>
+      <c r="A6079" s="10"/>
       <c r="B6079" s="2"/>
-      <c r="C6079" s="7"/>
+      <c r="C6079" s="6"/>
     </row>
     <row r="6080">
-      <c r="A6080" s="6"/>
+      <c r="A6080" s="10"/>
       <c r="B6080" s="2"/>
-      <c r="C6080" s="7"/>
+      <c r="C6080" s="6"/>
     </row>
     <row r="6081">
-      <c r="A6081" s="6"/>
+      <c r="A6081" s="10"/>
       <c r="B6081" s="2"/>
-      <c r="C6081" s="7"/>
+      <c r="C6081" s="6"/>
     </row>
     <row r="6082">
-      <c r="A6082" s="6"/>
+      <c r="A6082" s="10"/>
       <c r="B6082" s="2"/>
-      <c r="C6082" s="7"/>
+      <c r="C6082" s="6"/>
     </row>
     <row r="6083">
-      <c r="A6083" s="6"/>
+      <c r="A6083" s="10"/>
       <c r="B6083" s="2"/>
-      <c r="C6083" s="7"/>
+      <c r="C6083" s="6"/>
     </row>
     <row r="6084">
-      <c r="A6084" s="6"/>
+      <c r="A6084" s="10"/>
       <c r="B6084" s="2"/>
-      <c r="C6084" s="7"/>
+      <c r="C6084" s="6"/>
     </row>
     <row r="6085">
-      <c r="A6085" s="6"/>
+      <c r="A6085" s="10"/>
       <c r="B6085" s="2"/>
-      <c r="C6085" s="7"/>
+      <c r="C6085" s="6"/>
     </row>
     <row r="6086">
-      <c r="A6086" s="6"/>
+      <c r="A6086" s="10"/>
       <c r="B6086" s="2"/>
-      <c r="C6086" s="7"/>
+      <c r="C6086" s="6"/>
     </row>
     <row r="6087">
-      <c r="A6087" s="6"/>
+      <c r="A6087" s="10"/>
       <c r="B6087" s="2"/>
-      <c r="C6087" s="7"/>
+      <c r="C6087" s="6"/>
     </row>
     <row r="6088">
-      <c r="A6088" s="6"/>
+      <c r="A6088" s="10"/>
       <c r="B6088" s="2"/>
-      <c r="C6088" s="7"/>
+      <c r="C6088" s="6"/>
     </row>
     <row r="6089">
-      <c r="A6089" s="6"/>
+      <c r="A6089" s="10"/>
       <c r="B6089" s="2"/>
-      <c r="C6089" s="7"/>
+      <c r="C6089" s="6"/>
     </row>
     <row r="6090">
-      <c r="A6090" s="6"/>
+      <c r="A6090" s="10"/>
       <c r="B6090" s="2"/>
-      <c r="C6090" s="7"/>
+      <c r="C6090" s="6"/>
     </row>
     <row r="6091">
-      <c r="A6091" s="6"/>
+      <c r="A6091" s="10"/>
       <c r="B6091" s="2"/>
-      <c r="C6091" s="7"/>
+      <c r="C6091" s="6"/>
     </row>
     <row r="6092">
-      <c r="A6092" s="6"/>
+      <c r="A6092" s="10"/>
       <c r="B6092" s="2"/>
-      <c r="C6092" s="7"/>
+      <c r="C6092" s="6"/>
     </row>
     <row r="6093">
-      <c r="A6093" s="6"/>
+      <c r="A6093" s="10"/>
       <c r="B6093" s="2"/>
-      <c r="C6093" s="7"/>
+      <c r="C6093" s="6"/>
     </row>
     <row r="6094">
-      <c r="A6094" s="6"/>
+      <c r="A6094" s="10"/>
       <c r="B6094" s="2"/>
-      <c r="C6094" s="7"/>
+      <c r="C6094" s="6"/>
     </row>
     <row r="6095">
-      <c r="A6095" s="6"/>
+      <c r="A6095" s="10"/>
       <c r="B6095" s="2"/>
-      <c r="C6095" s="7"/>
+      <c r="C6095" s="6"/>
     </row>
     <row r="6096">
-      <c r="A6096" s="6"/>
+      <c r="A6096" s="10"/>
       <c r="B6096" s="2"/>
-      <c r="C6096" s="7"/>
+      <c r="C6096" s="6"/>
     </row>
     <row r="6097">
-      <c r="A6097" s="6"/>
+      <c r="A6097" s="10"/>
       <c r="B6097" s="2"/>
-      <c r="C6097" s="7"/>
+      <c r="C6097" s="6"/>
     </row>
     <row r="6098">
-      <c r="A6098" s="6"/>
+      <c r="A6098" s="10"/>
       <c r="B6098" s="2"/>
-      <c r="C6098" s="7"/>
+      <c r="C6098" s="6"/>
     </row>
     <row r="6099">
-      <c r="A6099" s="6"/>
+      <c r="A6099" s="10"/>
       <c r="B6099" s="2"/>
-      <c r="C6099" s="7"/>
+      <c r="C6099" s="6"/>
     </row>
     <row r="6100">
-      <c r="A6100" s="6"/>
+      <c r="A6100" s="10"/>
       <c r="B6100" s="2"/>
-      <c r="C6100" s="7"/>
+      <c r="C6100" s="6"/>
     </row>
     <row r="6101">
-      <c r="A6101" s="6"/>
+      <c r="A6101" s="10"/>
       <c r="B6101" s="2"/>
-      <c r="C6101" s="7"/>
+      <c r="C6101" s="6"/>
     </row>
     <row r="6102">
-      <c r="A6102" s="6"/>
+      <c r="A6102" s="10"/>
       <c r="B6102" s="2"/>
-      <c r="C6102" s="7"/>
+      <c r="C6102" s="6"/>
     </row>
     <row r="6103">
-      <c r="A6103" s="6"/>
+      <c r="A6103" s="10"/>
       <c r="B6103" s="2"/>
-      <c r="C6103" s="7"/>
+      <c r="C6103" s="6"/>
     </row>
     <row r="6104">
-      <c r="A6104" s="6"/>
+      <c r="A6104" s="10"/>
       <c r="B6104" s="2"/>
-      <c r="C6104" s="7"/>
+      <c r="C6104" s="6"/>
     </row>
     <row r="6105">
-      <c r="A6105" s="6"/>
+      <c r="A6105" s="10"/>
       <c r="B6105" s="2"/>
-      <c r="C6105" s="7"/>
+      <c r="C6105" s="6"/>
     </row>
     <row r="6106">
-      <c r="A6106" s="6"/>
+      <c r="A6106" s="10"/>
       <c r="B6106" s="2"/>
-      <c r="C6106" s="7"/>
+      <c r="C6106" s="6"/>
     </row>
     <row r="6107">
-      <c r="A6107" s="6"/>
+      <c r="A6107" s="10"/>
       <c r="B6107" s="2"/>
-      <c r="C6107" s="7"/>
+      <c r="C6107" s="6"/>
     </row>
     <row r="6108">
-      <c r="A6108" s="6"/>
+      <c r="A6108" s="10"/>
       <c r="B6108" s="2"/>
-      <c r="C6108" s="7"/>
+      <c r="C6108" s="6"/>
     </row>
     <row r="6109">
-      <c r="A6109" s="6"/>
+      <c r="A6109" s="10"/>
       <c r="B6109" s="2"/>
-      <c r="C6109" s="7"/>
+      <c r="C6109" s="6"/>
     </row>
     <row r="6110">
-      <c r="A6110" s="6"/>
+      <c r="A6110" s="10"/>
       <c r="B6110" s="2"/>
-      <c r="C6110" s="7"/>
+      <c r="C6110" s="6"/>
     </row>
     <row r="6111">
-      <c r="A6111" s="6"/>
+      <c r="A6111" s="10"/>
       <c r="B6111" s="2"/>
-      <c r="C6111" s="7"/>
+      <c r="C6111" s="6"/>
     </row>
     <row r="6112">
-      <c r="A6112" s="6"/>
+      <c r="A6112" s="10"/>
       <c r="B6112" s="2"/>
-      <c r="C6112" s="7"/>
+      <c r="C6112" s="6"/>
     </row>
     <row r="6113">
-      <c r="A6113" s="6"/>
+      <c r="A6113" s="10"/>
       <c r="B6113" s="2"/>
-      <c r="C6113" s="7"/>
+      <c r="C6113" s="6"/>
     </row>
     <row r="6114">
-      <c r="A6114" s="6"/>
+      <c r="A6114" s="10"/>
       <c r="B6114" s="2"/>
-      <c r="C6114" s="7"/>
+      <c r="C6114" s="6"/>
     </row>
     <row r="6115">
-      <c r="A6115" s="6"/>
+      <c r="A6115" s="10"/>
       <c r="B6115" s="2"/>
-      <c r="C6115" s="7"/>
+      <c r="C6115" s="6"/>
     </row>
     <row r="6116">
-      <c r="A6116" s="6"/>
+      <c r="A6116" s="10"/>
       <c r="B6116" s="2"/>
-      <c r="C6116" s="7"/>
+      <c r="C6116" s="6"/>
     </row>
     <row r="6117">
-      <c r="A6117" s="6"/>
+      <c r="A6117" s="10"/>
       <c r="B6117" s="2"/>
-      <c r="C6117" s="7"/>
+      <c r="C6117" s="6"/>
     </row>
     <row r="6118">
-      <c r="A6118" s="6"/>
+      <c r="A6118" s="10"/>
       <c r="B6118" s="2"/>
-      <c r="C6118" s="7"/>
+      <c r="C6118" s="6"/>
     </row>
     <row r="6119">
-      <c r="A6119" s="6"/>
+      <c r="A6119" s="10"/>
       <c r="B6119" s="2"/>
-      <c r="C6119" s="7"/>
+      <c r="C6119" s="6"/>
     </row>
     <row r="6120">
-      <c r="A6120" s="6"/>
+      <c r="A6120" s="10"/>
       <c r="B6120" s="2"/>
-      <c r="C6120" s="7"/>
+      <c r="C6120" s="6"/>
     </row>
     <row r="6121">
-      <c r="A6121" s="6"/>
+      <c r="A6121" s="10"/>
       <c r="B6121" s="2"/>
-      <c r="C6121" s="7"/>
+      <c r="C6121" s="6"/>
     </row>
     <row r="6122">
-      <c r="A6122" s="6"/>
+      <c r="A6122" s="10"/>
       <c r="B6122" s="2"/>
-      <c r="C6122" s="7"/>
+      <c r="C6122" s="6"/>
     </row>
     <row r="6123">
-      <c r="A6123" s="6"/>
+      <c r="A6123" s="10"/>
       <c r="B6123" s="2"/>
-      <c r="C6123" s="7"/>
+      <c r="C6123" s="6"/>
     </row>
     <row r="6124">
-      <c r="A6124" s="6"/>
+      <c r="A6124" s="10"/>
       <c r="B6124" s="2"/>
-      <c r="C6124" s="7"/>
+      <c r="C6124" s="6"/>
     </row>
     <row r="6125">
-      <c r="A6125" s="6"/>
+      <c r="A6125" s="10"/>
       <c r="B6125" s="2"/>
-      <c r="C6125" s="7"/>
+      <c r="C6125" s="6"/>
     </row>
     <row r="6126">
-      <c r="A6126" s="6"/>
+      <c r="A6126" s="10"/>
       <c r="B6126" s="2"/>
-      <c r="C6126" s="7"/>
+      <c r="C6126" s="6"/>
     </row>
     <row r="6127">
-      <c r="A6127" s="6"/>
+      <c r="A6127" s="10"/>
       <c r="B6127" s="2"/>
-      <c r="C6127" s="7"/>
+      <c r="C6127" s="6"/>
     </row>
     <row r="6128">
-      <c r="A6128" s="6"/>
+      <c r="A6128" s="10"/>
       <c r="B6128" s="2"/>
-      <c r="C6128" s="7"/>
+      <c r="C6128" s="6"/>
     </row>
     <row r="6129">
-      <c r="A6129" s="6"/>
+      <c r="A6129" s="10"/>
       <c r="B6129" s="2"/>
-      <c r="C6129" s="7"/>
+      <c r="C6129" s="6"/>
     </row>
     <row r="6130">
-      <c r="A6130" s="6"/>
+      <c r="A6130" s="10"/>
       <c r="B6130" s="2"/>
-      <c r="C6130" s="7"/>
+      <c r="C6130" s="6"/>
     </row>
     <row r="6131">
-      <c r="A6131" s="6"/>
+      <c r="A6131" s="10"/>
       <c r="B6131" s="2"/>
-      <c r="C6131" s="7"/>
+      <c r="C6131" s="6"/>
     </row>
     <row r="6132">
-      <c r="A6132" s="6"/>
+      <c r="A6132" s="10"/>
       <c r="B6132" s="2"/>
-      <c r="C6132" s="7"/>
+      <c r="C6132" s="6"/>
     </row>
     <row r="6133">
-      <c r="A6133" s="6"/>
+      <c r="A6133" s="10"/>
       <c r="B6133" s="2"/>
-      <c r="C6133" s="7"/>
+      <c r="C6133" s="6"/>
     </row>
     <row r="6134">
-      <c r="A6134" s="6"/>
+      <c r="A6134" s="10"/>
       <c r="B6134" s="2"/>
-      <c r="C6134" s="7"/>
+      <c r="C6134" s="6"/>
     </row>
     <row r="6135">
-      <c r="A6135" s="6"/>
+      <c r="A6135" s="10"/>
       <c r="B6135" s="2"/>
-      <c r="C6135" s="7"/>
+      <c r="C6135" s="6"/>
     </row>
     <row r="6136">
-      <c r="A6136" s="6"/>
+      <c r="A6136" s="10"/>
       <c r="B6136" s="2"/>
-      <c r="C6136" s="7"/>
+      <c r="C6136" s="6"/>
     </row>
     <row r="6137">
-      <c r="A6137" s="6"/>
+      <c r="A6137" s="10"/>
       <c r="B6137" s="2"/>
-      <c r="C6137" s="7"/>
+      <c r="C6137" s="6"/>
     </row>
     <row r="6138">
-      <c r="A6138" s="6"/>
+      <c r="A6138" s="10"/>
       <c r="B6138" s="2"/>
-      <c r="C6138" s="7"/>
+      <c r="C6138" s="6"/>
     </row>
     <row r="6139">
-      <c r="A6139" s="6"/>
+      <c r="A6139" s="10"/>
       <c r="B6139" s="2"/>
-      <c r="C6139" s="7"/>
+      <c r="C6139" s="6"/>
     </row>
     <row r="6140">
-      <c r="A6140" s="6"/>
+      <c r="A6140" s="10"/>
       <c r="B6140" s="2"/>
-      <c r="C6140" s="7"/>
+      <c r="C6140" s="6"/>
     </row>
     <row r="6141">
-      <c r="A6141" s="6"/>
+      <c r="A6141" s="10"/>
       <c r="B6141" s="2"/>
-      <c r="C6141" s="7"/>
+      <c r="C6141" s="6"/>
     </row>
     <row r="6142">
-      <c r="A6142" s="6"/>
+      <c r="A6142" s="10"/>
       <c r="B6142" s="2"/>
-      <c r="C6142" s="7"/>
+      <c r="C6142" s="6"/>
     </row>
     <row r="6143">
-      <c r="A6143" s="6"/>
+      <c r="A6143" s="10"/>
       <c r="B6143" s="2"/>
-      <c r="C6143" s="7"/>
+      <c r="C6143" s="6"/>
     </row>
     <row r="6144">
-      <c r="A6144" s="6"/>
+      <c r="A6144" s="10"/>
       <c r="B6144" s="2"/>
-      <c r="C6144" s="7"/>
+      <c r="C6144" s="6"/>
     </row>
     <row r="6145">
-      <c r="A6145" s="6"/>
+      <c r="A6145" s="10"/>
       <c r="B6145" s="2"/>
-      <c r="C6145" s="7"/>
+      <c r="C6145" s="6"/>
     </row>
     <row r="6146">
-      <c r="A6146" s="6"/>
+      <c r="A6146" s="10"/>
       <c r="B6146" s="2"/>
-      <c r="C6146" s="7"/>
+      <c r="C6146" s="6"/>
     </row>
     <row r="6147">
-      <c r="A6147" s="6"/>
+      <c r="A6147" s="10"/>
       <c r="B6147" s="2"/>
-      <c r="C6147" s="7"/>
+      <c r="C6147" s="6"/>
     </row>
     <row r="6148">
-      <c r="A6148" s="6"/>
+      <c r="A6148" s="10"/>
       <c r="B6148" s="2"/>
-      <c r="C6148" s="7"/>
+      <c r="C6148" s="6"/>
     </row>
     <row r="6149">
-      <c r="A6149" s="6"/>
+      <c r="A6149" s="10"/>
       <c r="B6149" s="2"/>
-      <c r="C6149" s="7"/>
+      <c r="C6149" s="6"/>
     </row>
     <row r="6150">
-      <c r="A6150" s="6"/>
+      <c r="A6150" s="10"/>
       <c r="B6150" s="2"/>
-      <c r="C6150" s="7"/>
+      <c r="C6150" s="6"/>
     </row>
     <row r="6151">
-      <c r="A6151" s="6"/>
+      <c r="A6151" s="10"/>
       <c r="B6151" s="2"/>
-      <c r="C6151" s="7"/>
+      <c r="C6151" s="6"/>
     </row>
     <row r="6152">
-      <c r="A6152" s="6"/>
+      <c r="A6152" s="10"/>
       <c r="B6152" s="2"/>
-      <c r="C6152" s="7"/>
+      <c r="C6152" s="6"/>
     </row>
     <row r="6153">
-      <c r="A6153" s="6"/>
+      <c r="A6153" s="10"/>
       <c r="B6153" s="2"/>
-      <c r="C6153" s="7"/>
+      <c r="C6153" s="6"/>
     </row>
     <row r="6154">
-      <c r="A6154" s="6"/>
+      <c r="A6154" s="10"/>
       <c r="B6154" s="2"/>
-      <c r="C6154" s="7"/>
+      <c r="C6154" s="6"/>
     </row>
     <row r="6155">
-      <c r="A6155" s="6"/>
+      <c r="A6155" s="10"/>
       <c r="B6155" s="2"/>
-      <c r="C6155" s="7"/>
+      <c r="C6155" s="6"/>
     </row>
     <row r="6156">
-      <c r="A6156" s="6"/>
+      <c r="A6156" s="10"/>
       <c r="B6156" s="2"/>
-      <c r="C6156" s="7"/>
+      <c r="C6156" s="6"/>
     </row>
     <row r="6157">
-      <c r="A6157" s="6"/>
+      <c r="A6157" s="10"/>
       <c r="B6157" s="2"/>
-      <c r="C6157" s="7"/>
+      <c r="C6157" s="6"/>
     </row>
     <row r="6158">
-      <c r="A6158" s="6"/>
+      <c r="A6158" s="10"/>
       <c r="B6158" s="2"/>
-      <c r="C6158" s="7"/>
+      <c r="C6158" s="6"/>
     </row>
     <row r="6159">
-      <c r="A6159" s="6"/>
+      <c r="A6159" s="10"/>
       <c r="B6159" s="2"/>
-      <c r="C6159" s="7"/>
+      <c r="C6159" s="6"/>
     </row>
     <row r="6160">
-      <c r="A6160" s="6"/>
+      <c r="A6160" s="10"/>
       <c r="B6160" s="2"/>
-      <c r="C6160" s="7"/>
+      <c r="C6160" s="6"/>
     </row>
     <row r="6161">
-      <c r="A6161" s="6"/>
+      <c r="A6161" s="10"/>
       <c r="B6161" s="2"/>
-      <c r="C6161" s="7"/>
+      <c r="C6161" s="6"/>
     </row>
     <row r="6162">
-      <c r="A6162" s="6"/>
+      <c r="A6162" s="10"/>
       <c r="B6162" s="2"/>
-      <c r="C6162" s="7"/>
+      <c r="C6162" s="6"/>
     </row>
     <row r="6163">
-      <c r="A6163" s="6"/>
+      <c r="A6163" s="10"/>
       <c r="B6163" s="2"/>
-      <c r="C6163" s="7"/>
+      <c r="C6163" s="6"/>
     </row>
     <row r="6164">
-      <c r="A6164" s="6"/>
+      <c r="A6164" s="10"/>
       <c r="B6164" s="2"/>
-      <c r="C6164" s="7"/>
+      <c r="C6164" s="6"/>
     </row>
     <row r="6165">
-      <c r="A6165" s="6"/>
+      <c r="A6165" s="10"/>
       <c r="B6165" s="2"/>
-      <c r="C6165" s="7"/>
+      <c r="C6165" s="6"/>
     </row>
     <row r="6166">
-      <c r="A6166" s="6"/>
+      <c r="A6166" s="10"/>
       <c r="B6166" s="2"/>
-      <c r="C6166" s="7"/>
+      <c r="C6166" s="6"/>
     </row>
     <row r="6167">
-      <c r="A6167" s="6"/>
+      <c r="A6167" s="10"/>
       <c r="B6167" s="2"/>
-      <c r="C6167" s="7"/>
+      <c r="C6167" s="6"/>
     </row>
     <row r="6168">
-      <c r="A6168" s="6"/>
+      <c r="A6168" s="10"/>
       <c r="B6168" s="2"/>
-      <c r="C6168" s="7"/>
+      <c r="C6168" s="6"/>
     </row>
     <row r="6169">
-      <c r="A6169" s="6"/>
+      <c r="A6169" s="10"/>
       <c r="B6169" s="2"/>
-      <c r="C6169" s="7"/>
+      <c r="C6169" s="6"/>
     </row>
     <row r="6170">
-      <c r="A6170" s="6"/>
+      <c r="A6170" s="10"/>
       <c r="B6170" s="2"/>
-      <c r="C6170" s="7"/>
+      <c r="C6170" s="6"/>
     </row>
     <row r="6171">
-      <c r="A6171" s="6"/>
+      <c r="A6171" s="10"/>
       <c r="B6171" s="2"/>
-      <c r="C6171" s="7"/>
+      <c r="C6171" s="6"/>
     </row>
     <row r="6172">
-      <c r="A6172" s="6"/>
+      <c r="A6172" s="10"/>
       <c r="B6172" s="2"/>
-      <c r="C6172" s="7"/>
+      <c r="C6172" s="6"/>
     </row>
     <row r="6173">
-      <c r="A6173" s="6"/>
+      <c r="A6173" s="10"/>
       <c r="B6173" s="2"/>
-      <c r="C6173" s="7"/>
+      <c r="C6173" s="6"/>
     </row>
     <row r="6174">
-      <c r="A6174" s="6"/>
+      <c r="A6174" s="10"/>
       <c r="B6174" s="2"/>
-      <c r="C6174" s="7"/>
+      <c r="C6174" s="6"/>
     </row>
     <row r="6175">
-      <c r="A6175" s="6"/>
+      <c r="A6175" s="10"/>
       <c r="B6175" s="2"/>
-      <c r="C6175" s="7"/>
+      <c r="C6175" s="6"/>
     </row>
     <row r="6176">
-      <c r="A6176" s="6"/>
+      <c r="A6176" s="10"/>
       <c r="B6176" s="2"/>
-      <c r="C6176" s="7"/>
+      <c r="C6176" s="6"/>
     </row>
     <row r="6177">
-      <c r="A6177" s="6"/>
+      <c r="A6177" s="10"/>
       <c r="B6177" s="2"/>
-      <c r="C6177" s="7"/>
+      <c r="C6177" s="6"/>
     </row>
     <row r="6178">
-      <c r="A6178" s="6"/>
+      <c r="A6178" s="10"/>
       <c r="B6178" s="2"/>
-      <c r="C6178" s="7"/>
+      <c r="C6178" s="6"/>
     </row>
     <row r="6179">
-      <c r="A6179" s="6"/>
+      <c r="A6179" s="10"/>
       <c r="B6179" s="2"/>
-      <c r="C6179" s="7"/>
+      <c r="C6179" s="6"/>
     </row>
     <row r="6180">
-      <c r="A6180" s="6"/>
+      <c r="A6180" s="10"/>
       <c r="B6180" s="2"/>
-      <c r="C6180" s="7"/>
+      <c r="C6180" s="6"/>
     </row>
     <row r="6181">
-      <c r="A6181" s="6"/>
+      <c r="A6181" s="10"/>
       <c r="B6181" s="2"/>
-      <c r="C6181" s="7"/>
+      <c r="C6181" s="6"/>
     </row>
     <row r="6182">
-      <c r="A6182" s="6"/>
+      <c r="A6182" s="10"/>
       <c r="B6182" s="2"/>
-      <c r="C6182" s="7"/>
+      <c r="C6182" s="6"/>
     </row>
     <row r="6183">
-      <c r="A6183" s="6"/>
+      <c r="A6183" s="10"/>
       <c r="B6183" s="2"/>
-      <c r="C6183" s="7"/>
+      <c r="C6183" s="6"/>
     </row>
     <row r="6184">
-      <c r="A6184" s="6"/>
+      <c r="A6184" s="10"/>
       <c r="B6184" s="2"/>
-      <c r="C6184" s="7"/>
+      <c r="C6184" s="6"/>
     </row>
     <row r="6185">
-      <c r="A6185" s="6"/>
+      <c r="A6185" s="10"/>
       <c r="B6185" s="2"/>
-      <c r="C6185" s="7"/>
+      <c r="C6185" s="6"/>
     </row>
     <row r="6186">
-      <c r="A6186" s="6"/>
+      <c r="A6186" s="10"/>
       <c r="B6186" s="2"/>
-      <c r="C6186" s="7"/>
+      <c r="C6186" s="6"/>
     </row>
     <row r="6187">
-      <c r="A6187" s="6"/>
+      <c r="A6187" s="10"/>
       <c r="B6187" s="2"/>
-      <c r="C6187" s="7"/>
+      <c r="C6187" s="6"/>
     </row>
     <row r="6188">
-      <c r="A6188" s="6"/>
+      <c r="A6188" s="10"/>
       <c r="B6188" s="2"/>
-      <c r="C6188" s="7"/>
+      <c r="C6188" s="6"/>
     </row>
     <row r="6189">
-      <c r="A6189" s="6"/>
+      <c r="A6189" s="10"/>
       <c r="B6189" s="2"/>
-      <c r="C6189" s="7"/>
+      <c r="C6189" s="6"/>
     </row>
     <row r="6190">
-      <c r="A6190" s="6"/>
+      <c r="A6190" s="10"/>
       <c r="B6190" s="2"/>
-      <c r="C6190" s="7"/>
+      <c r="C6190" s="6"/>
     </row>
     <row r="6191">
-      <c r="A6191" s="6"/>
+      <c r="A6191" s="10"/>
       <c r="B6191" s="2"/>
-      <c r="C6191" s="7"/>
+      <c r="C6191" s="6"/>
     </row>
     <row r="6192">
-      <c r="A6192" s="6"/>
+      <c r="A6192" s="10"/>
       <c r="B6192" s="2"/>
-      <c r="C6192" s="7"/>
+      <c r="C6192" s="6"/>
     </row>
     <row r="6193">
-      <c r="A6193" s="6"/>
+      <c r="A6193" s="10"/>
       <c r="B6193" s="2"/>
-      <c r="C6193" s="7"/>
+      <c r="C6193" s="6"/>
     </row>
     <row r="6194">
-      <c r="A6194" s="6"/>
+      <c r="A6194" s="10"/>
       <c r="B6194" s="2"/>
-      <c r="C6194" s="7"/>
+      <c r="C6194" s="6"/>
     </row>
     <row r="6195">
-      <c r="A6195" s="6"/>
+      <c r="A6195" s="10"/>
       <c r="B6195" s="2"/>
-      <c r="C6195" s="7"/>
+      <c r="C6195" s="6"/>
     </row>
     <row r="6196">
-      <c r="A6196" s="6"/>
+      <c r="A6196" s="10"/>
       <c r="B6196" s="2"/>
-      <c r="C6196" s="7"/>
+      <c r="C6196" s="6"/>
     </row>
     <row r="6197">
-      <c r="A6197" s="6"/>
+      <c r="A6197" s="10"/>
       <c r="B6197" s="2"/>
-      <c r="C6197" s="7"/>
+      <c r="C6197" s="6"/>
     </row>
     <row r="6198">
-      <c r="A6198" s="6"/>
+      <c r="A6198" s="10"/>
       <c r="B6198" s="2"/>
-      <c r="C6198" s="7"/>
+      <c r="C6198" s="6"/>
     </row>
     <row r="6199">
-      <c r="A6199" s="6"/>
+      <c r="A6199" s="10"/>
       <c r="B6199" s="2"/>
-      <c r="C6199" s="7"/>
+      <c r="C6199" s="6"/>
     </row>
     <row r="6200">
-      <c r="A6200" s="6"/>
+      <c r="A6200" s="10"/>
       <c r="B6200" s="2"/>
-      <c r="C6200" s="7"/>
+      <c r="C6200" s="6"/>
     </row>
     <row r="6201">
-      <c r="A6201" s="6"/>
+      <c r="A6201" s="10"/>
       <c r="B6201" s="2"/>
-      <c r="C6201" s="7"/>
+      <c r="C6201" s="6"/>
     </row>
     <row r="6202">
-      <c r="A6202" s="6"/>
+      <c r="A6202" s="10"/>
       <c r="B6202" s="2"/>
-      <c r="C6202" s="7"/>
+      <c r="C6202" s="6"/>
     </row>
     <row r="6203">
-      <c r="A6203" s="6"/>
+      <c r="A6203" s="10"/>
       <c r="B6203" s="2"/>
-      <c r="C6203" s="7"/>
+      <c r="C6203" s="6"/>
     </row>
     <row r="6204">
-      <c r="A6204" s="6"/>
+      <c r="A6204" s="10"/>
       <c r="B6204" s="2"/>
-      <c r="C6204" s="7"/>
+      <c r="C6204" s="6"/>
     </row>
     <row r="6205">
-      <c r="A6205" s="6"/>
+      <c r="A6205" s="10"/>
       <c r="B6205" s="2"/>
-      <c r="C6205" s="7"/>
+      <c r="C6205" s="6"/>
     </row>
     <row r="6206">
-      <c r="A6206" s="6"/>
+      <c r="A6206" s="10"/>
       <c r="B6206" s="2"/>
-      <c r="C6206" s="7"/>
+      <c r="C6206" s="6"/>
     </row>
     <row r="6207">
-      <c r="A6207" s="6"/>
+      <c r="A6207" s="10"/>
       <c r="B6207" s="2"/>
-      <c r="C6207" s="7"/>
+      <c r="C6207" s="6"/>
     </row>
     <row r="6208">
-      <c r="A6208" s="6"/>
+      <c r="A6208" s="10"/>
       <c r="B6208" s="2"/>
-      <c r="C6208" s="7"/>
+      <c r="C6208" s="6"/>
     </row>
     <row r="6209">
-      <c r="A6209" s="6"/>
+      <c r="A6209" s="10"/>
       <c r="B6209" s="2"/>
-      <c r="C6209" s="7"/>
+      <c r="C6209" s="6"/>
     </row>
     <row r="6210">
-      <c r="A6210" s="6"/>
+      <c r="A6210" s="10"/>
       <c r="B6210" s="2"/>
-      <c r="C6210" s="7"/>
+      <c r="C6210" s="6"/>
     </row>
     <row r="6211">
-      <c r="A6211" s="6"/>
+      <c r="A6211" s="10"/>
       <c r="B6211" s="2"/>
-      <c r="C6211" s="7"/>
+      <c r="C6211" s="6"/>
     </row>
     <row r="6212">
-      <c r="A6212" s="6"/>
+      <c r="A6212" s="10"/>
       <c r="B6212" s="2"/>
-      <c r="C6212" s="7"/>
+      <c r="C6212" s="6"/>
     </row>
     <row r="6213">
-      <c r="A6213" s="6"/>
+      <c r="A6213" s="10"/>
       <c r="B6213" s="2"/>
-      <c r="C6213" s="7"/>
+      <c r="C6213" s="6"/>
     </row>
     <row r="6214">
-      <c r="A6214" s="6"/>
+      <c r="A6214" s="10"/>
       <c r="B6214" s="2"/>
-      <c r="C6214" s="7"/>
+      <c r="C6214" s="6"/>
     </row>
     <row r="6215">
-      <c r="A6215" s="6"/>
+      <c r="A6215" s="10"/>
       <c r="B6215" s="2"/>
-      <c r="C6215" s="7"/>
+      <c r="C6215" s="6"/>
     </row>
     <row r="6216">
-      <c r="A6216" s="6"/>
+      <c r="A6216" s="10"/>
       <c r="B6216" s="2"/>
-      <c r="C6216" s="7"/>
+      <c r="C6216" s="6"/>
     </row>
     <row r="6217">
-      <c r="A6217" s="6"/>
+      <c r="A6217" s="10"/>
       <c r="B6217" s="2"/>
-      <c r="C6217" s="7"/>
+      <c r="C6217" s="6"/>
     </row>
     <row r="6218">
-      <c r="A6218" s="6"/>
+      <c r="A6218" s="10"/>
       <c r="B6218" s="2"/>
-      <c r="C6218" s="7"/>
+      <c r="C6218" s="6"/>
     </row>
     <row r="6219">
-      <c r="A6219" s="6"/>
+      <c r="A6219" s="10"/>
       <c r="B6219" s="2"/>
-      <c r="C6219" s="7"/>
+      <c r="C6219" s="6"/>
     </row>
     <row r="6220">
-      <c r="A6220" s="6"/>
+      <c r="A6220" s="10"/>
       <c r="B6220" s="2"/>
-      <c r="C6220" s="7"/>
+      <c r="C6220" s="6"/>
     </row>
     <row r="6221">
-      <c r="A6221" s="6"/>
+      <c r="A6221" s="10"/>
       <c r="B6221" s="2"/>
-      <c r="C6221" s="7"/>
+      <c r="C6221" s="6"/>
     </row>
     <row r="6222">
-      <c r="A6222" s="6"/>
+      <c r="A6222" s="10"/>
       <c r="B6222" s="2"/>
-      <c r="C6222" s="7"/>
+      <c r="C6222" s="6"/>
     </row>
     <row r="6223">
-      <c r="A6223" s="6"/>
+      <c r="A6223" s="10"/>
       <c r="B6223" s="2"/>
-      <c r="C6223" s="7"/>
+      <c r="C6223" s="6"/>
     </row>
     <row r="6224">
-      <c r="A6224" s="6"/>
+      <c r="A6224" s="10"/>
       <c r="B6224" s="2"/>
-      <c r="C6224" s="7"/>
+      <c r="C6224" s="6"/>
     </row>
     <row r="6225">
-      <c r="A6225" s="6"/>
+      <c r="A6225" s="10"/>
       <c r="B6225" s="2"/>
-      <c r="C6225" s="7"/>
+      <c r="C6225" s="6"/>
     </row>
     <row r="6226">
-      <c r="A6226" s="6"/>
+      <c r="A6226" s="10"/>
       <c r="B6226" s="2"/>
-      <c r="C6226" s="7"/>
+      <c r="C6226" s="6"/>
     </row>
     <row r="6227">
-      <c r="A6227" s="6"/>
+      <c r="A6227" s="10"/>
       <c r="B6227" s="2"/>
-      <c r="C6227" s="7"/>
+      <c r="C6227" s="6"/>
     </row>
     <row r="6228">
-      <c r="A6228" s="6"/>
+      <c r="A6228" s="10"/>
       <c r="B6228" s="2"/>
-      <c r="C6228" s="7"/>
+      <c r="C6228" s="6"/>
     </row>
     <row r="6229">
-      <c r="A6229" s="6"/>
+      <c r="A6229" s="10"/>
       <c r="B6229" s="2"/>
-      <c r="C6229" s="7"/>
+      <c r="C6229" s="6"/>
     </row>
     <row r="6230">
-      <c r="A6230" s="6"/>
+      <c r="A6230" s="10"/>
       <c r="B6230" s="2"/>
-      <c r="C6230" s="7"/>
+      <c r="C6230" s="6"/>
     </row>
     <row r="6231">
-      <c r="A6231" s="6"/>
+      <c r="A6231" s="10"/>
       <c r="B6231" s="2"/>
-      <c r="C6231" s="7"/>
+      <c r="C6231" s="6"/>
     </row>
     <row r="6232">
-      <c r="A6232" s="6"/>
+      <c r="A6232" s="10"/>
       <c r="B6232" s="2"/>
-      <c r="C6232" s="7"/>
+      <c r="C6232" s="6"/>
     </row>
     <row r="6233">
-      <c r="A6233" s="6"/>
+      <c r="A6233" s="10"/>
       <c r="B6233" s="2"/>
-      <c r="C6233" s="7"/>
+      <c r="C6233" s="6"/>
     </row>
     <row r="6234">
-      <c r="A6234" s="6"/>
+      <c r="A6234" s="10"/>
       <c r="B6234" s="2"/>
-      <c r="C6234" s="7"/>
+      <c r="C6234" s="6"/>
     </row>
     <row r="6235">
-      <c r="A6235" s="6"/>
+      <c r="A6235" s="10"/>
       <c r="B6235" s="2"/>
-      <c r="C6235" s="7"/>
+      <c r="C6235" s="6"/>
     </row>
     <row r="6236">
-      <c r="A6236" s="6"/>
+      <c r="A6236" s="10"/>
       <c r="B6236" s="2"/>
-      <c r="C6236" s="7"/>
+      <c r="C6236" s="6"/>
     </row>
     <row r="6237">
-      <c r="A6237" s="6"/>
+      <c r="A6237" s="10"/>
       <c r="B6237" s="2"/>
-      <c r="C6237" s="7"/>
+      <c r="C6237" s="6"/>
     </row>
     <row r="6238">
-      <c r="A6238" s="6"/>
+      <c r="A6238" s="10"/>
       <c r="B6238" s="2"/>
-      <c r="C6238" s="7"/>
+      <c r="C6238" s="6"/>
     </row>
     <row r="6239">
-      <c r="A6239" s="6"/>
+      <c r="A6239" s="10"/>
       <c r="B6239" s="2"/>
-      <c r="C6239" s="7"/>
+      <c r="C6239" s="6"/>
     </row>
     <row r="6240">
-      <c r="A6240" s="6"/>
+      <c r="A6240" s="10"/>
       <c r="B6240" s="2"/>
-      <c r="C6240" s="7"/>
+      <c r="C6240" s="6"/>
     </row>
     <row r="6241">
-      <c r="A6241" s="6"/>
+      <c r="A6241" s="10"/>
       <c r="B6241" s="2"/>
-      <c r="C6241" s="7"/>
+      <c r="C6241" s="6"/>
     </row>
     <row r="6242">
-      <c r="A6242" s="6"/>
+      <c r="A6242" s="10"/>
       <c r="B6242" s="2"/>
-      <c r="C6242" s="7"/>
+      <c r="C6242" s="6"/>
     </row>
     <row r="6243">
-      <c r="A6243" s="6"/>
+      <c r="A6243" s="10"/>
       <c r="B6243" s="2"/>
-      <c r="C6243" s="7"/>
+      <c r="C6243" s="6"/>
     </row>
     <row r="6244">
-      <c r="A6244" s="6"/>
+      <c r="A6244" s="10"/>
       <c r="B6244" s="2"/>
-      <c r="C6244" s="7"/>
+      <c r="C6244" s="6"/>
     </row>
     <row r="6245">
-      <c r="A6245" s="6"/>
+      <c r="A6245" s="10"/>
       <c r="B6245" s="2"/>
-      <c r="C6245" s="7"/>
+      <c r="C6245" s="6"/>
     </row>
     <row r="6246">
-      <c r="A6246" s="6"/>
+      <c r="A6246" s="10"/>
       <c r="B6246" s="2"/>
-      <c r="C6246" s="7"/>
+      <c r="C6246" s="6"/>
     </row>
     <row r="6247">
-      <c r="A6247" s="6"/>
+      <c r="A6247" s="10"/>
       <c r="B6247" s="2"/>
-      <c r="C6247" s="7"/>
+      <c r="C6247" s="6"/>
     </row>
     <row r="6248">
-      <c r="A6248" s="6"/>
+      <c r="A6248" s="10"/>
       <c r="B6248" s="2"/>
-      <c r="C6248" s="7"/>
+      <c r="C6248" s="6"/>
     </row>
     <row r="6249">
-      <c r="A6249" s="6"/>
+      <c r="A6249" s="10"/>
       <c r="B6249" s="2"/>
-      <c r="C6249" s="7"/>
+      <c r="C6249" s="6"/>
     </row>
     <row r="6250">
-      <c r="A6250" s="6"/>
+      <c r="A6250" s="10"/>
       <c r="B6250" s="2"/>
-      <c r="C6250" s="7"/>
+      <c r="C6250" s="6"/>
     </row>
     <row r="6251">
-      <c r="A6251" s="6"/>
+      <c r="A6251" s="10"/>
       <c r="B6251" s="2"/>
-      <c r="C6251" s="7"/>
+      <c r="C6251" s="6"/>
     </row>
     <row r="6252">
-      <c r="A6252" s="6"/>
+      <c r="A6252" s="10"/>
       <c r="B6252" s="2"/>
-      <c r="C6252" s="7"/>
+      <c r="C6252" s="6"/>
     </row>
     <row r="6253">
-      <c r="A6253" s="6"/>
+      <c r="A6253" s="10"/>
       <c r="B6253" s="2"/>
-      <c r="C6253" s="7"/>
+      <c r="C6253" s="6"/>
     </row>
     <row r="6254">
-      <c r="A6254" s="6"/>
+      <c r="A6254" s="10"/>
       <c r="B6254" s="2"/>
-      <c r="C6254" s="7"/>
+      <c r="C6254" s="6"/>
     </row>
     <row r="6255">
-      <c r="A6255" s="6"/>
+      <c r="A6255" s="10"/>
       <c r="B6255" s="2"/>
-      <c r="C6255" s="7"/>
+      <c r="C6255" s="6"/>
     </row>
     <row r="6256">
-      <c r="A6256" s="6"/>
+      <c r="A6256" s="10"/>
       <c r="B6256" s="2"/>
-      <c r="C6256" s="7"/>
+      <c r="C6256" s="6"/>
     </row>
     <row r="6257">
-      <c r="A6257" s="6"/>
+      <c r="A6257" s="10"/>
       <c r="B6257" s="2"/>
-      <c r="C6257" s="7"/>
+      <c r="C6257" s="6"/>
     </row>
     <row r="6258">
-      <c r="A6258" s="6"/>
+      <c r="A6258" s="10"/>
       <c r="B6258" s="2"/>
-      <c r="C6258" s="7"/>
+      <c r="C6258" s="6"/>
     </row>
     <row r="6259">
-      <c r="A6259" s="6"/>
+      <c r="A6259" s="10"/>
       <c r="B6259" s="2"/>
-      <c r="C6259" s="7"/>
+      <c r="C6259" s="6"/>
     </row>
     <row r="6260">
-      <c r="A6260" s="6"/>
+      <c r="A6260" s="10"/>
       <c r="B6260" s="2"/>
-      <c r="C6260" s="7"/>
+      <c r="C6260" s="6"/>
     </row>
     <row r="6261">
-      <c r="A6261" s="6"/>
+      <c r="A6261" s="10"/>
       <c r="B6261" s="2"/>
-      <c r="C6261" s="7"/>
+      <c r="C6261" s="6"/>
     </row>
     <row r="6262">
-      <c r="A6262" s="6"/>
+      <c r="A6262" s="10"/>
       <c r="B6262" s="2"/>
-      <c r="C6262" s="7"/>
+      <c r="C6262" s="6"/>
     </row>
     <row r="6263">
-      <c r="A6263" s="6"/>
+      <c r="A6263" s="10"/>
       <c r="B6263" s="2"/>
-      <c r="C6263" s="7"/>
+      <c r="C6263" s="6"/>
     </row>
     <row r="6264">
-      <c r="A6264" s="6"/>
+      <c r="A6264" s="10"/>
       <c r="B6264" s="2"/>
-      <c r="C6264" s="7"/>
+      <c r="C6264" s="6"/>
     </row>
     <row r="6265">
-      <c r="A6265" s="6"/>
+      <c r="A6265" s="10"/>
       <c r="B6265" s="2"/>
-      <c r="C6265" s="7"/>
+      <c r="C6265" s="6"/>
     </row>
     <row r="6266">
-      <c r="A6266" s="6"/>
+      <c r="A6266" s="10"/>
       <c r="B6266" s="2"/>
-      <c r="C6266" s="7"/>
+      <c r="C6266" s="6"/>
     </row>
     <row r="6267">
-      <c r="A6267" s="6"/>
+      <c r="A6267" s="10"/>
       <c r="B6267" s="2"/>
-      <c r="C6267" s="7"/>
+      <c r="C6267" s="6"/>
     </row>
     <row r="6268">
-      <c r="A6268" s="6"/>
+      <c r="A6268" s="10"/>
       <c r="B6268" s="2"/>
-      <c r="C6268" s="7"/>
+      <c r="C6268" s="6"/>
     </row>
     <row r="6269">
-      <c r="A6269" s="6"/>
+      <c r="A6269" s="10"/>
       <c r="B6269" s="2"/>
-      <c r="C6269" s="7"/>
+      <c r="C6269" s="6"/>
     </row>
     <row r="6270">
-      <c r="A6270" s="6"/>
+      <c r="A6270" s="10"/>
       <c r="B6270" s="2"/>
-      <c r="C6270" s="7"/>
+      <c r="C6270" s="6"/>
     </row>
     <row r="6271">
-      <c r="A6271" s="6"/>
+      <c r="A6271" s="10"/>
       <c r="B6271" s="2"/>
-      <c r="C6271" s="7"/>
+      <c r="C6271" s="6"/>
     </row>
     <row r="6272">
-      <c r="A6272" s="6"/>
+      <c r="A6272" s="10"/>
       <c r="B6272" s="2"/>
-      <c r="C6272" s="7"/>
+      <c r="C6272" s="6"/>
     </row>
     <row r="6273">
-      <c r="A6273" s="6"/>
+      <c r="A6273" s="10"/>
       <c r="B6273" s="2"/>
-      <c r="C6273" s="7"/>
+      <c r="C6273" s="6"/>
     </row>
     <row r="6274">
-      <c r="A6274" s="6"/>
+      <c r="A6274" s="10"/>
       <c r="B6274" s="2"/>
-      <c r="C6274" s="7"/>
+      <c r="C6274" s="6"/>
     </row>
     <row r="6275">
-      <c r="A6275" s="6"/>
+      <c r="A6275" s="10"/>
       <c r="B6275" s="2"/>
-      <c r="C6275" s="7"/>
+      <c r="C6275" s="6"/>
     </row>
     <row r="6276">
-      <c r="A6276" s="6"/>
+      <c r="A6276" s="10"/>
       <c r="B6276" s="2"/>
-      <c r="C6276" s="7"/>
+      <c r="C6276" s="6"/>
     </row>
     <row r="6277">
-      <c r="A6277" s="6"/>
+      <c r="A6277" s="10"/>
       <c r="B6277" s="2"/>
-      <c r="C6277" s="7"/>
+      <c r="C6277" s="6"/>
     </row>
     <row r="6278">
-      <c r="A6278" s="6"/>
+      <c r="A6278" s="10"/>
       <c r="B6278" s="2"/>
-      <c r="C6278" s="7"/>
+      <c r="C6278" s="6"/>
     </row>
     <row r="6279">
-      <c r="A6279" s="6"/>
+      <c r="A6279" s="10"/>
       <c r="B6279" s="2"/>
-      <c r="C6279" s="7"/>
+      <c r="C6279" s="6"/>
     </row>
     <row r="6280">
-      <c r="A6280" s="6"/>
+      <c r="A6280" s="10"/>
       <c r="B6280" s="2"/>
-      <c r="C6280" s="7"/>
+      <c r="C6280" s="6"/>
     </row>
     <row r="6281">
-      <c r="A6281" s="6"/>
+      <c r="A6281" s="10"/>
       <c r="B6281" s="2"/>
-      <c r="C6281" s="7"/>
+      <c r="C6281" s="6"/>
     </row>
     <row r="6282">
-      <c r="A6282" s="6"/>
+      <c r="A6282" s="10"/>
       <c r="B6282" s="2"/>
-      <c r="C6282" s="7"/>
+      <c r="C6282" s="6"/>
     </row>
     <row r="6283">
-      <c r="A6283" s="6"/>
+      <c r="A6283" s="10"/>
       <c r="B6283" s="2"/>
-      <c r="C6283" s="7"/>
+      <c r="C6283" s="6"/>
     </row>
     <row r="6284">
-      <c r="A6284" s="6"/>
+      <c r="A6284" s="10"/>
       <c r="B6284" s="2"/>
-      <c r="C6284" s="7"/>
+      <c r="C6284" s="6"/>
     </row>
     <row r="6285">
-      <c r="A6285" s="6"/>
+      <c r="A6285" s="10"/>
       <c r="B6285" s="2"/>
-      <c r="C6285" s="7"/>
+      <c r="C6285" s="6"/>
     </row>
     <row r="6286">
-      <c r="A6286" s="6"/>
+      <c r="A6286" s="10"/>
       <c r="B6286" s="2"/>
-      <c r="C6286" s="7"/>
+      <c r="C6286" s="6"/>
     </row>
     <row r="6287">
-      <c r="A6287" s="6"/>
+      <c r="A6287" s="10"/>
       <c r="B6287" s="2"/>
-      <c r="C6287" s="7"/>
+      <c r="C6287" s="6"/>
     </row>
     <row r="6288">
-      <c r="A6288" s="6"/>
+      <c r="A6288" s="10"/>
       <c r="B6288" s="2"/>
-      <c r="C6288" s="7"/>
+      <c r="C6288" s="6"/>
     </row>
     <row r="6289">
-      <c r="A6289" s="6"/>
+      <c r="A6289" s="10"/>
       <c r="B6289" s="2"/>
-      <c r="C6289" s="7"/>
+      <c r="C6289" s="6"/>
     </row>
     <row r="6290">
-      <c r="A6290" s="6"/>
+      <c r="A6290" s="10"/>
       <c r="B6290" s="2"/>
-      <c r="C6290" s="7"/>
+      <c r="C6290" s="6"/>
     </row>
     <row r="6291">
-      <c r="A6291" s="6"/>
+      <c r="A6291" s="10"/>
       <c r="B6291" s="2"/>
-      <c r="C6291" s="7"/>
+      <c r="C6291" s="6"/>
     </row>
     <row r="6292">
-      <c r="A6292" s="6"/>
+      <c r="A6292" s="10"/>
       <c r="B6292" s="2"/>
-      <c r="C6292" s="7"/>
+      <c r="C6292" s="6"/>
     </row>
     <row r="6293">
-      <c r="A6293" s="6"/>
+      <c r="A6293" s="10"/>
       <c r="B6293" s="2"/>
-      <c r="C6293" s="7"/>
+      <c r="C6293" s="6"/>
     </row>
     <row r="6294">
-      <c r="A6294" s="6"/>
+      <c r="A6294" s="10"/>
       <c r="B6294" s="2"/>
-      <c r="C6294" s="7"/>
+      <c r="C6294" s="6"/>
     </row>
     <row r="6295">
-      <c r="A6295" s="6"/>
+      <c r="A6295" s="10"/>
       <c r="B6295" s="2"/>
-      <c r="C6295" s="7"/>
+      <c r="C6295" s="6"/>
     </row>
     <row r="6296">
-      <c r="A6296" s="6"/>
+      <c r="A6296" s="10"/>
       <c r="B6296" s="2"/>
-      <c r="C6296" s="7"/>
+      <c r="C6296" s="6"/>
     </row>
     <row r="6297">
-      <c r="A6297" s="6"/>
+      <c r="A6297" s="10"/>
       <c r="B6297" s="2"/>
-      <c r="C6297" s="7"/>
+      <c r="C6297" s="6"/>
     </row>
     <row r="6298">
-      <c r="A6298" s="6"/>
+      <c r="A6298" s="10"/>
       <c r="B6298" s="2"/>
-      <c r="C6298" s="7"/>
+      <c r="C6298" s="6"/>
     </row>
     <row r="6299">
-      <c r="A6299" s="6"/>
+      <c r="A6299" s="10"/>
       <c r="B6299" s="2"/>
-      <c r="C6299" s="7"/>
+      <c r="C6299" s="6"/>
     </row>
     <row r="6300">
-      <c r="A6300" s="6"/>
+      <c r="A6300" s="10"/>
       <c r="B6300" s="2"/>
-      <c r="C6300" s="7"/>
+      <c r="C6300" s="6"/>
     </row>
     <row r="6301">
-      <c r="A6301" s="6"/>
+      <c r="A6301" s="10"/>
       <c r="B6301" s="2"/>
-      <c r="C6301" s="7"/>
+      <c r="C6301" s="6"/>
     </row>
     <row r="6302">
-      <c r="A6302" s="6"/>
+      <c r="A6302" s="10"/>
       <c r="B6302" s="2"/>
-      <c r="C6302" s="7"/>
+      <c r="C6302" s="6"/>
     </row>
     <row r="6303">
-      <c r="A6303" s="6"/>
+      <c r="A6303" s="10"/>
       <c r="B6303" s="2"/>
-      <c r="C6303" s="7"/>
+      <c r="C6303" s="6"/>
     </row>
     <row r="6304">
-      <c r="A6304" s="6"/>
+      <c r="A6304" s="10"/>
       <c r="B6304" s="2"/>
-      <c r="C6304" s="7"/>
+      <c r="C6304" s="6"/>
     </row>
     <row r="6305">
-      <c r="A6305" s="6"/>
+      <c r="A6305" s="10"/>
       <c r="B6305" s="2"/>
-      <c r="C6305" s="7"/>
+      <c r="C6305" s="6"/>
     </row>
     <row r="6306">
-      <c r="A6306" s="6"/>
+      <c r="A6306" s="10"/>
       <c r="B6306" s="2"/>
-      <c r="C6306" s="7"/>
+      <c r="C6306" s="6"/>
     </row>
     <row r="6307">
-      <c r="A6307" s="6"/>
+      <c r="A6307" s="10"/>
       <c r="B6307" s="2"/>
-      <c r="C6307" s="7"/>
+      <c r="C6307" s="6"/>
     </row>
     <row r="6308">
-      <c r="A6308" s="6"/>
+      <c r="A6308" s="10"/>
       <c r="B6308" s="2"/>
-      <c r="C6308" s="7"/>
+      <c r="C6308" s="6"/>
     </row>
     <row r="6309">
-      <c r="A6309" s="6"/>
+      <c r="A6309" s="10"/>
       <c r="B6309" s="2"/>
-      <c r="C6309" s="7"/>
+      <c r="C6309" s="6"/>
     </row>
     <row r="6310">
-      <c r="A6310" s="6"/>
+      <c r="A6310" s="10"/>
       <c r="B6310" s="2"/>
-      <c r="C6310" s="7"/>
+      <c r="C6310" s="6"/>
     </row>
     <row r="6311">
-      <c r="A6311" s="6"/>
+      <c r="A6311" s="10"/>
       <c r="B6311" s="2"/>
-      <c r="C6311" s="7"/>
+      <c r="C6311" s="6"/>
     </row>
     <row r="6312">
-      <c r="A6312" s="6"/>
+      <c r="A6312" s="10"/>
       <c r="B6312" s="2"/>
-      <c r="C6312" s="7"/>
+      <c r="C6312" s="6"/>
     </row>
     <row r="6313">
-      <c r="A6313" s="6"/>
+      <c r="A6313" s="10"/>
       <c r="B6313" s="2"/>
-      <c r="C6313" s="7"/>
+      <c r="C6313" s="6"/>
     </row>
     <row r="6314">
-      <c r="A6314" s="6"/>
+      <c r="A6314" s="10"/>
       <c r="B6314" s="2"/>
-      <c r="C6314" s="7"/>
+      <c r="C6314" s="6"/>
     </row>
     <row r="6315">
-      <c r="A6315" s="6"/>
+      <c r="A6315" s="10"/>
       <c r="B6315" s="2"/>
-      <c r="C6315" s="7"/>
+      <c r="C6315" s="6"/>
     </row>
     <row r="6316">
-      <c r="A6316" s="6"/>
+      <c r="A6316" s="10"/>
       <c r="B6316" s="2"/>
-      <c r="C6316" s="7"/>
+      <c r="C6316" s="6"/>
     </row>
     <row r="6317">
-      <c r="A6317" s="6"/>
+      <c r="A6317" s="10"/>
       <c r="B6317" s="2"/>
-      <c r="C6317" s="7"/>
+      <c r="C6317" s="6"/>
     </row>
     <row r="6318">
-      <c r="A6318" s="6"/>
+      <c r="A6318" s="10"/>
       <c r="B6318" s="2"/>
-      <c r="C6318" s="7"/>
+      <c r="C6318" s="6"/>
     </row>
     <row r="6319">
-      <c r="A6319" s="6"/>
+      <c r="A6319" s="10"/>
       <c r="B6319" s="2"/>
-      <c r="C6319" s="7"/>
+      <c r="C6319" s="6"/>
     </row>
     <row r="6320">
-      <c r="A6320" s="6"/>
+      <c r="A6320" s="10"/>
       <c r="B6320" s="2"/>
-      <c r="C6320" s="7"/>
+      <c r="C6320" s="6"/>
     </row>
     <row r="6321">
-      <c r="A6321" s="6"/>
+      <c r="A6321" s="10"/>
       <c r="B6321" s="2"/>
-      <c r="C6321" s="7"/>
+      <c r="C6321" s="6"/>
     </row>
     <row r="6322">
-      <c r="A6322" s="6"/>
+      <c r="A6322" s="10"/>
       <c r="B6322" s="2"/>
-      <c r="C6322" s="7"/>
+      <c r="C6322" s="6"/>
     </row>
     <row r="6323">
-      <c r="A6323" s="6"/>
+      <c r="A6323" s="10"/>
       <c r="B6323" s="2"/>
-      <c r="C6323" s="7"/>
+      <c r="C6323" s="6"/>
     </row>
     <row r="6324">
-      <c r="A6324" s="6"/>
+      <c r="A6324" s="10"/>
       <c r="B6324" s="2"/>
-      <c r="C6324" s="7"/>
+      <c r="C6324" s="6"/>
     </row>
     <row r="6325">
-      <c r="A6325" s="6"/>
+      <c r="A6325" s="10"/>
       <c r="B6325" s="2"/>
-      <c r="C6325" s="7"/>
+      <c r="C6325" s="6"/>
     </row>
     <row r="6326">
-      <c r="A6326" s="6"/>
+      <c r="A6326" s="10"/>
       <c r="B6326" s="2"/>
-      <c r="C6326" s="7"/>
+      <c r="C6326" s="6"/>
     </row>
     <row r="6327">
-      <c r="A6327" s="6"/>
+      <c r="A6327" s="10"/>
       <c r="B6327" s="2"/>
-      <c r="C6327" s="7"/>
+      <c r="C6327" s="6"/>
     </row>
     <row r="6328">
-      <c r="A6328" s="6"/>
+      <c r="A6328" s="10"/>
       <c r="B6328" s="2"/>
-      <c r="C6328" s="7"/>
+      <c r="C6328" s="6"/>
     </row>
     <row r="6329">
-      <c r="A6329" s="6"/>
+      <c r="A6329" s="10"/>
       <c r="B6329" s="2"/>
-      <c r="C6329" s="7"/>
+      <c r="C6329" s="6"/>
     </row>
     <row r="6330">
-      <c r="A6330" s="6"/>
+      <c r="A6330" s="10"/>
       <c r="B6330" s="2"/>
-      <c r="C6330" s="7"/>
+      <c r="C6330" s="6"/>
     </row>
     <row r="6331">
-      <c r="A6331" s="6"/>
+      <c r="A6331" s="10"/>
       <c r="B6331" s="2"/>
-      <c r="C6331" s="7"/>
+      <c r="C6331" s="6"/>
     </row>
     <row r="6332">
-      <c r="A6332" s="6"/>
+      <c r="A6332" s="10"/>
       <c r="B6332" s="2"/>
-      <c r="C6332" s="7"/>
+      <c r="C6332" s="6"/>
     </row>
     <row r="6333">
-      <c r="A6333" s="6"/>
+      <c r="A6333" s="10"/>
       <c r="B6333" s="2"/>
-      <c r="C6333" s="7"/>
+      <c r="C6333" s="6"/>
     </row>
     <row r="6334">
-      <c r="A6334" s="6"/>
+      <c r="A6334" s="10"/>
       <c r="B6334" s="2"/>
-      <c r="C6334" s="7"/>
+      <c r="C6334" s="6"/>
     </row>
     <row r="6335">
-      <c r="A6335" s="6"/>
+      <c r="A6335" s="10"/>
       <c r="B6335" s="2"/>
-      <c r="C6335" s="7"/>
+      <c r="C6335" s="6"/>
     </row>
     <row r="6336">
-      <c r="A6336" s="6"/>
+      <c r="A6336" s="10"/>
       <c r="B6336" s="2"/>
-      <c r="C6336" s="7"/>
+      <c r="C6336" s="6"/>
     </row>
     <row r="6337">
-      <c r="A6337" s="6"/>
+      <c r="A6337" s="10"/>
       <c r="B6337" s="2"/>
-      <c r="C6337" s="7"/>
+      <c r="C6337" s="6"/>
     </row>
     <row r="6338">
-      <c r="A6338" s="6"/>
+      <c r="A6338" s="10"/>
       <c r="B6338" s="2"/>
-      <c r="C6338" s="7"/>
+      <c r="C6338" s="6"/>
     </row>
     <row r="6339">
-      <c r="A6339" s="6"/>
+      <c r="A6339" s="10"/>
       <c r="B6339" s="2"/>
-      <c r="C6339" s="7"/>
+      <c r="C6339" s="6"/>
     </row>
     <row r="6340">
-      <c r="A6340" s="6"/>
+      <c r="A6340" s="10"/>
       <c r="B6340" s="2"/>
-      <c r="C6340" s="7"/>
+      <c r="C6340" s="6"/>
     </row>
     <row r="6341">
-      <c r="A6341" s="6"/>
+      <c r="A6341" s="10"/>
       <c r="B6341" s="2"/>
-      <c r="C6341" s="7"/>
+      <c r="C6341" s="6"/>
     </row>
     <row r="6342">
-      <c r="A6342" s="6"/>
+      <c r="A6342" s="10"/>
       <c r="B6342" s="2"/>
-      <c r="C6342" s="7"/>
+      <c r="C6342" s="6"/>
     </row>
     <row r="6343">
-      <c r="A6343" s="6"/>
+      <c r="A6343" s="10"/>
       <c r="B6343" s="2"/>
-      <c r="C6343" s="7"/>
+      <c r="C6343" s="6"/>
     </row>
     <row r="6344">
-      <c r="A6344" s="6"/>
+      <c r="A6344" s="10"/>
       <c r="B6344" s="2"/>
-      <c r="C6344" s="7"/>
+      <c r="C6344" s="6"/>
     </row>
     <row r="6345">
-      <c r="A6345" s="6"/>
+      <c r="A6345" s="10"/>
       <c r="B6345" s="2"/>
-      <c r="C6345" s="7"/>
+      <c r="C6345" s="6"/>
     </row>
     <row r="6346">
-      <c r="A6346" s="6"/>
+      <c r="A6346" s="10"/>
       <c r="B6346" s="2"/>
-      <c r="C6346" s="7"/>
+      <c r="C6346" s="6"/>
     </row>
     <row r="6347">
-      <c r="A6347" s="6"/>
+      <c r="A6347" s="10"/>
       <c r="B6347" s="2"/>
-      <c r="C6347" s="7"/>
+      <c r="C6347" s="6"/>
     </row>
     <row r="6348">
-      <c r="A6348" s="6"/>
+      <c r="A6348" s="10"/>
       <c r="B6348" s="2"/>
-      <c r="C6348" s="7"/>
+      <c r="C6348" s="6"/>
     </row>
     <row r="6349">
-      <c r="A6349" s="6"/>
+      <c r="A6349" s="10"/>
       <c r="B6349" s="2"/>
-      <c r="C6349" s="7"/>
+      <c r="C6349" s="6"/>
     </row>
     <row r="6350">
-      <c r="A6350" s="6"/>
+      <c r="A6350" s="10"/>
       <c r="B6350" s="2"/>
-      <c r="C6350" s="7"/>
+      <c r="C6350" s="6"/>
     </row>
     <row r="6351">
-      <c r="A6351" s="6"/>
+      <c r="A6351" s="10"/>
       <c r="B6351" s="2"/>
-      <c r="C6351" s="7"/>
+      <c r="C6351" s="6"/>
     </row>
     <row r="6352">
-      <c r="A6352" s="6"/>
+      <c r="A6352" s="10"/>
       <c r="B6352" s="2"/>
-      <c r="C6352" s="7"/>
+      <c r="C6352" s="6"/>
     </row>
     <row r="6353">
-      <c r="A6353" s="6"/>
+      <c r="A6353" s="10"/>
       <c r="B6353" s="2"/>
-      <c r="C6353" s="7"/>
+      <c r="C6353" s="6"/>
     </row>
     <row r="6354">
-      <c r="A6354" s="6"/>
+      <c r="A6354" s="10"/>
       <c r="B6354" s="2"/>
-      <c r="C6354" s="7"/>
+      <c r="C6354" s="6"/>
     </row>
     <row r="6355">
-      <c r="A6355" s="6"/>
+      <c r="A6355" s="10"/>
       <c r="B6355" s="2"/>
-      <c r="C6355" s="7"/>
+      <c r="C6355" s="6"/>
     </row>
     <row r="6356">
-      <c r="A6356" s="6"/>
+      <c r="A6356" s="10"/>
       <c r="B6356" s="2"/>
-      <c r="C6356" s="7"/>
+      <c r="C6356" s="6"/>
     </row>
     <row r="6357">
-      <c r="A6357" s="6"/>
+      <c r="A6357" s="10"/>
       <c r="B6357" s="2"/>
-      <c r="C6357" s="7"/>
+      <c r="C6357" s="6"/>
     </row>
     <row r="6358">
-      <c r="A6358" s="6"/>
+      <c r="A6358" s="10"/>
       <c r="B6358" s="2"/>
-      <c r="C6358" s="7"/>
+      <c r="C6358" s="6"/>
     </row>
     <row r="6359">
-      <c r="A6359" s="6"/>
+      <c r="A6359" s="10"/>
       <c r="B6359" s="2"/>
-      <c r="C6359" s="7"/>
+      <c r="C6359" s="6"/>
     </row>
     <row r="6360">
-      <c r="A6360" s="6"/>
+      <c r="A6360" s="10"/>
       <c r="B6360" s="2"/>
-      <c r="C6360" s="7"/>
+      <c r="C6360" s="6"/>
     </row>
     <row r="6361">
-      <c r="A6361" s="6"/>
+      <c r="A6361" s="10"/>
       <c r="B6361" s="2"/>
-      <c r="C6361" s="7"/>
+      <c r="C6361" s="6"/>
     </row>
     <row r="6362">
-      <c r="A6362" s="6"/>
+      <c r="A6362" s="10"/>
       <c r="B6362" s="2"/>
-      <c r="C6362" s="7"/>
+      <c r="C6362" s="6"/>
     </row>
     <row r="6363">
-      <c r="A6363" s="6"/>
+      <c r="A6363" s="10"/>
       <c r="B6363" s="2"/>
-      <c r="C6363" s="7"/>
+      <c r="C6363" s="6"/>
     </row>
     <row r="6364">
-      <c r="A6364" s="6"/>
+      <c r="A6364" s="10"/>
       <c r="B6364" s="2"/>
-      <c r="C6364" s="7"/>
+      <c r="C6364" s="6"/>
     </row>
     <row r="6365">
-      <c r="A6365" s="6"/>
+      <c r="A6365" s="10"/>
       <c r="B6365" s="2"/>
-      <c r="C6365" s="7"/>
+      <c r="C6365" s="6"/>
     </row>
     <row r="6366">
-      <c r="A6366" s="6"/>
+      <c r="A6366" s="10"/>
       <c r="B6366" s="2"/>
-      <c r="C6366" s="7"/>
+      <c r="C6366" s="6"/>
     </row>
     <row r="6367">
-      <c r="A6367" s="6"/>
+      <c r="A6367" s="10"/>
       <c r="B6367" s="2"/>
-      <c r="C6367" s="7"/>
+      <c r="C6367" s="6"/>
     </row>
     <row r="6368">
-      <c r="A6368" s="6"/>
+      <c r="A6368" s="10"/>
       <c r="B6368" s="2"/>
-      <c r="C6368" s="7"/>
+      <c r="C6368" s="6"/>
     </row>
     <row r="6369">
-      <c r="A6369" s="6"/>
+      <c r="A6369" s="10"/>
       <c r="B6369" s="2"/>
-      <c r="C6369" s="7"/>
+      <c r="C6369" s="6"/>
     </row>
     <row r="6370">
-      <c r="A6370" s="6"/>
+      <c r="A6370" s="10"/>
       <c r="B6370" s="2"/>
-      <c r="C6370" s="7"/>
+      <c r="C6370" s="6"/>
     </row>
     <row r="6371">
-      <c r="A6371" s="6"/>
+      <c r="A6371" s="10"/>
       <c r="B6371" s="2"/>
-      <c r="C6371" s="7"/>
+      <c r="C6371" s="6"/>
     </row>
     <row r="6372">
-      <c r="A6372" s="6"/>
+      <c r="A6372" s="10"/>
       <c r="B6372" s="2"/>
-      <c r="C6372" s="7"/>
+      <c r="C6372" s="6"/>
     </row>
     <row r="6373">
-      <c r="A6373" s="6"/>
+      <c r="A6373" s="10"/>
       <c r="B6373" s="2"/>
-      <c r="C6373" s="7"/>
+      <c r="C6373" s="6"/>
     </row>
     <row r="6374">
-      <c r="A6374" s="6"/>
+      <c r="A6374" s="10"/>
       <c r="B6374" s="2"/>
-      <c r="C6374" s="7"/>
+      <c r="C6374" s="6"/>
     </row>
     <row r="6375">
-      <c r="A6375" s="6"/>
+      <c r="A6375" s="10"/>
       <c r="B6375" s="2"/>
-      <c r="C6375" s="7"/>
+      <c r="C6375" s="6"/>
     </row>
     <row r="6376">
-      <c r="A6376" s="6"/>
+      <c r="A6376" s="10"/>
       <c r="B6376" s="2"/>
-      <c r="C6376" s="7"/>
+      <c r="C6376" s="6"/>
     </row>
     <row r="6377">
-      <c r="A6377" s="6"/>
+      <c r="A6377" s="10"/>
       <c r="B6377" s="2"/>
-      <c r="C6377" s="7"/>
+      <c r="C6377" s="6"/>
     </row>
     <row r="6378">
-      <c r="A6378" s="6"/>
+      <c r="A6378" s="10"/>
       <c r="B6378" s="2"/>
-      <c r="C6378" s="7"/>
+      <c r="C6378" s="6"/>
     </row>
     <row r="6379">
-      <c r="A6379" s="6"/>
+      <c r="A6379" s="10"/>
       <c r="B6379" s="2"/>
-      <c r="C6379" s="7"/>
+      <c r="C6379" s="6"/>
     </row>
     <row r="6380">
-      <c r="A6380" s="6"/>
+      <c r="A6380" s="10"/>
       <c r="B6380" s="2"/>
-      <c r="C6380" s="7"/>
+      <c r="C6380" s="6"/>
     </row>
     <row r="6381">
-      <c r="A6381" s="6"/>
+      <c r="A6381" s="10"/>
       <c r="B6381" s="2"/>
-      <c r="C6381" s="7"/>
+      <c r="C6381" s="6"/>
     </row>
     <row r="6382">
-      <c r="A6382" s="6"/>
+      <c r="A6382" s="10"/>
       <c r="B6382" s="2"/>
-      <c r="C6382" s="7"/>
+      <c r="C6382" s="6"/>
     </row>
     <row r="6383">
-      <c r="A6383" s="6"/>
+      <c r="A6383" s="10"/>
       <c r="B6383" s="2"/>
-      <c r="C6383" s="7"/>
+      <c r="C6383" s="6"/>
     </row>
     <row r="6384">
-      <c r="A6384" s="6"/>
+      <c r="A6384" s="10"/>
       <c r="B6384" s="2"/>
-      <c r="C6384" s="7"/>
+      <c r="C6384" s="6"/>
     </row>
     <row r="6385">
-      <c r="A6385" s="6"/>
+      <c r="A6385" s="10"/>
       <c r="B6385" s="2"/>
-      <c r="C6385" s="7"/>
+      <c r="C6385" s="6"/>
     </row>
     <row r="6386">
-      <c r="A6386" s="6"/>
+      <c r="A6386" s="10"/>
       <c r="B6386" s="2"/>
-      <c r="C6386" s="7"/>
+      <c r="C6386" s="6"/>
     </row>
     <row r="6387">
-      <c r="A6387" s="6"/>
+      <c r="A6387" s="10"/>
       <c r="B6387" s="2"/>
-      <c r="C6387" s="7"/>
+      <c r="C6387" s="6"/>
     </row>
     <row r="6388">
-      <c r="A6388" s="6"/>
+      <c r="A6388" s="10"/>
       <c r="B6388" s="2"/>
-      <c r="C6388" s="7"/>
+      <c r="C6388" s="6"/>
     </row>
     <row r="6389">
-      <c r="A6389" s="6"/>
+      <c r="A6389" s="10"/>
       <c r="B6389" s="2"/>
-      <c r="C6389" s="7"/>
+      <c r="C6389" s="6"/>
     </row>
     <row r="6390">
-      <c r="A6390" s="6"/>
+      <c r="A6390" s="10"/>
       <c r="B6390" s="2"/>
-      <c r="C6390" s="7"/>
+      <c r="C6390" s="6"/>
     </row>
     <row r="6391">
-      <c r="A6391" s="6"/>
+      <c r="A6391" s="10"/>
       <c r="B6391" s="2"/>
-      <c r="C6391" s="7"/>
+      <c r="C6391" s="6"/>
     </row>
     <row r="6392">
-      <c r="A6392" s="6"/>
+      <c r="A6392" s="10"/>
       <c r="B6392" s="2"/>
-      <c r="C6392" s="7"/>
+      <c r="C6392" s="6"/>
     </row>
     <row r="6393">
-      <c r="A6393" s="6"/>
+      <c r="A6393" s="10"/>
       <c r="B6393" s="2"/>
-      <c r="C6393" s="7"/>
+      <c r="C6393" s="6"/>
     </row>
     <row r="6394">
-      <c r="A6394" s="6"/>
+      <c r="A6394" s="10"/>
       <c r="B6394" s="2"/>
-      <c r="C6394" s="7"/>
+      <c r="C6394" s="6"/>
     </row>
     <row r="6395">
-      <c r="A6395" s="6"/>
+      <c r="A6395" s="10"/>
       <c r="B6395" s="2"/>
-      <c r="C6395" s="7"/>
+      <c r="C6395" s="6"/>
     </row>
     <row r="6396">
-      <c r="A6396" s="6"/>
+      <c r="A6396" s="10"/>
       <c r="B6396" s="2"/>
-      <c r="C6396" s="7"/>
+      <c r="C6396" s="6"/>
     </row>
     <row r="6397">
-      <c r="A6397" s="6"/>
+      <c r="A6397" s="10"/>
       <c r="B6397" s="2"/>
-      <c r="C6397" s="7"/>
+      <c r="C6397" s="6"/>
     </row>
     <row r="6398">
-      <c r="A6398" s="6"/>
+      <c r="A6398" s="10"/>
       <c r="B6398" s="2"/>
-      <c r="C6398" s="7"/>
+      <c r="C6398" s="6"/>
     </row>
     <row r="6399">
-      <c r="A6399" s="6"/>
+      <c r="A6399" s="10"/>
       <c r="B6399" s="2"/>
-      <c r="C6399" s="7"/>
+      <c r="C6399" s="6"/>
     </row>
     <row r="6400">
-      <c r="A6400" s="6"/>
+      <c r="A6400" s="10"/>
       <c r="B6400" s="2"/>
-      <c r="C6400" s="7"/>
+      <c r="C6400" s="6"/>
     </row>
     <row r="6401">
-      <c r="A6401" s="6"/>
+      <c r="A6401" s="10"/>
       <c r="B6401" s="2"/>
-      <c r="C6401" s="7"/>
+      <c r="C6401" s="6"/>
     </row>
     <row r="6402">
-      <c r="A6402" s="6"/>
+      <c r="A6402" s="10"/>
       <c r="B6402" s="2"/>
-      <c r="C6402" s="7"/>
+      <c r="C6402" s="6"/>
     </row>
     <row r="6403">
-      <c r="A6403" s="6"/>
+      <c r="A6403" s="10"/>
       <c r="B6403" s="2"/>
-      <c r="C6403" s="7"/>
+      <c r="C6403" s="6"/>
     </row>
     <row r="6404">
-      <c r="A6404" s="6"/>
+      <c r="A6404" s="10"/>
       <c r="B6404" s="2"/>
-      <c r="C6404" s="7"/>
+      <c r="C6404" s="6"/>
     </row>
     <row r="6405">
-      <c r="A6405" s="6"/>
+      <c r="A6405" s="10"/>
       <c r="B6405" s="2"/>
-      <c r="C6405" s="7"/>
+      <c r="C6405" s="6"/>
     </row>
     <row r="6406">
-      <c r="A6406" s="6"/>
+      <c r="A6406" s="10"/>
       <c r="B6406" s="2"/>
-      <c r="C6406" s="7"/>
+      <c r="C6406" s="6"/>
     </row>
     <row r="6407">
-      <c r="A6407" s="6"/>
+      <c r="A6407" s="10"/>
       <c r="B6407" s="2"/>
-      <c r="C6407" s="7"/>
+      <c r="C6407" s="6"/>
     </row>
     <row r="6408">
-      <c r="A6408" s="6"/>
+      <c r="A6408" s="10"/>
       <c r="B6408" s="2"/>
-      <c r="C6408" s="7"/>
+      <c r="C6408" s="6"/>
     </row>
     <row r="6409">
-      <c r="A6409" s="6"/>
+      <c r="A6409" s="10"/>
       <c r="B6409" s="2"/>
-      <c r="C6409" s="7"/>
+      <c r="C6409" s="6"/>
     </row>
     <row r="6410">
-      <c r="A6410" s="6"/>
+      <c r="A6410" s="10"/>
       <c r="B6410" s="2"/>
-      <c r="C6410" s="7"/>
+      <c r="C6410" s="6"/>
     </row>
     <row r="6411">
-      <c r="A6411" s="6"/>
+      <c r="A6411" s="10"/>
       <c r="B6411" s="2"/>
-      <c r="C6411" s="7"/>
+      <c r="C6411" s="6"/>
     </row>
     <row r="6412">
-      <c r="A6412" s="6"/>
+      <c r="A6412" s="10"/>
       <c r="B6412" s="2"/>
-      <c r="C6412" s="7"/>
+      <c r="C6412" s="6"/>
     </row>
     <row r="6413">
-      <c r="A6413" s="6"/>
+      <c r="A6413" s="10"/>
       <c r="B6413" s="2"/>
-      <c r="C6413" s="7"/>
+      <c r="C6413" s="6"/>
     </row>
     <row r="6414">
-      <c r="A6414" s="6"/>
+      <c r="A6414" s="10"/>
       <c r="B6414" s="2"/>
-      <c r="C6414" s="7"/>
+      <c r="C6414" s="6"/>
     </row>
     <row r="6415">
-      <c r="A6415" s="6"/>
+      <c r="A6415" s="10"/>
       <c r="B6415" s="2"/>
-      <c r="C6415" s="7"/>
+      <c r="C6415" s="6"/>
     </row>
     <row r="6416">
-      <c r="A6416" s="6"/>
+      <c r="A6416" s="10"/>
       <c r="B6416" s="2"/>
-      <c r="C6416" s="7"/>
+      <c r="C6416" s="6"/>
     </row>
     <row r="6417">
-      <c r="A6417" s="6"/>
+      <c r="A6417" s="10"/>
       <c r="B6417" s="2"/>
-      <c r="C6417" s="7"/>
+      <c r="C6417" s="6"/>
     </row>
     <row r="6418">
-      <c r="A6418" s="6"/>
+      <c r="A6418" s="10"/>
       <c r="B6418" s="2"/>
-      <c r="C6418" s="7"/>
+      <c r="C6418" s="6"/>
     </row>
     <row r="6419">
-      <c r="A6419" s="6"/>
+      <c r="A6419" s="10"/>
       <c r="B6419" s="2"/>
-      <c r="C6419" s="7"/>
+      <c r="C6419" s="6"/>
     </row>
     <row r="6420">
-      <c r="A6420" s="6"/>
+      <c r="A6420" s="10"/>
       <c r="B6420" s="2"/>
-      <c r="C6420" s="7"/>
+      <c r="C6420" s="6"/>
     </row>
     <row r="6421">
-      <c r="A6421" s="6"/>
+      <c r="A6421" s="10"/>
       <c r="B6421" s="2"/>
-      <c r="C6421" s="7"/>
+      <c r="C6421" s="6"/>
     </row>
     <row r="6422">
-      <c r="A6422" s="6"/>
+      <c r="A6422" s="10"/>
       <c r="B6422" s="2"/>
-      <c r="C6422" s="7"/>
+      <c r="C6422" s="6"/>
     </row>
     <row r="6423">
-      <c r="A6423" s="6"/>
+      <c r="A6423" s="10"/>
       <c r="B6423" s="2"/>
-      <c r="C6423" s="7"/>
+      <c r="C6423" s="6"/>
     </row>
     <row r="6424">
-      <c r="A6424" s="6"/>
+      <c r="A6424" s="10"/>
       <c r="B6424" s="2"/>
-      <c r="C6424" s="7"/>
+      <c r="C6424" s="6"/>
     </row>
     <row r="6425">
-      <c r="A6425" s="6"/>
+      <c r="A6425" s="10"/>
       <c r="B6425" s="2"/>
-      <c r="C6425" s="7"/>
+      <c r="C6425" s="6"/>
     </row>
     <row r="6426">
-      <c r="A6426" s="6"/>
+      <c r="A6426" s="10"/>
       <c r="B6426" s="2"/>
-      <c r="C6426" s="7"/>
+      <c r="C6426" s="6"/>
     </row>
     <row r="6427">
-      <c r="A6427" s="6"/>
+      <c r="A6427" s="10"/>
       <c r="B6427" s="2"/>
-      <c r="C6427" s="7"/>
+      <c r="C6427" s="6"/>
     </row>
     <row r="6428">
-      <c r="A6428" s="6"/>
+      <c r="A6428" s="10"/>
       <c r="B6428" s="2"/>
-      <c r="C6428" s="7"/>
+      <c r="C6428" s="6"/>
     </row>
     <row r="6429">
-      <c r="A6429" s="6"/>
+      <c r="A6429" s="10"/>
       <c r="B6429" s="2"/>
-      <c r="C6429" s="7"/>
+      <c r="C6429" s="6"/>
     </row>
     <row r="6430">
-      <c r="A6430" s="6"/>
+      <c r="A6430" s="10"/>
       <c r="B6430" s="2"/>
-      <c r="C6430" s="7"/>
+      <c r="C6430" s="6"/>
     </row>
     <row r="6431">
-      <c r="A6431" s="6"/>
+      <c r="A6431" s="10"/>
       <c r="B6431" s="2"/>
-      <c r="C6431" s="7"/>
+      <c r="C6431" s="6"/>
     </row>
     <row r="6432">
-      <c r="A6432" s="6"/>
+      <c r="A6432" s="10"/>
       <c r="B6432" s="2"/>
-      <c r="C6432" s="7"/>
+      <c r="C6432" s="6"/>
     </row>
     <row r="6433">
-      <c r="A6433" s="6"/>
+      <c r="A6433" s="10"/>
       <c r="B6433" s="2"/>
-      <c r="C6433" s="7"/>
+      <c r="C6433" s="6"/>
     </row>
     <row r="6434">
-      <c r="A6434" s="6"/>
+      <c r="A6434" s="10"/>
       <c r="B6434" s="2"/>
-      <c r="C6434" s="7"/>
+      <c r="C6434" s="6"/>
     </row>
     <row r="6435">
-      <c r="A6435" s="6"/>
+      <c r="A6435" s="10"/>
       <c r="B6435" s="2"/>
-      <c r="C6435" s="7"/>
+      <c r="C6435" s="6"/>
     </row>
     <row r="6436">
-      <c r="A6436" s="6"/>
+      <c r="A6436" s="10"/>
       <c r="B6436" s="2"/>
-      <c r="C6436" s="7"/>
+      <c r="C6436" s="6"/>
     </row>
     <row r="6437">
-      <c r="A6437" s="6"/>
+      <c r="A6437" s="10"/>
       <c r="B6437" s="2"/>
-      <c r="C6437" s="7"/>
+      <c r="C6437" s="6"/>
     </row>
     <row r="6438">
-      <c r="A6438" s="6"/>
+      <c r="A6438" s="10"/>
       <c r="B6438" s="2"/>
-      <c r="C6438" s="7"/>
+      <c r="C6438" s="6"/>
     </row>
     <row r="6439">
-      <c r="A6439" s="6"/>
+      <c r="A6439" s="10"/>
       <c r="B6439" s="2"/>
-      <c r="C6439" s="7"/>
+      <c r="C6439" s="6"/>
     </row>
     <row r="6440">
-      <c r="A6440" s="6"/>
+      <c r="A6440" s="10"/>
       <c r="B6440" s="2"/>
-      <c r="C6440" s="7"/>
+      <c r="C6440" s="6"/>
     </row>
     <row r="6441">
-      <c r="A6441" s="6"/>
+      <c r="A6441" s="10"/>
       <c r="B6441" s="2"/>
-      <c r="C6441" s="7"/>
+      <c r="C6441" s="6"/>
     </row>
     <row r="6442">
-      <c r="A6442" s="6"/>
+      <c r="A6442" s="10"/>
       <c r="B6442" s="2"/>
-      <c r="C6442" s="7"/>
+      <c r="C6442" s="6"/>
     </row>
     <row r="6443">
-      <c r="A6443" s="6"/>
+      <c r="A6443" s="10"/>
       <c r="B6443" s="2"/>
-      <c r="C6443" s="7"/>
+      <c r="C6443" s="6"/>
     </row>
     <row r="6444">
-      <c r="A6444" s="6"/>
+      <c r="A6444" s="10"/>
       <c r="B6444" s="2"/>
-      <c r="C6444" s="7"/>
+      <c r="C6444" s="6"/>
     </row>
     <row r="6445">
-      <c r="A6445" s="6"/>
+      <c r="A6445" s="10"/>
       <c r="B6445" s="2"/>
-      <c r="C6445" s="7"/>
+      <c r="C6445" s="6"/>
     </row>
     <row r="6446">
-      <c r="A6446" s="6"/>
+      <c r="A6446" s="10"/>
       <c r="B6446" s="2"/>
-      <c r="C6446" s="7"/>
+      <c r="C6446" s="6"/>
     </row>
     <row r="6447">
-      <c r="A6447" s="6"/>
+      <c r="A6447" s="10"/>
       <c r="B6447" s="2"/>
-      <c r="C6447" s="7"/>
+      <c r="C6447" s="6"/>
     </row>
     <row r="6448">
-      <c r="A6448" s="6"/>
+      <c r="A6448" s="10"/>
       <c r="B6448" s="2"/>
-      <c r="C6448" s="7"/>
+      <c r="C6448" s="6"/>
     </row>
     <row r="6449">
-      <c r="A6449" s="6"/>
+      <c r="A6449" s="10"/>
       <c r="B6449" s="2"/>
-      <c r="C6449" s="7"/>
+      <c r="C6449" s="6"/>
     </row>
     <row r="6450">
-      <c r="A6450" s="6"/>
+      <c r="A6450" s="10"/>
       <c r="B6450" s="2"/>
-      <c r="C6450" s="7"/>
+      <c r="C6450" s="6"/>
     </row>
     <row r="6451">
-      <c r="A6451" s="6"/>
+      <c r="A6451" s="10"/>
       <c r="B6451" s="2"/>
-      <c r="C6451" s="7"/>
+      <c r="C6451" s="6"/>
     </row>
     <row r="6452">
-      <c r="A6452" s="6"/>
+      <c r="A6452" s="10"/>
       <c r="B6452" s="2"/>
-      <c r="C6452" s="7"/>
+      <c r="C6452" s="6"/>
     </row>
     <row r="6453">
-      <c r="A6453" s="6"/>
+      <c r="A6453" s="10"/>
       <c r="B6453" s="2"/>
-      <c r="C6453" s="7"/>
+      <c r="C6453" s="6"/>
     </row>
     <row r="6454">
-      <c r="A6454" s="6"/>
+      <c r="A6454" s="10"/>
       <c r="B6454" s="2"/>
-      <c r="C6454" s="7"/>
+      <c r="C6454" s="6"/>
     </row>
     <row r="6455">
-      <c r="A6455" s="6"/>
+      <c r="A6455" s="10"/>
       <c r="B6455" s="2"/>
-      <c r="C6455" s="7"/>
+      <c r="C6455" s="6"/>
     </row>
     <row r="6456">
-      <c r="A6456" s="6"/>
+      <c r="A6456" s="10"/>
       <c r="B6456" s="2"/>
-      <c r="C6456" s="7"/>
+      <c r="C6456" s="6"/>
     </row>
     <row r="6457">
-      <c r="A6457" s="6"/>
+      <c r="A6457" s="10"/>
       <c r="B6457" s="2"/>
-      <c r="C6457" s="7"/>
+      <c r="C6457" s="6"/>
     </row>
     <row r="6458">
-      <c r="A6458" s="6"/>
+      <c r="A6458" s="10"/>
       <c r="B6458" s="2"/>
-      <c r="C6458" s="7"/>
+      <c r="C6458" s="6"/>
     </row>
     <row r="6459">
-      <c r="A6459" s="6"/>
+      <c r="A6459" s="10"/>
       <c r="B6459" s="2"/>
-      <c r="C6459" s="7"/>
+      <c r="C6459" s="6"/>
     </row>
     <row r="6460">
-      <c r="A6460" s="6"/>
+      <c r="A6460" s="10"/>
       <c r="B6460" s="2"/>
-      <c r="C6460" s="7"/>
+      <c r="C6460" s="6"/>
     </row>
     <row r="6461">
-      <c r="A6461" s="6"/>
+      <c r="A6461" s="10"/>
       <c r="B6461" s="2"/>
-      <c r="C6461" s="7"/>
+      <c r="C6461" s="6"/>
     </row>
     <row r="6462">
-      <c r="A6462" s="6"/>
+      <c r="A6462" s="10"/>
       <c r="B6462" s="2"/>
-      <c r="C6462" s="7"/>
+      <c r="C6462" s="6"/>
     </row>
     <row r="6463">
-      <c r="A6463" s="6"/>
+      <c r="A6463" s="10"/>
       <c r="B6463" s="2"/>
-      <c r="C6463" s="7"/>
+      <c r="C6463" s="6"/>
     </row>
     <row r="6464">
-      <c r="A6464" s="6"/>
+      <c r="A6464" s="10"/>
       <c r="B6464" s="2"/>
-      <c r="C6464" s="7"/>
+      <c r="C6464" s="6"/>
     </row>
     <row r="6465">
-      <c r="A6465" s="6"/>
+      <c r="A6465" s="10"/>
       <c r="B6465" s="2"/>
-      <c r="C6465" s="7"/>
+      <c r="C6465" s="6"/>
     </row>
     <row r="6466">
-      <c r="A6466" s="6"/>
+      <c r="A6466" s="10"/>
       <c r="B6466" s="2"/>
-      <c r="C6466" s="7"/>
+      <c r="C6466" s="6"/>
     </row>
     <row r="6467">
-      <c r="A6467" s="6"/>
+      <c r="A6467" s="10"/>
       <c r="B6467" s="2"/>
-      <c r="C6467" s="7"/>
+      <c r="C6467" s="6"/>
     </row>
     <row r="6468">
-      <c r="A6468" s="6"/>
+      <c r="A6468" s="10"/>
       <c r="B6468" s="2"/>
-      <c r="C6468" s="7"/>
+      <c r="C6468" s="6"/>
     </row>
     <row r="6469">
-      <c r="A6469" s="6"/>
+      <c r="A6469" s="10"/>
       <c r="B6469" s="2"/>
-      <c r="C6469" s="7"/>
+      <c r="C6469" s="6"/>
     </row>
     <row r="6470">
-      <c r="A6470" s="6"/>
+      <c r="A6470" s="10"/>
       <c r="B6470" s="2"/>
-      <c r="C6470" s="7"/>
+      <c r="C6470" s="6"/>
     </row>
     <row r="6471">
-      <c r="A6471" s="6"/>
+      <c r="A6471" s="10"/>
       <c r="B6471" s="2"/>
-      <c r="C6471" s="7"/>
+      <c r="C6471" s="6"/>
     </row>
     <row r="6472">
-      <c r="A6472" s="6"/>
+      <c r="A6472" s="10"/>
       <c r="B6472" s="2"/>
-      <c r="C6472" s="7"/>
+      <c r="C6472" s="6"/>
     </row>
     <row r="6473">
-      <c r="A6473" s="6"/>
+      <c r="A6473" s="10"/>
       <c r="B6473" s="2"/>
-      <c r="C6473" s="7"/>
+      <c r="C6473" s="6"/>
     </row>
     <row r="6474">
-      <c r="A6474" s="6"/>
+      <c r="A6474" s="10"/>
       <c r="B6474" s="2"/>
-      <c r="C6474" s="7"/>
+      <c r="C6474" s="6"/>
     </row>
     <row r="6475">
-      <c r="A6475" s="6"/>
+      <c r="A6475" s="10"/>
       <c r="B6475" s="2"/>
-      <c r="C6475" s="7"/>
+      <c r="C6475" s="6"/>
     </row>
     <row r="6476">
-      <c r="A6476" s="6"/>
+      <c r="A6476" s="10"/>
       <c r="B6476" s="2"/>
-      <c r="C6476" s="7"/>
+      <c r="C6476" s="6"/>
     </row>
     <row r="6477">
-      <c r="A6477" s="6"/>
+      <c r="A6477" s="10"/>
       <c r="B6477" s="2"/>
-      <c r="C6477" s="7"/>
+      <c r="C6477" s="6"/>
     </row>
     <row r="6478">
-      <c r="A6478" s="6"/>
+      <c r="A6478" s="10"/>
       <c r="B6478" s="2"/>
-      <c r="C6478" s="7"/>
+      <c r="C6478" s="6"/>
     </row>
     <row r="6479">
-      <c r="A6479" s="6"/>
+      <c r="A6479" s="10"/>
       <c r="B6479" s="2"/>
-      <c r="C6479" s="7"/>
+      <c r="C6479" s="6"/>
     </row>
     <row r="6480">
-      <c r="A6480" s="6"/>
+      <c r="A6480" s="10"/>
       <c r="B6480" s="2"/>
-      <c r="C6480" s="7"/>
+      <c r="C6480" s="6"/>
     </row>
     <row r="6481">
-      <c r="A6481" s="6"/>
+      <c r="A6481" s="10"/>
       <c r="B6481" s="2"/>
-      <c r="C6481" s="7"/>
+      <c r="C6481" s="6"/>
     </row>
     <row r="6482">
-      <c r="A6482" s="6"/>
+      <c r="A6482" s="10"/>
       <c r="B6482" s="2"/>
-      <c r="C6482" s="7"/>
+      <c r="C6482" s="6"/>
     </row>
     <row r="6483">
-      <c r="A6483" s="6"/>
+      <c r="A6483" s="10"/>
       <c r="B6483" s="2"/>
-      <c r="C6483" s="7"/>
+      <c r="C6483" s="6"/>
     </row>
     <row r="6484">
-      <c r="A6484" s="6"/>
+      <c r="A6484" s="10"/>
       <c r="B6484" s="2"/>
-      <c r="C6484" s="7"/>
+      <c r="C6484" s="6"/>
     </row>
     <row r="6485">
-      <c r="A6485" s="6"/>
+      <c r="A6485" s="10"/>
       <c r="B6485" s="2"/>
-      <c r="C6485" s="7"/>
+      <c r="C6485" s="6"/>
     </row>
     <row r="6486">
-      <c r="A6486" s="6"/>
+      <c r="A6486" s="10"/>
       <c r="B6486" s="2"/>
-      <c r="C6486" s="7"/>
+      <c r="C6486" s="6"/>
     </row>
     <row r="6487">
-      <c r="A6487" s="6"/>
+      <c r="A6487" s="10"/>
       <c r="B6487" s="2"/>
-      <c r="C6487" s="7"/>
+      <c r="C6487" s="6"/>
     </row>
     <row r="6488">
-      <c r="A6488" s="6"/>
+      <c r="A6488" s="10"/>
       <c r="B6488" s="2"/>
-      <c r="C6488" s="7"/>
+      <c r="C6488" s="6"/>
     </row>
     <row r="6489">
-      <c r="A6489" s="6"/>
+      <c r="A6489" s="10"/>
       <c r="B6489" s="2"/>
-      <c r="C6489" s="7"/>
+      <c r="C6489" s="6"/>
     </row>
     <row r="6490">
-      <c r="A6490" s="6"/>
+      <c r="A6490" s="10"/>
       <c r="B6490" s="2"/>
-      <c r="C6490" s="7"/>
+      <c r="C6490" s="6"/>
     </row>
     <row r="6491">
-      <c r="A6491" s="6"/>
+      <c r="A6491" s="10"/>
       <c r="B6491" s="2"/>
-      <c r="C6491" s="7"/>
+      <c r="C6491" s="6"/>
     </row>
     <row r="6492">
-      <c r="A6492" s="6"/>
+      <c r="A6492" s="10"/>
       <c r="B6492" s="2"/>
-      <c r="C6492" s="7"/>
+      <c r="C6492" s="6"/>
     </row>
     <row r="6493">
-      <c r="A6493" s="6"/>
+      <c r="A6493" s="10"/>
       <c r="B6493" s="2"/>
-      <c r="C6493" s="7"/>
+      <c r="C6493" s="6"/>
     </row>
     <row r="6494">
-      <c r="A6494" s="6"/>
+      <c r="A6494" s="10"/>
       <c r="B6494" s="2"/>
-      <c r="C6494" s="7"/>
+      <c r="C6494" s="6"/>
     </row>
     <row r="6495">
-      <c r="A6495" s="6"/>
+      <c r="A6495" s="10"/>
       <c r="B6495" s="2"/>
-      <c r="C6495" s="7"/>
+      <c r="C6495" s="6"/>
     </row>
     <row r="6496">
-      <c r="A6496" s="6"/>
+      <c r="A6496" s="10"/>
       <c r="B6496" s="2"/>
-      <c r="C6496" s="7"/>
+      <c r="C6496" s="6"/>
     </row>
     <row r="6497">
-      <c r="A6497" s="6"/>
+      <c r="A6497" s="10"/>
       <c r="B6497" s="2"/>
-      <c r="C6497" s="7"/>
+      <c r="C6497" s="6"/>
     </row>
     <row r="6498">
-      <c r="A6498" s="6"/>
+      <c r="A6498" s="10"/>
       <c r="B6498" s="2"/>
-      <c r="C6498" s="7"/>
+      <c r="C6498" s="6"/>
     </row>
     <row r="6499">
-      <c r="A6499" s="6"/>
+      <c r="A6499" s="10"/>
       <c r="B6499" s="2"/>
-      <c r="C6499" s="7"/>
+      <c r="C6499" s="6"/>
     </row>
     <row r="6500">
-      <c r="A6500" s="6"/>
+      <c r="A6500" s="10"/>
       <c r="B6500" s="2"/>
-      <c r="C6500" s="7"/>
+      <c r="C6500" s="6"/>
     </row>
     <row r="6501">
-      <c r="A6501" s="6"/>
+      <c r="A6501" s="10"/>
       <c r="B6501" s="2"/>
-      <c r="C6501" s="7"/>
+      <c r="C6501" s="6"/>
     </row>
     <row r="6502">
-      <c r="A6502" s="6"/>
+      <c r="A6502" s="10"/>
       <c r="B6502" s="2"/>
-      <c r="C6502" s="7"/>
+      <c r="C6502" s="6"/>
     </row>
     <row r="6503">
-      <c r="A6503" s="6"/>
+      <c r="A6503" s="10"/>
       <c r="B6503" s="2"/>
-      <c r="C6503" s="7"/>
+      <c r="C6503" s="6"/>
     </row>
     <row r="6504">
-      <c r="A6504" s="6"/>
+      <c r="A6504" s="10"/>
       <c r="B6504" s="2"/>
-      <c r="C6504" s="7"/>
+      <c r="C6504" s="6"/>
     </row>
     <row r="6505">
-      <c r="A6505" s="6"/>
+      <c r="A6505" s="10"/>
       <c r="B6505" s="2"/>
-      <c r="C6505" s="7"/>
+      <c r="C6505" s="6"/>
     </row>
     <row r="6506">
-      <c r="A6506" s="6"/>
+      <c r="A6506" s="10"/>
       <c r="B6506" s="2"/>
-      <c r="C6506" s="7"/>
+      <c r="C6506" s="6"/>
     </row>
     <row r="6507">
-      <c r="A6507" s="6"/>
+      <c r="A6507" s="10"/>
       <c r="B6507" s="2"/>
-      <c r="C6507" s="7"/>
+      <c r="C6507" s="6"/>
     </row>
     <row r="6508">
-      <c r="A6508" s="6"/>
+      <c r="A6508" s="10"/>
       <c r="B6508" s="2"/>
-      <c r="C6508" s="7"/>
+      <c r="C6508" s="6"/>
     </row>
     <row r="6509">
-      <c r="A6509" s="6"/>
+      <c r="A6509" s="10"/>
       <c r="B6509" s="2"/>
-      <c r="C6509" s="7"/>
+      <c r="C6509" s="6"/>
     </row>
     <row r="6510">
-      <c r="A6510" s="6"/>
+      <c r="A6510" s="10"/>
       <c r="B6510" s="2"/>
-      <c r="C6510" s="7"/>
+      <c r="C6510" s="6"/>
     </row>
     <row r="6511">
-      <c r="A6511" s="6"/>
+      <c r="A6511" s="10"/>
       <c r="B6511" s="2"/>
-      <c r="C6511" s="7"/>
+      <c r="C6511" s="6"/>
     </row>
     <row r="6512">
-      <c r="A6512" s="6"/>
+      <c r="A6512" s="10"/>
       <c r="B6512" s="2"/>
-      <c r="C6512" s="7"/>
+      <c r="C6512" s="6"/>
     </row>
     <row r="6513">
-      <c r="A6513" s="6"/>
+      <c r="A6513" s="10"/>
       <c r="B6513" s="2"/>
-      <c r="C6513" s="7"/>
+      <c r="C6513" s="6"/>
     </row>
     <row r="6514">
-      <c r="A6514" s="6"/>
+      <c r="A6514" s="10"/>
       <c r="B6514" s="2"/>
-      <c r="C6514" s="7"/>
+      <c r="C6514" s="6"/>
     </row>
     <row r="6515">
-      <c r="A6515" s="6"/>
+      <c r="A6515" s="10"/>
       <c r="B6515" s="2"/>
-      <c r="C6515" s="7"/>
+      <c r="C6515" s="6"/>
     </row>
     <row r="6516">
-      <c r="A6516" s="6"/>
+      <c r="A6516" s="10"/>
       <c r="B6516" s="2"/>
-      <c r="C6516" s="7"/>
+      <c r="C6516" s="6"/>
     </row>
     <row r="6517">
-      <c r="A6517" s="6"/>
+      <c r="A6517" s="10"/>
       <c r="B6517" s="2"/>
-      <c r="C6517" s="7"/>
+      <c r="C6517" s="6"/>
     </row>
     <row r="6518">
-      <c r="A6518" s="6"/>
+      <c r="A6518" s="10"/>
       <c r="B6518" s="2"/>
-      <c r="C6518" s="7"/>
+      <c r="C6518" s="6"/>
     </row>
     <row r="6519">
-      <c r="A6519" s="6"/>
+      <c r="A6519" s="10"/>
       <c r="B6519" s="2"/>
-      <c r="C6519" s="7"/>
+      <c r="C6519" s="6"/>
     </row>
     <row r="6520">
-      <c r="A6520" s="6"/>
+      <c r="A6520" s="10"/>
       <c r="B6520" s="2"/>
-      <c r="C6520" s="7"/>
+      <c r="C6520" s="6"/>
     </row>
     <row r="6521">
-      <c r="A6521" s="6"/>
+      <c r="A6521" s="10"/>
       <c r="B6521" s="2"/>
-      <c r="C6521" s="7"/>
+      <c r="C6521" s="6"/>
     </row>
     <row r="6522">
-      <c r="A6522" s="6"/>
+      <c r="A6522" s="10"/>
       <c r="B6522" s="2"/>
-      <c r="C6522" s="7"/>
+      <c r="C6522" s="6"/>
     </row>
     <row r="6523">
-      <c r="A6523" s="6"/>
+      <c r="A6523" s="10"/>
       <c r="B6523" s="2"/>
-      <c r="C6523" s="7"/>
+      <c r="C6523" s="6"/>
     </row>
     <row r="6524">
-      <c r="A6524" s="6"/>
+      <c r="A6524" s="10"/>
       <c r="B6524" s="2"/>
-      <c r="C6524" s="7"/>
+      <c r="C6524" s="6"/>
     </row>
     <row r="6525">
-      <c r="A6525" s="6"/>
+      <c r="A6525" s="10"/>
       <c r="B6525" s="2"/>
-      <c r="C6525" s="7"/>
+      <c r="C6525" s="6"/>
     </row>
     <row r="6526">
-      <c r="A6526" s="6"/>
+      <c r="A6526" s="10"/>
       <c r="B6526" s="2"/>
-      <c r="C6526" s="7"/>
+      <c r="C6526" s="6"/>
     </row>
     <row r="6527">
-      <c r="A6527" s="6"/>
+      <c r="A6527" s="10"/>
       <c r="B6527" s="2"/>
-      <c r="C6527" s="7"/>
+      <c r="C6527" s="6"/>
     </row>
     <row r="6528">
-      <c r="A6528" s="6"/>
+      <c r="A6528" s="10"/>
       <c r="B6528" s="2"/>
-      <c r="C6528" s="7"/>
+      <c r="C6528" s="6"/>
     </row>
     <row r="6529">
-      <c r="A6529" s="6"/>
+      <c r="A6529" s="10"/>
       <c r="B6529" s="2"/>
-      <c r="C6529" s="7"/>
+      <c r="C6529" s="6"/>
     </row>
     <row r="6530">
-      <c r="A6530" s="6"/>
+      <c r="A6530" s="10"/>
       <c r="B6530" s="2"/>
-      <c r="C6530" s="7"/>
+      <c r="C6530" s="6"/>
     </row>
     <row r="6531">
-      <c r="A6531" s="6"/>
+      <c r="A6531" s="10"/>
       <c r="B6531" s="2"/>
-      <c r="C6531" s="7"/>
+      <c r="C6531" s="6"/>
     </row>
     <row r="6532">
-      <c r="A6532" s="6"/>
+      <c r="A6532" s="10"/>
       <c r="B6532" s="2"/>
-      <c r="C6532" s="7"/>
+      <c r="C6532" s="6"/>
     </row>
     <row r="6533">
-      <c r="A6533" s="6"/>
+      <c r="A6533" s="10"/>
       <c r="B6533" s="2"/>
-      <c r="C6533" s="7"/>
+      <c r="C6533" s="6"/>
     </row>
     <row r="6534">
-      <c r="A6534" s="6"/>
+      <c r="A6534" s="10"/>
       <c r="B6534" s="2"/>
-      <c r="C6534" s="7"/>
+      <c r="C6534" s="6"/>
     </row>
     <row r="6535">
-      <c r="A6535" s="6"/>
+      <c r="A6535" s="10"/>
       <c r="B6535" s="2"/>
-      <c r="C6535" s="7"/>
+      <c r="C6535" s="6"/>
     </row>
     <row r="6536">
-      <c r="A6536" s="6"/>
+      <c r="A6536" s="10"/>
       <c r="B6536" s="2"/>
-      <c r="C6536" s="7"/>
+      <c r="C6536" s="6"/>
     </row>
     <row r="6537">
-      <c r="A6537" s="6"/>
+      <c r="A6537" s="10"/>
       <c r="B6537" s="2"/>
-      <c r="C6537" s="7"/>
+      <c r="C6537" s="6"/>
     </row>
     <row r="6538">
-      <c r="A6538" s="6"/>
+      <c r="A6538" s="10"/>
       <c r="B6538" s="2"/>
-      <c r="C6538" s="7"/>
+      <c r="C6538" s="6"/>
     </row>
     <row r="6539">
-      <c r="A6539" s="6"/>
+      <c r="A6539" s="10"/>
       <c r="B6539" s="2"/>
-      <c r="C6539" s="7"/>
+      <c r="C6539" s="6"/>
     </row>
     <row r="6540">
-      <c r="A6540" s="6"/>
+      <c r="A6540" s="10"/>
       <c r="B6540" s="2"/>
-      <c r="C6540" s="7"/>
+      <c r="C6540" s="6"/>
     </row>
     <row r="6541">
-      <c r="A6541" s="6"/>
+      <c r="A6541" s="10"/>
       <c r="B6541" s="2"/>
-      <c r="C6541" s="7"/>
+      <c r="C6541" s="6"/>
     </row>
     <row r="6542">
-      <c r="A6542" s="6"/>
+      <c r="A6542" s="10"/>
       <c r="B6542" s="2"/>
-      <c r="C6542" s="7"/>
+      <c r="C6542" s="6"/>
     </row>
     <row r="6543">
-      <c r="A6543" s="6"/>
+      <c r="A6543" s="10"/>
       <c r="B6543" s="2"/>
-      <c r="C6543" s="7"/>
+      <c r="C6543" s="6"/>
     </row>
     <row r="6544">
-      <c r="A6544" s="6"/>
+      <c r="A6544" s="10"/>
       <c r="B6544" s="2"/>
-      <c r="C6544" s="7"/>
+      <c r="C6544" s="6"/>
     </row>
     <row r="6545">
-      <c r="A6545" s="6"/>
+      <c r="A6545" s="10"/>
       <c r="B6545" s="2"/>
-      <c r="C6545" s="7"/>
+      <c r="C6545" s="6"/>
     </row>
     <row r="6546">
-      <c r="A6546" s="6"/>
+      <c r="A6546" s="10"/>
       <c r="B6546" s="2"/>
-      <c r="C6546" s="7"/>
+      <c r="C6546" s="6"/>
     </row>
     <row r="6547">
-      <c r="A6547" s="6"/>
+      <c r="A6547" s="10"/>
       <c r="B6547" s="2"/>
-      <c r="C6547" s="7"/>
+      <c r="C6547" s="6"/>
     </row>
     <row r="6548">
-      <c r="A6548" s="6"/>
+      <c r="A6548" s="10"/>
       <c r="B6548" s="2"/>
-      <c r="C6548" s="7"/>
+      <c r="C6548" s="6"/>
     </row>
     <row r="6549">
-      <c r="A6549" s="6"/>
+      <c r="A6549" s="10"/>
       <c r="B6549" s="2"/>
-      <c r="C6549" s="7"/>
+      <c r="C6549" s="6"/>
     </row>
     <row r="6550">
-      <c r="A6550" s="6"/>
+      <c r="A6550" s="10"/>
       <c r="B6550" s="2"/>
-      <c r="C6550" s="7"/>
+      <c r="C6550" s="6"/>
     </row>
     <row r="6551">
-      <c r="A6551" s="6"/>
+      <c r="A6551" s="10"/>
       <c r="B6551" s="2"/>
-      <c r="C6551" s="7"/>
+      <c r="C6551" s="6"/>
     </row>
     <row r="6552">
-      <c r="A6552" s="6"/>
+      <c r="A6552" s="10"/>
       <c r="B6552" s="2"/>
-      <c r="C6552" s="7"/>
+      <c r="C6552" s="6"/>
     </row>
     <row r="6553">
-      <c r="A6553" s="6"/>
+      <c r="A6553" s="10"/>
       <c r="B6553" s="2"/>
-      <c r="C6553" s="7"/>
+      <c r="C6553" s="6"/>
     </row>
     <row r="6554">
-      <c r="A6554" s="6"/>
+      <c r="A6554" s="10"/>
       <c r="B6554" s="2"/>
-      <c r="C6554" s="7"/>
+      <c r="C6554" s="6"/>
     </row>
     <row r="6555">
-      <c r="A6555" s="6"/>
+      <c r="A6555" s="10"/>
       <c r="B6555" s="2"/>
-      <c r="C6555" s="7"/>
+      <c r="C6555" s="6"/>
     </row>
     <row r="6556">
-      <c r="A6556" s="6"/>
+      <c r="A6556" s="10"/>
       <c r="B6556" s="2"/>
-      <c r="C6556" s="7"/>
+      <c r="C6556" s="6"/>
     </row>
     <row r="6557">
-      <c r="A6557" s="6"/>
+      <c r="A6557" s="10"/>
       <c r="B6557" s="2"/>
-      <c r="C6557" s="7"/>
+      <c r="C6557" s="6"/>
     </row>
     <row r="6558">
-      <c r="A6558" s="6"/>
+      <c r="A6558" s="10"/>
       <c r="B6558" s="2"/>
-      <c r="C6558" s="7"/>
+      <c r="C6558" s="6"/>
     </row>
     <row r="6559">
-      <c r="A6559" s="6"/>
+      <c r="A6559" s="10"/>
       <c r="B6559" s="2"/>
-      <c r="C6559" s="7"/>
+      <c r="C6559" s="6"/>
     </row>
     <row r="6560">
-      <c r="A6560" s="6"/>
+      <c r="A6560" s="10"/>
       <c r="B6560" s="2"/>
-      <c r="C6560" s="7"/>
+      <c r="C6560" s="6"/>
     </row>
     <row r="6561">
-      <c r="A6561" s="6"/>
+      <c r="A6561" s="10"/>
       <c r="B6561" s="2"/>
-      <c r="C6561" s="7"/>
+      <c r="C6561" s="6"/>
     </row>
     <row r="6562">
-      <c r="A6562" s="6"/>
+      <c r="A6562" s="10"/>
       <c r="B6562" s="2"/>
-      <c r="C6562" s="7"/>
+      <c r="C6562" s="6"/>
     </row>
     <row r="6563">
-      <c r="A6563" s="6"/>
+      <c r="A6563" s="10"/>
       <c r="B6563" s="2"/>
-      <c r="C6563" s="7"/>
+      <c r="C6563" s="6"/>
     </row>
     <row r="6564">
-      <c r="A6564" s="6"/>
+      <c r="A6564" s="10"/>
       <c r="B6564" s="2"/>
-      <c r="C6564" s="7"/>
+      <c r="C6564" s="6"/>
     </row>
     <row r="6565">
-      <c r="A6565" s="6"/>
+      <c r="A6565" s="10"/>
       <c r="B6565" s="2"/>
-      <c r="C6565" s="7"/>
+      <c r="C6565" s="6"/>
     </row>
     <row r="6566">
-      <c r="A6566" s="6"/>
+      <c r="A6566" s="10"/>
       <c r="B6566" s="2"/>
-      <c r="C6566" s="7"/>
+      <c r="C6566" s="6"/>
     </row>
     <row r="6567">
-      <c r="A6567" s="6"/>
+      <c r="A6567" s="10"/>
       <c r="B6567" s="2"/>
-      <c r="C6567" s="7"/>
+      <c r="C6567" s="6"/>
     </row>
     <row r="6568">
-      <c r="A6568" s="6"/>
+      <c r="A6568" s="10"/>
       <c r="B6568" s="2"/>
-      <c r="C6568" s="7"/>
+      <c r="C6568" s="6"/>
     </row>
     <row r="6569">
-      <c r="A6569" s="6"/>
+      <c r="A6569" s="10"/>
       <c r="B6569" s="2"/>
-      <c r="C6569" s="7"/>
+      <c r="C6569" s="6"/>
     </row>
     <row r="6570">
-      <c r="A6570" s="6"/>
+      <c r="A6570" s="10"/>
       <c r="B6570" s="2"/>
-      <c r="C6570" s="7"/>
+      <c r="C6570" s="6"/>
     </row>
     <row r="6571">
-      <c r="A6571" s="6"/>
+      <c r="A6571" s="10"/>
       <c r="B6571" s="2"/>
-      <c r="C6571" s="7"/>
+      <c r="C6571" s="6"/>
     </row>
     <row r="6572">
-      <c r="A6572" s="6"/>
+      <c r="A6572" s="10"/>
       <c r="B6572" s="2"/>
-      <c r="C6572" s="7"/>
+      <c r="C6572" s="6"/>
     </row>
     <row r="6573">
-      <c r="A6573" s="6"/>
+      <c r="A6573" s="10"/>
       <c r="B6573" s="2"/>
-      <c r="C6573" s="7"/>
+      <c r="C6573" s="6"/>
     </row>
     <row r="6574">
-      <c r="A6574" s="6"/>
+      <c r="A6574" s="10"/>
       <c r="B6574" s="2"/>
-      <c r="C6574" s="7"/>
+      <c r="C6574" s="6"/>
     </row>
     <row r="6575">
-      <c r="A6575" s="6"/>
+      <c r="A6575" s="10"/>
       <c r="B6575" s="2"/>
-      <c r="C6575" s="7"/>
+      <c r="C6575" s="6"/>
     </row>
     <row r="6576">
-      <c r="A6576" s="6"/>
+      <c r="A6576" s="10"/>
       <c r="B6576" s="2"/>
-      <c r="C6576" s="7"/>
+      <c r="C6576" s="6"/>
     </row>
     <row r="6577">
-      <c r="A6577" s="6"/>
+      <c r="A6577" s="10"/>
       <c r="B6577" s="2"/>
-      <c r="C6577" s="7"/>
+      <c r="C6577" s="6"/>
     </row>
     <row r="6578">
-      <c r="A6578" s="6"/>
+      <c r="A6578" s="10"/>
       <c r="B6578" s="2"/>
-      <c r="C6578" s="7"/>
+      <c r="C6578" s="6"/>
     </row>
     <row r="6579">
-      <c r="A6579" s="6"/>
+      <c r="A6579" s="10"/>
       <c r="B6579" s="2"/>
-      <c r="C6579" s="7"/>
+      <c r="C6579" s="6"/>
     </row>
     <row r="6580">
-      <c r="A6580" s="6"/>
+      <c r="A6580" s="10"/>
       <c r="B6580" s="2"/>
-      <c r="C6580" s="7"/>
+      <c r="C6580" s="6"/>
     </row>
     <row r="6581">
-      <c r="A6581" s="6"/>
+      <c r="A6581" s="10"/>
       <c r="B6581" s="2"/>
-      <c r="C6581" s="7"/>
+      <c r="C6581" s="6"/>
     </row>
     <row r="6582">
-      <c r="A6582" s="6"/>
+      <c r="A6582" s="10"/>
       <c r="B6582" s="2"/>
-      <c r="C6582" s="7"/>
+      <c r="C6582" s="6"/>
     </row>
     <row r="6583">
-      <c r="A6583" s="6"/>
+      <c r="A6583" s="10"/>
       <c r="B6583" s="2"/>
-      <c r="C6583" s="7"/>
+      <c r="C6583" s="6"/>
     </row>
     <row r="6584">
-      <c r="A6584" s="6"/>
+      <c r="A6584" s="10"/>
       <c r="B6584" s="2"/>
-      <c r="C6584" s="7"/>
+      <c r="C6584" s="6"/>
     </row>
     <row r="6585">
-      <c r="A6585" s="6"/>
+      <c r="A6585" s="10"/>
       <c r="B6585" s="2"/>
-      <c r="C6585" s="7"/>
+      <c r="C6585" s="6"/>
     </row>
     <row r="6586">
-      <c r="A6586" s="6"/>
+      <c r="A6586" s="10"/>
       <c r="B6586" s="2"/>
-      <c r="C6586" s="7"/>
+      <c r="C6586" s="6"/>
     </row>
     <row r="6587">
-      <c r="A6587" s="6"/>
+      <c r="A6587" s="10"/>
       <c r="B6587" s="2"/>
-      <c r="C6587" s="7"/>
+      <c r="C6587" s="6"/>
     </row>
     <row r="6588">
-      <c r="A6588" s="6"/>
+      <c r="A6588" s="10"/>
       <c r="B6588" s="2"/>
-      <c r="C6588" s="7"/>
+      <c r="C6588" s="6"/>
     </row>
     <row r="6589">
-      <c r="A6589" s="6"/>
+      <c r="A6589" s="10"/>
       <c r="B6589" s="2"/>
-      <c r="C6589" s="7"/>
+      <c r="C6589" s="6"/>
     </row>
     <row r="6590">
-      <c r="A6590" s="6"/>
+      <c r="A6590" s="10"/>
       <c r="B6590" s="2"/>
-      <c r="C6590" s="7"/>
+      <c r="C6590" s="6"/>
     </row>
     <row r="6591">
-      <c r="A6591" s="6"/>
+      <c r="A6591" s="10"/>
       <c r="B6591" s="2"/>
-      <c r="C6591" s="7"/>
+      <c r="C6591" s="6"/>
     </row>
     <row r="6592">
-      <c r="A6592" s="6"/>
+      <c r="A6592" s="10"/>
       <c r="B6592" s="2"/>
-      <c r="C6592" s="7"/>
+      <c r="C6592" s="6"/>
     </row>
     <row r="6593">
-      <c r="A6593" s="6"/>
+      <c r="A6593" s="10"/>
       <c r="B6593" s="2"/>
-      <c r="C6593" s="7"/>
+      <c r="C6593" s="6"/>
     </row>
     <row r="6594">
-      <c r="A6594" s="6"/>
+      <c r="A6594" s="10"/>
       <c r="B6594" s="2"/>
-      <c r="C6594" s="7"/>
+      <c r="C6594" s="6"/>
     </row>
     <row r="6595">
-      <c r="A6595" s="6"/>
+      <c r="A6595" s="10"/>
       <c r="B6595" s="2"/>
-      <c r="C6595" s="7"/>
+      <c r="C6595" s="6"/>
     </row>
     <row r="6596">
-      <c r="A6596" s="6"/>
+      <c r="A6596" s="10"/>
       <c r="B6596" s="2"/>
-      <c r="C6596" s="7"/>
+      <c r="C6596" s="6"/>
     </row>
     <row r="6597">
-      <c r="A6597" s="6"/>
+      <c r="A6597" s="10"/>
       <c r="B6597" s="2"/>
-      <c r="C6597" s="7"/>
+      <c r="C6597" s="6"/>
     </row>
     <row r="6598">
-      <c r="A6598" s="6"/>
+      <c r="A6598" s="10"/>
       <c r="B6598" s="2"/>
-      <c r="C6598" s="7"/>
+      <c r="C6598" s="6"/>
     </row>
     <row r="6599">
-      <c r="A6599" s="6"/>
+      <c r="A6599" s="10"/>
       <c r="B6599" s="2"/>
-      <c r="C6599" s="7"/>
+      <c r="C6599" s="6"/>
     </row>
     <row r="6600">
-      <c r="A6600" s="6"/>
+      <c r="A6600" s="10"/>
       <c r="B6600" s="2"/>
-      <c r="C6600" s="7"/>
+      <c r="C6600" s="6"/>
     </row>
     <row r="6601">
-      <c r="A6601" s="6"/>
+      <c r="A6601" s="10"/>
       <c r="B6601" s="2"/>
-      <c r="C6601" s="7"/>
+      <c r="C6601" s="6"/>
     </row>
     <row r="6602">
-      <c r="A6602" s="6"/>
+      <c r="A6602" s="10"/>
       <c r="B6602" s="2"/>
-      <c r="C6602" s="7"/>
+      <c r="C6602" s="6"/>
     </row>
     <row r="6603">
-      <c r="A6603" s="6"/>
+      <c r="A6603" s="10"/>
       <c r="B6603" s="2"/>
-      <c r="C6603" s="7"/>
+      <c r="C6603" s="6"/>
     </row>
     <row r="6604">
-      <c r="A6604" s="6"/>
+      <c r="A6604" s="10"/>
       <c r="B6604" s="2"/>
-      <c r="C6604" s="7"/>
+      <c r="C6604" s="6"/>
     </row>
     <row r="6605">
-      <c r="A6605" s="6"/>
+      <c r="A6605" s="10"/>
       <c r="B6605" s="2"/>
-      <c r="C6605" s="7"/>
+      <c r="C6605" s="6"/>
     </row>
     <row r="6606">
-      <c r="A6606" s="6"/>
+      <c r="A6606" s="10"/>
       <c r="B6606" s="2"/>
-      <c r="C6606" s="7"/>
+      <c r="C6606" s="6"/>
     </row>
     <row r="6607">
-      <c r="A6607" s="6"/>
+      <c r="A6607" s="10"/>
       <c r="B6607" s="2"/>
-      <c r="C6607" s="7"/>
+      <c r="C6607" s="6"/>
     </row>
     <row r="6608">
-      <c r="A6608" s="6"/>
+      <c r="A6608" s="10"/>
       <c r="B6608" s="2"/>
-      <c r="C6608" s="7"/>
+      <c r="C6608" s="6"/>
     </row>
     <row r="6609">
-      <c r="A6609" s="6"/>
+      <c r="A6609" s="10"/>
       <c r="B6609" s="2"/>
-      <c r="C6609" s="7"/>
+      <c r="C6609" s="6"/>
     </row>
     <row r="6610">
-      <c r="A6610" s="6"/>
+      <c r="A6610" s="10"/>
       <c r="B6610" s="2"/>
-      <c r="C6610" s="7"/>
+      <c r="C6610" s="6"/>
     </row>
     <row r="6611">
-      <c r="A6611" s="6"/>
+      <c r="A6611" s="10"/>
       <c r="B6611" s="2"/>
-      <c r="C6611" s="7"/>
+      <c r="C6611" s="6"/>
     </row>
     <row r="6612">
-      <c r="A6612" s="6"/>
+      <c r="A6612" s="10"/>
       <c r="B6612" s="2"/>
-      <c r="C6612" s="7"/>
+      <c r="C6612" s="6"/>
     </row>
     <row r="6613">
-      <c r="A6613" s="6"/>
+      <c r="A6613" s="10"/>
       <c r="B6613" s="2"/>
-      <c r="C6613" s="7"/>
+      <c r="C6613" s="6"/>
     </row>
     <row r="6614">
-      <c r="A6614" s="6"/>
+      <c r="A6614" s="10"/>
       <c r="B6614" s="2"/>
-      <c r="C6614" s="7"/>
+      <c r="C6614" s="6"/>
     </row>
     <row r="6615">
-      <c r="A6615" s="6"/>
+      <c r="A6615" s="10"/>
       <c r="B6615" s="2"/>
-      <c r="C6615" s="7"/>
+      <c r="C6615" s="6"/>
     </row>
     <row r="6616">
-      <c r="A6616" s="6"/>
+      <c r="A6616" s="10"/>
       <c r="B6616" s="2"/>
-      <c r="C6616" s="7"/>
+      <c r="C6616" s="6"/>
     </row>
     <row r="6617">
-      <c r="A6617" s="6"/>
+      <c r="A6617" s="10"/>
       <c r="B6617" s="2"/>
-      <c r="C6617" s="7"/>
+      <c r="C6617" s="6"/>
     </row>
     <row r="6618">
-      <c r="A6618" s="6"/>
+      <c r="A6618" s="10"/>
       <c r="B6618" s="2"/>
-      <c r="C6618" s="7"/>
+      <c r="C6618" s="6"/>
     </row>
     <row r="6619">
-      <c r="A6619" s="6"/>
+      <c r="A6619" s="10"/>
       <c r="B6619" s="2"/>
-      <c r="C6619" s="7"/>
+      <c r="C6619" s="6"/>
     </row>
     <row r="6620">
-      <c r="A6620" s="6"/>
+      <c r="A6620" s="10"/>
       <c r="B6620" s="2"/>
-      <c r="C6620" s="7"/>
+      <c r="C6620" s="6"/>
     </row>
     <row r="6621">
-      <c r="A6621" s="6"/>
+      <c r="A6621" s="10"/>
       <c r="B6621" s="2"/>
-      <c r="C6621" s="7"/>
+      <c r="C6621" s="6"/>
     </row>
     <row r="6622">
-      <c r="A6622" s="6"/>
+      <c r="A6622" s="10"/>
       <c r="B6622" s="2"/>
-      <c r="C6622" s="7"/>
+      <c r="C6622" s="6"/>
     </row>
     <row r="6623">
-      <c r="A6623" s="6"/>
+      <c r="A6623" s="10"/>
       <c r="B6623" s="2"/>
-      <c r="C6623" s="7"/>
+      <c r="C6623" s="6"/>
     </row>
     <row r="6624">
-      <c r="A6624" s="6"/>
+      <c r="A6624" s="10"/>
       <c r="B6624" s="2"/>
-      <c r="C6624" s="7"/>
+      <c r="C6624" s="6"/>
     </row>
     <row r="6625">
-      <c r="A6625" s="6"/>
+      <c r="A6625" s="10"/>
       <c r="B6625" s="2"/>
-      <c r="C6625" s="7"/>
+      <c r="C6625" s="6"/>
     </row>
     <row r="6626">
-      <c r="A6626" s="6"/>
+      <c r="A6626" s="10"/>
       <c r="B6626" s="2"/>
-      <c r="C6626" s="7"/>
+      <c r="C6626" s="6"/>
     </row>
     <row r="6627">
-      <c r="A6627" s="6"/>
+      <c r="A6627" s="10"/>
       <c r="B6627" s="2"/>
-      <c r="C6627" s="7"/>
+      <c r="C6627" s="6"/>
     </row>
     <row r="6628">
-      <c r="A6628" s="6"/>
+      <c r="A6628" s="10"/>
       <c r="B6628" s="2"/>
-      <c r="C6628" s="7"/>
+      <c r="C6628" s="6"/>
     </row>
     <row r="6629">
-      <c r="A6629" s="6"/>
+      <c r="A6629" s="10"/>
       <c r="B6629" s="2"/>
-      <c r="C6629" s="7"/>
+      <c r="C6629" s="6"/>
     </row>
     <row r="6630">
-      <c r="A6630" s="6"/>
+      <c r="A6630" s="10"/>
       <c r="B6630" s="2"/>
-      <c r="C6630" s="7"/>
+      <c r="C6630" s="6"/>
     </row>
     <row r="6631">
-      <c r="A6631" s="6"/>
+      <c r="A6631" s="10"/>
       <c r="B6631" s="2"/>
-      <c r="C6631" s="7"/>
+      <c r="C6631" s="6"/>
     </row>
     <row r="6632">
-      <c r="A6632" s="6"/>
+      <c r="A6632" s="10"/>
       <c r="B6632" s="2"/>
-      <c r="C6632" s="7"/>
+      <c r="C6632" s="6"/>
     </row>
     <row r="6633">
-      <c r="A6633" s="6"/>
+      <c r="A6633" s="10"/>
       <c r="B6633" s="2"/>
-      <c r="C6633" s="7"/>
+      <c r="C6633" s="6"/>
     </row>
     <row r="6634">
-      <c r="A6634" s="6"/>
+      <c r="A6634" s="10"/>
       <c r="B6634" s="2"/>
-      <c r="C6634" s="7"/>
+      <c r="C6634" s="6"/>
     </row>
     <row r="6635">
-      <c r="A6635" s="6"/>
+      <c r="A6635" s="10"/>
       <c r="B6635" s="2"/>
-      <c r="C6635" s="7"/>
+      <c r="C6635" s="6"/>
     </row>
     <row r="6636">
-      <c r="A6636" s="6"/>
+      <c r="A6636" s="10"/>
       <c r="B6636" s="2"/>
-      <c r="C6636" s="7"/>
+      <c r="C6636" s="6"/>
     </row>
     <row r="6637">
-      <c r="A6637" s="6"/>
+      <c r="A6637" s="10"/>
       <c r="B6637" s="2"/>
-      <c r="C6637" s="7"/>
+      <c r="C6637" s="6"/>
     </row>
     <row r="6638">
-      <c r="A6638" s="6"/>
+      <c r="A6638" s="10"/>
       <c r="B6638" s="2"/>
-      <c r="C6638" s="7"/>
+      <c r="C6638" s="6"/>
     </row>
     <row r="6639">
-      <c r="A6639" s="6"/>
+      <c r="A6639" s="10"/>
       <c r="B6639" s="2"/>
-      <c r="C6639" s="7"/>
+      <c r="C6639" s="6"/>
     </row>
     <row r="6640">
-      <c r="A6640" s="6"/>
+      <c r="A6640" s="10"/>
       <c r="B6640" s="2"/>
-      <c r="C6640" s="7"/>
+      <c r="C6640" s="6"/>
     </row>
     <row r="6641">
-      <c r="A6641" s="6"/>
+      <c r="A6641" s="10"/>
       <c r="B6641" s="2"/>
-      <c r="C6641" s="7"/>
+      <c r="C6641" s="6"/>
     </row>
     <row r="6642">
-      <c r="A6642" s="6"/>
+      <c r="A6642" s="10"/>
       <c r="B6642" s="2"/>
-      <c r="C6642" s="7"/>
+      <c r="C6642" s="6"/>
     </row>
     <row r="6643">
-      <c r="A6643" s="6"/>
+      <c r="A6643" s="10"/>
       <c r="B6643" s="2"/>
-      <c r="C6643" s="7"/>
+      <c r="C6643" s="6"/>
     </row>
     <row r="6644">
-      <c r="A6644" s="6"/>
+      <c r="A6644" s="10"/>
       <c r="B6644" s="2"/>
-      <c r="C6644" s="7"/>
+      <c r="C6644" s="6"/>
     </row>
     <row r="6645">
-      <c r="A6645" s="6"/>
+      <c r="A6645" s="10"/>
       <c r="B6645" s="2"/>
-      <c r="C6645" s="7"/>
+      <c r="C6645" s="6"/>
     </row>
     <row r="6646">
-      <c r="A6646" s="6"/>
+      <c r="A6646" s="10"/>
       <c r="B6646" s="2"/>
-      <c r="C6646" s="7"/>
+      <c r="C6646" s="6"/>
     </row>
     <row r="6647">
-      <c r="A6647" s="6"/>
+      <c r="A6647" s="10"/>
       <c r="B6647" s="2"/>
-      <c r="C6647" s="7"/>
+      <c r="C6647" s="6"/>
     </row>
     <row r="6648">
-      <c r="A6648" s="6"/>
+      <c r="A6648" s="10"/>
       <c r="B6648" s="2"/>
-      <c r="C6648" s="7"/>
+      <c r="C6648" s="6"/>
     </row>
     <row r="6649">
-      <c r="A6649" s="6"/>
+      <c r="A6649" s="10"/>
       <c r="B6649" s="2"/>
-      <c r="C6649" s="7"/>
+      <c r="C6649" s="6"/>
     </row>
     <row r="6650">
-      <c r="A6650" s="6"/>
+      <c r="A6650" s="10"/>
       <c r="B6650" s="2"/>
-      <c r="C6650" s="7"/>
+      <c r="C6650" s="6"/>
     </row>
     <row r="6651">
-      <c r="A6651" s="6"/>
+      <c r="A6651" s="10"/>
       <c r="B6651" s="2"/>
-      <c r="C6651" s="7"/>
+      <c r="C6651" s="6"/>
     </row>
     <row r="6652">
-      <c r="A6652" s="6"/>
+      <c r="A6652" s="10"/>
       <c r="B6652" s="2"/>
-      <c r="C6652" s="7"/>
+      <c r="C6652" s="6"/>
     </row>
     <row r="6653">
-      <c r="A6653" s="6"/>
+      <c r="A6653" s="10"/>
       <c r="B6653" s="2"/>
-      <c r="C6653" s="7"/>
+      <c r="C6653" s="6"/>
     </row>
     <row r="6654">
-      <c r="A6654" s="6"/>
+      <c r="A6654" s="10"/>
       <c r="B6654" s="2"/>
-      <c r="C6654" s="7"/>
+      <c r="C6654" s="6"/>
     </row>
     <row r="6655">
-      <c r="A6655" s="6"/>
+      <c r="A6655" s="10"/>
       <c r="B6655" s="2"/>
-      <c r="C6655" s="7"/>
+      <c r="C6655" s="6"/>
     </row>
     <row r="6656">
-      <c r="A6656" s="6"/>
+      <c r="A6656" s="10"/>
       <c r="B6656" s="2"/>
-      <c r="C6656" s="7"/>
+      <c r="C6656" s="6"/>
     </row>
     <row r="6657">
-      <c r="A6657" s="6"/>
+      <c r="A6657" s="10"/>
       <c r="B6657" s="2"/>
-      <c r="C6657" s="7"/>
+      <c r="C6657" s="6"/>
     </row>
     <row r="6658">
-      <c r="A6658" s="6"/>
+      <c r="A6658" s="10"/>
       <c r="B6658" s="2"/>
-      <c r="C6658" s="7"/>
+      <c r="C6658" s="6"/>
     </row>
     <row r="6659">
-      <c r="A6659" s="6"/>
+      <c r="A6659" s="10"/>
       <c r="B6659" s="2"/>
-      <c r="C6659" s="7"/>
+      <c r="C6659" s="6"/>
     </row>
     <row r="6660">
-      <c r="A6660" s="6"/>
+      <c r="A6660" s="10"/>
       <c r="B6660" s="2"/>
-      <c r="C6660" s="7"/>
+      <c r="C6660" s="6"/>
     </row>
     <row r="6661">
-      <c r="A6661" s="6"/>
+      <c r="A6661" s="10"/>
       <c r="B6661" s="2"/>
-      <c r="C6661" s="7"/>
+      <c r="C6661" s="6"/>
     </row>
     <row r="6662">
-      <c r="A6662" s="6"/>
+      <c r="A6662" s="10"/>
       <c r="B6662" s="2"/>
-      <c r="C6662" s="7"/>
+      <c r="C6662" s="6"/>
     </row>
     <row r="6663">
-      <c r="A6663" s="6"/>
+      <c r="A6663" s="10"/>
       <c r="B6663" s="2"/>
-      <c r="C6663" s="7"/>
+      <c r="C6663" s="6"/>
     </row>
     <row r="6664">
-      <c r="A6664" s="6"/>
+      <c r="A6664" s="10"/>
       <c r="B6664" s="2"/>
-      <c r="C6664" s="7"/>
+      <c r="C6664" s="6"/>
     </row>
     <row r="6665">
-      <c r="A6665" s="6"/>
+      <c r="A6665" s="10"/>
       <c r="B6665" s="2"/>
-      <c r="C6665" s="7"/>
+      <c r="C6665" s="6"/>
     </row>
     <row r="6666">
-      <c r="A6666" s="6"/>
+      <c r="A6666" s="10"/>
       <c r="B6666" s="2"/>
-      <c r="C6666" s="7"/>
+      <c r="C6666" s="6"/>
     </row>
     <row r="6667">
-      <c r="A6667" s="6"/>
+      <c r="A6667" s="10"/>
       <c r="B6667" s="2"/>
-      <c r="C6667" s="7"/>
+      <c r="C6667" s="6"/>
     </row>
     <row r="6668">
-      <c r="A6668" s="6"/>
+      <c r="A6668" s="10"/>
       <c r="B6668" s="2"/>
-      <c r="C6668" s="7"/>
+      <c r="C6668" s="6"/>
     </row>
     <row r="6669">
-      <c r="A6669" s="6"/>
+      <c r="A6669" s="10"/>
       <c r="B6669" s="2"/>
-      <c r="C6669" s="7"/>
+      <c r="C6669" s="6"/>
     </row>
     <row r="6670">
-      <c r="A6670" s="6"/>
+      <c r="A6670" s="10"/>
       <c r="B6670" s="2"/>
-      <c r="C6670" s="7"/>
+      <c r="C6670" s="6"/>
     </row>
     <row r="6671">
-      <c r="A6671" s="6"/>
+      <c r="A6671" s="10"/>
       <c r="B6671" s="2"/>
-      <c r="C6671" s="7"/>
+      <c r="C6671" s="6"/>
     </row>
     <row r="6672">
-      <c r="A6672" s="6"/>
+      <c r="A6672" s="10"/>
       <c r="B6672" s="2"/>
-      <c r="C6672" s="7"/>
+      <c r="C6672" s="6"/>
     </row>
     <row r="6673">
-      <c r="A6673" s="6"/>
+      <c r="A6673" s="10"/>
       <c r="B6673" s="2"/>
-      <c r="C6673" s="7"/>
+      <c r="C6673" s="6"/>
     </row>
     <row r="6674">
-      <c r="A6674" s="6"/>
+      <c r="A6674" s="10"/>
       <c r="B6674" s="2"/>
-      <c r="C6674" s="7"/>
+      <c r="C6674" s="6"/>
     </row>
     <row r="6675">
-      <c r="A6675" s="6"/>
+      <c r="A6675" s="10"/>
       <c r="B6675" s="2"/>
-      <c r="C6675" s="7"/>
+      <c r="C6675" s="6"/>
     </row>
     <row r="6676">
-      <c r="A6676" s="6"/>
+      <c r="A6676" s="10"/>
       <c r="B6676" s="2"/>
-      <c r="C6676" s="7"/>
+      <c r="C6676" s="6"/>
     </row>
     <row r="6677">
-      <c r="A6677" s="6"/>
+      <c r="A6677" s="10"/>
       <c r="B6677" s="2"/>
-      <c r="C6677" s="7"/>
+      <c r="C6677" s="6"/>
     </row>
     <row r="6678">
-      <c r="A6678" s="6"/>
+      <c r="A6678" s="10"/>
       <c r="B6678" s="2"/>
-      <c r="C6678" s="7"/>
+      <c r="C6678" s="6"/>
     </row>
     <row r="6679">
-      <c r="A6679" s="6"/>
+      <c r="A6679" s="10"/>
       <c r="B6679" s="2"/>
-      <c r="C6679" s="7"/>
+      <c r="C6679" s="6"/>
     </row>
     <row r="6680">
-      <c r="A6680" s="6"/>
+      <c r="A6680" s="10"/>
       <c r="B6680" s="2"/>
-      <c r="C6680" s="7"/>
+      <c r="C6680" s="6"/>
     </row>
     <row r="6681">
-      <c r="A6681" s="6"/>
+      <c r="A6681" s="10"/>
       <c r="B6681" s="2"/>
-      <c r="C6681" s="7"/>
+      <c r="C6681" s="6"/>
     </row>
     <row r="6682">
-      <c r="A6682" s="6"/>
+      <c r="A6682" s="10"/>
       <c r="B6682" s="2"/>
-      <c r="C6682" s="7"/>
+      <c r="C6682" s="6"/>
     </row>
     <row r="6683">
-      <c r="A6683" s="6"/>
+      <c r="A6683" s="10"/>
       <c r="B6683" s="2"/>
-      <c r="C6683" s="7"/>
+      <c r="C6683" s="6"/>
     </row>
     <row r="6684">
-      <c r="A6684" s="6"/>
+      <c r="A6684" s="10"/>
       <c r="B6684" s="2"/>
-      <c r="C6684" s="7"/>
+      <c r="C6684" s="6"/>
     </row>
     <row r="6685">
-      <c r="A6685" s="6"/>
+      <c r="A6685" s="10"/>
       <c r="B6685" s="2"/>
-      <c r="C6685" s="7"/>
+      <c r="C6685" s="6"/>
     </row>
     <row r="6686">
-      <c r="A6686" s="6"/>
+      <c r="A6686" s="10"/>
       <c r="B6686" s="2"/>
-      <c r="C6686" s="7"/>
+      <c r="C6686" s="6"/>
     </row>
     <row r="6687">
-      <c r="A6687" s="6"/>
+      <c r="A6687" s="10"/>
       <c r="B6687" s="2"/>
-      <c r="C6687" s="7"/>
+      <c r="C6687" s="6"/>
     </row>
     <row r="6688">
-      <c r="A6688" s="6"/>
+      <c r="A6688" s="10"/>
       <c r="B6688" s="2"/>
-      <c r="C6688" s="7"/>
+      <c r="C6688" s="6"/>
     </row>
     <row r="6689">
-      <c r="A6689" s="6"/>
+      <c r="A6689" s="10"/>
       <c r="B6689" s="2"/>
-      <c r="C6689" s="7"/>
+      <c r="C6689" s="6"/>
     </row>
     <row r="6690">
-      <c r="A6690" s="6"/>
+      <c r="A6690" s="10"/>
       <c r="B6690" s="2"/>
-      <c r="C6690" s="7"/>
+      <c r="C6690" s="6"/>
     </row>
     <row r="6691">
-      <c r="A6691" s="6"/>
+      <c r="A6691" s="10"/>
       <c r="B6691" s="2"/>
-      <c r="C6691" s="7"/>
+      <c r="C6691" s="6"/>
     </row>
     <row r="6692">
-      <c r="A6692" s="6"/>
+      <c r="A6692" s="10"/>
       <c r="B6692" s="2"/>
-      <c r="C6692" s="7"/>
+      <c r="C6692" s="6"/>
     </row>
     <row r="6693">
-      <c r="A6693" s="6"/>
+      <c r="A6693" s="10"/>
       <c r="B6693" s="2"/>
-      <c r="C6693" s="7"/>
+      <c r="C6693" s="6"/>
     </row>
     <row r="6694">
-      <c r="A6694" s="6"/>
+      <c r="A6694" s="10"/>
       <c r="B6694" s="2"/>
-      <c r="C6694" s="7"/>
+      <c r="C6694" s="6"/>
     </row>
     <row r="6695">
-      <c r="A6695" s="6"/>
+      <c r="A6695" s="10"/>
       <c r="B6695" s="2"/>
-      <c r="C6695" s="7"/>
+      <c r="C6695" s="6"/>
     </row>
     <row r="6696">
-      <c r="A6696" s="6"/>
+      <c r="A6696" s="10"/>
       <c r="B6696" s="2"/>
-      <c r="C6696" s="7"/>
+      <c r="C6696" s="6"/>
     </row>
     <row r="6697">
-      <c r="A6697" s="6"/>
+      <c r="A6697" s="10"/>
       <c r="B6697" s="2"/>
-      <c r="C6697" s="7"/>
+      <c r="C6697" s="6"/>
     </row>
     <row r="6698">
-      <c r="A6698" s="6"/>
+      <c r="A6698" s="10"/>
       <c r="B6698" s="2"/>
-      <c r="C6698" s="7"/>
+      <c r="C6698" s="6"/>
     </row>
     <row r="6699">
-      <c r="A6699" s="6"/>
+      <c r="A6699" s="10"/>
       <c r="B6699" s="2"/>
-      <c r="C6699" s="7"/>
+      <c r="C6699" s="6"/>
     </row>
     <row r="6700">
-      <c r="A6700" s="6"/>
+      <c r="A6700" s="10"/>
       <c r="B6700" s="2"/>
-      <c r="C6700" s="7"/>
+      <c r="C6700" s="6"/>
     </row>
     <row r="6701">
-      <c r="A6701" s="6"/>
+      <c r="A6701" s="10"/>
       <c r="B6701" s="2"/>
-      <c r="C6701" s="7"/>
+      <c r="C6701" s="6"/>
     </row>
     <row r="6702">
-      <c r="A6702" s="6"/>
+      <c r="A6702" s="10"/>
       <c r="B6702" s="2"/>
-      <c r="C6702" s="7"/>
+      <c r="C6702" s="6"/>
     </row>
     <row r="6703">
-      <c r="A6703" s="6"/>
+      <c r="A6703" s="10"/>
       <c r="B6703" s="2"/>
-      <c r="C6703" s="7"/>
+      <c r="C6703" s="6"/>
     </row>
     <row r="6704">
-      <c r="A6704" s="6"/>
+      <c r="A6704" s="10"/>
       <c r="B6704" s="2"/>
-      <c r="C6704" s="7"/>
+      <c r="C6704" s="6"/>
     </row>
     <row r="6705">
-      <c r="A6705" s="6"/>
+      <c r="A6705" s="10"/>
       <c r="B6705" s="2"/>
-      <c r="C6705" s="7"/>
+      <c r="C6705" s="6"/>
     </row>
     <row r="6706">
-      <c r="A6706" s="6"/>
+      <c r="A6706" s="10"/>
       <c r="B6706" s="2"/>
-      <c r="C6706" s="7"/>
+      <c r="C6706" s="6"/>
     </row>
     <row r="6707">
-      <c r="A6707" s="6"/>
+      <c r="A6707" s="10"/>
       <c r="B6707" s="2"/>
-      <c r="C6707" s="7"/>
+      <c r="C6707" s="6"/>
     </row>
     <row r="6708">
-      <c r="A6708" s="6"/>
+      <c r="A6708" s="10"/>
       <c r="B6708" s="2"/>
-      <c r="C6708" s="7"/>
+      <c r="C6708" s="6"/>
     </row>
     <row r="6709">
-      <c r="A6709" s="6"/>
+      <c r="A6709" s="10"/>
       <c r="B6709" s="2"/>
-      <c r="C6709" s="7"/>
+      <c r="C6709" s="6"/>
     </row>
     <row r="6710">
-      <c r="A6710" s="6"/>
+      <c r="A6710" s="10"/>
       <c r="B6710" s="2"/>
-      <c r="C6710" s="7"/>
+      <c r="C6710" s="6"/>
     </row>
     <row r="6711">
-      <c r="A6711" s="6"/>
+      <c r="A6711" s="10"/>
       <c r="B6711" s="2"/>
-      <c r="C6711" s="7"/>
+      <c r="C6711" s="6"/>
     </row>
     <row r="6712">
-      <c r="A6712" s="6"/>
+      <c r="A6712" s="10"/>
       <c r="B6712" s="2"/>
-      <c r="C6712" s="7"/>
+      <c r="C6712" s="6"/>
     </row>
     <row r="6713">
-      <c r="A6713" s="6"/>
+      <c r="A6713" s="10"/>
       <c r="B6713" s="2"/>
-      <c r="C6713" s="7"/>
+      <c r="C6713" s="6"/>
     </row>
     <row r="6714">
-      <c r="A6714" s="6"/>
+      <c r="A6714" s="10"/>
       <c r="B6714" s="2"/>
-      <c r="C6714" s="7"/>
+      <c r="C6714" s="6"/>
     </row>
     <row r="6715">
-      <c r="A6715" s="6"/>
+      <c r="A6715" s="10"/>
       <c r="B6715" s="2"/>
-      <c r="C6715" s="7"/>
+      <c r="C6715" s="6"/>
     </row>
     <row r="6716">
-      <c r="A6716" s="6"/>
+      <c r="A6716" s="10"/>
       <c r="B6716" s="2"/>
-      <c r="C6716" s="7"/>
+      <c r="C6716" s="6"/>
     </row>
     <row r="6717">
-      <c r="A6717" s="6"/>
+      <c r="A6717" s="10"/>
       <c r="B6717" s="2"/>
-      <c r="C6717" s="7"/>
+      <c r="C6717" s="6"/>
     </row>
     <row r="6718">
-      <c r="A6718" s="6"/>
+      <c r="A6718" s="10"/>
       <c r="B6718" s="2"/>
-      <c r="C6718" s="7"/>
+      <c r="C6718" s="6"/>
     </row>
     <row r="6719">
-      <c r="A6719" s="6"/>
+      <c r="A6719" s="10"/>
       <c r="B6719" s="2"/>
-      <c r="C6719" s="7"/>
+      <c r="C6719" s="6"/>
     </row>
     <row r="6720">
-      <c r="A6720" s="6"/>
+      <c r="A6720" s="10"/>
       <c r="B6720" s="2"/>
-      <c r="C6720" s="7"/>
+      <c r="C6720" s="6"/>
     </row>
     <row r="6721">
-      <c r="A6721" s="6"/>
+      <c r="A6721" s="10"/>
       <c r="B6721" s="2"/>
-      <c r="C6721" s="7"/>
+      <c r="C6721" s="6"/>
     </row>
     <row r="6722">
-      <c r="A6722" s="6"/>
+      <c r="A6722" s="10"/>
       <c r="B6722" s="2"/>
-      <c r="C6722" s="7"/>
+      <c r="C6722" s="6"/>
     </row>
     <row r="6723">
-      <c r="A6723" s="6"/>
+      <c r="A6723" s="10"/>
       <c r="B6723" s="2"/>
-      <c r="C6723" s="7"/>
+      <c r="C6723" s="6"/>
     </row>
     <row r="6724">
-      <c r="A6724" s="6"/>
+      <c r="A6724" s="10"/>
       <c r="B6724" s="2"/>
-      <c r="C6724" s="7"/>
+      <c r="C6724" s="6"/>
     </row>
     <row r="6725">
-      <c r="A6725" s="6"/>
+      <c r="A6725" s="10"/>
       <c r="B6725" s="2"/>
-      <c r="C6725" s="7"/>
+      <c r="C6725" s="6"/>
     </row>
     <row r="6726">
-      <c r="A6726" s="6"/>
+      <c r="A6726" s="10"/>
       <c r="B6726" s="2"/>
-      <c r="C6726" s="7"/>
+      <c r="C6726" s="6"/>
     </row>
     <row r="6727">
-      <c r="A6727" s="6"/>
+      <c r="A6727" s="10"/>
       <c r="B6727" s="2"/>
-      <c r="C6727" s="7"/>
+      <c r="C6727" s="6"/>
     </row>
     <row r="6728">
-      <c r="A6728" s="6"/>
+      <c r="A6728" s="10"/>
       <c r="B6728" s="2"/>
-      <c r="C6728" s="7"/>
+      <c r="C6728" s="6"/>
     </row>
     <row r="6729">
-      <c r="A6729" s="6"/>
+      <c r="A6729" s="10"/>
       <c r="B6729" s="2"/>
-      <c r="C6729" s="7"/>
+      <c r="C6729" s="6"/>
     </row>
     <row r="6730">
-      <c r="A6730" s="6"/>
+      <c r="A6730" s="10"/>
       <c r="B6730" s="2"/>
-      <c r="C6730" s="7"/>
+      <c r="C6730" s="6"/>
     </row>
     <row r="6731">
-      <c r="A6731" s="6"/>
+      <c r="A6731" s="10"/>
       <c r="B6731" s="2"/>
-      <c r="C6731" s="7"/>
+      <c r="C6731" s="6"/>
     </row>
     <row r="6732">
-      <c r="A6732" s="6"/>
+      <c r="A6732" s="10"/>
       <c r="B6732" s="2"/>
-      <c r="C6732" s="7"/>
+      <c r="C6732" s="6"/>
     </row>
     <row r="6733">
-      <c r="A6733" s="6"/>
+      <c r="A6733" s="10"/>
       <c r="B6733" s="2"/>
-      <c r="C6733" s="7"/>
+      <c r="C6733" s="6"/>
     </row>
     <row r="6734">
-      <c r="A6734" s="6"/>
+      <c r="A6734" s="10"/>
       <c r="B6734" s="2"/>
-      <c r="C6734" s="7"/>
+      <c r="C6734" s="6"/>
     </row>
     <row r="6735">
-      <c r="A6735" s="6"/>
+      <c r="A6735" s="10"/>
       <c r="B6735" s="2"/>
-      <c r="C6735" s="7"/>
+      <c r="C6735" s="6"/>
     </row>
     <row r="6736">
-      <c r="A6736" s="6"/>
+      <c r="A6736" s="10"/>
       <c r="B6736" s="2"/>
-      <c r="C6736" s="7"/>
+      <c r="C6736" s="6"/>
     </row>
     <row r="6737">
-      <c r="A6737" s="6"/>
+      <c r="A6737" s="10"/>
       <c r="B6737" s="2"/>
-      <c r="C6737" s="7"/>
+      <c r="C6737" s="6"/>
     </row>
     <row r="6738">
-      <c r="A6738" s="6"/>
+      <c r="A6738" s="10"/>
       <c r="B6738" s="2"/>
-      <c r="C6738" s="7"/>
+      <c r="C6738" s="6"/>
     </row>
     <row r="6739">
-      <c r="A6739" s="6"/>
+      <c r="A6739" s="10"/>
       <c r="B6739" s="2"/>
-      <c r="C6739" s="7"/>
+      <c r="C6739" s="6"/>
     </row>
     <row r="6740">
-      <c r="A6740" s="6"/>
+      <c r="A6740" s="10"/>
       <c r="B6740" s="2"/>
-      <c r="C6740" s="7"/>
+      <c r="C6740" s="6"/>
     </row>
     <row r="6741">
-      <c r="A6741" s="6"/>
+      <c r="A6741" s="10"/>
       <c r="B6741" s="2"/>
-      <c r="C6741" s="7"/>
+      <c r="C6741" s="6"/>
     </row>
     <row r="6742">
-      <c r="A6742" s="6"/>
+      <c r="A6742" s="10"/>
       <c r="B6742" s="2"/>
-      <c r="C6742" s="7"/>
+      <c r="C6742" s="6"/>
     </row>
     <row r="6743">
-      <c r="A6743" s="6"/>
+      <c r="A6743" s="10"/>
       <c r="B6743" s="2"/>
-      <c r="C6743" s="7"/>
+      <c r="C6743" s="6"/>
     </row>
     <row r="6744">
-      <c r="A6744" s="6"/>
+      <c r="A6744" s="10"/>
       <c r="B6744" s="2"/>
-      <c r="C6744" s="7"/>
+      <c r="C6744" s="6"/>
     </row>
     <row r="6745">
-      <c r="A6745" s="6"/>
+      <c r="A6745" s="10"/>
       <c r="B6745" s="2"/>
-      <c r="C6745" s="7"/>
+      <c r="C6745" s="6"/>
     </row>
     <row r="6746">
-      <c r="A6746" s="6"/>
+      <c r="A6746" s="10"/>
       <c r="B6746" s="2"/>
-      <c r="C6746" s="7"/>
+      <c r="C6746" s="6"/>
     </row>
     <row r="6747">
-      <c r="A6747" s="6"/>
+      <c r="A6747" s="10"/>
       <c r="B6747" s="2"/>
-      <c r="C6747" s="7"/>
+      <c r="C6747" s="6"/>
     </row>
     <row r="6748">
-      <c r="A6748" s="6"/>
+      <c r="A6748" s="10"/>
       <c r="B6748" s="2"/>
-      <c r="C6748" s="7"/>
+      <c r="C6748" s="6"/>
     </row>
     <row r="6749">
-      <c r="A6749" s="6"/>
+      <c r="A6749" s="10"/>
       <c r="B6749" s="2"/>
-      <c r="C6749" s="7"/>
+      <c r="C6749" s="6"/>
     </row>
     <row r="6750">
-      <c r="A6750" s="6"/>
+      <c r="A6750" s="10"/>
       <c r="B6750" s="2"/>
-      <c r="C6750" s="7"/>
+      <c r="C6750" s="6"/>
     </row>
     <row r="6751">
-      <c r="A6751" s="6"/>
+      <c r="A6751" s="10"/>
       <c r="B6751" s="2"/>
-      <c r="C6751" s="7"/>
+      <c r="C6751" s="6"/>
     </row>
     <row r="6752">
-      <c r="A6752" s="6"/>
+      <c r="A6752" s="10"/>
       <c r="B6752" s="2"/>
-      <c r="C6752" s="7"/>
+      <c r="C6752" s="6"/>
     </row>
     <row r="6753">
-      <c r="A6753" s="6"/>
+      <c r="A6753" s="10"/>
       <c r="B6753" s="2"/>
-      <c r="C6753" s="7"/>
+      <c r="C6753" s="6"/>
     </row>
     <row r="6754">
-      <c r="A6754" s="6"/>
+      <c r="A6754" s="10"/>
       <c r="B6754" s="2"/>
-      <c r="C6754" s="7"/>
+      <c r="C6754" s="6"/>
     </row>
     <row r="6755">
-      <c r="A6755" s="6"/>
+      <c r="A6755" s="10"/>
       <c r="B6755" s="2"/>
-      <c r="C6755" s="7"/>
+      <c r="C6755" s="6"/>
     </row>
     <row r="6756">
-      <c r="A6756" s="6"/>
+      <c r="A6756" s="10"/>
       <c r="B6756" s="2"/>
-      <c r="C6756" s="7"/>
+      <c r="C6756" s="6"/>
     </row>
     <row r="6757">
-      <c r="A6757" s="6"/>
+      <c r="A6757" s="10"/>
       <c r="B6757" s="2"/>
-      <c r="C6757" s="7"/>
+      <c r="C6757" s="6"/>
     </row>
     <row r="6758">
-      <c r="A6758" s="6"/>
+      <c r="A6758" s="10"/>
       <c r="B6758" s="2"/>
-      <c r="C6758" s="7"/>
+      <c r="C6758" s="6"/>
     </row>
     <row r="6759">
-      <c r="A6759" s="6"/>
+      <c r="A6759" s="10"/>
       <c r="B6759" s="2"/>
-      <c r="C6759" s="7"/>
+      <c r="C6759" s="6"/>
     </row>
     <row r="6760">
-      <c r="A6760" s="6"/>
+      <c r="A6760" s="10"/>
       <c r="B6760" s="2"/>
-      <c r="C6760" s="7"/>
+      <c r="C6760" s="6"/>
     </row>
     <row r="6761">
-      <c r="A6761" s="6"/>
+      <c r="A6761" s="10"/>
       <c r="B6761" s="2"/>
-      <c r="C6761" s="7"/>
+      <c r="C6761" s="6"/>
     </row>
     <row r="6762">
-      <c r="A6762" s="6"/>
+      <c r="A6762" s="10"/>
       <c r="B6762" s="2"/>
-      <c r="C6762" s="7"/>
+      <c r="C6762" s="6"/>
     </row>
     <row r="6763">
-      <c r="A6763" s="6"/>
+      <c r="A6763" s="10"/>
       <c r="B6763" s="2"/>
-      <c r="C6763" s="7"/>
+      <c r="C6763" s="6"/>
     </row>
     <row r="6764">
-      <c r="A6764" s="6"/>
+      <c r="A6764" s="10"/>
       <c r="B6764" s="2"/>
-      <c r="C6764" s="7"/>
+      <c r="C6764" s="6"/>
     </row>
     <row r="6765">
-      <c r="A6765" s="6"/>
+      <c r="A6765" s="10"/>
       <c r="B6765" s="2"/>
-      <c r="C6765" s="7"/>
+      <c r="C6765" s="6"/>
     </row>
     <row r="6766">
-      <c r="A6766" s="6"/>
+      <c r="A6766" s="10"/>
       <c r="B6766" s="2"/>
-      <c r="C6766" s="7"/>
+      <c r="C6766" s="6"/>
     </row>
     <row r="6767">
-      <c r="A6767" s="6"/>
+      <c r="A6767" s="10"/>
       <c r="B6767" s="2"/>
-      <c r="C6767" s="7"/>
+      <c r="C6767" s="6"/>
     </row>
     <row r="6768">
-      <c r="A6768" s="6"/>
+      <c r="A6768" s="10"/>
       <c r="B6768" s="2"/>
-      <c r="C6768" s="7"/>
+      <c r="C6768" s="6"/>
     </row>
     <row r="6769">
-      <c r="A6769" s="6"/>
+      <c r="A6769" s="10"/>
       <c r="B6769" s="2"/>
-      <c r="C6769" s="7"/>
+      <c r="C6769" s="6"/>
     </row>
     <row r="6770">
-      <c r="A6770" s="6"/>
+      <c r="A6770" s="10"/>
       <c r="B6770" s="2"/>
-      <c r="C6770" s="7"/>
+      <c r="C6770" s="6"/>
     </row>
     <row r="6771">
-      <c r="A6771" s="6"/>
+      <c r="A6771" s="10"/>
       <c r="B6771" s="2"/>
-      <c r="C6771" s="7"/>
+      <c r="C6771" s="6"/>
     </row>
     <row r="6772">
-      <c r="A6772" s="6"/>
+      <c r="A6772" s="10"/>
       <c r="B6772" s="2"/>
-      <c r="C6772" s="7"/>
+      <c r="C6772" s="6"/>
     </row>
     <row r="6773">
-      <c r="A6773" s="6"/>
+      <c r="A6773" s="10"/>
       <c r="B6773" s="2"/>
-      <c r="C6773" s="7"/>
+      <c r="C6773" s="6"/>
     </row>
     <row r="6774">
-      <c r="A6774" s="6"/>
+      <c r="A6774" s="10"/>
       <c r="B6774" s="2"/>
-      <c r="C6774" s="7"/>
+      <c r="C6774" s="6"/>
     </row>
     <row r="6775">
-      <c r="A6775" s="6"/>
+      <c r="A6775" s="10"/>
       <c r="B6775" s="2"/>
-      <c r="C6775" s="7"/>
+      <c r="C6775" s="6"/>
     </row>
     <row r="6776">
-      <c r="A6776" s="6"/>
+      <c r="A6776" s="10"/>
       <c r="B6776" s="2"/>
-      <c r="C6776" s="7"/>
+      <c r="C6776" s="6"/>
     </row>
     <row r="6777">
-      <c r="A6777" s="6"/>
+      <c r="A6777" s="10"/>
       <c r="B6777" s="2"/>
-      <c r="C6777" s="7"/>
+      <c r="C6777" s="6"/>
     </row>
     <row r="6778">
-      <c r="A6778" s="6"/>
+      <c r="A6778" s="10"/>
       <c r="B6778" s="2"/>
-      <c r="C6778" s="7"/>
+      <c r="C6778" s="6"/>
     </row>
     <row r="6779">
-      <c r="A6779" s="6"/>
+      <c r="A6779" s="10"/>
       <c r="B6779" s="2"/>
-      <c r="C6779" s="7"/>
+      <c r="C6779" s="6"/>
     </row>
     <row r="6780">
-      <c r="A6780" s="6"/>
+      <c r="A6780" s="10"/>
       <c r="B6780" s="2"/>
-      <c r="C6780" s="7"/>
+      <c r="C6780" s="6"/>
     </row>
     <row r="6781">
-      <c r="A6781" s="6"/>
+      <c r="A6781" s="10"/>
       <c r="B6781" s="2"/>
-      <c r="C6781" s="7"/>
+      <c r="C6781" s="6"/>
     </row>
     <row r="6782">
-      <c r="A6782" s="6"/>
+      <c r="A6782" s="10"/>
       <c r="B6782" s="2"/>
-      <c r="C6782" s="7"/>
+      <c r="C6782" s="6"/>
     </row>
     <row r="6783">
-      <c r="A6783" s="6"/>
+      <c r="A6783" s="10"/>
       <c r="B6783" s="2"/>
-      <c r="C6783" s="7"/>
+      <c r="C6783" s="6"/>
     </row>
     <row r="6784">
-      <c r="A6784" s="6"/>
+      <c r="A6784" s="10"/>
       <c r="B6784" s="2"/>
-      <c r="C6784" s="7"/>
+      <c r="C6784" s="6"/>
     </row>
     <row r="6785">
-      <c r="A6785" s="6"/>
+      <c r="A6785" s="10"/>
       <c r="B6785" s="2"/>
-      <c r="C6785" s="7"/>
+      <c r="C6785" s="6"/>
     </row>
     <row r="6786">
-      <c r="A6786" s="6"/>
+      <c r="A6786" s="10"/>
       <c r="B6786" s="2"/>
-      <c r="C6786" s="7"/>
+      <c r="C6786" s="6"/>
     </row>
     <row r="6787">
-      <c r="A6787" s="6"/>
+      <c r="A6787" s="10"/>
       <c r="B6787" s="2"/>
-      <c r="C6787" s="7"/>
+      <c r="C6787" s="6"/>
     </row>
     <row r="6788">
-      <c r="A6788" s="6"/>
+      <c r="A6788" s="10"/>
       <c r="B6788" s="2"/>
-      <c r="C6788" s="7"/>
+      <c r="C6788" s="6"/>
     </row>
     <row r="6789">
-      <c r="A6789" s="6"/>
+      <c r="A6789" s="10"/>
       <c r="B6789" s="2"/>
-      <c r="C6789" s="7"/>
+      <c r="C6789" s="6"/>
     </row>
     <row r="6790">
-      <c r="A6790" s="6"/>
+      <c r="A6790" s="10"/>
       <c r="B6790" s="2"/>
-      <c r="C6790" s="7"/>
+      <c r="C6790" s="6"/>
     </row>
     <row r="6791">
-      <c r="A6791" s="6"/>
+      <c r="A6791" s="10"/>
       <c r="B6791" s="2"/>
-      <c r="C6791" s="7"/>
+      <c r="C6791" s="6"/>
     </row>
     <row r="6792">
-      <c r="A6792" s="6"/>
+      <c r="A6792" s="10"/>
       <c r="B6792" s="2"/>
-      <c r="C6792" s="7"/>
+      <c r="C6792" s="6"/>
     </row>
     <row r="6793">
-      <c r="A6793" s="6"/>
+      <c r="A6793" s="10"/>
       <c r="B6793" s="2"/>
-      <c r="C6793" s="7"/>
+      <c r="C6793" s="6"/>
     </row>
     <row r="6794">
-      <c r="A6794" s="6"/>
+      <c r="A6794" s="10"/>
       <c r="B6794" s="2"/>
-      <c r="C6794" s="7"/>
+      <c r="C6794" s="6"/>
     </row>
     <row r="6795">
-      <c r="A6795" s="6"/>
+      <c r="A6795" s="10"/>
       <c r="B6795" s="2"/>
-      <c r="C6795" s="7"/>
+      <c r="C6795" s="6"/>
     </row>
     <row r="6796">
-      <c r="A6796" s="6"/>
+      <c r="A6796" s="10"/>
       <c r="B6796" s="2"/>
-      <c r="C6796" s="7"/>
+      <c r="C6796" s="6"/>
     </row>
     <row r="6797">
-      <c r="A6797" s="6"/>
+      <c r="A6797" s="10"/>
       <c r="B6797" s="2"/>
-      <c r="C6797" s="7"/>
+      <c r="C6797" s="6"/>
     </row>
     <row r="6798">
-      <c r="A6798" s="6"/>
+      <c r="A6798" s="10"/>
       <c r="B6798" s="2"/>
-      <c r="C6798" s="7"/>
+      <c r="C6798" s="6"/>
     </row>
     <row r="6799">
-      <c r="A6799" s="6"/>
+      <c r="A6799" s="10"/>
       <c r="B6799" s="2"/>
-      <c r="C6799" s="7"/>
+      <c r="C6799" s="6"/>
     </row>
     <row r="6800">
-      <c r="A6800" s="6"/>
+      <c r="A6800" s="10"/>
       <c r="B6800" s="2"/>
-      <c r="C6800" s="7"/>
+      <c r="C6800" s="6"/>
     </row>
     <row r="6801">
-      <c r="A6801" s="6"/>
+      <c r="A6801" s="10"/>
       <c r="B6801" s="2"/>
-      <c r="C6801" s="7"/>
+      <c r="C6801" s="6"/>
     </row>
     <row r="6802">
-      <c r="A6802" s="6"/>
+      <c r="A6802" s="10"/>
       <c r="B6802" s="2"/>
-      <c r="C6802" s="7"/>
+      <c r="C6802" s="6"/>
     </row>
     <row r="6803">
-      <c r="A6803" s="6"/>
+      <c r="A6803" s="10"/>
       <c r="B6803" s="2"/>
-      <c r="C6803" s="7"/>
+      <c r="C6803" s="6"/>
     </row>
     <row r="6804">
-      <c r="A6804" s="6"/>
+      <c r="A6804" s="10"/>
       <c r="B6804" s="2"/>
-      <c r="C6804" s="7"/>
+      <c r="C6804" s="6"/>
     </row>
     <row r="6805">
-      <c r="A6805" s="6"/>
+      <c r="A6805" s="10"/>
       <c r="B6805" s="2"/>
-      <c r="C6805" s="7"/>
+      <c r="C6805" s="6"/>
     </row>
     <row r="6806">
-      <c r="A6806" s="6"/>
+      <c r="A6806" s="10"/>
       <c r="B6806" s="2"/>
-      <c r="C6806" s="7"/>
+      <c r="C6806" s="6"/>
     </row>
     <row r="6807">
-      <c r="A6807" s="6"/>
+      <c r="A6807" s="10"/>
       <c r="B6807" s="2"/>
-      <c r="C6807" s="7"/>
+      <c r="C6807" s="6"/>
     </row>
     <row r="6808">
-      <c r="A6808" s="6"/>
+      <c r="A6808" s="10"/>
       <c r="B6808" s="2"/>
-      <c r="C6808" s="7"/>
+      <c r="C6808" s="6"/>
     </row>
     <row r="6809">
-      <c r="A6809" s="6"/>
+      <c r="A6809" s="10"/>
       <c r="B6809" s="2"/>
-      <c r="C6809" s="7"/>
+      <c r="C6809" s="6"/>
     </row>
     <row r="6810">
-      <c r="A6810" s="6"/>
+      <c r="A6810" s="10"/>
       <c r="B6810" s="2"/>
-      <c r="C6810" s="7"/>
+      <c r="C6810" s="6"/>
     </row>
     <row r="6811">
-      <c r="A6811" s="6"/>
+      <c r="A6811" s="10"/>
       <c r="B6811" s="2"/>
-      <c r="C6811" s="7"/>
+      <c r="C6811" s="6"/>
     </row>
     <row r="6812">
-      <c r="A6812" s="6"/>
+      <c r="A6812" s="10"/>
       <c r="B6812" s="2"/>
-      <c r="C6812" s="7"/>
+      <c r="C6812" s="6"/>
     </row>
     <row r="6813">
-      <c r="A6813" s="6"/>
+      <c r="A6813" s="10"/>
       <c r="B6813" s="2"/>
-      <c r="C6813" s="7"/>
+      <c r="C6813" s="6"/>
     </row>
     <row r="6814">
-      <c r="A6814" s="6"/>
+      <c r="A6814" s="10"/>
       <c r="B6814" s="2"/>
-      <c r="C6814" s="7"/>
+      <c r="C6814" s="6"/>
     </row>
     <row r="6815">
-      <c r="A6815" s="6"/>
+      <c r="A6815" s="10"/>
       <c r="B6815" s="2"/>
-      <c r="C6815" s="7"/>
+      <c r="C6815" s="6"/>
     </row>
     <row r="6816">
-      <c r="A6816" s="6"/>
+      <c r="A6816" s="10"/>
       <c r="B6816" s="2"/>
-      <c r="C6816" s="7"/>
+      <c r="C6816" s="6"/>
     </row>
     <row r="6817">
-      <c r="A6817" s="6"/>
+      <c r="A6817" s="10"/>
       <c r="B6817" s="2"/>
-      <c r="C6817" s="7"/>
+      <c r="C6817" s="6"/>
     </row>
     <row r="6818">
-      <c r="A6818" s="6"/>
+      <c r="A6818" s="10"/>
       <c r="B6818" s="2"/>
-      <c r="C6818" s="7"/>
+      <c r="C6818" s="6"/>
     </row>
     <row r="6819">
-      <c r="A6819" s="6"/>
+      <c r="A6819" s="10"/>
       <c r="B6819" s="2"/>
-      <c r="C6819" s="7"/>
+      <c r="C6819" s="6"/>
     </row>
     <row r="6820">
-      <c r="A6820" s="6"/>
+      <c r="A6820" s="10"/>
       <c r="B6820" s="2"/>
-      <c r="C6820" s="7"/>
+      <c r="C6820" s="6"/>
     </row>
     <row r="6821">
-      <c r="A6821" s="6"/>
+      <c r="A6821" s="10"/>
       <c r="B6821" s="2"/>
-      <c r="C6821" s="7"/>
+      <c r="C6821" s="6"/>
     </row>
     <row r="6822">
-      <c r="A6822" s="6"/>
+      <c r="A6822" s="10"/>
       <c r="B6822" s="2"/>
-      <c r="C6822" s="7"/>
+      <c r="C6822" s="6"/>
     </row>
     <row r="6823">
-      <c r="A6823" s="6"/>
+      <c r="A6823" s="10"/>
       <c r="B6823" s="2"/>
-      <c r="C6823" s="7"/>
+      <c r="C6823" s="6"/>
     </row>
     <row r="6824">
-      <c r="A6824" s="6"/>
+      <c r="A6824" s="10"/>
       <c r="B6824" s="2"/>
-      <c r="C6824" s="7"/>
+      <c r="C6824" s="6"/>
     </row>
     <row r="6825">
-      <c r="A6825" s="6"/>
+      <c r="A6825" s="10"/>
       <c r="B6825" s="2"/>
-      <c r="C6825" s="7"/>
+      <c r="C6825" s="6"/>
     </row>
     <row r="6826">
-      <c r="A6826" s="6"/>
+      <c r="A6826" s="10"/>
       <c r="B6826" s="2"/>
-      <c r="C6826" s="7"/>
+      <c r="C6826" s="6"/>
     </row>
     <row r="6827">
-      <c r="A6827" s="6"/>
+      <c r="A6827" s="10"/>
       <c r="B6827" s="2"/>
-      <c r="C6827" s="7"/>
+      <c r="C6827" s="6"/>
     </row>
     <row r="6828">
-      <c r="A6828" s="6"/>
+      <c r="A6828" s="10"/>
       <c r="B6828" s="2"/>
-      <c r="C6828" s="7"/>
+      <c r="C6828" s="6"/>
     </row>
     <row r="6829">
-      <c r="A6829" s="6"/>
+      <c r="A6829" s="10"/>
       <c r="B6829" s="2"/>
-      <c r="C6829" s="7"/>
+      <c r="C6829" s="6"/>
     </row>
     <row r="6830">
-      <c r="A6830" s="6"/>
+      <c r="A6830" s="10"/>
       <c r="B6830" s="2"/>
-      <c r="C6830" s="7"/>
+      <c r="C6830" s="6"/>
     </row>
     <row r="6831">
-      <c r="A6831" s="6"/>
+      <c r="A6831" s="10"/>
       <c r="B6831" s="2"/>
-      <c r="C6831" s="7"/>
+      <c r="C6831" s="6"/>
     </row>
     <row r="6832">
-      <c r="A6832" s="6"/>
+      <c r="A6832" s="10"/>
       <c r="B6832" s="2"/>
-      <c r="C6832" s="7"/>
+      <c r="C6832" s="6"/>
     </row>
     <row r="6833">
-      <c r="A6833" s="6"/>
+      <c r="A6833" s="10"/>
       <c r="B6833" s="2"/>
-      <c r="C6833" s="7"/>
+      <c r="C6833" s="6"/>
     </row>
     <row r="6834">
-      <c r="A6834" s="6"/>
+      <c r="A6834" s="10"/>
       <c r="B6834" s="2"/>
-      <c r="C6834" s="7"/>
+      <c r="C6834" s="6"/>
     </row>
     <row r="6835">
-      <c r="A6835" s="6"/>
+      <c r="A6835" s="10"/>
       <c r="B6835" s="2"/>
-      <c r="C6835" s="7"/>
+      <c r="C6835" s="6"/>
     </row>
     <row r="6836">
-      <c r="A6836" s="6"/>
+      <c r="A6836" s="10"/>
       <c r="B6836" s="2"/>
-      <c r="C6836" s="7"/>
+      <c r="C6836" s="6"/>
     </row>
     <row r="6837">
-      <c r="A6837" s="6"/>
+      <c r="A6837" s="10"/>
       <c r="B6837" s="2"/>
-      <c r="C6837" s="7"/>
+      <c r="C6837" s="6"/>
     </row>
     <row r="6838">
-      <c r="A6838" s="6"/>
+      <c r="A6838" s="10"/>
       <c r="B6838" s="2"/>
-      <c r="C6838" s="7"/>
+      <c r="C6838" s="6"/>
     </row>
     <row r="6839">
-      <c r="A6839" s="6"/>
+      <c r="A6839" s="10"/>
       <c r="B6839" s="2"/>
-      <c r="C6839" s="7"/>
+      <c r="C6839" s="6"/>
     </row>
     <row r="6840">
-      <c r="A6840" s="6"/>
+      <c r="A6840" s="10"/>
       <c r="B6840" s="2"/>
-      <c r="C6840" s="7"/>
+      <c r="C6840" s="6"/>
     </row>
     <row r="6841">
-      <c r="A6841" s="6"/>
+      <c r="A6841" s="10"/>
       <c r="B6841" s="2"/>
-      <c r="C6841" s="7"/>
+      <c r="C6841" s="6"/>
     </row>
     <row r="6842">
-      <c r="A6842" s="6"/>
+      <c r="A6842" s="10"/>
       <c r="B6842" s="2"/>
-      <c r="C6842" s="7"/>
+      <c r="C6842" s="6"/>
     </row>
     <row r="6843">
-      <c r="A6843" s="6"/>
+      <c r="A6843" s="10"/>
       <c r="B6843" s="2"/>
-      <c r="C6843" s="7"/>
+      <c r="C6843" s="6"/>
     </row>
     <row r="6844">
-      <c r="A6844" s="6"/>
+      <c r="A6844" s="10"/>
       <c r="B6844" s="2"/>
-      <c r="C6844" s="7"/>
+      <c r="C6844" s="6"/>
     </row>
     <row r="6845">
-      <c r="A6845" s="6"/>
+      <c r="A6845" s="10"/>
       <c r="B6845" s="2"/>
-      <c r="C6845" s="7"/>
+      <c r="C6845" s="6"/>
     </row>
     <row r="6846">
-      <c r="A6846" s="6"/>
+      <c r="A6846" s="10"/>
       <c r="B6846" s="2"/>
-      <c r="C6846" s="7"/>
+      <c r="C6846" s="6"/>
     </row>
     <row r="6847">
-      <c r="A6847" s="6"/>
+      <c r="A6847" s="10"/>
       <c r="B6847" s="2"/>
-      <c r="C6847" s="7"/>
+      <c r="C6847" s="6"/>
     </row>
     <row r="6848">
-      <c r="A6848" s="6"/>
+      <c r="A6848" s="10"/>
       <c r="B6848" s="2"/>
-      <c r="C6848" s="7"/>
+      <c r="C6848" s="6"/>
     </row>
     <row r="6849">
-      <c r="A6849" s="6"/>
+      <c r="A6849" s="10"/>
       <c r="B6849" s="2"/>
-      <c r="C6849" s="7"/>
+      <c r="C6849" s="6"/>
     </row>
     <row r="6850">
-      <c r="A6850" s="6"/>
+      <c r="A6850" s="10"/>
       <c r="B6850" s="2"/>
-      <c r="C6850" s="7"/>
+      <c r="C6850" s="6"/>
     </row>
     <row r="6851">
-      <c r="A6851" s="6"/>
+      <c r="A6851" s="10"/>
       <c r="B6851" s="2"/>
-      <c r="C6851" s="7"/>
+      <c r="C6851" s="6"/>
     </row>
     <row r="6852">
-      <c r="A6852" s="6"/>
+      <c r="A6852" s="10"/>
       <c r="B6852" s="2"/>
-      <c r="C6852" s="7"/>
+      <c r="C6852" s="6"/>
     </row>
     <row r="6853">
-      <c r="A6853" s="6"/>
+      <c r="A6853" s="10"/>
       <c r="B6853" s="2"/>
-      <c r="C6853" s="7"/>
+      <c r="C6853" s="6"/>
     </row>
     <row r="6854">
-      <c r="A6854" s="6"/>
+      <c r="A6854" s="10"/>
       <c r="B6854" s="2"/>
-      <c r="C6854" s="7"/>
+      <c r="C6854" s="6"/>
     </row>
     <row r="6855">
-      <c r="A6855" s="6"/>
+      <c r="A6855" s="10"/>
       <c r="B6855" s="2"/>
-      <c r="C6855" s="7"/>
+      <c r="C6855" s="6"/>
     </row>
     <row r="6856">
-      <c r="A6856" s="6"/>
+      <c r="A6856" s="10"/>
       <c r="B6856" s="2"/>
-      <c r="C6856" s="7"/>
+      <c r="C6856" s="6"/>
     </row>
     <row r="6857">
-      <c r="A6857" s="6"/>
+      <c r="A6857" s="10"/>
       <c r="B6857" s="2"/>
-      <c r="C6857" s="7"/>
+      <c r="C6857" s="6"/>
     </row>
     <row r="6858">
-      <c r="A6858" s="6"/>
+      <c r="A6858" s="10"/>
       <c r="B6858" s="2"/>
-      <c r="C6858" s="7"/>
+      <c r="C6858" s="6"/>
     </row>
     <row r="6859">
-      <c r="A6859" s="6"/>
+      <c r="A6859" s="10"/>
       <c r="B6859" s="2"/>
-      <c r="C6859" s="7"/>
+      <c r="C6859" s="6"/>
     </row>
     <row r="6860">
-      <c r="A6860" s="6"/>
+      <c r="A6860" s="10"/>
       <c r="B6860" s="2"/>
-      <c r="C6860" s="7"/>
+      <c r="C6860" s="6"/>
     </row>
     <row r="6861">
-      <c r="A6861" s="6"/>
+      <c r="A6861" s="10"/>
       <c r="B6861" s="2"/>
-      <c r="C6861" s="7"/>
+      <c r="C6861" s="6"/>
     </row>
     <row r="6862">
-      <c r="A6862" s="6"/>
+      <c r="A6862" s="10"/>
       <c r="B6862" s="2"/>
-      <c r="C6862" s="7"/>
+      <c r="C6862" s="6"/>
     </row>
     <row r="6863">
-      <c r="A6863" s="6"/>
+      <c r="A6863" s="10"/>
       <c r="B6863" s="2"/>
-      <c r="C6863" s="7"/>
+      <c r="C6863" s="6"/>
     </row>
     <row r="6864">
-      <c r="A6864" s="6"/>
+      <c r="A6864" s="10"/>
       <c r="B6864" s="2"/>
-      <c r="C6864" s="7"/>
+      <c r="C6864" s="6"/>
     </row>
     <row r="6865">
-      <c r="A6865" s="6"/>
+      <c r="A6865" s="10"/>
       <c r="B6865" s="2"/>
-      <c r="C6865" s="7"/>
+      <c r="C6865" s="6"/>
     </row>
     <row r="6866">
-      <c r="A6866" s="6"/>
+      <c r="A6866" s="10"/>
       <c r="B6866" s="2"/>
-      <c r="C6866" s="7"/>
+      <c r="C6866" s="6"/>
     </row>
     <row r="6867">
-      <c r="A6867" s="6"/>
+      <c r="A6867" s="10"/>
       <c r="B6867" s="2"/>
-      <c r="C6867" s="7"/>
+      <c r="C6867" s="6"/>
     </row>
     <row r="6868">
-      <c r="A6868" s="6"/>
+      <c r="A6868" s="10"/>
       <c r="B6868" s="2"/>
-      <c r="C6868" s="7"/>
+      <c r="C6868" s="6"/>
     </row>
     <row r="6869">
-      <c r="A6869" s="6"/>
+      <c r="A6869" s="10"/>
       <c r="B6869" s="2"/>
-      <c r="C6869" s="7"/>
+      <c r="C6869" s="6"/>
     </row>
     <row r="6870">
-      <c r="A6870" s="6"/>
+      <c r="A6870" s="10"/>
       <c r="B6870" s="2"/>
-      <c r="C6870" s="7"/>
+      <c r="C6870" s="6"/>
     </row>
     <row r="6871">
-      <c r="A6871" s="6"/>
+      <c r="A6871" s="10"/>
       <c r="B6871" s="2"/>
-      <c r="C6871" s="7"/>
+      <c r="C6871" s="6"/>
     </row>
     <row r="6872">
-      <c r="A6872" s="6"/>
+      <c r="A6872" s="10"/>
       <c r="B6872" s="2"/>
-      <c r="C6872" s="7"/>
+      <c r="C6872" s="6"/>
     </row>
     <row r="6873">
-      <c r="A6873" s="6"/>
+      <c r="A6873" s="10"/>
       <c r="B6873" s="2"/>
-      <c r="C6873" s="7"/>
+      <c r="C6873" s="6"/>
     </row>
     <row r="6874">
-      <c r="A6874" s="6"/>
+      <c r="A6874" s="10"/>
       <c r="B6874" s="2"/>
-      <c r="C6874" s="7"/>
+      <c r="C6874" s="6"/>
     </row>
     <row r="6875">
-      <c r="A6875" s="6"/>
+      <c r="A6875" s="10"/>
       <c r="B6875" s="2"/>
-      <c r="C6875" s="7"/>
+      <c r="C6875" s="6"/>
     </row>
     <row r="6876">
-      <c r="A6876" s="6"/>
+      <c r="A6876" s="10"/>
       <c r="B6876" s="2"/>
-      <c r="C6876" s="7"/>
+      <c r="C6876" s="6"/>
     </row>
     <row r="6877">
-      <c r="A6877" s="6"/>
+      <c r="A6877" s="10"/>
       <c r="B6877" s="2"/>
-      <c r="C6877" s="7"/>
+      <c r="C6877" s="6"/>
     </row>
     <row r="6878">
-      <c r="A6878" s="6"/>
+      <c r="A6878" s="10"/>
       <c r="B6878" s="2"/>
-      <c r="C6878" s="7"/>
+      <c r="C6878" s="6"/>
     </row>
     <row r="6879">
-      <c r="A6879" s="6"/>
+      <c r="A6879" s="10"/>
       <c r="B6879" s="2"/>
-      <c r="C6879" s="7"/>
+      <c r="C6879" s="6"/>
     </row>
     <row r="6880">
-      <c r="A6880" s="6"/>
+      <c r="A6880" s="10"/>
       <c r="B6880" s="2"/>
-      <c r="C6880" s="7"/>
+      <c r="C6880" s="6"/>
     </row>
     <row r="6881">
-      <c r="A6881" s="6"/>
+      <c r="A6881" s="10"/>
       <c r="B6881" s="2"/>
-      <c r="C6881" s="7"/>
+      <c r="C6881" s="6"/>
     </row>
     <row r="6882">
-      <c r="A6882" s="6"/>
+      <c r="A6882" s="10"/>
       <c r="B6882" s="2"/>
-      <c r="C6882" s="7"/>
+      <c r="C6882" s="6"/>
     </row>
     <row r="6883">
-      <c r="A6883" s="6"/>
+      <c r="A6883" s="10"/>
       <c r="B6883" s="2"/>
-      <c r="C6883" s="7"/>
+      <c r="C6883" s="6"/>
     </row>
     <row r="6884">
-      <c r="A6884" s="6"/>
+      <c r="A6884" s="10"/>
       <c r="B6884" s="2"/>
-      <c r="C6884" s="7"/>
+      <c r="C6884" s="6"/>
     </row>
     <row r="6885">
-      <c r="A6885" s="6"/>
+      <c r="A6885" s="10"/>
       <c r="B6885" s="2"/>
-      <c r="C6885" s="7"/>
+      <c r="C6885" s="6"/>
     </row>
     <row r="6886">
-      <c r="A6886" s="6"/>
+      <c r="A6886" s="10"/>
       <c r="B6886" s="2"/>
-      <c r="C6886" s="7"/>
+      <c r="C6886" s="6"/>
     </row>
     <row r="6887">
-      <c r="A6887" s="6"/>
+      <c r="A6887" s="10"/>
       <c r="B6887" s="2"/>
-      <c r="C6887" s="7"/>
+      <c r="C6887" s="6"/>
     </row>
     <row r="6888">
-      <c r="A6888" s="6"/>
+      <c r="A6888" s="10"/>
       <c r="B6888" s="2"/>
-      <c r="C6888" s="7"/>
+      <c r="C6888" s="6"/>
     </row>
     <row r="6889">
-      <c r="A6889" s="6"/>
+      <c r="A6889" s="10"/>
       <c r="B6889" s="2"/>
-      <c r="C6889" s="7"/>
+      <c r="C6889" s="6"/>
     </row>
     <row r="6890">
-      <c r="A6890" s="6"/>
+      <c r="A6890" s="10"/>
       <c r="B6890" s="2"/>
-      <c r="C6890" s="7"/>
+      <c r="C6890" s="6"/>
     </row>
     <row r="6891">
-      <c r="A6891" s="6"/>
+      <c r="A6891" s="10"/>
       <c r="B6891" s="2"/>
-      <c r="C6891" s="7"/>
+      <c r="C6891" s="6"/>
     </row>
     <row r="6892">
-      <c r="A6892" s="6"/>
+      <c r="A6892" s="10"/>
       <c r="B6892" s="2"/>
-      <c r="C6892" s="7"/>
+      <c r="C6892" s="6"/>
     </row>
     <row r="6893">
-      <c r="A6893" s="6"/>
+      <c r="A6893" s="10"/>
       <c r="B6893" s="2"/>
-      <c r="C6893" s="7"/>
+      <c r="C6893" s="6"/>
     </row>
     <row r="6894">
-      <c r="A6894" s="6"/>
+      <c r="A6894" s="10"/>
       <c r="B6894" s="2"/>
-      <c r="C6894" s="7"/>
+      <c r="C6894" s="6"/>
     </row>
     <row r="6895">
-      <c r="A6895" s="6"/>
+      <c r="A6895" s="10"/>
       <c r="B6895" s="2"/>
-      <c r="C6895" s="7"/>
+      <c r="C6895" s="6"/>
     </row>
     <row r="6896">
-      <c r="A6896" s="6"/>
+      <c r="A6896" s="10"/>
       <c r="B6896" s="2"/>
-      <c r="C6896" s="7"/>
+      <c r="C6896" s="6"/>
     </row>
     <row r="6897">
-      <c r="A6897" s="6"/>
+      <c r="A6897" s="10"/>
       <c r="B6897" s="2"/>
-      <c r="C6897" s="7"/>
+      <c r="C6897" s="6"/>
     </row>
     <row r="6898">
-      <c r="A6898" s="6"/>
+      <c r="A6898" s="10"/>
       <c r="B6898" s="2"/>
-      <c r="C6898" s="7"/>
+      <c r="C6898" s="6"/>
     </row>
     <row r="6899">
-      <c r="A6899" s="6"/>
+      <c r="A6899" s="10"/>
       <c r="B6899" s="2"/>
-      <c r="C6899" s="7"/>
+      <c r="C6899" s="6"/>
     </row>
     <row r="6900">
-      <c r="A6900" s="6"/>
+      <c r="A6900" s="10"/>
       <c r="B6900" s="2"/>
-      <c r="C6900" s="7"/>
+      <c r="C6900" s="6"/>
     </row>
     <row r="6901">
-      <c r="A6901" s="6"/>
+      <c r="A6901" s="10"/>
       <c r="B6901" s="2"/>
-      <c r="C6901" s="7"/>
+      <c r="C6901" s="6"/>
     </row>
     <row r="6902">
-      <c r="A6902" s="6"/>
+      <c r="A6902" s="10"/>
       <c r="B6902" s="2"/>
-      <c r="C6902" s="7"/>
+      <c r="C6902" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -51,6 +51,11 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Aptos Narrow&quot;"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -66,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -99,6 +104,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -66112,4607 +66123,4811 @@
       </c>
     </row>
     <row r="5982">
-      <c r="A5982" s="11"/>
-      <c r="B5982" s="2"/>
-      <c r="C5982" s="6"/>
+      <c r="A5982" s="11">
+        <v>46177.0</v>
+      </c>
+      <c r="B5982" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5982" s="12">
+        <v>136.958828</v>
+      </c>
     </row>
     <row r="5983">
-      <c r="A5983" s="11"/>
-      <c r="B5983" s="2"/>
-      <c r="C5983" s="6"/>
+      <c r="A5983" s="11">
+        <v>46178.0</v>
+      </c>
+      <c r="B5983" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5983" s="12">
+        <v>136.760281</v>
+      </c>
     </row>
     <row r="5984">
-      <c r="A5984" s="11"/>
-      <c r="B5984" s="2"/>
-      <c r="C5984" s="6"/>
+      <c r="A5984" s="11">
+        <v>46179.0</v>
+      </c>
+      <c r="B5984" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5984" s="12">
+        <v>133.387083</v>
+      </c>
     </row>
     <row r="5985">
-      <c r="A5985" s="11"/>
-      <c r="B5985" s="2"/>
-      <c r="C5985" s="6"/>
+      <c r="A5985" s="11">
+        <v>46180.0</v>
+      </c>
+      <c r="B5985" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5985" s="12">
+        <v>99.961288</v>
+      </c>
     </row>
     <row r="5986">
-      <c r="A5986" s="11"/>
-      <c r="B5986" s="2"/>
-      <c r="C5986" s="6"/>
+      <c r="A5986" s="11">
+        <v>46181.0</v>
+      </c>
+      <c r="B5986" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5986" s="12">
+        <v>142.884987</v>
+      </c>
     </row>
     <row r="5987">
-      <c r="A5987" s="11"/>
-      <c r="B5987" s="2"/>
-      <c r="C5987" s="6"/>
+      <c r="A5987" s="11">
+        <v>46182.0</v>
+      </c>
+      <c r="B5987" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5987" s="12">
+        <v>145.747088</v>
+      </c>
     </row>
     <row r="5988">
-      <c r="A5988" s="11"/>
-      <c r="B5988" s="2"/>
-      <c r="C5988" s="6"/>
+      <c r="A5988" s="11">
+        <v>46183.0</v>
+      </c>
+      <c r="B5988" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5988" s="12">
+        <v>146.650671</v>
+      </c>
     </row>
     <row r="5989">
-      <c r="A5989" s="11"/>
-      <c r="B5989" s="2"/>
-      <c r="C5989" s="6"/>
+      <c r="A5989" s="11">
+        <v>46184.0</v>
+      </c>
+      <c r="B5989" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5989" s="12">
+        <v>127.233222</v>
+      </c>
     </row>
     <row r="5990">
-      <c r="A5990" s="11"/>
-      <c r="B5990" s="2"/>
-      <c r="C5990" s="6"/>
+      <c r="A5990" s="11">
+        <v>46185.0</v>
+      </c>
+      <c r="B5990" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5990" s="12">
+        <v>113.430649</v>
+      </c>
     </row>
     <row r="5991">
-      <c r="A5991" s="11"/>
-      <c r="B5991" s="2"/>
-      <c r="C5991" s="6"/>
+      <c r="A5991" s="11">
+        <v>46186.0</v>
+      </c>
+      <c r="B5991" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5991" s="12">
+        <v>95.062829</v>
+      </c>
     </row>
     <row r="5992">
-      <c r="A5992" s="11"/>
-      <c r="B5992" s="2"/>
-      <c r="C5992" s="6"/>
+      <c r="A5992" s="11">
+        <v>46187.0</v>
+      </c>
+      <c r="B5992" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5992" s="12">
+        <v>91.15201</v>
+      </c>
     </row>
     <row r="5993">
-      <c r="A5993" s="11"/>
-      <c r="B5993" s="2"/>
-      <c r="C5993" s="6"/>
+      <c r="A5993" s="11">
+        <v>46188.0</v>
+      </c>
+      <c r="B5993" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5993" s="12">
+        <v>130.016676</v>
+      </c>
     </row>
     <row r="5994">
-      <c r="A5994" s="11"/>
-      <c r="B5994" s="2"/>
-      <c r="C5994" s="6"/>
+      <c r="A5994" s="11">
+        <v>46189.0</v>
+      </c>
+      <c r="B5994" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5994" s="12">
+        <v>132.617046</v>
+      </c>
     </row>
     <row r="5995">
-      <c r="A5995" s="11"/>
-      <c r="B5995" s="2"/>
-      <c r="C5995" s="6"/>
+      <c r="A5995" s="11">
+        <v>46190.0</v>
+      </c>
+      <c r="B5995" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5995" s="12">
+        <v>134.537472</v>
+      </c>
     </row>
     <row r="5996">
-      <c r="A5996" s="11"/>
-      <c r="B5996" s="2"/>
-      <c r="C5996" s="6"/>
+      <c r="A5996" s="11">
+        <v>46191.0</v>
+      </c>
+      <c r="B5996" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5996" s="12">
+        <v>139.577148</v>
+      </c>
     </row>
     <row r="5997">
-      <c r="A5997" s="11"/>
-      <c r="B5997" s="2"/>
-      <c r="C5997" s="6"/>
+      <c r="A5997" s="11">
+        <v>46192.0</v>
+      </c>
+      <c r="B5997" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5997" s="12">
+        <v>136.585472</v>
+      </c>
     </row>
     <row r="5998">
-      <c r="A5998" s="11"/>
-      <c r="B5998" s="2"/>
-      <c r="C5998" s="6"/>
+      <c r="A5998" s="11">
+        <v>46193.0</v>
+      </c>
+      <c r="B5998" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5998" s="12">
+        <v>124.207667</v>
+      </c>
     </row>
     <row r="5999">
-      <c r="A5999" s="11"/>
-      <c r="B5999" s="2"/>
-      <c r="C5999" s="6"/>
+      <c r="A5999" s="11">
+        <v>46194.0</v>
+      </c>
+      <c r="B5999" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C5999" s="12">
+        <v>96.304834</v>
+      </c>
     </row>
     <row r="6000">
-      <c r="A6000" s="11"/>
-      <c r="B6000" s="2"/>
-      <c r="C6000" s="6"/>
+      <c r="A6000" s="11">
+        <v>46195.0</v>
+      </c>
+      <c r="B6000" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6000" s="12">
+        <v>141.811313</v>
+      </c>
     </row>
     <row r="6001">
-      <c r="A6001" s="11"/>
-      <c r="B6001" s="2"/>
-      <c r="C6001" s="6"/>
+      <c r="A6001" s="11">
+        <v>46196.0</v>
+      </c>
+      <c r="B6001" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6001" s="12">
+        <v>153.825928</v>
+      </c>
     </row>
     <row r="6002">
-      <c r="A6002" s="11"/>
-      <c r="B6002" s="2"/>
-      <c r="C6002" s="6"/>
+      <c r="A6002" s="11">
+        <v>46197.0</v>
+      </c>
+      <c r="B6002" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6002" s="12">
+        <v>162.656097</v>
+      </c>
     </row>
     <row r="6003">
-      <c r="A6003" s="11"/>
-      <c r="B6003" s="2"/>
-      <c r="C6003" s="6"/>
+      <c r="A6003" s="11">
+        <v>46198.0</v>
+      </c>
+      <c r="B6003" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6003" s="12">
+        <v>149.417096</v>
+      </c>
     </row>
     <row r="6004">
-      <c r="A6004" s="11"/>
-      <c r="B6004" s="2"/>
-      <c r="C6004" s="6"/>
+      <c r="A6004" s="11">
+        <v>46199.0</v>
+      </c>
+      <c r="B6004" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6004" s="12">
+        <v>155.45934</v>
+      </c>
     </row>
     <row r="6005">
-      <c r="A6005" s="11"/>
-      <c r="B6005" s="2"/>
-      <c r="C6005" s="6"/>
+      <c r="A6005" s="11">
+        <v>46200.0</v>
+      </c>
+      <c r="B6005" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6005" s="12">
+        <v>128.166041</v>
+      </c>
     </row>
     <row r="6006">
-      <c r="A6006" s="11"/>
-      <c r="B6006" s="2"/>
-      <c r="C6006" s="6"/>
+      <c r="A6006" s="11">
+        <v>46201.0</v>
+      </c>
+      <c r="B6006" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6006" s="12">
+        <v>121.367419</v>
+      </c>
     </row>
     <row r="6007">
-      <c r="A6007" s="11"/>
-      <c r="B6007" s="2"/>
-      <c r="C6007" s="6"/>
+      <c r="A6007" s="11">
+        <v>46202.0</v>
+      </c>
+      <c r="B6007" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6007" s="12">
+        <v>156.645459</v>
+      </c>
     </row>
     <row r="6008">
-      <c r="A6008" s="11"/>
-      <c r="B6008" s="2"/>
-      <c r="C6008" s="6"/>
+      <c r="A6008" s="11">
+        <v>46203.0</v>
+      </c>
+      <c r="B6008" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6008" s="12">
+        <v>153.138956</v>
+      </c>
     </row>
     <row r="6009">
-      <c r="A6009" s="11"/>
-      <c r="B6009" s="2"/>
-      <c r="C6009" s="6"/>
+      <c r="A6009" s="11">
+        <v>46204.0</v>
+      </c>
+      <c r="B6009" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6009" s="12">
+        <v>148.698461</v>
+      </c>
     </row>
     <row r="6010">
-      <c r="A6010" s="11"/>
-      <c r="B6010" s="2"/>
-      <c r="C6010" s="6"/>
+      <c r="A6010" s="11">
+        <v>46205.0</v>
+      </c>
+      <c r="B6010" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6010" s="12">
+        <v>142.101922</v>
+      </c>
     </row>
     <row r="6011">
-      <c r="A6011" s="11"/>
-      <c r="B6011" s="2"/>
-      <c r="C6011" s="6"/>
+      <c r="A6011" s="11">
+        <v>46206.0</v>
+      </c>
+      <c r="B6011" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6011" s="12">
+        <v>139.368173</v>
+      </c>
     </row>
     <row r="6012">
-      <c r="A6012" s="11"/>
-      <c r="B6012" s="2"/>
-      <c r="C6012" s="6"/>
+      <c r="A6012" s="11">
+        <v>46207.0</v>
+      </c>
+      <c r="B6012" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6012" s="12">
+        <v>105.29828</v>
+      </c>
     </row>
     <row r="6013">
-      <c r="A6013" s="11"/>
-      <c r="B6013" s="2"/>
-      <c r="C6013" s="6"/>
+      <c r="A6013" s="11">
+        <v>46208.0</v>
+      </c>
+      <c r="B6013" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6013" s="12">
+        <v>98.713707</v>
+      </c>
     </row>
     <row r="6014">
-      <c r="A6014" s="11"/>
-      <c r="B6014" s="2"/>
-      <c r="C6014" s="6"/>
+      <c r="A6014" s="11">
+        <v>46209.0</v>
+      </c>
+      <c r="B6014" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6014" s="12">
+        <v>144.028182</v>
+      </c>
     </row>
     <row r="6015">
-      <c r="A6015" s="11"/>
-      <c r="B6015" s="2"/>
-      <c r="C6015" s="6"/>
+      <c r="A6015" s="11">
+        <v>46210.0</v>
+      </c>
+      <c r="B6015" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6015" s="12">
+        <v>142.363213</v>
+      </c>
     </row>
     <row r="6016">
-      <c r="A6016" s="11"/>
+      <c r="A6016" s="13"/>
       <c r="B6016" s="2"/>
       <c r="C6016" s="6"/>
     </row>
     <row r="6017">
-      <c r="A6017" s="11"/>
+      <c r="A6017" s="13"/>
       <c r="B6017" s="2"/>
       <c r="C6017" s="6"/>
     </row>
     <row r="6018">
-      <c r="A6018" s="11"/>
+      <c r="A6018" s="13"/>
       <c r="B6018" s="2"/>
       <c r="C6018" s="6"/>
     </row>
     <row r="6019">
-      <c r="A6019" s="11"/>
+      <c r="A6019" s="13"/>
       <c r="B6019" s="2"/>
       <c r="C6019" s="6"/>
     </row>
     <row r="6020">
-      <c r="A6020" s="11"/>
+      <c r="A6020" s="13"/>
       <c r="B6020" s="2"/>
       <c r="C6020" s="6"/>
     </row>
     <row r="6021">
-      <c r="A6021" s="11"/>
+      <c r="A6021" s="13"/>
       <c r="B6021" s="2"/>
       <c r="C6021" s="6"/>
     </row>
     <row r="6022">
-      <c r="A6022" s="11"/>
+      <c r="A6022" s="13"/>
       <c r="B6022" s="2"/>
       <c r="C6022" s="6"/>
     </row>
     <row r="6023">
-      <c r="A6023" s="11"/>
+      <c r="A6023" s="13"/>
       <c r="B6023" s="2"/>
       <c r="C6023" s="6"/>
     </row>
     <row r="6024">
-      <c r="A6024" s="11"/>
+      <c r="A6024" s="13"/>
       <c r="B6024" s="2"/>
       <c r="C6024" s="6"/>
     </row>
     <row r="6025">
-      <c r="A6025" s="11"/>
+      <c r="A6025" s="13"/>
       <c r="B6025" s="2"/>
       <c r="C6025" s="6"/>
     </row>
     <row r="6026">
-      <c r="A6026" s="11"/>
+      <c r="A6026" s="13"/>
       <c r="B6026" s="2"/>
       <c r="C6026" s="6"/>
     </row>
     <row r="6027">
-      <c r="A6027" s="11"/>
+      <c r="A6027" s="13"/>
       <c r="B6027" s="2"/>
       <c r="C6027" s="6"/>
     </row>
     <row r="6028">
-      <c r="A6028" s="11"/>
+      <c r="A6028" s="13"/>
       <c r="B6028" s="2"/>
       <c r="C6028" s="6"/>
     </row>
     <row r="6029">
-      <c r="A6029" s="11"/>
+      <c r="A6029" s="13"/>
       <c r="B6029" s="2"/>
       <c r="C6029" s="6"/>
     </row>
     <row r="6030">
-      <c r="A6030" s="11"/>
+      <c r="A6030" s="13"/>
       <c r="B6030" s="2"/>
       <c r="C6030" s="6"/>
     </row>
     <row r="6031">
-      <c r="A6031" s="11"/>
+      <c r="A6031" s="13"/>
       <c r="B6031" s="2"/>
       <c r="C6031" s="6"/>
     </row>
     <row r="6032">
-      <c r="A6032" s="11"/>
+      <c r="A6032" s="13"/>
       <c r="B6032" s="2"/>
       <c r="C6032" s="6"/>
     </row>
     <row r="6033">
-      <c r="A6033" s="11"/>
+      <c r="A6033" s="13"/>
       <c r="B6033" s="2"/>
       <c r="C6033" s="6"/>
     </row>
     <row r="6034">
-      <c r="A6034" s="11"/>
+      <c r="A6034" s="13"/>
       <c r="B6034" s="2"/>
       <c r="C6034" s="6"/>
     </row>
     <row r="6035">
-      <c r="A6035" s="11"/>
+      <c r="A6035" s="13"/>
       <c r="B6035" s="2"/>
       <c r="C6035" s="6"/>
     </row>
     <row r="6036">
-      <c r="A6036" s="11"/>
+      <c r="A6036" s="13"/>
       <c r="B6036" s="2"/>
       <c r="C6036" s="6"/>
     </row>
     <row r="6037">
-      <c r="A6037" s="11"/>
+      <c r="A6037" s="13"/>
       <c r="B6037" s="2"/>
       <c r="C6037" s="6"/>
     </row>
     <row r="6038">
-      <c r="A6038" s="11"/>
+      <c r="A6038" s="13"/>
       <c r="B6038" s="2"/>
       <c r="C6038" s="6"/>
     </row>
     <row r="6039">
-      <c r="A6039" s="11"/>
+      <c r="A6039" s="13"/>
       <c r="B6039" s="2"/>
       <c r="C6039" s="6"/>
     </row>
     <row r="6040">
-      <c r="A6040" s="11"/>
+      <c r="A6040" s="13"/>
       <c r="B6040" s="2"/>
       <c r="C6040" s="6"/>
     </row>
     <row r="6041">
-      <c r="A6041" s="11"/>
+      <c r="A6041" s="13"/>
       <c r="B6041" s="2"/>
       <c r="C6041" s="6"/>
     </row>
     <row r="6042">
-      <c r="A6042" s="11"/>
+      <c r="A6042" s="13"/>
       <c r="B6042" s="2"/>
       <c r="C6042" s="6"/>
     </row>
     <row r="6043">
-      <c r="A6043" s="11"/>
+      <c r="A6043" s="13"/>
       <c r="B6043" s="2"/>
       <c r="C6043" s="6"/>
     </row>
     <row r="6044">
-      <c r="A6044" s="11"/>
+      <c r="A6044" s="13"/>
       <c r="B6044" s="2"/>
       <c r="C6044" s="6"/>
     </row>
     <row r="6045">
-      <c r="A6045" s="11"/>
+      <c r="A6045" s="13"/>
       <c r="B6045" s="2"/>
       <c r="C6045" s="6"/>
     </row>
     <row r="6046">
-      <c r="A6046" s="11"/>
+      <c r="A6046" s="13"/>
       <c r="B6046" s="2"/>
       <c r="C6046" s="6"/>
     </row>
     <row r="6047">
-      <c r="A6047" s="11"/>
+      <c r="A6047" s="13"/>
       <c r="B6047" s="2"/>
       <c r="C6047" s="6"/>
     </row>
     <row r="6048">
-      <c r="A6048" s="11"/>
+      <c r="A6048" s="13"/>
       <c r="B6048" s="2"/>
       <c r="C6048" s="6"/>
     </row>
     <row r="6049">
-      <c r="A6049" s="11"/>
+      <c r="A6049" s="13"/>
       <c r="B6049" s="2"/>
       <c r="C6049" s="6"/>
     </row>
     <row r="6050">
-      <c r="A6050" s="11"/>
+      <c r="A6050" s="13"/>
       <c r="B6050" s="2"/>
       <c r="C6050" s="6"/>
     </row>
     <row r="6051">
-      <c r="A6051" s="11"/>
+      <c r="A6051" s="13"/>
       <c r="B6051" s="2"/>
       <c r="C6051" s="6"/>
     </row>
     <row r="6052">
-      <c r="A6052" s="11"/>
+      <c r="A6052" s="13"/>
       <c r="B6052" s="2"/>
       <c r="C6052" s="6"/>
     </row>
     <row r="6053">
-      <c r="A6053" s="11"/>
+      <c r="A6053" s="13"/>
       <c r="B6053" s="2"/>
       <c r="C6053" s="6"/>
     </row>
     <row r="6054">
-      <c r="A6054" s="11"/>
+      <c r="A6054" s="13"/>
       <c r="B6054" s="2"/>
       <c r="C6054" s="6"/>
     </row>
     <row r="6055">
-      <c r="A6055" s="11"/>
+      <c r="A6055" s="13"/>
       <c r="B6055" s="2"/>
       <c r="C6055" s="6"/>
     </row>
     <row r="6056">
-      <c r="A6056" s="11"/>
+      <c r="A6056" s="13"/>
       <c r="B6056" s="2"/>
       <c r="C6056" s="6"/>
     </row>
     <row r="6057">
-      <c r="A6057" s="11"/>
+      <c r="A6057" s="13"/>
       <c r="B6057" s="2"/>
       <c r="C6057" s="6"/>
     </row>
     <row r="6058">
-      <c r="A6058" s="11"/>
+      <c r="A6058" s="13"/>
       <c r="B6058" s="2"/>
       <c r="C6058" s="6"/>
     </row>
     <row r="6059">
-      <c r="A6059" s="11"/>
+      <c r="A6059" s="13"/>
       <c r="B6059" s="2"/>
       <c r="C6059" s="6"/>
     </row>
     <row r="6060">
-      <c r="A6060" s="11"/>
+      <c r="A6060" s="13"/>
       <c r="B6060" s="2"/>
       <c r="C6060" s="6"/>
     </row>
     <row r="6061">
-      <c r="A6061" s="11"/>
+      <c r="A6061" s="13"/>
       <c r="B6061" s="2"/>
       <c r="C6061" s="6"/>
     </row>
     <row r="6062">
-      <c r="A6062" s="11"/>
+      <c r="A6062" s="13"/>
       <c r="B6062" s="2"/>
       <c r="C6062" s="6"/>
     </row>
     <row r="6063">
-      <c r="A6063" s="11"/>
+      <c r="A6063" s="13"/>
       <c r="B6063" s="2"/>
       <c r="C6063" s="6"/>
     </row>
     <row r="6064">
-      <c r="A6064" s="11"/>
+      <c r="A6064" s="13"/>
       <c r="B6064" s="2"/>
       <c r="C6064" s="6"/>
     </row>
     <row r="6065">
-      <c r="A6065" s="11"/>
+      <c r="A6065" s="13"/>
       <c r="B6065" s="2"/>
       <c r="C6065" s="6"/>
     </row>
     <row r="6066">
-      <c r="A6066" s="11"/>
+      <c r="A6066" s="13"/>
       <c r="B6066" s="2"/>
       <c r="C6066" s="6"/>
     </row>
     <row r="6067">
-      <c r="A6067" s="11"/>
+      <c r="A6067" s="13"/>
       <c r="B6067" s="2"/>
       <c r="C6067" s="6"/>
     </row>
     <row r="6068">
-      <c r="A6068" s="11"/>
+      <c r="A6068" s="13"/>
       <c r="B6068" s="2"/>
       <c r="C6068" s="6"/>
     </row>
     <row r="6069">
-      <c r="A6069" s="11"/>
+      <c r="A6069" s="13"/>
       <c r="B6069" s="2"/>
       <c r="C6069" s="6"/>
     </row>
     <row r="6070">
-      <c r="A6070" s="11"/>
+      <c r="A6070" s="13"/>
       <c r="B6070" s="2"/>
       <c r="C6070" s="6"/>
     </row>
     <row r="6071">
-      <c r="A6071" s="11"/>
+      <c r="A6071" s="13"/>
       <c r="B6071" s="2"/>
       <c r="C6071" s="6"/>
     </row>
     <row r="6072">
-      <c r="A6072" s="11"/>
+      <c r="A6072" s="13"/>
       <c r="B6072" s="2"/>
       <c r="C6072" s="6"/>
     </row>
     <row r="6073">
-      <c r="A6073" s="11"/>
+      <c r="A6073" s="13"/>
       <c r="B6073" s="2"/>
       <c r="C6073" s="6"/>
     </row>
     <row r="6074">
-      <c r="A6074" s="11"/>
+      <c r="A6074" s="13"/>
       <c r="B6074" s="2"/>
       <c r="C6074" s="6"/>
     </row>
     <row r="6075">
-      <c r="A6075" s="11"/>
+      <c r="A6075" s="13"/>
       <c r="B6075" s="2"/>
       <c r="C6075" s="6"/>
     </row>
     <row r="6076">
-      <c r="A6076" s="11"/>
+      <c r="A6076" s="13"/>
       <c r="B6076" s="2"/>
       <c r="C6076" s="6"/>
     </row>
     <row r="6077">
-      <c r="A6077" s="11"/>
+      <c r="A6077" s="13"/>
       <c r="B6077" s="2"/>
       <c r="C6077" s="6"/>
     </row>
     <row r="6078">
-      <c r="A6078" s="11"/>
+      <c r="A6078" s="13"/>
       <c r="B6078" s="2"/>
       <c r="C6078" s="6"/>
     </row>
     <row r="6079">
-      <c r="A6079" s="11"/>
+      <c r="A6079" s="13"/>
       <c r="B6079" s="2"/>
       <c r="C6079" s="6"/>
     </row>
     <row r="6080">
-      <c r="A6080" s="11"/>
+      <c r="A6080" s="13"/>
       <c r="B6080" s="2"/>
       <c r="C6080" s="6"/>
     </row>
     <row r="6081">
-      <c r="A6081" s="11"/>
+      <c r="A6081" s="13"/>
       <c r="B6081" s="2"/>
       <c r="C6081" s="6"/>
     </row>
     <row r="6082">
-      <c r="A6082" s="11"/>
+      <c r="A6082" s="13"/>
       <c r="B6082" s="2"/>
       <c r="C6082" s="6"/>
     </row>
     <row r="6083">
-      <c r="A6083" s="11"/>
+      <c r="A6083" s="13"/>
       <c r="B6083" s="2"/>
       <c r="C6083" s="6"/>
     </row>
     <row r="6084">
-      <c r="A6084" s="11"/>
+      <c r="A6084" s="13"/>
       <c r="B6084" s="2"/>
       <c r="C6084" s="6"/>
     </row>
     <row r="6085">
-      <c r="A6085" s="11"/>
+      <c r="A6085" s="13"/>
       <c r="B6085" s="2"/>
       <c r="C6085" s="6"/>
     </row>
     <row r="6086">
-      <c r="A6086" s="11"/>
+      <c r="A6086" s="13"/>
       <c r="B6086" s="2"/>
       <c r="C6086" s="6"/>
     </row>
     <row r="6087">
-      <c r="A6087" s="11"/>
+      <c r="A6087" s="13"/>
       <c r="B6087" s="2"/>
       <c r="C6087" s="6"/>
     </row>
     <row r="6088">
-      <c r="A6088" s="11"/>
+      <c r="A6088" s="13"/>
       <c r="B6088" s="2"/>
       <c r="C6088" s="6"/>
     </row>
     <row r="6089">
-      <c r="A6089" s="11"/>
+      <c r="A6089" s="13"/>
       <c r="B6089" s="2"/>
       <c r="C6089" s="6"/>
     </row>
     <row r="6090">
-      <c r="A6090" s="11"/>
+      <c r="A6090" s="13"/>
       <c r="B6090" s="2"/>
       <c r="C6090" s="6"/>
     </row>
     <row r="6091">
-      <c r="A6091" s="11"/>
+      <c r="A6091" s="13"/>
       <c r="B6091" s="2"/>
       <c r="C6091" s="6"/>
     </row>
     <row r="6092">
-      <c r="A6092" s="11"/>
+      <c r="A6092" s="13"/>
       <c r="B6092" s="2"/>
       <c r="C6092" s="6"/>
     </row>
     <row r="6093">
-      <c r="A6093" s="11"/>
+      <c r="A6093" s="13"/>
       <c r="B6093" s="2"/>
       <c r="C6093" s="6"/>
     </row>
     <row r="6094">
-      <c r="A6094" s="11"/>
+      <c r="A6094" s="13"/>
       <c r="B6094" s="2"/>
       <c r="C6094" s="6"/>
     </row>
     <row r="6095">
-      <c r="A6095" s="11"/>
+      <c r="A6095" s="13"/>
       <c r="B6095" s="2"/>
       <c r="C6095" s="6"/>
     </row>
     <row r="6096">
-      <c r="A6096" s="11"/>
+      <c r="A6096" s="13"/>
       <c r="B6096" s="2"/>
       <c r="C6096" s="6"/>
     </row>
     <row r="6097">
-      <c r="A6097" s="11"/>
+      <c r="A6097" s="13"/>
       <c r="B6097" s="2"/>
       <c r="C6097" s="6"/>
     </row>
     <row r="6098">
-      <c r="A6098" s="11"/>
+      <c r="A6098" s="13"/>
       <c r="B6098" s="2"/>
       <c r="C6098" s="6"/>
     </row>
     <row r="6099">
-      <c r="A6099" s="11"/>
+      <c r="A6099" s="13"/>
       <c r="B6099" s="2"/>
       <c r="C6099" s="6"/>
     </row>
     <row r="6100">
-      <c r="A6100" s="11"/>
+      <c r="A6100" s="13"/>
       <c r="B6100" s="2"/>
       <c r="C6100" s="6"/>
     </row>
     <row r="6101">
-      <c r="A6101" s="11"/>
+      <c r="A6101" s="13"/>
       <c r="B6101" s="2"/>
       <c r="C6101" s="6"/>
     </row>
     <row r="6102">
-      <c r="A6102" s="11"/>
+      <c r="A6102" s="13"/>
       <c r="B6102" s="2"/>
       <c r="C6102" s="6"/>
     </row>
     <row r="6103">
-      <c r="A6103" s="11"/>
+      <c r="A6103" s="13"/>
       <c r="B6103" s="2"/>
       <c r="C6103" s="6"/>
     </row>
     <row r="6104">
-      <c r="A6104" s="11"/>
+      <c r="A6104" s="13"/>
       <c r="B6104" s="2"/>
       <c r="C6104" s="6"/>
     </row>
     <row r="6105">
-      <c r="A6105" s="11"/>
+      <c r="A6105" s="13"/>
       <c r="B6105" s="2"/>
       <c r="C6105" s="6"/>
     </row>
     <row r="6106">
-      <c r="A6106" s="11"/>
+      <c r="A6106" s="13"/>
       <c r="B6106" s="2"/>
       <c r="C6106" s="6"/>
     </row>
     <row r="6107">
-      <c r="A6107" s="11"/>
+      <c r="A6107" s="13"/>
       <c r="B6107" s="2"/>
       <c r="C6107" s="6"/>
     </row>
     <row r="6108">
-      <c r="A6108" s="11"/>
+      <c r="A6108" s="13"/>
       <c r="B6108" s="2"/>
       <c r="C6108" s="6"/>
     </row>
     <row r="6109">
-      <c r="A6109" s="11"/>
+      <c r="A6109" s="13"/>
       <c r="B6109" s="2"/>
       <c r="C6109" s="6"/>
     </row>
     <row r="6110">
-      <c r="A6110" s="11"/>
+      <c r="A6110" s="13"/>
       <c r="B6110" s="2"/>
       <c r="C6110" s="6"/>
     </row>
     <row r="6111">
-      <c r="A6111" s="11"/>
+      <c r="A6111" s="13"/>
       <c r="B6111" s="2"/>
       <c r="C6111" s="6"/>
     </row>
     <row r="6112">
-      <c r="A6112" s="11"/>
+      <c r="A6112" s="13"/>
       <c r="B6112" s="2"/>
       <c r="C6112" s="6"/>
     </row>
     <row r="6113">
-      <c r="A6113" s="11"/>
+      <c r="A6113" s="13"/>
       <c r="B6113" s="2"/>
       <c r="C6113" s="6"/>
     </row>
     <row r="6114">
-      <c r="A6114" s="11"/>
+      <c r="A6114" s="13"/>
       <c r="B6114" s="2"/>
       <c r="C6114" s="6"/>
     </row>
     <row r="6115">
-      <c r="A6115" s="11"/>
+      <c r="A6115" s="13"/>
       <c r="B6115" s="2"/>
       <c r="C6115" s="6"/>
     </row>
     <row r="6116">
-      <c r="A6116" s="11"/>
+      <c r="A6116" s="13"/>
       <c r="B6116" s="2"/>
       <c r="C6116" s="6"/>
     </row>
     <row r="6117">
-      <c r="A6117" s="11"/>
+      <c r="A6117" s="13"/>
       <c r="B6117" s="2"/>
       <c r="C6117" s="6"/>
     </row>
     <row r="6118">
-      <c r="A6118" s="11"/>
+      <c r="A6118" s="13"/>
       <c r="B6118" s="2"/>
       <c r="C6118" s="6"/>
     </row>
     <row r="6119">
-      <c r="A6119" s="11"/>
+      <c r="A6119" s="13"/>
       <c r="B6119" s="2"/>
       <c r="C6119" s="6"/>
     </row>
     <row r="6120">
-      <c r="A6120" s="11"/>
+      <c r="A6120" s="13"/>
       <c r="B6120" s="2"/>
       <c r="C6120" s="6"/>
     </row>
     <row r="6121">
-      <c r="A6121" s="11"/>
+      <c r="A6121" s="13"/>
       <c r="B6121" s="2"/>
       <c r="C6121" s="6"/>
     </row>
     <row r="6122">
-      <c r="A6122" s="11"/>
+      <c r="A6122" s="13"/>
       <c r="B6122" s="2"/>
       <c r="C6122" s="6"/>
     </row>
     <row r="6123">
-      <c r="A6123" s="11"/>
+      <c r="A6123" s="13"/>
       <c r="B6123" s="2"/>
       <c r="C6123" s="6"/>
     </row>
     <row r="6124">
-      <c r="A6124" s="11"/>
+      <c r="A6124" s="13"/>
       <c r="B6124" s="2"/>
       <c r="C6124" s="6"/>
     </row>
     <row r="6125">
-      <c r="A6125" s="11"/>
+      <c r="A6125" s="13"/>
       <c r="B6125" s="2"/>
       <c r="C6125" s="6"/>
     </row>
     <row r="6126">
-      <c r="A6126" s="11"/>
+      <c r="A6126" s="13"/>
       <c r="B6126" s="2"/>
       <c r="C6126" s="6"/>
     </row>
     <row r="6127">
-      <c r="A6127" s="11"/>
+      <c r="A6127" s="13"/>
       <c r="B6127" s="2"/>
       <c r="C6127" s="6"/>
     </row>
     <row r="6128">
-      <c r="A6128" s="11"/>
+      <c r="A6128" s="13"/>
       <c r="B6128" s="2"/>
       <c r="C6128" s="6"/>
     </row>
     <row r="6129">
-      <c r="A6129" s="11"/>
+      <c r="A6129" s="13"/>
       <c r="B6129" s="2"/>
       <c r="C6129" s="6"/>
     </row>
     <row r="6130">
-      <c r="A6130" s="11"/>
+      <c r="A6130" s="13"/>
       <c r="B6130" s="2"/>
       <c r="C6130" s="6"/>
     </row>
     <row r="6131">
-      <c r="A6131" s="11"/>
+      <c r="A6131" s="13"/>
       <c r="B6131" s="2"/>
       <c r="C6131" s="6"/>
     </row>
     <row r="6132">
-      <c r="A6132" s="11"/>
+      <c r="A6132" s="13"/>
       <c r="B6132" s="2"/>
       <c r="C6132" s="6"/>
     </row>
     <row r="6133">
-      <c r="A6133" s="11"/>
+      <c r="A6133" s="13"/>
       <c r="B6133" s="2"/>
       <c r="C6133" s="6"/>
     </row>
     <row r="6134">
-      <c r="A6134" s="11"/>
+      <c r="A6134" s="13"/>
       <c r="B6134" s="2"/>
       <c r="C6134" s="6"/>
     </row>
     <row r="6135">
-      <c r="A6135" s="11"/>
+      <c r="A6135" s="13"/>
       <c r="B6135" s="2"/>
       <c r="C6135" s="6"/>
     </row>
     <row r="6136">
-      <c r="A6136" s="11"/>
+      <c r="A6136" s="13"/>
       <c r="B6136" s="2"/>
       <c r="C6136" s="6"/>
     </row>
     <row r="6137">
-      <c r="A6137" s="11"/>
+      <c r="A6137" s="13"/>
       <c r="B6137" s="2"/>
       <c r="C6137" s="6"/>
     </row>
     <row r="6138">
-      <c r="A6138" s="11"/>
+      <c r="A6138" s="13"/>
       <c r="B6138" s="2"/>
       <c r="C6138" s="6"/>
     </row>
     <row r="6139">
-      <c r="A6139" s="11"/>
+      <c r="A6139" s="13"/>
       <c r="B6139" s="2"/>
       <c r="C6139" s="6"/>
     </row>
     <row r="6140">
-      <c r="A6140" s="11"/>
+      <c r="A6140" s="13"/>
       <c r="B6140" s="2"/>
       <c r="C6140" s="6"/>
     </row>
     <row r="6141">
-      <c r="A6141" s="11"/>
+      <c r="A6141" s="13"/>
       <c r="B6141" s="2"/>
       <c r="C6141" s="6"/>
     </row>
     <row r="6142">
-      <c r="A6142" s="11"/>
+      <c r="A6142" s="13"/>
       <c r="B6142" s="2"/>
       <c r="C6142" s="6"/>
     </row>
     <row r="6143">
-      <c r="A6143" s="11"/>
+      <c r="A6143" s="13"/>
       <c r="B6143" s="2"/>
       <c r="C6143" s="6"/>
     </row>
     <row r="6144">
-      <c r="A6144" s="11"/>
+      <c r="A6144" s="13"/>
       <c r="B6144" s="2"/>
       <c r="C6144" s="6"/>
     </row>
     <row r="6145">
-      <c r="A6145" s="11"/>
+      <c r="A6145" s="13"/>
       <c r="B6145" s="2"/>
       <c r="C6145" s="6"/>
     </row>
     <row r="6146">
-      <c r="A6146" s="11"/>
+      <c r="A6146" s="13"/>
       <c r="B6146" s="2"/>
       <c r="C6146" s="6"/>
     </row>
     <row r="6147">
-      <c r="A6147" s="11"/>
+      <c r="A6147" s="13"/>
       <c r="B6147" s="2"/>
       <c r="C6147" s="6"/>
     </row>
     <row r="6148">
-      <c r="A6148" s="11"/>
+      <c r="A6148" s="13"/>
       <c r="B6148" s="2"/>
       <c r="C6148" s="6"/>
     </row>
     <row r="6149">
-      <c r="A6149" s="11"/>
+      <c r="A6149" s="13"/>
       <c r="B6149" s="2"/>
       <c r="C6149" s="6"/>
     </row>
     <row r="6150">
-      <c r="A6150" s="11"/>
+      <c r="A6150" s="13"/>
       <c r="B6150" s="2"/>
       <c r="C6150" s="6"/>
     </row>
     <row r="6151">
-      <c r="A6151" s="11"/>
+      <c r="A6151" s="13"/>
       <c r="B6151" s="2"/>
       <c r="C6151" s="6"/>
     </row>
     <row r="6152">
-      <c r="A6152" s="11"/>
+      <c r="A6152" s="13"/>
       <c r="B6152" s="2"/>
       <c r="C6152" s="6"/>
     </row>
     <row r="6153">
-      <c r="A6153" s="11"/>
+      <c r="A6153" s="13"/>
       <c r="B6153" s="2"/>
       <c r="C6153" s="6"/>
     </row>
     <row r="6154">
-      <c r="A6154" s="11"/>
+      <c r="A6154" s="13"/>
       <c r="B6154" s="2"/>
       <c r="C6154" s="6"/>
     </row>
     <row r="6155">
-      <c r="A6155" s="11"/>
+      <c r="A6155" s="13"/>
       <c r="B6155" s="2"/>
       <c r="C6155" s="6"/>
     </row>
     <row r="6156">
-      <c r="A6156" s="11"/>
+      <c r="A6156" s="13"/>
       <c r="B6156" s="2"/>
       <c r="C6156" s="6"/>
     </row>
     <row r="6157">
-      <c r="A6157" s="11"/>
+      <c r="A6157" s="13"/>
       <c r="B6157" s="2"/>
       <c r="C6157" s="6"/>
     </row>
     <row r="6158">
-      <c r="A6158" s="11"/>
+      <c r="A6158" s="13"/>
       <c r="B6158" s="2"/>
       <c r="C6158" s="6"/>
     </row>
     <row r="6159">
-      <c r="A6159" s="11"/>
+      <c r="A6159" s="13"/>
       <c r="B6159" s="2"/>
       <c r="C6159" s="6"/>
     </row>
     <row r="6160">
-      <c r="A6160" s="11"/>
+      <c r="A6160" s="13"/>
       <c r="B6160" s="2"/>
       <c r="C6160" s="6"/>
     </row>
     <row r="6161">
-      <c r="A6161" s="11"/>
+      <c r="A6161" s="13"/>
       <c r="B6161" s="2"/>
       <c r="C6161" s="6"/>
     </row>
     <row r="6162">
-      <c r="A6162" s="11"/>
+      <c r="A6162" s="13"/>
       <c r="B6162" s="2"/>
       <c r="C6162" s="6"/>
     </row>
     <row r="6163">
-      <c r="A6163" s="11"/>
+      <c r="A6163" s="13"/>
       <c r="B6163" s="2"/>
       <c r="C6163" s="6"/>
     </row>
     <row r="6164">
-      <c r="A6164" s="11"/>
+      <c r="A6164" s="13"/>
       <c r="B6164" s="2"/>
       <c r="C6164" s="6"/>
     </row>
     <row r="6165">
-      <c r="A6165" s="11"/>
+      <c r="A6165" s="13"/>
       <c r="B6165" s="2"/>
       <c r="C6165" s="6"/>
     </row>
     <row r="6166">
-      <c r="A6166" s="11"/>
+      <c r="A6166" s="13"/>
       <c r="B6166" s="2"/>
       <c r="C6166" s="6"/>
     </row>
     <row r="6167">
-      <c r="A6167" s="11"/>
+      <c r="A6167" s="13"/>
       <c r="B6167" s="2"/>
       <c r="C6167" s="6"/>
     </row>
     <row r="6168">
-      <c r="A6168" s="11"/>
+      <c r="A6168" s="13"/>
       <c r="B6168" s="2"/>
       <c r="C6168" s="6"/>
     </row>
     <row r="6169">
-      <c r="A6169" s="11"/>
+      <c r="A6169" s="13"/>
       <c r="B6169" s="2"/>
       <c r="C6169" s="6"/>
     </row>
     <row r="6170">
-      <c r="A6170" s="11"/>
+      <c r="A6170" s="13"/>
       <c r="B6170" s="2"/>
       <c r="C6170" s="6"/>
     </row>
     <row r="6171">
-      <c r="A6171" s="11"/>
+      <c r="A6171" s="13"/>
       <c r="B6171" s="2"/>
       <c r="C6171" s="6"/>
     </row>
     <row r="6172">
-      <c r="A6172" s="11"/>
+      <c r="A6172" s="13"/>
       <c r="B6172" s="2"/>
       <c r="C6172" s="6"/>
     </row>
     <row r="6173">
-      <c r="A6173" s="11"/>
+      <c r="A6173" s="13"/>
       <c r="B6173" s="2"/>
       <c r="C6173" s="6"/>
     </row>
     <row r="6174">
-      <c r="A6174" s="11"/>
+      <c r="A6174" s="13"/>
       <c r="B6174" s="2"/>
       <c r="C6174" s="6"/>
     </row>
     <row r="6175">
-      <c r="A6175" s="11"/>
+      <c r="A6175" s="13"/>
       <c r="B6175" s="2"/>
       <c r="C6175" s="6"/>
     </row>
     <row r="6176">
-      <c r="A6176" s="11"/>
+      <c r="A6176" s="13"/>
       <c r="B6176" s="2"/>
       <c r="C6176" s="6"/>
     </row>
     <row r="6177">
-      <c r="A6177" s="11"/>
+      <c r="A6177" s="13"/>
       <c r="B6177" s="2"/>
       <c r="C6177" s="6"/>
     </row>
     <row r="6178">
-      <c r="A6178" s="11"/>
+      <c r="A6178" s="13"/>
       <c r="B6178" s="2"/>
       <c r="C6178" s="6"/>
     </row>
     <row r="6179">
-      <c r="A6179" s="11"/>
+      <c r="A6179" s="13"/>
       <c r="B6179" s="2"/>
       <c r="C6179" s="6"/>
     </row>
     <row r="6180">
-      <c r="A6180" s="11"/>
+      <c r="A6180" s="13"/>
       <c r="B6180" s="2"/>
       <c r="C6180" s="6"/>
     </row>
     <row r="6181">
-      <c r="A6181" s="11"/>
+      <c r="A6181" s="13"/>
       <c r="B6181" s="2"/>
       <c r="C6181" s="6"/>
     </row>
     <row r="6182">
-      <c r="A6182" s="11"/>
+      <c r="A6182" s="13"/>
       <c r="B6182" s="2"/>
       <c r="C6182" s="6"/>
     </row>
     <row r="6183">
-      <c r="A6183" s="11"/>
+      <c r="A6183" s="13"/>
       <c r="B6183" s="2"/>
       <c r="C6183" s="6"/>
     </row>
     <row r="6184">
-      <c r="A6184" s="11"/>
+      <c r="A6184" s="13"/>
       <c r="B6184" s="2"/>
       <c r="C6184" s="6"/>
     </row>
     <row r="6185">
-      <c r="A6185" s="11"/>
+      <c r="A6185" s="13"/>
       <c r="B6185" s="2"/>
       <c r="C6185" s="6"/>
     </row>
     <row r="6186">
-      <c r="A6186" s="11"/>
+      <c r="A6186" s="13"/>
       <c r="B6186" s="2"/>
       <c r="C6186" s="6"/>
     </row>
     <row r="6187">
-      <c r="A6187" s="11"/>
+      <c r="A6187" s="13"/>
       <c r="B6187" s="2"/>
       <c r="C6187" s="6"/>
     </row>
     <row r="6188">
-      <c r="A6188" s="11"/>
+      <c r="A6188" s="13"/>
       <c r="B6188" s="2"/>
       <c r="C6188" s="6"/>
     </row>
     <row r="6189">
-      <c r="A6189" s="11"/>
+      <c r="A6189" s="13"/>
       <c r="B6189" s="2"/>
       <c r="C6189" s="6"/>
     </row>
     <row r="6190">
-      <c r="A6190" s="11"/>
+      <c r="A6190" s="13"/>
       <c r="B6190" s="2"/>
       <c r="C6190" s="6"/>
     </row>
     <row r="6191">
-      <c r="A6191" s="11"/>
+      <c r="A6191" s="13"/>
       <c r="B6191" s="2"/>
       <c r="C6191" s="6"/>
     </row>
     <row r="6192">
-      <c r="A6192" s="11"/>
+      <c r="A6192" s="13"/>
       <c r="B6192" s="2"/>
       <c r="C6192" s="6"/>
     </row>
     <row r="6193">
-      <c r="A6193" s="11"/>
+      <c r="A6193" s="13"/>
       <c r="B6193" s="2"/>
       <c r="C6193" s="6"/>
     </row>
     <row r="6194">
-      <c r="A6194" s="11"/>
+      <c r="A6194" s="13"/>
       <c r="B6194" s="2"/>
       <c r="C6194" s="6"/>
     </row>
     <row r="6195">
-      <c r="A6195" s="11"/>
+      <c r="A6195" s="13"/>
       <c r="B6195" s="2"/>
       <c r="C6195" s="6"/>
     </row>
     <row r="6196">
-      <c r="A6196" s="11"/>
+      <c r="A6196" s="13"/>
       <c r="B6196" s="2"/>
       <c r="C6196" s="6"/>
     </row>
     <row r="6197">
-      <c r="A6197" s="11"/>
+      <c r="A6197" s="13"/>
       <c r="B6197" s="2"/>
       <c r="C6197" s="6"/>
     </row>
     <row r="6198">
-      <c r="A6198" s="11"/>
+      <c r="A6198" s="13"/>
       <c r="B6198" s="2"/>
       <c r="C6198" s="6"/>
     </row>
     <row r="6199">
-      <c r="A6199" s="11"/>
+      <c r="A6199" s="13"/>
       <c r="B6199" s="2"/>
       <c r="C6199" s="6"/>
     </row>
     <row r="6200">
-      <c r="A6200" s="11"/>
+      <c r="A6200" s="13"/>
       <c r="B6200" s="2"/>
       <c r="C6200" s="6"/>
     </row>
     <row r="6201">
-      <c r="A6201" s="11"/>
+      <c r="A6201" s="13"/>
       <c r="B6201" s="2"/>
       <c r="C6201" s="6"/>
     </row>
     <row r="6202">
-      <c r="A6202" s="11"/>
+      <c r="A6202" s="13"/>
       <c r="B6202" s="2"/>
       <c r="C6202" s="6"/>
     </row>
     <row r="6203">
-      <c r="A6203" s="11"/>
+      <c r="A6203" s="13"/>
       <c r="B6203" s="2"/>
       <c r="C6203" s="6"/>
     </row>
     <row r="6204">
-      <c r="A6204" s="11"/>
+      <c r="A6204" s="13"/>
       <c r="B6204" s="2"/>
       <c r="C6204" s="6"/>
     </row>
     <row r="6205">
-      <c r="A6205" s="11"/>
+      <c r="A6205" s="13"/>
       <c r="B6205" s="2"/>
       <c r="C6205" s="6"/>
     </row>
     <row r="6206">
-      <c r="A6206" s="11"/>
+      <c r="A6206" s="13"/>
       <c r="B6206" s="2"/>
       <c r="C6206" s="6"/>
     </row>
     <row r="6207">
-      <c r="A6207" s="11"/>
+      <c r="A6207" s="13"/>
       <c r="B6207" s="2"/>
       <c r="C6207" s="6"/>
     </row>
     <row r="6208">
-      <c r="A6208" s="11"/>
+      <c r="A6208" s="13"/>
       <c r="B6208" s="2"/>
       <c r="C6208" s="6"/>
     </row>
     <row r="6209">
-      <c r="A6209" s="11"/>
+      <c r="A6209" s="13"/>
       <c r="B6209" s="2"/>
       <c r="C6209" s="6"/>
     </row>
     <row r="6210">
-      <c r="A6210" s="11"/>
+      <c r="A6210" s="13"/>
       <c r="B6210" s="2"/>
       <c r="C6210" s="6"/>
     </row>
     <row r="6211">
-      <c r="A6211" s="11"/>
+      <c r="A6211" s="13"/>
       <c r="B6211" s="2"/>
       <c r="C6211" s="6"/>
     </row>
     <row r="6212">
-      <c r="A6212" s="11"/>
+      <c r="A6212" s="13"/>
       <c r="B6212" s="2"/>
       <c r="C6212" s="6"/>
     </row>
     <row r="6213">
-      <c r="A6213" s="11"/>
+      <c r="A6213" s="13"/>
       <c r="B6213" s="2"/>
       <c r="C6213" s="6"/>
     </row>
     <row r="6214">
-      <c r="A6214" s="11"/>
+      <c r="A6214" s="13"/>
       <c r="B6214" s="2"/>
       <c r="C6214" s="6"/>
     </row>
     <row r="6215">
-      <c r="A6215" s="11"/>
+      <c r="A6215" s="13"/>
       <c r="B6215" s="2"/>
       <c r="C6215" s="6"/>
     </row>
     <row r="6216">
-      <c r="A6216" s="11"/>
+      <c r="A6216" s="13"/>
       <c r="B6216" s="2"/>
       <c r="C6216" s="6"/>
     </row>
     <row r="6217">
-      <c r="A6217" s="11"/>
+      <c r="A6217" s="13"/>
       <c r="B6217" s="2"/>
       <c r="C6217" s="6"/>
     </row>
     <row r="6218">
-      <c r="A6218" s="11"/>
+      <c r="A6218" s="13"/>
       <c r="B6218" s="2"/>
       <c r="C6218" s="6"/>
     </row>
     <row r="6219">
-      <c r="A6219" s="11"/>
+      <c r="A6219" s="13"/>
       <c r="B6219" s="2"/>
       <c r="C6219" s="6"/>
     </row>
     <row r="6220">
-      <c r="A6220" s="11"/>
+      <c r="A6220" s="13"/>
       <c r="B6220" s="2"/>
       <c r="C6220" s="6"/>
     </row>
     <row r="6221">
-      <c r="A6221" s="11"/>
+      <c r="A6221" s="13"/>
       <c r="B6221" s="2"/>
       <c r="C6221" s="6"/>
     </row>
     <row r="6222">
-      <c r="A6222" s="11"/>
+      <c r="A6222" s="13"/>
       <c r="B6222" s="2"/>
       <c r="C6222" s="6"/>
     </row>
     <row r="6223">
-      <c r="A6223" s="11"/>
+      <c r="A6223" s="13"/>
       <c r="B6223" s="2"/>
       <c r="C6223" s="6"/>
     </row>
     <row r="6224">
-      <c r="A6224" s="11"/>
+      <c r="A6224" s="13"/>
       <c r="B6224" s="2"/>
       <c r="C6224" s="6"/>
     </row>
     <row r="6225">
-      <c r="A6225" s="11"/>
+      <c r="A6225" s="13"/>
       <c r="B6225" s="2"/>
       <c r="C6225" s="6"/>
     </row>
     <row r="6226">
-      <c r="A6226" s="11"/>
+      <c r="A6226" s="13"/>
       <c r="B6226" s="2"/>
       <c r="C6226" s="6"/>
     </row>
     <row r="6227">
-      <c r="A6227" s="11"/>
+      <c r="A6227" s="13"/>
       <c r="B6227" s="2"/>
       <c r="C6227" s="6"/>
     </row>
     <row r="6228">
-      <c r="A6228" s="11"/>
+      <c r="A6228" s="13"/>
       <c r="B6228" s="2"/>
       <c r="C6228" s="6"/>
     </row>
     <row r="6229">
-      <c r="A6229" s="11"/>
+      <c r="A6229" s="13"/>
       <c r="B6229" s="2"/>
       <c r="C6229" s="6"/>
     </row>
     <row r="6230">
-      <c r="A6230" s="11"/>
+      <c r="A6230" s="13"/>
       <c r="B6230" s="2"/>
       <c r="C6230" s="6"/>
     </row>
     <row r="6231">
-      <c r="A6231" s="11"/>
+      <c r="A6231" s="13"/>
       <c r="B6231" s="2"/>
       <c r="C6231" s="6"/>
     </row>
     <row r="6232">
-      <c r="A6232" s="11"/>
+      <c r="A6232" s="13"/>
       <c r="B6232" s="2"/>
       <c r="C6232" s="6"/>
     </row>
     <row r="6233">
-      <c r="A6233" s="11"/>
+      <c r="A6233" s="13"/>
       <c r="B6233" s="2"/>
       <c r="C6233" s="6"/>
     </row>
     <row r="6234">
-      <c r="A6234" s="11"/>
+      <c r="A6234" s="13"/>
       <c r="B6234" s="2"/>
       <c r="C6234" s="6"/>
     </row>
     <row r="6235">
-      <c r="A6235" s="11"/>
+      <c r="A6235" s="13"/>
       <c r="B6235" s="2"/>
       <c r="C6235" s="6"/>
     </row>
     <row r="6236">
-      <c r="A6236" s="11"/>
+      <c r="A6236" s="13"/>
       <c r="B6236" s="2"/>
       <c r="C6236" s="6"/>
     </row>
     <row r="6237">
-      <c r="A6237" s="11"/>
+      <c r="A6237" s="13"/>
       <c r="B6237" s="2"/>
       <c r="C6237" s="6"/>
     </row>
     <row r="6238">
-      <c r="A6238" s="11"/>
+      <c r="A6238" s="13"/>
       <c r="B6238" s="2"/>
       <c r="C6238" s="6"/>
     </row>
     <row r="6239">
-      <c r="A6239" s="11"/>
+      <c r="A6239" s="13"/>
       <c r="B6239" s="2"/>
       <c r="C6239" s="6"/>
     </row>
     <row r="6240">
-      <c r="A6240" s="11"/>
+      <c r="A6240" s="13"/>
       <c r="B6240" s="2"/>
       <c r="C6240" s="6"/>
     </row>
     <row r="6241">
-      <c r="A6241" s="11"/>
+      <c r="A6241" s="13"/>
       <c r="B6241" s="2"/>
       <c r="C6241" s="6"/>
     </row>
     <row r="6242">
-      <c r="A6242" s="11"/>
+      <c r="A6242" s="13"/>
       <c r="B6242" s="2"/>
       <c r="C6242" s="6"/>
     </row>
     <row r="6243">
-      <c r="A6243" s="11"/>
+      <c r="A6243" s="13"/>
       <c r="B6243" s="2"/>
       <c r="C6243" s="6"/>
     </row>
     <row r="6244">
-      <c r="A6244" s="11"/>
+      <c r="A6244" s="13"/>
       <c r="B6244" s="2"/>
       <c r="C6244" s="6"/>
     </row>
     <row r="6245">
-      <c r="A6245" s="11"/>
+      <c r="A6245" s="13"/>
       <c r="B6245" s="2"/>
       <c r="C6245" s="6"/>
     </row>
     <row r="6246">
-      <c r="A6246" s="11"/>
+      <c r="A6246" s="13"/>
       <c r="B6246" s="2"/>
       <c r="C6246" s="6"/>
     </row>
     <row r="6247">
-      <c r="A6247" s="11"/>
+      <c r="A6247" s="13"/>
       <c r="B6247" s="2"/>
       <c r="C6247" s="6"/>
     </row>
     <row r="6248">
-      <c r="A6248" s="11"/>
+      <c r="A6248" s="13"/>
       <c r="B6248" s="2"/>
       <c r="C6248" s="6"/>
     </row>
     <row r="6249">
-      <c r="A6249" s="11"/>
+      <c r="A6249" s="13"/>
       <c r="B6249" s="2"/>
       <c r="C6249" s="6"/>
     </row>
     <row r="6250">
-      <c r="A6250" s="11"/>
+      <c r="A6250" s="13"/>
       <c r="B6250" s="2"/>
       <c r="C6250" s="6"/>
     </row>
     <row r="6251">
-      <c r="A6251" s="11"/>
+      <c r="A6251" s="13"/>
       <c r="B6251" s="2"/>
       <c r="C6251" s="6"/>
     </row>
     <row r="6252">
-      <c r="A6252" s="11"/>
+      <c r="A6252" s="13"/>
       <c r="B6252" s="2"/>
       <c r="C6252" s="6"/>
     </row>
     <row r="6253">
-      <c r="A6253" s="11"/>
+      <c r="A6253" s="13"/>
       <c r="B6253" s="2"/>
       <c r="C6253" s="6"/>
     </row>
     <row r="6254">
-      <c r="A6254" s="11"/>
+      <c r="A6254" s="13"/>
       <c r="B6254" s="2"/>
       <c r="C6254" s="6"/>
     </row>
     <row r="6255">
-      <c r="A6255" s="11"/>
+      <c r="A6255" s="13"/>
       <c r="B6255" s="2"/>
       <c r="C6255" s="6"/>
     </row>
     <row r="6256">
-      <c r="A6256" s="11"/>
+      <c r="A6256" s="13"/>
       <c r="B6256" s="2"/>
       <c r="C6256" s="6"/>
     </row>
     <row r="6257">
-      <c r="A6257" s="11"/>
+      <c r="A6257" s="13"/>
       <c r="B6257" s="2"/>
       <c r="C6257" s="6"/>
     </row>
     <row r="6258">
-      <c r="A6258" s="11"/>
+      <c r="A6258" s="13"/>
       <c r="B6258" s="2"/>
       <c r="C6258" s="6"/>
     </row>
     <row r="6259">
-      <c r="A6259" s="11"/>
+      <c r="A6259" s="13"/>
       <c r="B6259" s="2"/>
       <c r="C6259" s="6"/>
     </row>
     <row r="6260">
-      <c r="A6260" s="11"/>
+      <c r="A6260" s="13"/>
       <c r="B6260" s="2"/>
       <c r="C6260" s="6"/>
     </row>
     <row r="6261">
-      <c r="A6261" s="11"/>
+      <c r="A6261" s="13"/>
       <c r="B6261" s="2"/>
       <c r="C6261" s="6"/>
     </row>
     <row r="6262">
-      <c r="A6262" s="11"/>
+      <c r="A6262" s="13"/>
       <c r="B6262" s="2"/>
       <c r="C6262" s="6"/>
     </row>
     <row r="6263">
-      <c r="A6263" s="11"/>
+      <c r="A6263" s="13"/>
       <c r="B6263" s="2"/>
       <c r="C6263" s="6"/>
     </row>
     <row r="6264">
-      <c r="A6264" s="11"/>
+      <c r="A6264" s="13"/>
       <c r="B6264" s="2"/>
       <c r="C6264" s="6"/>
     </row>
     <row r="6265">
-      <c r="A6265" s="11"/>
+      <c r="A6265" s="13"/>
       <c r="B6265" s="2"/>
       <c r="C6265" s="6"/>
     </row>
     <row r="6266">
-      <c r="A6266" s="11"/>
+      <c r="A6266" s="13"/>
       <c r="B6266" s="2"/>
       <c r="C6266" s="6"/>
     </row>
     <row r="6267">
-      <c r="A6267" s="11"/>
+      <c r="A6267" s="13"/>
       <c r="B6267" s="2"/>
       <c r="C6267" s="6"/>
     </row>
     <row r="6268">
-      <c r="A6268" s="11"/>
+      <c r="A6268" s="13"/>
       <c r="B6268" s="2"/>
       <c r="C6268" s="6"/>
     </row>
     <row r="6269">
-      <c r="A6269" s="11"/>
+      <c r="A6269" s="13"/>
       <c r="B6269" s="2"/>
       <c r="C6269" s="6"/>
     </row>
     <row r="6270">
-      <c r="A6270" s="11"/>
+      <c r="A6270" s="13"/>
       <c r="B6270" s="2"/>
       <c r="C6270" s="6"/>
     </row>
     <row r="6271">
-      <c r="A6271" s="11"/>
+      <c r="A6271" s="13"/>
       <c r="B6271" s="2"/>
       <c r="C6271" s="6"/>
     </row>
     <row r="6272">
-      <c r="A6272" s="11"/>
+      <c r="A6272" s="13"/>
       <c r="B6272" s="2"/>
       <c r="C6272" s="6"/>
     </row>
     <row r="6273">
-      <c r="A6273" s="11"/>
+      <c r="A6273" s="13"/>
       <c r="B6273" s="2"/>
       <c r="C6273" s="6"/>
     </row>
     <row r="6274">
-      <c r="A6274" s="11"/>
+      <c r="A6274" s="13"/>
       <c r="B6274" s="2"/>
       <c r="C6274" s="6"/>
     </row>
     <row r="6275">
-      <c r="A6275" s="11"/>
+      <c r="A6275" s="13"/>
       <c r="B6275" s="2"/>
       <c r="C6275" s="6"/>
     </row>
     <row r="6276">
-      <c r="A6276" s="11"/>
+      <c r="A6276" s="13"/>
       <c r="B6276" s="2"/>
       <c r="C6276" s="6"/>
     </row>
     <row r="6277">
-      <c r="A6277" s="11"/>
+      <c r="A6277" s="13"/>
       <c r="B6277" s="2"/>
       <c r="C6277" s="6"/>
     </row>
     <row r="6278">
-      <c r="A6278" s="11"/>
+      <c r="A6278" s="13"/>
       <c r="B6278" s="2"/>
       <c r="C6278" s="6"/>
     </row>
     <row r="6279">
-      <c r="A6279" s="11"/>
+      <c r="A6279" s="13"/>
       <c r="B6279" s="2"/>
       <c r="C6279" s="6"/>
     </row>
     <row r="6280">
-      <c r="A6280" s="11"/>
+      <c r="A6280" s="13"/>
       <c r="B6280" s="2"/>
       <c r="C6280" s="6"/>
     </row>
     <row r="6281">
-      <c r="A6281" s="11"/>
+      <c r="A6281" s="13"/>
       <c r="B6281" s="2"/>
       <c r="C6281" s="6"/>
     </row>
     <row r="6282">
-      <c r="A6282" s="11"/>
+      <c r="A6282" s="13"/>
       <c r="B6282" s="2"/>
       <c r="C6282" s="6"/>
     </row>
     <row r="6283">
-      <c r="A6283" s="11"/>
+      <c r="A6283" s="13"/>
       <c r="B6283" s="2"/>
       <c r="C6283" s="6"/>
     </row>
     <row r="6284">
-      <c r="A6284" s="11"/>
+      <c r="A6284" s="13"/>
       <c r="B6284" s="2"/>
       <c r="C6284" s="6"/>
     </row>
     <row r="6285">
-      <c r="A6285" s="11"/>
+      <c r="A6285" s="13"/>
       <c r="B6285" s="2"/>
       <c r="C6285" s="6"/>
     </row>
     <row r="6286">
-      <c r="A6286" s="11"/>
+      <c r="A6286" s="13"/>
       <c r="B6286" s="2"/>
       <c r="C6286" s="6"/>
     </row>
     <row r="6287">
-      <c r="A6287" s="11"/>
+      <c r="A6287" s="13"/>
       <c r="B6287" s="2"/>
       <c r="C6287" s="6"/>
     </row>
     <row r="6288">
-      <c r="A6288" s="11"/>
+      <c r="A6288" s="13"/>
       <c r="B6288" s="2"/>
       <c r="C6288" s="6"/>
     </row>
     <row r="6289">
-      <c r="A6289" s="11"/>
+      <c r="A6289" s="13"/>
       <c r="B6289" s="2"/>
       <c r="C6289" s="6"/>
     </row>
     <row r="6290">
-      <c r="A6290" s="11"/>
+      <c r="A6290" s="13"/>
       <c r="B6290" s="2"/>
       <c r="C6290" s="6"/>
     </row>
     <row r="6291">
-      <c r="A6291" s="11"/>
+      <c r="A6291" s="13"/>
       <c r="B6291" s="2"/>
       <c r="C6291" s="6"/>
     </row>
     <row r="6292">
-      <c r="A6292" s="11"/>
+      <c r="A6292" s="13"/>
       <c r="B6292" s="2"/>
       <c r="C6292" s="6"/>
     </row>
     <row r="6293">
-      <c r="A6293" s="11"/>
+      <c r="A6293" s="13"/>
       <c r="B6293" s="2"/>
       <c r="C6293" s="6"/>
     </row>
     <row r="6294">
-      <c r="A6294" s="11"/>
+      <c r="A6294" s="13"/>
       <c r="B6294" s="2"/>
       <c r="C6294" s="6"/>
     </row>
     <row r="6295">
-      <c r="A6295" s="11"/>
+      <c r="A6295" s="13"/>
       <c r="B6295" s="2"/>
       <c r="C6295" s="6"/>
     </row>
     <row r="6296">
-      <c r="A6296" s="11"/>
+      <c r="A6296" s="13"/>
       <c r="B6296" s="2"/>
       <c r="C6296" s="6"/>
     </row>
     <row r="6297">
-      <c r="A6297" s="11"/>
+      <c r="A6297" s="13"/>
       <c r="B6297" s="2"/>
       <c r="C6297" s="6"/>
     </row>
     <row r="6298">
-      <c r="A6298" s="11"/>
+      <c r="A6298" s="13"/>
       <c r="B6298" s="2"/>
       <c r="C6298" s="6"/>
     </row>
     <row r="6299">
-      <c r="A6299" s="11"/>
+      <c r="A6299" s="13"/>
       <c r="B6299" s="2"/>
       <c r="C6299" s="6"/>
     </row>
     <row r="6300">
-      <c r="A6300" s="11"/>
+      <c r="A6300" s="13"/>
       <c r="B6300" s="2"/>
       <c r="C6300" s="6"/>
     </row>
     <row r="6301">
-      <c r="A6301" s="11"/>
+      <c r="A6301" s="13"/>
       <c r="B6301" s="2"/>
       <c r="C6301" s="6"/>
     </row>
     <row r="6302">
-      <c r="A6302" s="11"/>
+      <c r="A6302" s="13"/>
       <c r="B6302" s="2"/>
       <c r="C6302" s="6"/>
     </row>
     <row r="6303">
-      <c r="A6303" s="11"/>
+      <c r="A6303" s="13"/>
       <c r="B6303" s="2"/>
       <c r="C6303" s="6"/>
     </row>
     <row r="6304">
-      <c r="A6304" s="11"/>
+      <c r="A6304" s="13"/>
       <c r="B6304" s="2"/>
       <c r="C6304" s="6"/>
     </row>
     <row r="6305">
-      <c r="A6305" s="11"/>
+      <c r="A6305" s="13"/>
       <c r="B6305" s="2"/>
       <c r="C6305" s="6"/>
     </row>
     <row r="6306">
-      <c r="A6306" s="11"/>
+      <c r="A6306" s="13"/>
       <c r="B6306" s="2"/>
       <c r="C6306" s="6"/>
     </row>
     <row r="6307">
-      <c r="A6307" s="11"/>
+      <c r="A6307" s="13"/>
       <c r="B6307" s="2"/>
       <c r="C6307" s="6"/>
     </row>
     <row r="6308">
-      <c r="A6308" s="11"/>
+      <c r="A6308" s="13"/>
       <c r="B6308" s="2"/>
       <c r="C6308" s="6"/>
     </row>
     <row r="6309">
-      <c r="A6309" s="11"/>
+      <c r="A6309" s="13"/>
       <c r="B6309" s="2"/>
       <c r="C6309" s="6"/>
     </row>
     <row r="6310">
-      <c r="A6310" s="11"/>
+      <c r="A6310" s="13"/>
       <c r="B6310" s="2"/>
       <c r="C6310" s="6"/>
     </row>
     <row r="6311">
-      <c r="A6311" s="11"/>
+      <c r="A6311" s="13"/>
       <c r="B6311" s="2"/>
       <c r="C6311" s="6"/>
     </row>
     <row r="6312">
-      <c r="A6312" s="11"/>
+      <c r="A6312" s="13"/>
       <c r="B6312" s="2"/>
       <c r="C6312" s="6"/>
     </row>
     <row r="6313">
-      <c r="A6313" s="11"/>
+      <c r="A6313" s="13"/>
       <c r="B6313" s="2"/>
       <c r="C6313" s="6"/>
     </row>
     <row r="6314">
-      <c r="A6314" s="11"/>
+      <c r="A6314" s="13"/>
       <c r="B6314" s="2"/>
       <c r="C6314" s="6"/>
     </row>
     <row r="6315">
-      <c r="A6315" s="11"/>
+      <c r="A6315" s="13"/>
       <c r="B6315" s="2"/>
       <c r="C6315" s="6"/>
     </row>
     <row r="6316">
-      <c r="A6316" s="11"/>
+      <c r="A6316" s="13"/>
       <c r="B6316" s="2"/>
       <c r="C6316" s="6"/>
     </row>
     <row r="6317">
-      <c r="A6317" s="11"/>
+      <c r="A6317" s="13"/>
       <c r="B6317" s="2"/>
       <c r="C6317" s="6"/>
     </row>
     <row r="6318">
-      <c r="A6318" s="11"/>
+      <c r="A6318" s="13"/>
       <c r="B6318" s="2"/>
       <c r="C6318" s="6"/>
     </row>
     <row r="6319">
-      <c r="A6319" s="11"/>
+      <c r="A6319" s="13"/>
       <c r="B6319" s="2"/>
       <c r="C6319" s="6"/>
     </row>
     <row r="6320">
-      <c r="A6320" s="11"/>
+      <c r="A6320" s="13"/>
       <c r="B6320" s="2"/>
       <c r="C6320" s="6"/>
     </row>
     <row r="6321">
-      <c r="A6321" s="11"/>
+      <c r="A6321" s="13"/>
       <c r="B6321" s="2"/>
       <c r="C6321" s="6"/>
     </row>
     <row r="6322">
-      <c r="A6322" s="11"/>
+      <c r="A6322" s="13"/>
       <c r="B6322" s="2"/>
       <c r="C6322" s="6"/>
     </row>
     <row r="6323">
-      <c r="A6323" s="11"/>
+      <c r="A6323" s="13"/>
       <c r="B6323" s="2"/>
       <c r="C6323" s="6"/>
     </row>
     <row r="6324">
-      <c r="A6324" s="11"/>
+      <c r="A6324" s="13"/>
       <c r="B6324" s="2"/>
       <c r="C6324" s="6"/>
     </row>
     <row r="6325">
-      <c r="A6325" s="11"/>
+      <c r="A6325" s="13"/>
       <c r="B6325" s="2"/>
       <c r="C6325" s="6"/>
     </row>
     <row r="6326">
-      <c r="A6326" s="11"/>
+      <c r="A6326" s="13"/>
       <c r="B6326" s="2"/>
       <c r="C6326" s="6"/>
     </row>
     <row r="6327">
-      <c r="A6327" s="11"/>
+      <c r="A6327" s="13"/>
       <c r="B6327" s="2"/>
       <c r="C6327" s="6"/>
     </row>
     <row r="6328">
-      <c r="A6328" s="11"/>
+      <c r="A6328" s="13"/>
       <c r="B6328" s="2"/>
       <c r="C6328" s="6"/>
     </row>
     <row r="6329">
-      <c r="A6329" s="11"/>
+      <c r="A6329" s="13"/>
       <c r="B6329" s="2"/>
       <c r="C6329" s="6"/>
     </row>
     <row r="6330">
-      <c r="A6330" s="11"/>
+      <c r="A6330" s="13"/>
       <c r="B6330" s="2"/>
       <c r="C6330" s="6"/>
     </row>
     <row r="6331">
-      <c r="A6331" s="11"/>
+      <c r="A6331" s="13"/>
       <c r="B6331" s="2"/>
       <c r="C6331" s="6"/>
     </row>
     <row r="6332">
-      <c r="A6332" s="11"/>
+      <c r="A6332" s="13"/>
       <c r="B6332" s="2"/>
       <c r="C6332" s="6"/>
     </row>
     <row r="6333">
-      <c r="A6333" s="11"/>
+      <c r="A6333" s="13"/>
       <c r="B6333" s="2"/>
       <c r="C6333" s="6"/>
     </row>
     <row r="6334">
-      <c r="A6334" s="11"/>
+      <c r="A6334" s="13"/>
       <c r="B6334" s="2"/>
       <c r="C6334" s="6"/>
     </row>
     <row r="6335">
-      <c r="A6335" s="11"/>
+      <c r="A6335" s="13"/>
       <c r="B6335" s="2"/>
       <c r="C6335" s="6"/>
     </row>
     <row r="6336">
-      <c r="A6336" s="11"/>
+      <c r="A6336" s="13"/>
       <c r="B6336" s="2"/>
       <c r="C6336" s="6"/>
     </row>
     <row r="6337">
-      <c r="A6337" s="11"/>
+      <c r="A6337" s="13"/>
       <c r="B6337" s="2"/>
       <c r="C6337" s="6"/>
     </row>
     <row r="6338">
-      <c r="A6338" s="11"/>
+      <c r="A6338" s="13"/>
       <c r="B6338" s="2"/>
       <c r="C6338" s="6"/>
     </row>
     <row r="6339">
-      <c r="A6339" s="11"/>
+      <c r="A6339" s="13"/>
       <c r="B6339" s="2"/>
       <c r="C6339" s="6"/>
     </row>
     <row r="6340">
-      <c r="A6340" s="11"/>
+      <c r="A6340" s="13"/>
       <c r="B6340" s="2"/>
       <c r="C6340" s="6"/>
     </row>
     <row r="6341">
-      <c r="A6341" s="11"/>
+      <c r="A6341" s="13"/>
       <c r="B6341" s="2"/>
       <c r="C6341" s="6"/>
     </row>
     <row r="6342">
-      <c r="A6342" s="11"/>
+      <c r="A6342" s="13"/>
       <c r="B6342" s="2"/>
       <c r="C6342" s="6"/>
     </row>
     <row r="6343">
-      <c r="A6343" s="11"/>
+      <c r="A6343" s="13"/>
       <c r="B6343" s="2"/>
       <c r="C6343" s="6"/>
     </row>
     <row r="6344">
-      <c r="A6344" s="11"/>
+      <c r="A6344" s="13"/>
       <c r="B6344" s="2"/>
       <c r="C6344" s="6"/>
     </row>
     <row r="6345">
-      <c r="A6345" s="11"/>
+      <c r="A6345" s="13"/>
       <c r="B6345" s="2"/>
       <c r="C6345" s="6"/>
     </row>
     <row r="6346">
-      <c r="A6346" s="11"/>
+      <c r="A6346" s="13"/>
       <c r="B6346" s="2"/>
       <c r="C6346" s="6"/>
     </row>
     <row r="6347">
-      <c r="A6347" s="11"/>
+      <c r="A6347" s="13"/>
       <c r="B6347" s="2"/>
       <c r="C6347" s="6"/>
     </row>
     <row r="6348">
-      <c r="A6348" s="11"/>
+      <c r="A6348" s="13"/>
       <c r="B6348" s="2"/>
       <c r="C6348" s="6"/>
     </row>
     <row r="6349">
-      <c r="A6349" s="11"/>
+      <c r="A6349" s="13"/>
       <c r="B6349" s="2"/>
       <c r="C6349" s="6"/>
     </row>
     <row r="6350">
-      <c r="A6350" s="11"/>
+      <c r="A6350" s="13"/>
       <c r="B6350" s="2"/>
       <c r="C6350" s="6"/>
     </row>
     <row r="6351">
-      <c r="A6351" s="11"/>
+      <c r="A6351" s="13"/>
       <c r="B6351" s="2"/>
       <c r="C6351" s="6"/>
     </row>
     <row r="6352">
-      <c r="A6352" s="11"/>
+      <c r="A6352" s="13"/>
       <c r="B6352" s="2"/>
       <c r="C6352" s="6"/>
     </row>
     <row r="6353">
-      <c r="A6353" s="11"/>
+      <c r="A6353" s="13"/>
       <c r="B6353" s="2"/>
       <c r="C6353" s="6"/>
     </row>
     <row r="6354">
-      <c r="A6354" s="11"/>
+      <c r="A6354" s="13"/>
       <c r="B6354" s="2"/>
       <c r="C6354" s="6"/>
     </row>
     <row r="6355">
-      <c r="A6355" s="11"/>
+      <c r="A6355" s="13"/>
       <c r="B6355" s="2"/>
       <c r="C6355" s="6"/>
     </row>
     <row r="6356">
-      <c r="A6356" s="11"/>
+      <c r="A6356" s="13"/>
       <c r="B6356" s="2"/>
       <c r="C6356" s="6"/>
     </row>
     <row r="6357">
-      <c r="A6357" s="11"/>
+      <c r="A6357" s="13"/>
       <c r="B6357" s="2"/>
       <c r="C6357" s="6"/>
     </row>
     <row r="6358">
-      <c r="A6358" s="11"/>
+      <c r="A6358" s="13"/>
       <c r="B6358" s="2"/>
       <c r="C6358" s="6"/>
     </row>
     <row r="6359">
-      <c r="A6359" s="11"/>
+      <c r="A6359" s="13"/>
       <c r="B6359" s="2"/>
       <c r="C6359" s="6"/>
     </row>
     <row r="6360">
-      <c r="A6360" s="11"/>
+      <c r="A6360" s="13"/>
       <c r="B6360" s="2"/>
       <c r="C6360" s="6"/>
     </row>
     <row r="6361">
-      <c r="A6361" s="11"/>
+      <c r="A6361" s="13"/>
       <c r="B6361" s="2"/>
       <c r="C6361" s="6"/>
     </row>
     <row r="6362">
-      <c r="A6362" s="11"/>
+      <c r="A6362" s="13"/>
       <c r="B6362" s="2"/>
       <c r="C6362" s="6"/>
     </row>
     <row r="6363">
-      <c r="A6363" s="11"/>
+      <c r="A6363" s="13"/>
       <c r="B6363" s="2"/>
       <c r="C6363" s="6"/>
     </row>
     <row r="6364">
-      <c r="A6364" s="11"/>
+      <c r="A6364" s="13"/>
       <c r="B6364" s="2"/>
       <c r="C6364" s="6"/>
     </row>
     <row r="6365">
-      <c r="A6365" s="11"/>
+      <c r="A6365" s="13"/>
       <c r="B6365" s="2"/>
       <c r="C6365" s="6"/>
     </row>
     <row r="6366">
-      <c r="A6366" s="11"/>
+      <c r="A6366" s="13"/>
       <c r="B6366" s="2"/>
       <c r="C6366" s="6"/>
     </row>
     <row r="6367">
-      <c r="A6367" s="11"/>
+      <c r="A6367" s="13"/>
       <c r="B6367" s="2"/>
       <c r="C6367" s="6"/>
     </row>
     <row r="6368">
-      <c r="A6368" s="11"/>
+      <c r="A6368" s="13"/>
       <c r="B6368" s="2"/>
       <c r="C6368" s="6"/>
     </row>
     <row r="6369">
-      <c r="A6369" s="11"/>
+      <c r="A6369" s="13"/>
       <c r="B6369" s="2"/>
       <c r="C6369" s="6"/>
     </row>
     <row r="6370">
-      <c r="A6370" s="11"/>
+      <c r="A6370" s="13"/>
       <c r="B6370" s="2"/>
       <c r="C6370" s="6"/>
     </row>
     <row r="6371">
-      <c r="A6371" s="11"/>
+      <c r="A6371" s="13"/>
       <c r="B6371" s="2"/>
       <c r="C6371" s="6"/>
     </row>
     <row r="6372">
-      <c r="A6372" s="11"/>
+      <c r="A6372" s="13"/>
       <c r="B6372" s="2"/>
       <c r="C6372" s="6"/>
     </row>
     <row r="6373">
-      <c r="A6373" s="11"/>
+      <c r="A6373" s="13"/>
       <c r="B6373" s="2"/>
       <c r="C6373" s="6"/>
     </row>
     <row r="6374">
-      <c r="A6374" s="11"/>
+      <c r="A6374" s="13"/>
       <c r="B6374" s="2"/>
       <c r="C6374" s="6"/>
     </row>
     <row r="6375">
-      <c r="A6375" s="11"/>
+      <c r="A6375" s="13"/>
       <c r="B6375" s="2"/>
       <c r="C6375" s="6"/>
     </row>
     <row r="6376">
-      <c r="A6376" s="11"/>
+      <c r="A6376" s="13"/>
       <c r="B6376" s="2"/>
       <c r="C6376" s="6"/>
     </row>
     <row r="6377">
-      <c r="A6377" s="11"/>
+      <c r="A6377" s="13"/>
       <c r="B6377" s="2"/>
       <c r="C6377" s="6"/>
     </row>
     <row r="6378">
-      <c r="A6378" s="11"/>
+      <c r="A6378" s="13"/>
       <c r="B6378" s="2"/>
       <c r="C6378" s="6"/>
     </row>
     <row r="6379">
-      <c r="A6379" s="11"/>
+      <c r="A6379" s="13"/>
       <c r="B6379" s="2"/>
       <c r="C6379" s="6"/>
     </row>
     <row r="6380">
-      <c r="A6380" s="11"/>
+      <c r="A6380" s="13"/>
       <c r="B6380" s="2"/>
       <c r="C6380" s="6"/>
     </row>
     <row r="6381">
-      <c r="A6381" s="11"/>
+      <c r="A6381" s="13"/>
       <c r="B6381" s="2"/>
       <c r="C6381" s="6"/>
     </row>
     <row r="6382">
-      <c r="A6382" s="11"/>
+      <c r="A6382" s="13"/>
       <c r="B6382" s="2"/>
       <c r="C6382" s="6"/>
     </row>
     <row r="6383">
-      <c r="A6383" s="11"/>
+      <c r="A6383" s="13"/>
       <c r="B6383" s="2"/>
       <c r="C6383" s="6"/>
     </row>
     <row r="6384">
-      <c r="A6384" s="11"/>
+      <c r="A6384" s="13"/>
       <c r="B6384" s="2"/>
       <c r="C6384" s="6"/>
     </row>
     <row r="6385">
-      <c r="A6385" s="11"/>
+      <c r="A6385" s="13"/>
       <c r="B6385" s="2"/>
       <c r="C6385" s="6"/>
     </row>
     <row r="6386">
-      <c r="A6386" s="11"/>
+      <c r="A6386" s="13"/>
       <c r="B6386" s="2"/>
       <c r="C6386" s="6"/>
     </row>
     <row r="6387">
-      <c r="A6387" s="11"/>
+      <c r="A6387" s="13"/>
       <c r="B6387" s="2"/>
       <c r="C6387" s="6"/>
     </row>
     <row r="6388">
-      <c r="A6388" s="11"/>
+      <c r="A6388" s="13"/>
       <c r="B6388" s="2"/>
       <c r="C6388" s="6"/>
     </row>
     <row r="6389">
-      <c r="A6389" s="11"/>
+      <c r="A6389" s="13"/>
       <c r="B6389" s="2"/>
       <c r="C6389" s="6"/>
     </row>
     <row r="6390">
-      <c r="A6390" s="11"/>
+      <c r="A6390" s="13"/>
       <c r="B6390" s="2"/>
       <c r="C6390" s="6"/>
     </row>
     <row r="6391">
-      <c r="A6391" s="11"/>
+      <c r="A6391" s="13"/>
       <c r="B6391" s="2"/>
       <c r="C6391" s="6"/>
     </row>
     <row r="6392">
-      <c r="A6392" s="11"/>
+      <c r="A6392" s="13"/>
       <c r="B6392" s="2"/>
       <c r="C6392" s="6"/>
     </row>
     <row r="6393">
-      <c r="A6393" s="11"/>
+      <c r="A6393" s="13"/>
       <c r="B6393" s="2"/>
       <c r="C6393" s="6"/>
     </row>
     <row r="6394">
-      <c r="A6394" s="11"/>
+      <c r="A6394" s="13"/>
       <c r="B6394" s="2"/>
       <c r="C6394" s="6"/>
     </row>
     <row r="6395">
-      <c r="A6395" s="11"/>
+      <c r="A6395" s="13"/>
       <c r="B6395" s="2"/>
       <c r="C6395" s="6"/>
     </row>
     <row r="6396">
-      <c r="A6396" s="11"/>
+      <c r="A6396" s="13"/>
       <c r="B6396" s="2"/>
       <c r="C6396" s="6"/>
     </row>
     <row r="6397">
-      <c r="A6397" s="11"/>
+      <c r="A6397" s="13"/>
       <c r="B6397" s="2"/>
       <c r="C6397" s="6"/>
     </row>
     <row r="6398">
-      <c r="A6398" s="11"/>
+      <c r="A6398" s="13"/>
       <c r="B6398" s="2"/>
       <c r="C6398" s="6"/>
     </row>
     <row r="6399">
-      <c r="A6399" s="11"/>
+      <c r="A6399" s="13"/>
       <c r="B6399" s="2"/>
       <c r="C6399" s="6"/>
     </row>
     <row r="6400">
-      <c r="A6400" s="11"/>
+      <c r="A6400" s="13"/>
       <c r="B6400" s="2"/>
       <c r="C6400" s="6"/>
     </row>
     <row r="6401">
-      <c r="A6401" s="11"/>
+      <c r="A6401" s="13"/>
       <c r="B6401" s="2"/>
       <c r="C6401" s="6"/>
     </row>
     <row r="6402">
-      <c r="A6402" s="11"/>
+      <c r="A6402" s="13"/>
       <c r="B6402" s="2"/>
       <c r="C6402" s="6"/>
     </row>
     <row r="6403">
-      <c r="A6403" s="11"/>
+      <c r="A6403" s="13"/>
       <c r="B6403" s="2"/>
       <c r="C6403" s="6"/>
     </row>
     <row r="6404">
-      <c r="A6404" s="11"/>
+      <c r="A6404" s="13"/>
       <c r="B6404" s="2"/>
       <c r="C6404" s="6"/>
     </row>
     <row r="6405">
-      <c r="A6405" s="11"/>
+      <c r="A6405" s="13"/>
       <c r="B6405" s="2"/>
       <c r="C6405" s="6"/>
     </row>
     <row r="6406">
-      <c r="A6406" s="11"/>
+      <c r="A6406" s="13"/>
       <c r="B6406" s="2"/>
       <c r="C6406" s="6"/>
     </row>
     <row r="6407">
-      <c r="A6407" s="11"/>
+      <c r="A6407" s="13"/>
       <c r="B6407" s="2"/>
       <c r="C6407" s="6"/>
     </row>
     <row r="6408">
-      <c r="A6408" s="11"/>
+      <c r="A6408" s="13"/>
       <c r="B6408" s="2"/>
       <c r="C6408" s="6"/>
     </row>
     <row r="6409">
-      <c r="A6409" s="11"/>
+      <c r="A6409" s="13"/>
       <c r="B6409" s="2"/>
       <c r="C6409" s="6"/>
     </row>
     <row r="6410">
-      <c r="A6410" s="11"/>
+      <c r="A6410" s="13"/>
       <c r="B6410" s="2"/>
       <c r="C6410" s="6"/>
     </row>
     <row r="6411">
-      <c r="A6411" s="11"/>
+      <c r="A6411" s="13"/>
       <c r="B6411" s="2"/>
       <c r="C6411" s="6"/>
     </row>
     <row r="6412">
-      <c r="A6412" s="11"/>
+      <c r="A6412" s="13"/>
       <c r="B6412" s="2"/>
       <c r="C6412" s="6"/>
     </row>
     <row r="6413">
-      <c r="A6413" s="11"/>
+      <c r="A6413" s="13"/>
       <c r="B6413" s="2"/>
       <c r="C6413" s="6"/>
     </row>
     <row r="6414">
-      <c r="A6414" s="11"/>
+      <c r="A6414" s="13"/>
       <c r="B6414" s="2"/>
       <c r="C6414" s="6"/>
     </row>
     <row r="6415">
-      <c r="A6415" s="11"/>
+      <c r="A6415" s="13"/>
       <c r="B6415" s="2"/>
       <c r="C6415" s="6"/>
     </row>
     <row r="6416">
-      <c r="A6416" s="11"/>
+      <c r="A6416" s="13"/>
       <c r="B6416" s="2"/>
       <c r="C6416" s="6"/>
     </row>
     <row r="6417">
-      <c r="A6417" s="11"/>
+      <c r="A6417" s="13"/>
       <c r="B6417" s="2"/>
       <c r="C6417" s="6"/>
     </row>
     <row r="6418">
-      <c r="A6418" s="11"/>
+      <c r="A6418" s="13"/>
       <c r="B6418" s="2"/>
       <c r="C6418" s="6"/>
     </row>
     <row r="6419">
-      <c r="A6419" s="11"/>
+      <c r="A6419" s="13"/>
       <c r="B6419" s="2"/>
       <c r="C6419" s="6"/>
     </row>
     <row r="6420">
-      <c r="A6420" s="11"/>
+      <c r="A6420" s="13"/>
       <c r="B6420" s="2"/>
       <c r="C6420" s="6"/>
     </row>
     <row r="6421">
-      <c r="A6421" s="11"/>
+      <c r="A6421" s="13"/>
       <c r="B6421" s="2"/>
       <c r="C6421" s="6"/>
     </row>
     <row r="6422">
-      <c r="A6422" s="11"/>
+      <c r="A6422" s="13"/>
       <c r="B6422" s="2"/>
       <c r="C6422" s="6"/>
     </row>
     <row r="6423">
-      <c r="A6423" s="11"/>
+      <c r="A6423" s="13"/>
       <c r="B6423" s="2"/>
       <c r="C6423" s="6"/>
     </row>
     <row r="6424">
-      <c r="A6424" s="11"/>
+      <c r="A6424" s="13"/>
       <c r="B6424" s="2"/>
       <c r="C6424" s="6"/>
     </row>
     <row r="6425">
-      <c r="A6425" s="11"/>
+      <c r="A6425" s="13"/>
       <c r="B6425" s="2"/>
       <c r="C6425" s="6"/>
     </row>
     <row r="6426">
-      <c r="A6426" s="11"/>
+      <c r="A6426" s="13"/>
       <c r="B6426" s="2"/>
       <c r="C6426" s="6"/>
     </row>
     <row r="6427">
-      <c r="A6427" s="11"/>
+      <c r="A6427" s="13"/>
       <c r="B6427" s="2"/>
       <c r="C6427" s="6"/>
     </row>
     <row r="6428">
-      <c r="A6428" s="11"/>
+      <c r="A6428" s="13"/>
       <c r="B6428" s="2"/>
       <c r="C6428" s="6"/>
     </row>
     <row r="6429">
-      <c r="A6429" s="11"/>
+      <c r="A6429" s="13"/>
       <c r="B6429" s="2"/>
       <c r="C6429" s="6"/>
     </row>
     <row r="6430">
-      <c r="A6430" s="11"/>
+      <c r="A6430" s="13"/>
       <c r="B6430" s="2"/>
       <c r="C6430" s="6"/>
     </row>
     <row r="6431">
-      <c r="A6431" s="11"/>
+      <c r="A6431" s="13"/>
       <c r="B6431" s="2"/>
       <c r="C6431" s="6"/>
     </row>
     <row r="6432">
-      <c r="A6432" s="11"/>
+      <c r="A6432" s="13"/>
       <c r="B6432" s="2"/>
       <c r="C6432" s="6"/>
     </row>
     <row r="6433">
-      <c r="A6433" s="11"/>
+      <c r="A6433" s="13"/>
       <c r="B6433" s="2"/>
       <c r="C6433" s="6"/>
     </row>
     <row r="6434">
-      <c r="A6434" s="11"/>
+      <c r="A6434" s="13"/>
       <c r="B6434" s="2"/>
       <c r="C6434" s="6"/>
     </row>
     <row r="6435">
-      <c r="A6435" s="11"/>
+      <c r="A6435" s="13"/>
       <c r="B6435" s="2"/>
       <c r="C6435" s="6"/>
     </row>
     <row r="6436">
-      <c r="A6436" s="11"/>
+      <c r="A6436" s="13"/>
       <c r="B6436" s="2"/>
       <c r="C6436" s="6"/>
     </row>
     <row r="6437">
-      <c r="A6437" s="11"/>
+      <c r="A6437" s="13"/>
       <c r="B6437" s="2"/>
       <c r="C6437" s="6"/>
     </row>
     <row r="6438">
-      <c r="A6438" s="11"/>
+      <c r="A6438" s="13"/>
       <c r="B6438" s="2"/>
       <c r="C6438" s="6"/>
     </row>
     <row r="6439">
-      <c r="A6439" s="11"/>
+      <c r="A6439" s="13"/>
       <c r="B6439" s="2"/>
       <c r="C6439" s="6"/>
     </row>
     <row r="6440">
-      <c r="A6440" s="11"/>
+      <c r="A6440" s="13"/>
       <c r="B6440" s="2"/>
       <c r="C6440" s="6"/>
     </row>
     <row r="6441">
-      <c r="A6441" s="11"/>
+      <c r="A6441" s="13"/>
       <c r="B6441" s="2"/>
       <c r="C6441" s="6"/>
     </row>
     <row r="6442">
-      <c r="A6442" s="11"/>
+      <c r="A6442" s="13"/>
       <c r="B6442" s="2"/>
       <c r="C6442" s="6"/>
     </row>
     <row r="6443">
-      <c r="A6443" s="11"/>
+      <c r="A6443" s="13"/>
       <c r="B6443" s="2"/>
       <c r="C6443" s="6"/>
     </row>
     <row r="6444">
-      <c r="A6444" s="11"/>
+      <c r="A6444" s="13"/>
       <c r="B6444" s="2"/>
       <c r="C6444" s="6"/>
     </row>
     <row r="6445">
-      <c r="A6445" s="11"/>
+      <c r="A6445" s="13"/>
       <c r="B6445" s="2"/>
       <c r="C6445" s="6"/>
     </row>
     <row r="6446">
-      <c r="A6446" s="11"/>
+      <c r="A6446" s="13"/>
       <c r="B6446" s="2"/>
       <c r="C6446" s="6"/>
     </row>
     <row r="6447">
-      <c r="A6447" s="11"/>
+      <c r="A6447" s="13"/>
       <c r="B6447" s="2"/>
       <c r="C6447" s="6"/>
     </row>
     <row r="6448">
-      <c r="A6448" s="11"/>
+      <c r="A6448" s="13"/>
       <c r="B6448" s="2"/>
       <c r="C6448" s="6"/>
     </row>
     <row r="6449">
-      <c r="A6449" s="11"/>
+      <c r="A6449" s="13"/>
       <c r="B6449" s="2"/>
       <c r="C6449" s="6"/>
     </row>
     <row r="6450">
-      <c r="A6450" s="11"/>
+      <c r="A6450" s="13"/>
       <c r="B6450" s="2"/>
       <c r="C6450" s="6"/>
     </row>
     <row r="6451">
-      <c r="A6451" s="11"/>
+      <c r="A6451" s="13"/>
       <c r="B6451" s="2"/>
       <c r="C6451" s="6"/>
     </row>
     <row r="6452">
-      <c r="A6452" s="11"/>
+      <c r="A6452" s="13"/>
       <c r="B6452" s="2"/>
       <c r="C6452" s="6"/>
     </row>
     <row r="6453">
-      <c r="A6453" s="11"/>
+      <c r="A6453" s="13"/>
       <c r="B6453" s="2"/>
       <c r="C6453" s="6"/>
     </row>
     <row r="6454">
-      <c r="A6454" s="11"/>
+      <c r="A6454" s="13"/>
       <c r="B6454" s="2"/>
       <c r="C6454" s="6"/>
     </row>
     <row r="6455">
-      <c r="A6455" s="11"/>
+      <c r="A6455" s="13"/>
       <c r="B6455" s="2"/>
       <c r="C6455" s="6"/>
     </row>
     <row r="6456">
-      <c r="A6456" s="11"/>
+      <c r="A6456" s="13"/>
       <c r="B6456" s="2"/>
       <c r="C6456" s="6"/>
     </row>
     <row r="6457">
-      <c r="A6457" s="11"/>
+      <c r="A6457" s="13"/>
       <c r="B6457" s="2"/>
       <c r="C6457" s="6"/>
     </row>
     <row r="6458">
-      <c r="A6458" s="11"/>
+      <c r="A6458" s="13"/>
       <c r="B6458" s="2"/>
       <c r="C6458" s="6"/>
     </row>
     <row r="6459">
-      <c r="A6459" s="11"/>
+      <c r="A6459" s="13"/>
       <c r="B6459" s="2"/>
       <c r="C6459" s="6"/>
     </row>
     <row r="6460">
-      <c r="A6460" s="11"/>
+      <c r="A6460" s="13"/>
       <c r="B6460" s="2"/>
       <c r="C6460" s="6"/>
     </row>
     <row r="6461">
-      <c r="A6461" s="11"/>
+      <c r="A6461" s="13"/>
       <c r="B6461" s="2"/>
       <c r="C6461" s="6"/>
     </row>
     <row r="6462">
-      <c r="A6462" s="11"/>
+      <c r="A6462" s="13"/>
       <c r="B6462" s="2"/>
       <c r="C6462" s="6"/>
     </row>
     <row r="6463">
-      <c r="A6463" s="11"/>
+      <c r="A6463" s="13"/>
       <c r="B6463" s="2"/>
       <c r="C6463" s="6"/>
     </row>
     <row r="6464">
-      <c r="A6464" s="11"/>
+      <c r="A6464" s="13"/>
       <c r="B6464" s="2"/>
       <c r="C6464" s="6"/>
     </row>
     <row r="6465">
-      <c r="A6465" s="11"/>
+      <c r="A6465" s="13"/>
       <c r="B6465" s="2"/>
       <c r="C6465" s="6"/>
     </row>
     <row r="6466">
-      <c r="A6466" s="11"/>
+      <c r="A6466" s="13"/>
       <c r="B6466" s="2"/>
       <c r="C6466" s="6"/>
     </row>
     <row r="6467">
-      <c r="A6467" s="11"/>
+      <c r="A6467" s="13"/>
       <c r="B6467" s="2"/>
       <c r="C6467" s="6"/>
     </row>
     <row r="6468">
-      <c r="A6468" s="11"/>
+      <c r="A6468" s="13"/>
       <c r="B6468" s="2"/>
       <c r="C6468" s="6"/>
     </row>
     <row r="6469">
-      <c r="A6469" s="11"/>
+      <c r="A6469" s="13"/>
       <c r="B6469" s="2"/>
       <c r="C6469" s="6"/>
     </row>
     <row r="6470">
-      <c r="A6470" s="11"/>
+      <c r="A6470" s="13"/>
       <c r="B6470" s="2"/>
       <c r="C6470" s="6"/>
     </row>
     <row r="6471">
-      <c r="A6471" s="11"/>
+      <c r="A6471" s="13"/>
       <c r="B6471" s="2"/>
       <c r="C6471" s="6"/>
     </row>
     <row r="6472">
-      <c r="A6472" s="11"/>
+      <c r="A6472" s="13"/>
       <c r="B6472" s="2"/>
       <c r="C6472" s="6"/>
     </row>
     <row r="6473">
-      <c r="A6473" s="11"/>
+      <c r="A6473" s="13"/>
       <c r="B6473" s="2"/>
       <c r="C6473" s="6"/>
     </row>
     <row r="6474">
-      <c r="A6474" s="11"/>
+      <c r="A6474" s="13"/>
       <c r="B6474" s="2"/>
       <c r="C6474" s="6"/>
     </row>
     <row r="6475">
-      <c r="A6475" s="11"/>
+      <c r="A6475" s="13"/>
       <c r="B6475" s="2"/>
       <c r="C6475" s="6"/>
     </row>
     <row r="6476">
-      <c r="A6476" s="11"/>
+      <c r="A6476" s="13"/>
       <c r="B6476" s="2"/>
       <c r="C6476" s="6"/>
     </row>
     <row r="6477">
-      <c r="A6477" s="11"/>
+      <c r="A6477" s="13"/>
       <c r="B6477" s="2"/>
       <c r="C6477" s="6"/>
     </row>
     <row r="6478">
-      <c r="A6478" s="11"/>
+      <c r="A6478" s="13"/>
       <c r="B6478" s="2"/>
       <c r="C6478" s="6"/>
     </row>
     <row r="6479">
-      <c r="A6479" s="11"/>
+      <c r="A6479" s="13"/>
       <c r="B6479" s="2"/>
       <c r="C6479" s="6"/>
     </row>
     <row r="6480">
-      <c r="A6480" s="11"/>
+      <c r="A6480" s="13"/>
       <c r="B6480" s="2"/>
       <c r="C6480" s="6"/>
     </row>
     <row r="6481">
-      <c r="A6481" s="11"/>
+      <c r="A6481" s="13"/>
       <c r="B6481" s="2"/>
       <c r="C6481" s="6"/>
     </row>
     <row r="6482">
-      <c r="A6482" s="11"/>
+      <c r="A6482" s="13"/>
       <c r="B6482" s="2"/>
       <c r="C6482" s="6"/>
     </row>
     <row r="6483">
-      <c r="A6483" s="11"/>
+      <c r="A6483" s="13"/>
       <c r="B6483" s="2"/>
       <c r="C6483" s="6"/>
     </row>
     <row r="6484">
-      <c r="A6484" s="11"/>
+      <c r="A6484" s="13"/>
       <c r="B6484" s="2"/>
       <c r="C6484" s="6"/>
     </row>
     <row r="6485">
-      <c r="A6485" s="11"/>
+      <c r="A6485" s="13"/>
       <c r="B6485" s="2"/>
       <c r="C6485" s="6"/>
     </row>
     <row r="6486">
-      <c r="A6486" s="11"/>
+      <c r="A6486" s="13"/>
       <c r="B6486" s="2"/>
       <c r="C6486" s="6"/>
     </row>
     <row r="6487">
-      <c r="A6487" s="11"/>
+      <c r="A6487" s="13"/>
       <c r="B6487" s="2"/>
       <c r="C6487" s="6"/>
     </row>
     <row r="6488">
-      <c r="A6488" s="11"/>
+      <c r="A6488" s="13"/>
       <c r="B6488" s="2"/>
       <c r="C6488" s="6"/>
     </row>
     <row r="6489">
-      <c r="A6489" s="11"/>
+      <c r="A6489" s="13"/>
       <c r="B6489" s="2"/>
       <c r="C6489" s="6"/>
     </row>
     <row r="6490">
-      <c r="A6490" s="11"/>
+      <c r="A6490" s="13"/>
       <c r="B6490" s="2"/>
       <c r="C6490" s="6"/>
     </row>
     <row r="6491">
-      <c r="A6491" s="11"/>
+      <c r="A6491" s="13"/>
       <c r="B6491" s="2"/>
       <c r="C6491" s="6"/>
     </row>
     <row r="6492">
-      <c r="A6492" s="11"/>
+      <c r="A6492" s="13"/>
       <c r="B6492" s="2"/>
       <c r="C6492" s="6"/>
     </row>
     <row r="6493">
-      <c r="A6493" s="11"/>
+      <c r="A6493" s="13"/>
       <c r="B6493" s="2"/>
       <c r="C6493" s="6"/>
     </row>
     <row r="6494">
-      <c r="A6494" s="11"/>
+      <c r="A6494" s="13"/>
       <c r="B6494" s="2"/>
       <c r="C6494" s="6"/>
     </row>
     <row r="6495">
-      <c r="A6495" s="11"/>
+      <c r="A6495" s="13"/>
       <c r="B6495" s="2"/>
       <c r="C6495" s="6"/>
     </row>
     <row r="6496">
-      <c r="A6496" s="11"/>
+      <c r="A6496" s="13"/>
       <c r="B6496" s="2"/>
       <c r="C6496" s="6"/>
     </row>
     <row r="6497">
-      <c r="A6497" s="11"/>
+      <c r="A6497" s="13"/>
       <c r="B6497" s="2"/>
       <c r="C6497" s="6"/>
     </row>
     <row r="6498">
-      <c r="A6498" s="11"/>
+      <c r="A6498" s="13"/>
       <c r="B6498" s="2"/>
       <c r="C6498" s="6"/>
     </row>
     <row r="6499">
-      <c r="A6499" s="11"/>
+      <c r="A6499" s="13"/>
       <c r="B6499" s="2"/>
       <c r="C6499" s="6"/>
     </row>
     <row r="6500">
-      <c r="A6500" s="11"/>
+      <c r="A6500" s="13"/>
       <c r="B6500" s="2"/>
       <c r="C6500" s="6"/>
     </row>
     <row r="6501">
-      <c r="A6501" s="11"/>
+      <c r="A6501" s="13"/>
       <c r="B6501" s="2"/>
       <c r="C6501" s="6"/>
     </row>
     <row r="6502">
-      <c r="A6502" s="11"/>
+      <c r="A6502" s="13"/>
       <c r="B6502" s="2"/>
       <c r="C6502" s="6"/>
     </row>
     <row r="6503">
-      <c r="A6503" s="11"/>
+      <c r="A6503" s="13"/>
       <c r="B6503" s="2"/>
       <c r="C6503" s="6"/>
     </row>
     <row r="6504">
-      <c r="A6504" s="11"/>
+      <c r="A6504" s="13"/>
       <c r="B6504" s="2"/>
       <c r="C6504" s="6"/>
     </row>
     <row r="6505">
-      <c r="A6505" s="11"/>
+      <c r="A6505" s="13"/>
       <c r="B6505" s="2"/>
       <c r="C6505" s="6"/>
     </row>
     <row r="6506">
-      <c r="A6506" s="11"/>
+      <c r="A6506" s="13"/>
       <c r="B6506" s="2"/>
       <c r="C6506" s="6"/>
     </row>
     <row r="6507">
-      <c r="A6507" s="11"/>
+      <c r="A6507" s="13"/>
       <c r="B6507" s="2"/>
       <c r="C6507" s="6"/>
     </row>
     <row r="6508">
-      <c r="A6508" s="11"/>
+      <c r="A6508" s="13"/>
       <c r="B6508" s="2"/>
       <c r="C6508" s="6"/>
     </row>
     <row r="6509">
-      <c r="A6509" s="11"/>
+      <c r="A6509" s="13"/>
       <c r="B6509" s="2"/>
       <c r="C6509" s="6"/>
     </row>
     <row r="6510">
-      <c r="A6510" s="11"/>
+      <c r="A6510" s="13"/>
       <c r="B6510" s="2"/>
       <c r="C6510" s="6"/>
     </row>
     <row r="6511">
-      <c r="A6511" s="11"/>
+      <c r="A6511" s="13"/>
       <c r="B6511" s="2"/>
       <c r="C6511" s="6"/>
     </row>
     <row r="6512">
-      <c r="A6512" s="11"/>
+      <c r="A6512" s="13"/>
       <c r="B6512" s="2"/>
       <c r="C6512" s="6"/>
     </row>
     <row r="6513">
-      <c r="A6513" s="11"/>
+      <c r="A6513" s="13"/>
       <c r="B6513" s="2"/>
       <c r="C6513" s="6"/>
     </row>
     <row r="6514">
-      <c r="A6514" s="11"/>
+      <c r="A6514" s="13"/>
       <c r="B6514" s="2"/>
       <c r="C6514" s="6"/>
     </row>
     <row r="6515">
-      <c r="A6515" s="11"/>
+      <c r="A6515" s="13"/>
       <c r="B6515" s="2"/>
       <c r="C6515" s="6"/>
     </row>
     <row r="6516">
-      <c r="A6516" s="11"/>
+      <c r="A6516" s="13"/>
       <c r="B6516" s="2"/>
       <c r="C6516" s="6"/>
     </row>
     <row r="6517">
-      <c r="A6517" s="11"/>
+      <c r="A6517" s="13"/>
       <c r="B6517" s="2"/>
       <c r="C6517" s="6"/>
     </row>
     <row r="6518">
-      <c r="A6518" s="11"/>
+      <c r="A6518" s="13"/>
       <c r="B6518" s="2"/>
       <c r="C6518" s="6"/>
     </row>
     <row r="6519">
-      <c r="A6519" s="11"/>
+      <c r="A6519" s="13"/>
       <c r="B6519" s="2"/>
       <c r="C6519" s="6"/>
     </row>
     <row r="6520">
-      <c r="A6520" s="11"/>
+      <c r="A6520" s="13"/>
       <c r="B6520" s="2"/>
       <c r="C6520" s="6"/>
     </row>
     <row r="6521">
-      <c r="A6521" s="11"/>
+      <c r="A6521" s="13"/>
       <c r="B6521" s="2"/>
       <c r="C6521" s="6"/>
     </row>
     <row r="6522">
-      <c r="A6522" s="11"/>
+      <c r="A6522" s="13"/>
       <c r="B6522" s="2"/>
       <c r="C6522" s="6"/>
     </row>
     <row r="6523">
-      <c r="A6523" s="11"/>
+      <c r="A6523" s="13"/>
       <c r="B6523" s="2"/>
       <c r="C6523" s="6"/>
     </row>
     <row r="6524">
-      <c r="A6524" s="11"/>
+      <c r="A6524" s="13"/>
       <c r="B6524" s="2"/>
       <c r="C6524" s="6"/>
     </row>
     <row r="6525">
-      <c r="A6525" s="11"/>
+      <c r="A6525" s="13"/>
       <c r="B6525" s="2"/>
       <c r="C6525" s="6"/>
     </row>
     <row r="6526">
-      <c r="A6526" s="11"/>
+      <c r="A6526" s="13"/>
       <c r="B6526" s="2"/>
       <c r="C6526" s="6"/>
     </row>
     <row r="6527">
-      <c r="A6527" s="11"/>
+      <c r="A6527" s="13"/>
       <c r="B6527" s="2"/>
       <c r="C6527" s="6"/>
     </row>
     <row r="6528">
-      <c r="A6528" s="11"/>
+      <c r="A6528" s="13"/>
       <c r="B6528" s="2"/>
       <c r="C6528" s="6"/>
     </row>
     <row r="6529">
-      <c r="A6529" s="11"/>
+      <c r="A6529" s="13"/>
       <c r="B6529" s="2"/>
       <c r="C6529" s="6"/>
     </row>
     <row r="6530">
-      <c r="A6530" s="11"/>
+      <c r="A6530" s="13"/>
       <c r="B6530" s="2"/>
       <c r="C6530" s="6"/>
     </row>
     <row r="6531">
-      <c r="A6531" s="11"/>
+      <c r="A6531" s="13"/>
       <c r="B6531" s="2"/>
       <c r="C6531" s="6"/>
     </row>
     <row r="6532">
-      <c r="A6532" s="11"/>
+      <c r="A6532" s="13"/>
       <c r="B6532" s="2"/>
       <c r="C6532" s="6"/>
     </row>
     <row r="6533">
-      <c r="A6533" s="11"/>
+      <c r="A6533" s="13"/>
       <c r="B6533" s="2"/>
       <c r="C6533" s="6"/>
     </row>
     <row r="6534">
-      <c r="A6534" s="11"/>
+      <c r="A6534" s="13"/>
       <c r="B6534" s="2"/>
       <c r="C6534" s="6"/>
     </row>
     <row r="6535">
-      <c r="A6535" s="11"/>
+      <c r="A6535" s="13"/>
       <c r="B6535" s="2"/>
       <c r="C6535" s="6"/>
     </row>
     <row r="6536">
-      <c r="A6536" s="11"/>
+      <c r="A6536" s="13"/>
       <c r="B6536" s="2"/>
       <c r="C6536" s="6"/>
     </row>
     <row r="6537">
-      <c r="A6537" s="11"/>
+      <c r="A6537" s="13"/>
       <c r="B6537" s="2"/>
       <c r="C6537" s="6"/>
     </row>
     <row r="6538">
-      <c r="A6538" s="11"/>
+      <c r="A6538" s="13"/>
       <c r="B6538" s="2"/>
       <c r="C6538" s="6"/>
     </row>
     <row r="6539">
-      <c r="A6539" s="11"/>
+      <c r="A6539" s="13"/>
       <c r="B6539" s="2"/>
       <c r="C6539" s="6"/>
     </row>
     <row r="6540">
-      <c r="A6540" s="11"/>
+      <c r="A6540" s="13"/>
       <c r="B6540" s="2"/>
       <c r="C6540" s="6"/>
     </row>
     <row r="6541">
-      <c r="A6541" s="11"/>
+      <c r="A6541" s="13"/>
       <c r="B6541" s="2"/>
       <c r="C6541" s="6"/>
     </row>
     <row r="6542">
-      <c r="A6542" s="11"/>
+      <c r="A6542" s="13"/>
       <c r="B6542" s="2"/>
       <c r="C6542" s="6"/>
     </row>
     <row r="6543">
-      <c r="A6543" s="11"/>
+      <c r="A6543" s="13"/>
       <c r="B6543" s="2"/>
       <c r="C6543" s="6"/>
     </row>
     <row r="6544">
-      <c r="A6544" s="11"/>
+      <c r="A6544" s="13"/>
       <c r="B6544" s="2"/>
       <c r="C6544" s="6"/>
     </row>
     <row r="6545">
-      <c r="A6545" s="11"/>
+      <c r="A6545" s="13"/>
       <c r="B6545" s="2"/>
       <c r="C6545" s="6"/>
     </row>
     <row r="6546">
-      <c r="A6546" s="11"/>
+      <c r="A6546" s="13"/>
       <c r="B6546" s="2"/>
       <c r="C6546" s="6"/>
     </row>
     <row r="6547">
-      <c r="A6547" s="11"/>
+      <c r="A6547" s="13"/>
       <c r="B6547" s="2"/>
       <c r="C6547" s="6"/>
     </row>
     <row r="6548">
-      <c r="A6548" s="11"/>
+      <c r="A6548" s="13"/>
       <c r="B6548" s="2"/>
       <c r="C6548" s="6"/>
     </row>
     <row r="6549">
-      <c r="A6549" s="11"/>
+      <c r="A6549" s="13"/>
       <c r="B6549" s="2"/>
       <c r="C6549" s="6"/>
     </row>
     <row r="6550">
-      <c r="A6550" s="11"/>
+      <c r="A6550" s="13"/>
       <c r="B6550" s="2"/>
       <c r="C6550" s="6"/>
     </row>
     <row r="6551">
-      <c r="A6551" s="11"/>
+      <c r="A6551" s="13"/>
       <c r="B6551" s="2"/>
       <c r="C6551" s="6"/>
     </row>
     <row r="6552">
-      <c r="A6552" s="11"/>
+      <c r="A6552" s="13"/>
       <c r="B6552" s="2"/>
       <c r="C6552" s="6"/>
     </row>
     <row r="6553">
-      <c r="A6553" s="11"/>
+      <c r="A6553" s="13"/>
       <c r="B6553" s="2"/>
       <c r="C6553" s="6"/>
     </row>
     <row r="6554">
-      <c r="A6554" s="11"/>
+      <c r="A6554" s="13"/>
       <c r="B6554" s="2"/>
       <c r="C6554" s="6"/>
     </row>
     <row r="6555">
-      <c r="A6555" s="11"/>
+      <c r="A6555" s="13"/>
       <c r="B6555" s="2"/>
       <c r="C6555" s="6"/>
     </row>
     <row r="6556">
-      <c r="A6556" s="11"/>
+      <c r="A6556" s="13"/>
       <c r="B6556" s="2"/>
       <c r="C6556" s="6"/>
     </row>
     <row r="6557">
-      <c r="A6557" s="11"/>
+      <c r="A6557" s="13"/>
       <c r="B6557" s="2"/>
       <c r="C6557" s="6"/>
     </row>
     <row r="6558">
-      <c r="A6558" s="11"/>
+      <c r="A6558" s="13"/>
       <c r="B6558" s="2"/>
       <c r="C6558" s="6"/>
     </row>
     <row r="6559">
-      <c r="A6559" s="11"/>
+      <c r="A6559" s="13"/>
       <c r="B6559" s="2"/>
       <c r="C6559" s="6"/>
     </row>
     <row r="6560">
-      <c r="A6560" s="11"/>
+      <c r="A6560" s="13"/>
       <c r="B6560" s="2"/>
       <c r="C6560" s="6"/>
     </row>
     <row r="6561">
-      <c r="A6561" s="11"/>
+      <c r="A6561" s="13"/>
       <c r="B6561" s="2"/>
       <c r="C6561" s="6"/>
     </row>
     <row r="6562">
-      <c r="A6562" s="11"/>
+      <c r="A6562" s="13"/>
       <c r="B6562" s="2"/>
       <c r="C6562" s="6"/>
     </row>
     <row r="6563">
-      <c r="A6563" s="11"/>
+      <c r="A6563" s="13"/>
       <c r="B6563" s="2"/>
       <c r="C6563" s="6"/>
     </row>
     <row r="6564">
-      <c r="A6564" s="11"/>
+      <c r="A6564" s="13"/>
       <c r="B6564" s="2"/>
       <c r="C6564" s="6"/>
     </row>
     <row r="6565">
-      <c r="A6565" s="11"/>
+      <c r="A6565" s="13"/>
       <c r="B6565" s="2"/>
       <c r="C6565" s="6"/>
     </row>
     <row r="6566">
-      <c r="A6566" s="11"/>
+      <c r="A6566" s="13"/>
       <c r="B6566" s="2"/>
       <c r="C6566" s="6"/>
     </row>
     <row r="6567">
-      <c r="A6567" s="11"/>
+      <c r="A6567" s="13"/>
       <c r="B6567" s="2"/>
       <c r="C6567" s="6"/>
     </row>
     <row r="6568">
-      <c r="A6568" s="11"/>
+      <c r="A6568" s="13"/>
       <c r="B6568" s="2"/>
       <c r="C6568" s="6"/>
     </row>
     <row r="6569">
-      <c r="A6569" s="11"/>
+      <c r="A6569" s="13"/>
       <c r="B6569" s="2"/>
       <c r="C6569" s="6"/>
     </row>
     <row r="6570">
-      <c r="A6570" s="11"/>
+      <c r="A6570" s="13"/>
       <c r="B6570" s="2"/>
       <c r="C6570" s="6"/>
     </row>
     <row r="6571">
-      <c r="A6571" s="11"/>
+      <c r="A6571" s="13"/>
       <c r="B6571" s="2"/>
       <c r="C6571" s="6"/>
     </row>
     <row r="6572">
-      <c r="A6572" s="11"/>
+      <c r="A6572" s="13"/>
       <c r="B6572" s="2"/>
       <c r="C6572" s="6"/>
     </row>
     <row r="6573">
-      <c r="A6573" s="11"/>
+      <c r="A6573" s="13"/>
       <c r="B6573" s="2"/>
       <c r="C6573" s="6"/>
     </row>
     <row r="6574">
-      <c r="A6574" s="11"/>
+      <c r="A6574" s="13"/>
       <c r="B6574" s="2"/>
       <c r="C6574" s="6"/>
     </row>
     <row r="6575">
-      <c r="A6575" s="11"/>
+      <c r="A6575" s="13"/>
       <c r="B6575" s="2"/>
       <c r="C6575" s="6"/>
     </row>
     <row r="6576">
-      <c r="A6576" s="11"/>
+      <c r="A6576" s="13"/>
       <c r="B6576" s="2"/>
       <c r="C6576" s="6"/>
     </row>
     <row r="6577">
-      <c r="A6577" s="11"/>
+      <c r="A6577" s="13"/>
       <c r="B6577" s="2"/>
       <c r="C6577" s="6"/>
     </row>
     <row r="6578">
-      <c r="A6578" s="11"/>
+      <c r="A6578" s="13"/>
       <c r="B6578" s="2"/>
       <c r="C6578" s="6"/>
     </row>
     <row r="6579">
-      <c r="A6579" s="11"/>
+      <c r="A6579" s="13"/>
       <c r="B6579" s="2"/>
       <c r="C6579" s="6"/>
     </row>
     <row r="6580">
-      <c r="A6580" s="11"/>
+      <c r="A6580" s="13"/>
       <c r="B6580" s="2"/>
       <c r="C6580" s="6"/>
     </row>
     <row r="6581">
-      <c r="A6581" s="11"/>
+      <c r="A6581" s="13"/>
       <c r="B6581" s="2"/>
       <c r="C6581" s="6"/>
     </row>
     <row r="6582">
-      <c r="A6582" s="11"/>
+      <c r="A6582" s="13"/>
       <c r="B6582" s="2"/>
       <c r="C6582" s="6"/>
     </row>
     <row r="6583">
-      <c r="A6583" s="11"/>
+      <c r="A6583" s="13"/>
       <c r="B6583" s="2"/>
       <c r="C6583" s="6"/>
     </row>
     <row r="6584">
-      <c r="A6584" s="11"/>
+      <c r="A6584" s="13"/>
       <c r="B6584" s="2"/>
       <c r="C6584" s="6"/>
     </row>
     <row r="6585">
-      <c r="A6585" s="11"/>
+      <c r="A6585" s="13"/>
       <c r="B6585" s="2"/>
       <c r="C6585" s="6"/>
     </row>
     <row r="6586">
-      <c r="A6586" s="11"/>
+      <c r="A6586" s="13"/>
       <c r="B6586" s="2"/>
       <c r="C6586" s="6"/>
     </row>
     <row r="6587">
-      <c r="A6587" s="11"/>
+      <c r="A6587" s="13"/>
       <c r="B6587" s="2"/>
       <c r="C6587" s="6"/>
     </row>
     <row r="6588">
-      <c r="A6588" s="11"/>
+      <c r="A6588" s="13"/>
       <c r="B6588" s="2"/>
       <c r="C6588" s="6"/>
     </row>
     <row r="6589">
-      <c r="A6589" s="11"/>
+      <c r="A6589" s="13"/>
       <c r="B6589" s="2"/>
       <c r="C6589" s="6"/>
     </row>
     <row r="6590">
-      <c r="A6590" s="11"/>
+      <c r="A6590" s="13"/>
       <c r="B6590" s="2"/>
       <c r="C6590" s="6"/>
     </row>
     <row r="6591">
-      <c r="A6591" s="11"/>
+      <c r="A6591" s="13"/>
       <c r="B6591" s="2"/>
       <c r="C6591" s="6"/>
     </row>
     <row r="6592">
-      <c r="A6592" s="11"/>
+      <c r="A6592" s="13"/>
       <c r="B6592" s="2"/>
       <c r="C6592" s="6"/>
     </row>
     <row r="6593">
-      <c r="A6593" s="11"/>
+      <c r="A6593" s="13"/>
       <c r="B6593" s="2"/>
       <c r="C6593" s="6"/>
     </row>
     <row r="6594">
-      <c r="A6594" s="11"/>
+      <c r="A6594" s="13"/>
       <c r="B6594" s="2"/>
       <c r="C6594" s="6"/>
     </row>
     <row r="6595">
-      <c r="A6595" s="11"/>
+      <c r="A6595" s="13"/>
       <c r="B6595" s="2"/>
       <c r="C6595" s="6"/>
     </row>
     <row r="6596">
-      <c r="A6596" s="11"/>
+      <c r="A6596" s="13"/>
       <c r="B6596" s="2"/>
       <c r="C6596" s="6"/>
     </row>
     <row r="6597">
-      <c r="A6597" s="11"/>
+      <c r="A6597" s="13"/>
       <c r="B6597" s="2"/>
       <c r="C6597" s="6"/>
     </row>
     <row r="6598">
-      <c r="A6598" s="11"/>
+      <c r="A6598" s="13"/>
       <c r="B6598" s="2"/>
       <c r="C6598" s="6"/>
     </row>
     <row r="6599">
-      <c r="A6599" s="11"/>
+      <c r="A6599" s="13"/>
       <c r="B6599" s="2"/>
       <c r="C6599" s="6"/>
     </row>
     <row r="6600">
-      <c r="A6600" s="11"/>
+      <c r="A6600" s="13"/>
       <c r="B6600" s="2"/>
       <c r="C6600" s="6"/>
     </row>
     <row r="6601">
-      <c r="A6601" s="11"/>
+      <c r="A6601" s="13"/>
       <c r="B6601" s="2"/>
       <c r="C6601" s="6"/>
     </row>
     <row r="6602">
-      <c r="A6602" s="11"/>
+      <c r="A6602" s="13"/>
       <c r="B6602" s="2"/>
       <c r="C6602" s="6"/>
     </row>
     <row r="6603">
-      <c r="A6603" s="11"/>
+      <c r="A6603" s="13"/>
       <c r="B6603" s="2"/>
       <c r="C6603" s="6"/>
     </row>
     <row r="6604">
-      <c r="A6604" s="11"/>
+      <c r="A6604" s="13"/>
       <c r="B6604" s="2"/>
       <c r="C6604" s="6"/>
     </row>
     <row r="6605">
-      <c r="A6605" s="11"/>
+      <c r="A6605" s="13"/>
       <c r="B6605" s="2"/>
       <c r="C6605" s="6"/>
     </row>
     <row r="6606">
-      <c r="A6606" s="11"/>
+      <c r="A6606" s="13"/>
       <c r="B6606" s="2"/>
       <c r="C6606" s="6"/>
     </row>
     <row r="6607">
-      <c r="A6607" s="11"/>
+      <c r="A6607" s="13"/>
       <c r="B6607" s="2"/>
       <c r="C6607" s="6"/>
     </row>
     <row r="6608">
-      <c r="A6608" s="11"/>
+      <c r="A6608" s="13"/>
       <c r="B6608" s="2"/>
       <c r="C6608" s="6"/>
     </row>
     <row r="6609">
-      <c r="A6609" s="11"/>
+      <c r="A6609" s="13"/>
       <c r="B6609" s="2"/>
       <c r="C6609" s="6"/>
     </row>
     <row r="6610">
-      <c r="A6610" s="11"/>
+      <c r="A6610" s="13"/>
       <c r="B6610" s="2"/>
       <c r="C6610" s="6"/>
     </row>
     <row r="6611">
-      <c r="A6611" s="11"/>
+      <c r="A6611" s="13"/>
       <c r="B6611" s="2"/>
       <c r="C6611" s="6"/>
     </row>
     <row r="6612">
-      <c r="A6612" s="11"/>
+      <c r="A6612" s="13"/>
       <c r="B6612" s="2"/>
       <c r="C6612" s="6"/>
     </row>
     <row r="6613">
-      <c r="A6613" s="11"/>
+      <c r="A6613" s="13"/>
       <c r="B6613" s="2"/>
       <c r="C6613" s="6"/>
     </row>
     <row r="6614">
-      <c r="A6614" s="11"/>
+      <c r="A6614" s="13"/>
       <c r="B6614" s="2"/>
       <c r="C6614" s="6"/>
     </row>
     <row r="6615">
-      <c r="A6615" s="11"/>
+      <c r="A6615" s="13"/>
       <c r="B6615" s="2"/>
       <c r="C6615" s="6"/>
     </row>
     <row r="6616">
-      <c r="A6616" s="11"/>
+      <c r="A6616" s="13"/>
       <c r="B6616" s="2"/>
       <c r="C6616" s="6"/>
     </row>
     <row r="6617">
-      <c r="A6617" s="11"/>
+      <c r="A6617" s="13"/>
       <c r="B6617" s="2"/>
       <c r="C6617" s="6"/>
     </row>
     <row r="6618">
-      <c r="A6618" s="11"/>
+      <c r="A6618" s="13"/>
       <c r="B6618" s="2"/>
       <c r="C6618" s="6"/>
     </row>
     <row r="6619">
-      <c r="A6619" s="11"/>
+      <c r="A6619" s="13"/>
       <c r="B6619" s="2"/>
       <c r="C6619" s="6"/>
     </row>
     <row r="6620">
-      <c r="A6620" s="11"/>
+      <c r="A6620" s="13"/>
       <c r="B6620" s="2"/>
       <c r="C6620" s="6"/>
     </row>
     <row r="6621">
-      <c r="A6621" s="11"/>
+      <c r="A6621" s="13"/>
       <c r="B6621" s="2"/>
       <c r="C6621" s="6"/>
     </row>
     <row r="6622">
-      <c r="A6622" s="11"/>
+      <c r="A6622" s="13"/>
       <c r="B6622" s="2"/>
       <c r="C6622" s="6"/>
     </row>
     <row r="6623">
-      <c r="A6623" s="11"/>
+      <c r="A6623" s="13"/>
       <c r="B6623" s="2"/>
       <c r="C6623" s="6"/>
     </row>
     <row r="6624">
-      <c r="A6624" s="11"/>
+      <c r="A6624" s="13"/>
       <c r="B6624" s="2"/>
       <c r="C6624" s="6"/>
     </row>
     <row r="6625">
-      <c r="A6625" s="11"/>
+      <c r="A6625" s="13"/>
       <c r="B6625" s="2"/>
       <c r="C6625" s="6"/>
     </row>
     <row r="6626">
-      <c r="A6626" s="11"/>
+      <c r="A6626" s="13"/>
       <c r="B6626" s="2"/>
       <c r="C6626" s="6"/>
     </row>
     <row r="6627">
-      <c r="A6627" s="11"/>
+      <c r="A6627" s="13"/>
       <c r="B6627" s="2"/>
       <c r="C6627" s="6"/>
     </row>
     <row r="6628">
-      <c r="A6628" s="11"/>
+      <c r="A6628" s="13"/>
       <c r="B6628" s="2"/>
       <c r="C6628" s="6"/>
     </row>
     <row r="6629">
-      <c r="A6629" s="11"/>
+      <c r="A6629" s="13"/>
       <c r="B6629" s="2"/>
       <c r="C6629" s="6"/>
     </row>
     <row r="6630">
-      <c r="A6630" s="11"/>
+      <c r="A6630" s="13"/>
       <c r="B6630" s="2"/>
       <c r="C6630" s="6"/>
     </row>
     <row r="6631">
-      <c r="A6631" s="11"/>
+      <c r="A6631" s="13"/>
       <c r="B6631" s="2"/>
       <c r="C6631" s="6"/>
     </row>
     <row r="6632">
-      <c r="A6632" s="11"/>
+      <c r="A6632" s="13"/>
       <c r="B6632" s="2"/>
       <c r="C6632" s="6"/>
     </row>
     <row r="6633">
-      <c r="A6633" s="11"/>
+      <c r="A6633" s="13"/>
       <c r="B6633" s="2"/>
       <c r="C6633" s="6"/>
     </row>
     <row r="6634">
-      <c r="A6634" s="11"/>
+      <c r="A6634" s="13"/>
       <c r="B6634" s="2"/>
       <c r="C6634" s="6"/>
     </row>
     <row r="6635">
-      <c r="A6635" s="11"/>
+      <c r="A6635" s="13"/>
       <c r="B6635" s="2"/>
       <c r="C6635" s="6"/>
     </row>
     <row r="6636">
-      <c r="A6636" s="11"/>
+      <c r="A6636" s="13"/>
       <c r="B6636" s="2"/>
       <c r="C6636" s="6"/>
     </row>
     <row r="6637">
-      <c r="A6637" s="11"/>
+      <c r="A6637" s="13"/>
       <c r="B6637" s="2"/>
       <c r="C6637" s="6"/>
     </row>
     <row r="6638">
-      <c r="A6638" s="11"/>
+      <c r="A6638" s="13"/>
       <c r="B6638" s="2"/>
       <c r="C6638" s="6"/>
     </row>
     <row r="6639">
-      <c r="A6639" s="11"/>
+      <c r="A6639" s="13"/>
       <c r="B6639" s="2"/>
       <c r="C6639" s="6"/>
     </row>
     <row r="6640">
-      <c r="A6640" s="11"/>
+      <c r="A6640" s="13"/>
       <c r="B6640" s="2"/>
       <c r="C6640" s="6"/>
     </row>
     <row r="6641">
-      <c r="A6641" s="11"/>
+      <c r="A6641" s="13"/>
       <c r="B6641" s="2"/>
       <c r="C6641" s="6"/>
     </row>
     <row r="6642">
-      <c r="A6642" s="11"/>
+      <c r="A6642" s="13"/>
       <c r="B6642" s="2"/>
       <c r="C6642" s="6"/>
     </row>
     <row r="6643">
-      <c r="A6643" s="11"/>
+      <c r="A6643" s="13"/>
       <c r="B6643" s="2"/>
       <c r="C6643" s="6"/>
     </row>
     <row r="6644">
-      <c r="A6644" s="11"/>
+      <c r="A6644" s="13"/>
       <c r="B6644" s="2"/>
       <c r="C6644" s="6"/>
     </row>
     <row r="6645">
-      <c r="A6645" s="11"/>
+      <c r="A6645" s="13"/>
       <c r="B6645" s="2"/>
       <c r="C6645" s="6"/>
     </row>
     <row r="6646">
-      <c r="A6646" s="11"/>
+      <c r="A6646" s="13"/>
       <c r="B6646" s="2"/>
       <c r="C6646" s="6"/>
     </row>
     <row r="6647">
-      <c r="A6647" s="11"/>
+      <c r="A6647" s="13"/>
       <c r="B6647" s="2"/>
       <c r="C6647" s="6"/>
     </row>
     <row r="6648">
-      <c r="A6648" s="11"/>
+      <c r="A6648" s="13"/>
       <c r="B6648" s="2"/>
       <c r="C6648" s="6"/>
     </row>
     <row r="6649">
-      <c r="A6649" s="11"/>
+      <c r="A6649" s="13"/>
       <c r="B6649" s="2"/>
       <c r="C6649" s="6"/>
     </row>
     <row r="6650">
-      <c r="A6650" s="11"/>
+      <c r="A6650" s="13"/>
       <c r="B6650" s="2"/>
       <c r="C6650" s="6"/>
     </row>
     <row r="6651">
-      <c r="A6651" s="11"/>
+      <c r="A6651" s="13"/>
       <c r="B6651" s="2"/>
       <c r="C6651" s="6"/>
     </row>
     <row r="6652">
-      <c r="A6652" s="11"/>
+      <c r="A6652" s="13"/>
       <c r="B6652" s="2"/>
       <c r="C6652" s="6"/>
     </row>
     <row r="6653">
-      <c r="A6653" s="11"/>
+      <c r="A6653" s="13"/>
       <c r="B6653" s="2"/>
       <c r="C6653" s="6"/>
     </row>
     <row r="6654">
-      <c r="A6654" s="11"/>
+      <c r="A6654" s="13"/>
       <c r="B6654" s="2"/>
       <c r="C6654" s="6"/>
     </row>
     <row r="6655">
-      <c r="A6655" s="11"/>
+      <c r="A6655" s="13"/>
       <c r="B6655" s="2"/>
       <c r="C6655" s="6"/>
     </row>
     <row r="6656">
-      <c r="A6656" s="11"/>
+      <c r="A6656" s="13"/>
       <c r="B6656" s="2"/>
       <c r="C6656" s="6"/>
     </row>
     <row r="6657">
-      <c r="A6657" s="11"/>
+      <c r="A6657" s="13"/>
       <c r="B6657" s="2"/>
       <c r="C6657" s="6"/>
     </row>
     <row r="6658">
-      <c r="A6658" s="11"/>
+      <c r="A6658" s="13"/>
       <c r="B6658" s="2"/>
       <c r="C6658" s="6"/>
     </row>
     <row r="6659">
-      <c r="A6659" s="11"/>
+      <c r="A6659" s="13"/>
       <c r="B6659" s="2"/>
       <c r="C6659" s="6"/>
     </row>
     <row r="6660">
-      <c r="A6660" s="11"/>
+      <c r="A6660" s="13"/>
       <c r="B6660" s="2"/>
       <c r="C6660" s="6"/>
     </row>
     <row r="6661">
-      <c r="A6661" s="11"/>
+      <c r="A6661" s="13"/>
       <c r="B6661" s="2"/>
       <c r="C6661" s="6"/>
     </row>
     <row r="6662">
-      <c r="A6662" s="11"/>
+      <c r="A6662" s="13"/>
       <c r="B6662" s="2"/>
       <c r="C6662" s="6"/>
     </row>
     <row r="6663">
-      <c r="A6663" s="11"/>
+      <c r="A6663" s="13"/>
       <c r="B6663" s="2"/>
       <c r="C6663" s="6"/>
     </row>
     <row r="6664">
-      <c r="A6664" s="11"/>
+      <c r="A6664" s="13"/>
       <c r="B6664" s="2"/>
       <c r="C6664" s="6"/>
     </row>
     <row r="6665">
-      <c r="A6665" s="11"/>
+      <c r="A6665" s="13"/>
       <c r="B6665" s="2"/>
       <c r="C6665" s="6"/>
     </row>
     <row r="6666">
-      <c r="A6666" s="11"/>
+      <c r="A6666" s="13"/>
       <c r="B6666" s="2"/>
       <c r="C6666" s="6"/>
     </row>
     <row r="6667">
-      <c r="A6667" s="11"/>
+      <c r="A6667" s="13"/>
       <c r="B6667" s="2"/>
       <c r="C6667" s="6"/>
     </row>
     <row r="6668">
-      <c r="A6668" s="11"/>
+      <c r="A6668" s="13"/>
       <c r="B6668" s="2"/>
       <c r="C6668" s="6"/>
     </row>
     <row r="6669">
-      <c r="A6669" s="11"/>
+      <c r="A6669" s="13"/>
       <c r="B6669" s="2"/>
       <c r="C6669" s="6"/>
     </row>
     <row r="6670">
-      <c r="A6670" s="11"/>
+      <c r="A6670" s="13"/>
       <c r="B6670" s="2"/>
       <c r="C6670" s="6"/>
     </row>
     <row r="6671">
-      <c r="A6671" s="11"/>
+      <c r="A6671" s="13"/>
       <c r="B6671" s="2"/>
       <c r="C6671" s="6"/>
     </row>
     <row r="6672">
-      <c r="A6672" s="11"/>
+      <c r="A6672" s="13"/>
       <c r="B6672" s="2"/>
       <c r="C6672" s="6"/>
     </row>
     <row r="6673">
-      <c r="A6673" s="11"/>
+      <c r="A6673" s="13"/>
       <c r="B6673" s="2"/>
       <c r="C6673" s="6"/>
     </row>
     <row r="6674">
-      <c r="A6674" s="11"/>
+      <c r="A6674" s="13"/>
       <c r="B6674" s="2"/>
       <c r="C6674" s="6"/>
     </row>
     <row r="6675">
-      <c r="A6675" s="11"/>
+      <c r="A6675" s="13"/>
       <c r="B6675" s="2"/>
       <c r="C6675" s="6"/>
     </row>
     <row r="6676">
-      <c r="A6676" s="11"/>
+      <c r="A6676" s="13"/>
       <c r="B6676" s="2"/>
       <c r="C6676" s="6"/>
     </row>
     <row r="6677">
-      <c r="A6677" s="11"/>
+      <c r="A6677" s="13"/>
       <c r="B6677" s="2"/>
       <c r="C6677" s="6"/>
     </row>
     <row r="6678">
-      <c r="A6678" s="11"/>
+      <c r="A6678" s="13"/>
       <c r="B6678" s="2"/>
       <c r="C6678" s="6"/>
     </row>
     <row r="6679">
-      <c r="A6679" s="11"/>
+      <c r="A6679" s="13"/>
       <c r="B6679" s="2"/>
       <c r="C6679" s="6"/>
     </row>
     <row r="6680">
-      <c r="A6680" s="11"/>
+      <c r="A6680" s="13"/>
       <c r="B6680" s="2"/>
       <c r="C6680" s="6"/>
     </row>
     <row r="6681">
-      <c r="A6681" s="11"/>
+      <c r="A6681" s="13"/>
       <c r="B6681" s="2"/>
       <c r="C6681" s="6"/>
     </row>
     <row r="6682">
-      <c r="A6682" s="11"/>
+      <c r="A6682" s="13"/>
       <c r="B6682" s="2"/>
       <c r="C6682" s="6"/>
     </row>
     <row r="6683">
-      <c r="A6683" s="11"/>
+      <c r="A6683" s="13"/>
       <c r="B6683" s="2"/>
       <c r="C6683" s="6"/>
     </row>
     <row r="6684">
-      <c r="A6684" s="11"/>
+      <c r="A6684" s="13"/>
       <c r="B6684" s="2"/>
       <c r="C6684" s="6"/>
     </row>
     <row r="6685">
-      <c r="A6685" s="11"/>
+      <c r="A6685" s="13"/>
       <c r="B6685" s="2"/>
       <c r="C6685" s="6"/>
     </row>
     <row r="6686">
-      <c r="A6686" s="11"/>
+      <c r="A6686" s="13"/>
       <c r="B6686" s="2"/>
       <c r="C6686" s="6"/>
     </row>
     <row r="6687">
-      <c r="A6687" s="11"/>
+      <c r="A6687" s="13"/>
       <c r="B6687" s="2"/>
       <c r="C6687" s="6"/>
     </row>
     <row r="6688">
-      <c r="A6688" s="11"/>
+      <c r="A6688" s="13"/>
       <c r="B6688" s="2"/>
       <c r="C6688" s="6"/>
     </row>
     <row r="6689">
-      <c r="A6689" s="11"/>
+      <c r="A6689" s="13"/>
       <c r="B6689" s="2"/>
       <c r="C6689" s="6"/>
     </row>
     <row r="6690">
-      <c r="A6690" s="11"/>
+      <c r="A6690" s="13"/>
       <c r="B6690" s="2"/>
       <c r="C6690" s="6"/>
     </row>
     <row r="6691">
-      <c r="A6691" s="11"/>
+      <c r="A6691" s="13"/>
       <c r="B6691" s="2"/>
       <c r="C6691" s="6"/>
     </row>
     <row r="6692">
-      <c r="A6692" s="11"/>
+      <c r="A6692" s="13"/>
       <c r="B6692" s="2"/>
       <c r="C6692" s="6"/>
     </row>
     <row r="6693">
-      <c r="A6693" s="11"/>
+      <c r="A6693" s="13"/>
       <c r="B6693" s="2"/>
       <c r="C6693" s="6"/>
     </row>
     <row r="6694">
-      <c r="A6694" s="11"/>
+      <c r="A6694" s="13"/>
       <c r="B6694" s="2"/>
       <c r="C6694" s="6"/>
     </row>
     <row r="6695">
-      <c r="A6695" s="11"/>
+      <c r="A6695" s="13"/>
       <c r="B6695" s="2"/>
       <c r="C6695" s="6"/>
     </row>
     <row r="6696">
-      <c r="A6696" s="11"/>
+      <c r="A6696" s="13"/>
       <c r="B6696" s="2"/>
       <c r="C6696" s="6"/>
     </row>
     <row r="6697">
-      <c r="A6697" s="11"/>
+      <c r="A6697" s="13"/>
       <c r="B6697" s="2"/>
       <c r="C6697" s="6"/>
     </row>
     <row r="6698">
-      <c r="A6698" s="11"/>
+      <c r="A6698" s="13"/>
       <c r="B6698" s="2"/>
       <c r="C6698" s="6"/>
     </row>
     <row r="6699">
-      <c r="A6699" s="11"/>
+      <c r="A6699" s="13"/>
       <c r="B6699" s="2"/>
       <c r="C6699" s="6"/>
     </row>
     <row r="6700">
-      <c r="A6700" s="11"/>
+      <c r="A6700" s="13"/>
       <c r="B6700" s="2"/>
       <c r="C6700" s="6"/>
     </row>
     <row r="6701">
-      <c r="A6701" s="11"/>
+      <c r="A6701" s="13"/>
       <c r="B6701" s="2"/>
       <c r="C6701" s="6"/>
     </row>
     <row r="6702">
-      <c r="A6702" s="11"/>
+      <c r="A6702" s="13"/>
       <c r="B6702" s="2"/>
       <c r="C6702" s="6"/>
     </row>
     <row r="6703">
-      <c r="A6703" s="11"/>
+      <c r="A6703" s="13"/>
       <c r="B6703" s="2"/>
       <c r="C6703" s="6"/>
     </row>
     <row r="6704">
-      <c r="A6704" s="11"/>
+      <c r="A6704" s="13"/>
       <c r="B6704" s="2"/>
       <c r="C6704" s="6"/>
     </row>
     <row r="6705">
-      <c r="A6705" s="11"/>
+      <c r="A6705" s="13"/>
       <c r="B6705" s="2"/>
       <c r="C6705" s="6"/>
     </row>
     <row r="6706">
-      <c r="A6706" s="11"/>
+      <c r="A6706" s="13"/>
       <c r="B6706" s="2"/>
       <c r="C6706" s="6"/>
     </row>
     <row r="6707">
-      <c r="A6707" s="11"/>
+      <c r="A6707" s="13"/>
       <c r="B6707" s="2"/>
       <c r="C6707" s="6"/>
     </row>
     <row r="6708">
-      <c r="A6708" s="11"/>
+      <c r="A6708" s="13"/>
       <c r="B6708" s="2"/>
       <c r="C6708" s="6"/>
     </row>
     <row r="6709">
-      <c r="A6709" s="11"/>
+      <c r="A6709" s="13"/>
       <c r="B6709" s="2"/>
       <c r="C6709" s="6"/>
     </row>
     <row r="6710">
-      <c r="A6710" s="11"/>
+      <c r="A6710" s="13"/>
       <c r="B6710" s="2"/>
       <c r="C6710" s="6"/>
     </row>
     <row r="6711">
-      <c r="A6711" s="11"/>
+      <c r="A6711" s="13"/>
       <c r="B6711" s="2"/>
       <c r="C6711" s="6"/>
     </row>
     <row r="6712">
-      <c r="A6712" s="11"/>
+      <c r="A6712" s="13"/>
       <c r="B6712" s="2"/>
       <c r="C6712" s="6"/>
     </row>
     <row r="6713">
-      <c r="A6713" s="11"/>
+      <c r="A6713" s="13"/>
       <c r="B6713" s="2"/>
       <c r="C6713" s="6"/>
     </row>
     <row r="6714">
-      <c r="A6714" s="11"/>
+      <c r="A6714" s="13"/>
       <c r="B6714" s="2"/>
       <c r="C6714" s="6"/>
     </row>
     <row r="6715">
-      <c r="A6715" s="11"/>
+      <c r="A6715" s="13"/>
       <c r="B6715" s="2"/>
       <c r="C6715" s="6"/>
     </row>
     <row r="6716">
-      <c r="A6716" s="11"/>
+      <c r="A6716" s="13"/>
       <c r="B6716" s="2"/>
       <c r="C6716" s="6"/>
     </row>
     <row r="6717">
-      <c r="A6717" s="11"/>
+      <c r="A6717" s="13"/>
       <c r="B6717" s="2"/>
       <c r="C6717" s="6"/>
     </row>
     <row r="6718">
-      <c r="A6718" s="11"/>
+      <c r="A6718" s="13"/>
       <c r="B6718" s="2"/>
       <c r="C6718" s="6"/>
     </row>
     <row r="6719">
-      <c r="A6719" s="11"/>
+      <c r="A6719" s="13"/>
       <c r="B6719" s="2"/>
       <c r="C6719" s="6"/>
     </row>
     <row r="6720">
-      <c r="A6720" s="11"/>
+      <c r="A6720" s="13"/>
       <c r="B6720" s="2"/>
       <c r="C6720" s="6"/>
     </row>
     <row r="6721">
-      <c r="A6721" s="11"/>
+      <c r="A6721" s="13"/>
       <c r="B6721" s="2"/>
       <c r="C6721" s="6"/>
     </row>
     <row r="6722">
-      <c r="A6722" s="11"/>
+      <c r="A6722" s="13"/>
       <c r="B6722" s="2"/>
       <c r="C6722" s="6"/>
     </row>
     <row r="6723">
-      <c r="A6723" s="11"/>
+      <c r="A6723" s="13"/>
       <c r="B6723" s="2"/>
       <c r="C6723" s="6"/>
     </row>
     <row r="6724">
-      <c r="A6724" s="11"/>
+      <c r="A6724" s="13"/>
       <c r="B6724" s="2"/>
       <c r="C6724" s="6"/>
     </row>
     <row r="6725">
-      <c r="A6725" s="11"/>
+      <c r="A6725" s="13"/>
       <c r="B6725" s="2"/>
       <c r="C6725" s="6"/>
     </row>
     <row r="6726">
-      <c r="A6726" s="11"/>
+      <c r="A6726" s="13"/>
       <c r="B6726" s="2"/>
       <c r="C6726" s="6"/>
     </row>
     <row r="6727">
-      <c r="A6727" s="11"/>
+      <c r="A6727" s="13"/>
       <c r="B6727" s="2"/>
       <c r="C6727" s="6"/>
     </row>
     <row r="6728">
-      <c r="A6728" s="11"/>
+      <c r="A6728" s="13"/>
       <c r="B6728" s="2"/>
       <c r="C6728" s="6"/>
     </row>
     <row r="6729">
-      <c r="A6729" s="11"/>
+      <c r="A6729" s="13"/>
       <c r="B6729" s="2"/>
       <c r="C6729" s="6"/>
     </row>
     <row r="6730">
-      <c r="A6730" s="11"/>
+      <c r="A6730" s="13"/>
       <c r="B6730" s="2"/>
       <c r="C6730" s="6"/>
     </row>
     <row r="6731">
-      <c r="A6731" s="11"/>
+      <c r="A6731" s="13"/>
       <c r="B6731" s="2"/>
       <c r="C6731" s="6"/>
     </row>
     <row r="6732">
-      <c r="A6732" s="11"/>
+      <c r="A6732" s="13"/>
       <c r="B6732" s="2"/>
       <c r="C6732" s="6"/>
     </row>
     <row r="6733">
-      <c r="A6733" s="11"/>
+      <c r="A6733" s="13"/>
       <c r="B6733" s="2"/>
       <c r="C6733" s="6"/>
     </row>
     <row r="6734">
-      <c r="A6734" s="11"/>
+      <c r="A6734" s="13"/>
       <c r="B6734" s="2"/>
       <c r="C6734" s="6"/>
     </row>
     <row r="6735">
-      <c r="A6735" s="11"/>
+      <c r="A6735" s="13"/>
       <c r="B6735" s="2"/>
       <c r="C6735" s="6"/>
     </row>
     <row r="6736">
-      <c r="A6736" s="11"/>
+      <c r="A6736" s="13"/>
       <c r="B6736" s="2"/>
       <c r="C6736" s="6"/>
     </row>
     <row r="6737">
-      <c r="A6737" s="11"/>
+      <c r="A6737" s="13"/>
       <c r="B6737" s="2"/>
       <c r="C6737" s="6"/>
     </row>
     <row r="6738">
-      <c r="A6738" s="11"/>
+      <c r="A6738" s="13"/>
       <c r="B6738" s="2"/>
       <c r="C6738" s="6"/>
     </row>
     <row r="6739">
-      <c r="A6739" s="11"/>
+      <c r="A6739" s="13"/>
       <c r="B6739" s="2"/>
       <c r="C6739" s="6"/>
     </row>
     <row r="6740">
-      <c r="A6740" s="11"/>
+      <c r="A6740" s="13"/>
       <c r="B6740" s="2"/>
       <c r="C6740" s="6"/>
     </row>
     <row r="6741">
-      <c r="A6741" s="11"/>
+      <c r="A6741" s="13"/>
       <c r="B6741" s="2"/>
       <c r="C6741" s="6"/>
     </row>
     <row r="6742">
-      <c r="A6742" s="11"/>
+      <c r="A6742" s="13"/>
       <c r="B6742" s="2"/>
       <c r="C6742" s="6"/>
     </row>
     <row r="6743">
-      <c r="A6743" s="11"/>
+      <c r="A6743" s="13"/>
       <c r="B6743" s="2"/>
       <c r="C6743" s="6"/>
     </row>
     <row r="6744">
-      <c r="A6744" s="11"/>
+      <c r="A6744" s="13"/>
       <c r="B6744" s="2"/>
       <c r="C6744" s="6"/>
     </row>
     <row r="6745">
-      <c r="A6745" s="11"/>
+      <c r="A6745" s="13"/>
       <c r="B6745" s="2"/>
       <c r="C6745" s="6"/>
     </row>
     <row r="6746">
-      <c r="A6746" s="11"/>
+      <c r="A6746" s="13"/>
       <c r="B6746" s="2"/>
       <c r="C6746" s="6"/>
     </row>
     <row r="6747">
-      <c r="A6747" s="11"/>
+      <c r="A6747" s="13"/>
       <c r="B6747" s="2"/>
       <c r="C6747" s="6"/>
     </row>
     <row r="6748">
-      <c r="A6748" s="11"/>
+      <c r="A6748" s="13"/>
       <c r="B6748" s="2"/>
       <c r="C6748" s="6"/>
     </row>
     <row r="6749">
-      <c r="A6749" s="11"/>
+      <c r="A6749" s="13"/>
       <c r="B6749" s="2"/>
       <c r="C6749" s="6"/>
     </row>
     <row r="6750">
-      <c r="A6750" s="11"/>
+      <c r="A6750" s="13"/>
       <c r="B6750" s="2"/>
       <c r="C6750" s="6"/>
     </row>
     <row r="6751">
-      <c r="A6751" s="11"/>
+      <c r="A6751" s="13"/>
       <c r="B6751" s="2"/>
       <c r="C6751" s="6"/>
     </row>
     <row r="6752">
-      <c r="A6752" s="11"/>
+      <c r="A6752" s="13"/>
       <c r="B6752" s="2"/>
       <c r="C6752" s="6"/>
     </row>
     <row r="6753">
-      <c r="A6753" s="11"/>
+      <c r="A6753" s="13"/>
       <c r="B6753" s="2"/>
       <c r="C6753" s="6"/>
     </row>
     <row r="6754">
-      <c r="A6754" s="11"/>
+      <c r="A6754" s="13"/>
       <c r="B6754" s="2"/>
       <c r="C6754" s="6"/>
     </row>
     <row r="6755">
-      <c r="A6755" s="11"/>
+      <c r="A6755" s="13"/>
       <c r="B6755" s="2"/>
       <c r="C6755" s="6"/>
     </row>
     <row r="6756">
-      <c r="A6756" s="11"/>
+      <c r="A6756" s="13"/>
       <c r="B6756" s="2"/>
       <c r="C6756" s="6"/>
     </row>
     <row r="6757">
-      <c r="A6757" s="11"/>
+      <c r="A6757" s="13"/>
       <c r="B6757" s="2"/>
       <c r="C6757" s="6"/>
     </row>
     <row r="6758">
-      <c r="A6758" s="11"/>
+      <c r="A6758" s="13"/>
       <c r="B6758" s="2"/>
       <c r="C6758" s="6"/>
     </row>
     <row r="6759">
-      <c r="A6759" s="11"/>
+      <c r="A6759" s="13"/>
       <c r="B6759" s="2"/>
       <c r="C6759" s="6"/>
     </row>
     <row r="6760">
-      <c r="A6760" s="11"/>
+      <c r="A6760" s="13"/>
       <c r="B6760" s="2"/>
       <c r="C6760" s="6"/>
     </row>
     <row r="6761">
-      <c r="A6761" s="11"/>
+      <c r="A6761" s="13"/>
       <c r="B6761" s="2"/>
       <c r="C6761" s="6"/>
     </row>
     <row r="6762">
-      <c r="A6762" s="11"/>
+      <c r="A6762" s="13"/>
       <c r="B6762" s="2"/>
       <c r="C6762" s="6"/>
     </row>
     <row r="6763">
-      <c r="A6763" s="11"/>
+      <c r="A6763" s="13"/>
       <c r="B6763" s="2"/>
       <c r="C6763" s="6"/>
     </row>
     <row r="6764">
-      <c r="A6764" s="11"/>
+      <c r="A6764" s="13"/>
       <c r="B6764" s="2"/>
       <c r="C6764" s="6"/>
     </row>
     <row r="6765">
-      <c r="A6765" s="11"/>
+      <c r="A6765" s="13"/>
       <c r="B6765" s="2"/>
       <c r="C6765" s="6"/>
     </row>
     <row r="6766">
-      <c r="A6766" s="11"/>
+      <c r="A6766" s="13"/>
       <c r="B6766" s="2"/>
       <c r="C6766" s="6"/>
     </row>
     <row r="6767">
-      <c r="A6767" s="11"/>
+      <c r="A6767" s="13"/>
       <c r="B6767" s="2"/>
       <c r="C6767" s="6"/>
     </row>
     <row r="6768">
-      <c r="A6768" s="11"/>
+      <c r="A6768" s="13"/>
       <c r="B6768" s="2"/>
       <c r="C6768" s="6"/>
     </row>
     <row r="6769">
-      <c r="A6769" s="11"/>
+      <c r="A6769" s="13"/>
       <c r="B6769" s="2"/>
       <c r="C6769" s="6"/>
     </row>
     <row r="6770">
-      <c r="A6770" s="11"/>
+      <c r="A6770" s="13"/>
       <c r="B6770" s="2"/>
       <c r="C6770" s="6"/>
     </row>
     <row r="6771">
-      <c r="A6771" s="11"/>
+      <c r="A6771" s="13"/>
       <c r="B6771" s="2"/>
       <c r="C6771" s="6"/>
     </row>
     <row r="6772">
-      <c r="A6772" s="11"/>
+      <c r="A6772" s="13"/>
       <c r="B6772" s="2"/>
       <c r="C6772" s="6"/>
     </row>
     <row r="6773">
-      <c r="A6773" s="11"/>
+      <c r="A6773" s="13"/>
       <c r="B6773" s="2"/>
       <c r="C6773" s="6"/>
     </row>
     <row r="6774">
-      <c r="A6774" s="11"/>
+      <c r="A6774" s="13"/>
       <c r="B6774" s="2"/>
       <c r="C6774" s="6"/>
     </row>
     <row r="6775">
-      <c r="A6775" s="11"/>
+      <c r="A6775" s="13"/>
       <c r="B6775" s="2"/>
       <c r="C6775" s="6"/>
     </row>
     <row r="6776">
-      <c r="A6776" s="11"/>
+      <c r="A6776" s="13"/>
       <c r="B6776" s="2"/>
       <c r="C6776" s="6"/>
     </row>
     <row r="6777">
-      <c r="A6777" s="11"/>
+      <c r="A6777" s="13"/>
       <c r="B6777" s="2"/>
       <c r="C6777" s="6"/>
     </row>
     <row r="6778">
-      <c r="A6778" s="11"/>
+      <c r="A6778" s="13"/>
       <c r="B6778" s="2"/>
       <c r="C6778" s="6"/>
     </row>
     <row r="6779">
-      <c r="A6779" s="11"/>
+      <c r="A6779" s="13"/>
       <c r="B6779" s="2"/>
       <c r="C6779" s="6"/>
     </row>
     <row r="6780">
-      <c r="A6780" s="11"/>
+      <c r="A6780" s="13"/>
       <c r="B6780" s="2"/>
       <c r="C6780" s="6"/>
     </row>
     <row r="6781">
-      <c r="A6781" s="11"/>
+      <c r="A6781" s="13"/>
       <c r="B6781" s="2"/>
       <c r="C6781" s="6"/>
     </row>
     <row r="6782">
-      <c r="A6782" s="11"/>
+      <c r="A6782" s="13"/>
       <c r="B6782" s="2"/>
       <c r="C6782" s="6"/>
     </row>
     <row r="6783">
-      <c r="A6783" s="11"/>
+      <c r="A6783" s="13"/>
       <c r="B6783" s="2"/>
       <c r="C6783" s="6"/>
     </row>
     <row r="6784">
-      <c r="A6784" s="11"/>
+      <c r="A6784" s="13"/>
       <c r="B6784" s="2"/>
       <c r="C6784" s="6"/>
     </row>
     <row r="6785">
-      <c r="A6785" s="11"/>
+      <c r="A6785" s="13"/>
       <c r="B6785" s="2"/>
       <c r="C6785" s="6"/>
     </row>
     <row r="6786">
-      <c r="A6786" s="11"/>
+      <c r="A6786" s="13"/>
       <c r="B6786" s="2"/>
       <c r="C6786" s="6"/>
     </row>
     <row r="6787">
-      <c r="A6787" s="11"/>
+      <c r="A6787" s="13"/>
       <c r="B6787" s="2"/>
       <c r="C6787" s="6"/>
     </row>
     <row r="6788">
-      <c r="A6788" s="11"/>
+      <c r="A6788" s="13"/>
       <c r="B6788" s="2"/>
       <c r="C6788" s="6"/>
     </row>
     <row r="6789">
-      <c r="A6789" s="11"/>
+      <c r="A6789" s="13"/>
       <c r="B6789" s="2"/>
       <c r="C6789" s="6"/>
     </row>
     <row r="6790">
-      <c r="A6790" s="11"/>
+      <c r="A6790" s="13"/>
       <c r="B6790" s="2"/>
       <c r="C6790" s="6"/>
     </row>
     <row r="6791">
-      <c r="A6791" s="11"/>
+      <c r="A6791" s="13"/>
       <c r="B6791" s="2"/>
       <c r="C6791" s="6"/>
     </row>
     <row r="6792">
-      <c r="A6792" s="11"/>
+      <c r="A6792" s="13"/>
       <c r="B6792" s="2"/>
       <c r="C6792" s="6"/>
     </row>
     <row r="6793">
-      <c r="A6793" s="11"/>
+      <c r="A6793" s="13"/>
       <c r="B6793" s="2"/>
       <c r="C6793" s="6"/>
     </row>
     <row r="6794">
-      <c r="A6794" s="11"/>
+      <c r="A6794" s="13"/>
       <c r="B6794" s="2"/>
       <c r="C6794" s="6"/>
     </row>
     <row r="6795">
-      <c r="A6795" s="11"/>
+      <c r="A6795" s="13"/>
       <c r="B6795" s="2"/>
       <c r="C6795" s="6"/>
     </row>
     <row r="6796">
-      <c r="A6796" s="11"/>
+      <c r="A6796" s="13"/>
       <c r="B6796" s="2"/>
       <c r="C6796" s="6"/>
     </row>
     <row r="6797">
-      <c r="A6797" s="11"/>
+      <c r="A6797" s="13"/>
       <c r="B6797" s="2"/>
       <c r="C6797" s="6"/>
     </row>
     <row r="6798">
-      <c r="A6798" s="11"/>
+      <c r="A6798" s="13"/>
       <c r="B6798" s="2"/>
       <c r="C6798" s="6"/>
     </row>
     <row r="6799">
-      <c r="A6799" s="11"/>
+      <c r="A6799" s="13"/>
       <c r="B6799" s="2"/>
       <c r="C6799" s="6"/>
     </row>
     <row r="6800">
-      <c r="A6800" s="11"/>
+      <c r="A6800" s="13"/>
       <c r="B6800" s="2"/>
       <c r="C6800" s="6"/>
     </row>
     <row r="6801">
-      <c r="A6801" s="11"/>
+      <c r="A6801" s="13"/>
       <c r="B6801" s="2"/>
       <c r="C6801" s="6"/>
     </row>
     <row r="6802">
-      <c r="A6802" s="11"/>
+      <c r="A6802" s="13"/>
       <c r="B6802" s="2"/>
       <c r="C6802" s="6"/>
     </row>
     <row r="6803">
-      <c r="A6803" s="11"/>
+      <c r="A6803" s="13"/>
       <c r="B6803" s="2"/>
       <c r="C6803" s="6"/>
     </row>
     <row r="6804">
-      <c r="A6804" s="11"/>
+      <c r="A6804" s="13"/>
       <c r="B6804" s="2"/>
       <c r="C6804" s="6"/>
     </row>
     <row r="6805">
-      <c r="A6805" s="11"/>
+      <c r="A6805" s="13"/>
       <c r="B6805" s="2"/>
       <c r="C6805" s="6"/>
     </row>
     <row r="6806">
-      <c r="A6806" s="11"/>
+      <c r="A6806" s="13"/>
       <c r="B6806" s="2"/>
       <c r="C6806" s="6"/>
     </row>
     <row r="6807">
-      <c r="A6807" s="11"/>
+      <c r="A6807" s="13"/>
       <c r="B6807" s="2"/>
       <c r="C6807" s="6"/>
     </row>
     <row r="6808">
-      <c r="A6808" s="11"/>
+      <c r="A6808" s="13"/>
       <c r="B6808" s="2"/>
       <c r="C6808" s="6"/>
     </row>
     <row r="6809">
-      <c r="A6809" s="11"/>
+      <c r="A6809" s="13"/>
       <c r="B6809" s="2"/>
       <c r="C6809" s="6"/>
     </row>
     <row r="6810">
-      <c r="A6810" s="11"/>
+      <c r="A6810" s="13"/>
       <c r="B6810" s="2"/>
       <c r="C6810" s="6"/>
     </row>
     <row r="6811">
-      <c r="A6811" s="11"/>
+      <c r="A6811" s="13"/>
       <c r="B6811" s="2"/>
       <c r="C6811" s="6"/>
     </row>
     <row r="6812">
-      <c r="A6812" s="11"/>
+      <c r="A6812" s="13"/>
       <c r="B6812" s="2"/>
       <c r="C6812" s="6"/>
     </row>
     <row r="6813">
-      <c r="A6813" s="11"/>
+      <c r="A6813" s="13"/>
       <c r="B6813" s="2"/>
       <c r="C6813" s="6"/>
     </row>
     <row r="6814">
-      <c r="A6814" s="11"/>
+      <c r="A6814" s="13"/>
       <c r="B6814" s="2"/>
       <c r="C6814" s="6"/>
     </row>
     <row r="6815">
-      <c r="A6815" s="11"/>
+      <c r="A6815" s="13"/>
       <c r="B6815" s="2"/>
       <c r="C6815" s="6"/>
     </row>
     <row r="6816">
-      <c r="A6816" s="11"/>
+      <c r="A6816" s="13"/>
       <c r="B6816" s="2"/>
       <c r="C6816" s="6"/>
     </row>
     <row r="6817">
-      <c r="A6817" s="11"/>
+      <c r="A6817" s="13"/>
       <c r="B6817" s="2"/>
       <c r="C6817" s="6"/>
     </row>
     <row r="6818">
-      <c r="A6818" s="11"/>
+      <c r="A6818" s="13"/>
       <c r="B6818" s="2"/>
       <c r="C6818" s="6"/>
     </row>
     <row r="6819">
-      <c r="A6819" s="11"/>
+      <c r="A6819" s="13"/>
       <c r="B6819" s="2"/>
       <c r="C6819" s="6"/>
     </row>
     <row r="6820">
-      <c r="A6820" s="11"/>
+      <c r="A6820" s="13"/>
       <c r="B6820" s="2"/>
       <c r="C6820" s="6"/>
     </row>
     <row r="6821">
-      <c r="A6821" s="11"/>
+      <c r="A6821" s="13"/>
       <c r="B6821" s="2"/>
       <c r="C6821" s="6"/>
     </row>
     <row r="6822">
-      <c r="A6822" s="11"/>
+      <c r="A6822" s="13"/>
       <c r="B6822" s="2"/>
       <c r="C6822" s="6"/>
     </row>
     <row r="6823">
-      <c r="A6823" s="11"/>
+      <c r="A6823" s="13"/>
       <c r="B6823" s="2"/>
       <c r="C6823" s="6"/>
     </row>
     <row r="6824">
-      <c r="A6824" s="11"/>
+      <c r="A6824" s="13"/>
       <c r="B6824" s="2"/>
       <c r="C6824" s="6"/>
     </row>
     <row r="6825">
-      <c r="A6825" s="11"/>
+      <c r="A6825" s="13"/>
       <c r="B6825" s="2"/>
       <c r="C6825" s="6"/>
     </row>
     <row r="6826">
-      <c r="A6826" s="11"/>
+      <c r="A6826" s="13"/>
       <c r="B6826" s="2"/>
       <c r="C6826" s="6"/>
     </row>
     <row r="6827">
-      <c r="A6827" s="11"/>
+      <c r="A6827" s="13"/>
       <c r="B6827" s="2"/>
       <c r="C6827" s="6"/>
     </row>
     <row r="6828">
-      <c r="A6828" s="11"/>
+      <c r="A6828" s="13"/>
       <c r="B6828" s="2"/>
       <c r="C6828" s="6"/>
     </row>
     <row r="6829">
-      <c r="A6829" s="11"/>
+      <c r="A6829" s="13"/>
       <c r="B6829" s="2"/>
       <c r="C6829" s="6"/>
     </row>
     <row r="6830">
-      <c r="A6830" s="11"/>
+      <c r="A6830" s="13"/>
       <c r="B6830" s="2"/>
       <c r="C6830" s="6"/>
     </row>
     <row r="6831">
-      <c r="A6831" s="11"/>
+      <c r="A6831" s="13"/>
       <c r="B6831" s="2"/>
       <c r="C6831" s="6"/>
     </row>
     <row r="6832">
-      <c r="A6832" s="11"/>
+      <c r="A6832" s="13"/>
       <c r="B6832" s="2"/>
       <c r="C6832" s="6"/>
     </row>
     <row r="6833">
-      <c r="A6833" s="11"/>
+      <c r="A6833" s="13"/>
       <c r="B6833" s="2"/>
       <c r="C6833" s="6"/>
     </row>
     <row r="6834">
-      <c r="A6834" s="11"/>
+      <c r="A6834" s="13"/>
       <c r="B6834" s="2"/>
       <c r="C6834" s="6"/>
     </row>
     <row r="6835">
-      <c r="A6835" s="11"/>
+      <c r="A6835" s="13"/>
       <c r="B6835" s="2"/>
       <c r="C6835" s="6"/>
     </row>
     <row r="6836">
-      <c r="A6836" s="11"/>
+      <c r="A6836" s="13"/>
       <c r="B6836" s="2"/>
       <c r="C6836" s="6"/>
     </row>
     <row r="6837">
-      <c r="A6837" s="11"/>
+      <c r="A6837" s="13"/>
       <c r="B6837" s="2"/>
       <c r="C6837" s="6"/>
     </row>
     <row r="6838">
-      <c r="A6838" s="11"/>
+      <c r="A6838" s="13"/>
       <c r="B6838" s="2"/>
       <c r="C6838" s="6"/>
     </row>
     <row r="6839">
-      <c r="A6839" s="11"/>
+      <c r="A6839" s="13"/>
       <c r="B6839" s="2"/>
       <c r="C6839" s="6"/>
     </row>
     <row r="6840">
-      <c r="A6840" s="11"/>
+      <c r="A6840" s="13"/>
       <c r="B6840" s="2"/>
       <c r="C6840" s="6"/>
     </row>
     <row r="6841">
-      <c r="A6841" s="11"/>
+      <c r="A6841" s="13"/>
       <c r="B6841" s="2"/>
       <c r="C6841" s="6"/>
     </row>
     <row r="6842">
-      <c r="A6842" s="11"/>
+      <c r="A6842" s="13"/>
       <c r="B6842" s="2"/>
       <c r="C6842" s="6"/>
     </row>
     <row r="6843">
-      <c r="A6843" s="11"/>
+      <c r="A6843" s="13"/>
       <c r="B6843" s="2"/>
       <c r="C6843" s="6"/>
     </row>
     <row r="6844">
-      <c r="A6844" s="11"/>
+      <c r="A6844" s="13"/>
       <c r="B6844" s="2"/>
       <c r="C6844" s="6"/>
     </row>
     <row r="6845">
-      <c r="A6845" s="11"/>
+      <c r="A6845" s="13"/>
       <c r="B6845" s="2"/>
       <c r="C6845" s="6"/>
     </row>
     <row r="6846">
-      <c r="A6846" s="11"/>
+      <c r="A6846" s="13"/>
       <c r="B6846" s="2"/>
       <c r="C6846" s="6"/>
     </row>
     <row r="6847">
-      <c r="A6847" s="11"/>
+      <c r="A6847" s="13"/>
       <c r="B6847" s="2"/>
       <c r="C6847" s="6"/>
     </row>
     <row r="6848">
-      <c r="A6848" s="11"/>
+      <c r="A6848" s="13"/>
       <c r="B6848" s="2"/>
       <c r="C6848" s="6"/>
     </row>
     <row r="6849">
-      <c r="A6849" s="11"/>
+      <c r="A6849" s="13"/>
       <c r="B6849" s="2"/>
       <c r="C6849" s="6"/>
     </row>
     <row r="6850">
-      <c r="A6850" s="11"/>
+      <c r="A6850" s="13"/>
       <c r="B6850" s="2"/>
       <c r="C6850" s="6"/>
     </row>
     <row r="6851">
-      <c r="A6851" s="11"/>
+      <c r="A6851" s="13"/>
       <c r="B6851" s="2"/>
       <c r="C6851" s="6"/>
     </row>
     <row r="6852">
-      <c r="A6852" s="11"/>
+      <c r="A6852" s="13"/>
       <c r="B6852" s="2"/>
       <c r="C6852" s="6"/>
     </row>
     <row r="6853">
-      <c r="A6853" s="11"/>
+      <c r="A6853" s="13"/>
       <c r="B6853" s="2"/>
       <c r="C6853" s="6"/>
     </row>
     <row r="6854">
-      <c r="A6854" s="11"/>
+      <c r="A6854" s="13"/>
       <c r="B6854" s="2"/>
       <c r="C6854" s="6"/>
     </row>
     <row r="6855">
-      <c r="A6855" s="11"/>
+      <c r="A6855" s="13"/>
       <c r="B6855" s="2"/>
       <c r="C6855" s="6"/>
     </row>
     <row r="6856">
-      <c r="A6856" s="11"/>
+      <c r="A6856" s="13"/>
       <c r="B6856" s="2"/>
       <c r="C6856" s="6"/>
     </row>
     <row r="6857">
-      <c r="A6857" s="11"/>
+      <c r="A6857" s="13"/>
       <c r="B6857" s="2"/>
       <c r="C6857" s="6"/>
     </row>
     <row r="6858">
-      <c r="A6858" s="11"/>
+      <c r="A6858" s="13"/>
       <c r="B6858" s="2"/>
       <c r="C6858" s="6"/>
     </row>
     <row r="6859">
-      <c r="A6859" s="11"/>
+      <c r="A6859" s="13"/>
       <c r="B6859" s="2"/>
       <c r="C6859" s="6"/>
     </row>
     <row r="6860">
-      <c r="A6860" s="11"/>
+      <c r="A6860" s="13"/>
       <c r="B6860" s="2"/>
       <c r="C6860" s="6"/>
     </row>
     <row r="6861">
-      <c r="A6861" s="11"/>
+      <c r="A6861" s="13"/>
       <c r="B6861" s="2"/>
       <c r="C6861" s="6"/>
     </row>
     <row r="6862">
-      <c r="A6862" s="11"/>
+      <c r="A6862" s="13"/>
       <c r="B6862" s="2"/>
       <c r="C6862" s="6"/>
     </row>
     <row r="6863">
-      <c r="A6863" s="11"/>
+      <c r="A6863" s="13"/>
       <c r="B6863" s="2"/>
       <c r="C6863" s="6"/>
     </row>
     <row r="6864">
-      <c r="A6864" s="11"/>
+      <c r="A6864" s="13"/>
       <c r="B6864" s="2"/>
       <c r="C6864" s="6"/>
     </row>
     <row r="6865">
-      <c r="A6865" s="11"/>
+      <c r="A6865" s="13"/>
       <c r="B6865" s="2"/>
       <c r="C6865" s="6"/>
     </row>
     <row r="6866">
-      <c r="A6866" s="11"/>
+      <c r="A6866" s="13"/>
       <c r="B6866" s="2"/>
       <c r="C6866" s="6"/>
     </row>
     <row r="6867">
-      <c r="A6867" s="11"/>
+      <c r="A6867" s="13"/>
       <c r="B6867" s="2"/>
       <c r="C6867" s="6"/>
     </row>
     <row r="6868">
-      <c r="A6868" s="11"/>
+      <c r="A6868" s="13"/>
       <c r="B6868" s="2"/>
       <c r="C6868" s="6"/>
     </row>
     <row r="6869">
-      <c r="A6869" s="11"/>
+      <c r="A6869" s="13"/>
       <c r="B6869" s="2"/>
       <c r="C6869" s="6"/>
     </row>
     <row r="6870">
-      <c r="A6870" s="11"/>
+      <c r="A6870" s="13"/>
       <c r="B6870" s="2"/>
       <c r="C6870" s="6"/>
     </row>
     <row r="6871">
-      <c r="A6871" s="11"/>
+      <c r="A6871" s="13"/>
       <c r="B6871" s="2"/>
       <c r="C6871" s="6"/>
     </row>
     <row r="6872">
-      <c r="A6872" s="11"/>
+      <c r="A6872" s="13"/>
       <c r="B6872" s="2"/>
       <c r="C6872" s="6"/>
     </row>
     <row r="6873">
-      <c r="A6873" s="11"/>
+      <c r="A6873" s="13"/>
       <c r="B6873" s="2"/>
       <c r="C6873" s="6"/>
     </row>
     <row r="6874">
-      <c r="A6874" s="11"/>
+      <c r="A6874" s="13"/>
       <c r="B6874" s="2"/>
       <c r="C6874" s="6"/>
     </row>
     <row r="6875">
-      <c r="A6875" s="11"/>
+      <c r="A6875" s="13"/>
       <c r="B6875" s="2"/>
       <c r="C6875" s="6"/>
     </row>
     <row r="6876">
-      <c r="A6876" s="11"/>
+      <c r="A6876" s="13"/>
       <c r="B6876" s="2"/>
       <c r="C6876" s="6"/>
     </row>
     <row r="6877">
-      <c r="A6877" s="11"/>
+      <c r="A6877" s="13"/>
       <c r="B6877" s="2"/>
       <c r="C6877" s="6"/>
     </row>
     <row r="6878">
-      <c r="A6878" s="11"/>
+      <c r="A6878" s="13"/>
       <c r="B6878" s="2"/>
       <c r="C6878" s="6"/>
     </row>
     <row r="6879">
-      <c r="A6879" s="11"/>
+      <c r="A6879" s="13"/>
       <c r="B6879" s="2"/>
       <c r="C6879" s="6"/>
     </row>
     <row r="6880">
-      <c r="A6880" s="11"/>
+      <c r="A6880" s="13"/>
       <c r="B6880" s="2"/>
       <c r="C6880" s="6"/>
     </row>
     <row r="6881">
-      <c r="A6881" s="11"/>
+      <c r="A6881" s="13"/>
       <c r="B6881" s="2"/>
       <c r="C6881" s="6"/>
     </row>
     <row r="6882">
-      <c r="A6882" s="11"/>
+      <c r="A6882" s="13"/>
       <c r="B6882" s="2"/>
       <c r="C6882" s="6"/>
     </row>
     <row r="6883">
-      <c r="A6883" s="11"/>
+      <c r="A6883" s="13"/>
       <c r="B6883" s="2"/>
       <c r="C6883" s="6"/>
     </row>
     <row r="6884">
-      <c r="A6884" s="11"/>
+      <c r="A6884" s="13"/>
       <c r="B6884" s="2"/>
       <c r="C6884" s="6"/>
     </row>
     <row r="6885">
-      <c r="A6885" s="11"/>
+      <c r="A6885" s="13"/>
       <c r="B6885" s="2"/>
       <c r="C6885" s="6"/>
     </row>
     <row r="6886">
-      <c r="A6886" s="11"/>
+      <c r="A6886" s="13"/>
       <c r="B6886" s="2"/>
       <c r="C6886" s="6"/>
     </row>
     <row r="6887">
-      <c r="A6887" s="11"/>
+      <c r="A6887" s="13"/>
       <c r="B6887" s="2"/>
       <c r="C6887" s="6"/>
     </row>
     <row r="6888">
-      <c r="A6888" s="11"/>
+      <c r="A6888" s="13"/>
       <c r="B6888" s="2"/>
       <c r="C6888" s="6"/>
     </row>
     <row r="6889">
-      <c r="A6889" s="11"/>
+      <c r="A6889" s="13"/>
       <c r="B6889" s="2"/>
       <c r="C6889" s="6"/>
     </row>
     <row r="6890">
-      <c r="A6890" s="11"/>
+      <c r="A6890" s="13"/>
       <c r="B6890" s="2"/>
       <c r="C6890" s="6"/>
     </row>
     <row r="6891">
-      <c r="A6891" s="11"/>
+      <c r="A6891" s="13"/>
       <c r="B6891" s="2"/>
       <c r="C6891" s="6"/>
     </row>
     <row r="6892">
-      <c r="A6892" s="11"/>
+      <c r="A6892" s="13"/>
       <c r="B6892" s="2"/>
       <c r="C6892" s="6"/>
     </row>
     <row r="6893">
-      <c r="A6893" s="11"/>
+      <c r="A6893" s="13"/>
       <c r="B6893" s="2"/>
       <c r="C6893" s="6"/>
     </row>
     <row r="6894">
-      <c r="A6894" s="11"/>
+      <c r="A6894" s="13"/>
       <c r="B6894" s="2"/>
       <c r="C6894" s="6"/>
     </row>
     <row r="6895">
-      <c r="A6895" s="11"/>
+      <c r="A6895" s="13"/>
       <c r="B6895" s="2"/>
       <c r="C6895" s="6"/>
     </row>
     <row r="6896">
-      <c r="A6896" s="11"/>
+      <c r="A6896" s="13"/>
       <c r="B6896" s="2"/>
       <c r="C6896" s="6"/>
     </row>
     <row r="6897">
-      <c r="A6897" s="11"/>
+      <c r="A6897" s="13"/>
       <c r="B6897" s="2"/>
       <c r="C6897" s="6"/>
     </row>
     <row r="6898">
-      <c r="A6898" s="11"/>
+      <c r="A6898" s="13"/>
       <c r="B6898" s="2"/>
       <c r="C6898" s="6"/>
     </row>
     <row r="6899">
-      <c r="A6899" s="11"/>
+      <c r="A6899" s="13"/>
       <c r="B6899" s="2"/>
       <c r="C6899" s="6"/>
     </row>
     <row r="6900">
-      <c r="A6900" s="11"/>
+      <c r="A6900" s="13"/>
       <c r="B6900" s="2"/>
       <c r="C6900" s="6"/>
     </row>
     <row r="6901">
-      <c r="A6901" s="11"/>
+      <c r="A6901" s="13"/>
       <c r="B6901" s="2"/>
       <c r="C6901" s="6"/>
     </row>
     <row r="6902">
-      <c r="A6902" s="11"/>
+      <c r="A6902" s="13"/>
       <c r="B6902" s="2"/>
       <c r="C6902" s="6"/>
     </row>

--- a/Data/Pun_ts_price.xlsx
+++ b/Data/Pun_ts_price.xlsx
@@ -66497,114 +66497,246 @@
       </c>
     </row>
     <row r="6016">
-      <c r="A6016" s="13"/>
-      <c r="B6016" s="2"/>
-      <c r="C6016" s="6"/>
+      <c r="A6016" s="11">
+        <v>46211.0</v>
+      </c>
+      <c r="B6016" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6016" s="12">
+        <v>146.427282</v>
+      </c>
     </row>
     <row r="6017">
-      <c r="A6017" s="13"/>
-      <c r="B6017" s="2"/>
-      <c r="C6017" s="6"/>
+      <c r="A6017" s="11">
+        <v>46212.0</v>
+      </c>
+      <c r="B6017" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6017" s="12">
+        <v>153.733705</v>
+      </c>
     </row>
     <row r="6018">
-      <c r="A6018" s="13"/>
-      <c r="B6018" s="2"/>
-      <c r="C6018" s="6"/>
+      <c r="A6018" s="11">
+        <v>46213.0</v>
+      </c>
+      <c r="B6018" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6018" s="12">
+        <v>148.426305</v>
+      </c>
     </row>
     <row r="6019">
-      <c r="A6019" s="13"/>
-      <c r="B6019" s="2"/>
-      <c r="C6019" s="6"/>
+      <c r="A6019" s="11">
+        <v>46214.0</v>
+      </c>
+      <c r="B6019" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6019" s="12">
+        <v>144.108266</v>
+      </c>
     </row>
     <row r="6020">
-      <c r="A6020" s="13"/>
-      <c r="B6020" s="2"/>
-      <c r="C6020" s="6"/>
+      <c r="A6020" s="11">
+        <v>46215.0</v>
+      </c>
+      <c r="B6020" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6020" s="12">
+        <v>129.538302</v>
+      </c>
     </row>
     <row r="6021">
-      <c r="A6021" s="13"/>
-      <c r="B6021" s="2"/>
-      <c r="C6021" s="6"/>
+      <c r="A6021" s="11">
+        <v>46216.0</v>
+      </c>
+      <c r="B6021" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6021" s="12">
+        <v>152.108264</v>
+      </c>
     </row>
     <row r="6022">
-      <c r="A6022" s="13"/>
-      <c r="B6022" s="2"/>
-      <c r="C6022" s="6"/>
+      <c r="A6022" s="11">
+        <v>46217.0</v>
+      </c>
+      <c r="B6022" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6022" s="12">
+        <v>151.886774</v>
+      </c>
     </row>
     <row r="6023">
-      <c r="A6023" s="13"/>
-      <c r="B6023" s="2"/>
-      <c r="C6023" s="6"/>
+      <c r="A6023" s="11">
+        <v>46218.0</v>
+      </c>
+      <c r="B6023" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6023" s="12">
+        <v>165.906756</v>
+      </c>
     </row>
     <row r="6024">
-      <c r="A6024" s="13"/>
-      <c r="B6024" s="2"/>
-      <c r="C6024" s="6"/>
+      <c r="A6024" s="11">
+        <v>46219.0</v>
+      </c>
+      <c r="B6024" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6024" s="12">
+        <v>170.473369</v>
+      </c>
     </row>
     <row r="6025">
-      <c r="A6025" s="13"/>
-      <c r="B6025" s="2"/>
-      <c r="C6025" s="6"/>
+      <c r="A6025" s="11">
+        <v>46220.0</v>
+      </c>
+      <c r="B6025" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6025" s="12">
+        <v>168.728406</v>
+      </c>
     </row>
     <row r="6026">
-      <c r="A6026" s="13"/>
-      <c r="B6026" s="2"/>
-      <c r="C6026" s="6"/>
+      <c r="A6026" s="11">
+        <v>46221.0</v>
+      </c>
+      <c r="B6026" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6026" s="12">
+        <v>166.835055</v>
+      </c>
     </row>
     <row r="6027">
-      <c r="A6027" s="13"/>
-      <c r="B6027" s="2"/>
-      <c r="C6027" s="6"/>
+      <c r="A6027" s="11">
+        <v>46222.0</v>
+      </c>
+      <c r="B6027" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6027" s="12">
+        <v>152.693564</v>
+      </c>
     </row>
     <row r="6028">
-      <c r="A6028" s="13"/>
-      <c r="B6028" s="2"/>
-      <c r="C6028" s="6"/>
+      <c r="A6028" s="11">
+        <v>46223.0</v>
+      </c>
+      <c r="B6028" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6028" s="12">
+        <v>172.563314</v>
+      </c>
     </row>
     <row r="6029">
-      <c r="A6029" s="13"/>
-      <c r="B6029" s="2"/>
-      <c r="C6029" s="6"/>
+      <c r="A6029" s="11">
+        <v>46224.0</v>
+      </c>
+      <c r="B6029" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6029" s="12">
+        <v>177.29975</v>
+      </c>
     </row>
     <row r="6030">
-      <c r="A6030" s="13"/>
-      <c r="B6030" s="2"/>
-      <c r="C6030" s="6"/>
+      <c r="A6030" s="11">
+        <v>46225.0</v>
+      </c>
+      <c r="B6030" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6030" s="12">
+        <v>170.206665</v>
+      </c>
     </row>
     <row r="6031">
-      <c r="A6031" s="13"/>
-      <c r="B6031" s="2"/>
-      <c r="C6031" s="6"/>
+      <c r="A6031" s="11">
+        <v>46226.0</v>
+      </c>
+      <c r="B6031" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6031" s="12">
+        <v>181.080908</v>
+      </c>
     </row>
     <row r="6032">
-      <c r="A6032" s="13"/>
-      <c r="B6032" s="2"/>
-      <c r="C6032" s="6"/>
+      <c r="A6032" s="11">
+        <v>46227.0</v>
+      </c>
+      <c r="B6032" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6032" s="12">
+        <v>170.234746</v>
+      </c>
     </row>
     <row r="6033">
-      <c r="A6033" s="13"/>
-      <c r="B6033" s="2"/>
-      <c r="C6033" s="6"/>
+      <c r="A6033" s="11">
+        <v>46228.0</v>
+      </c>
+      <c r="B6033" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6033" s="12">
+        <v>157.082125</v>
+      </c>
     </row>
     <row r="6034">
-      <c r="A6034" s="13"/>
-      <c r="B6034" s="2"/>
-      <c r="C6034" s="6"/>
+      <c r="A6034" s="11">
+        <v>46229.0</v>
+      </c>
+      <c r="B6034" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6034" s="12">
+        <v>161.36289</v>
+      </c>
     </row>
     <row r="6035">
-      <c r="A6035" s="13"/>
-      <c r="B6035" s="2"/>
-      <c r="C6035" s="6"/>
+      <c r="A6035" s="11">
+        <v>46230.0</v>
+      </c>
+      <c r="B6035" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6035" s="12">
+        <v>185.058184</v>
+      </c>
     </row>
     <row r="6036">
-      <c r="A6036" s="13"/>
-      <c r="B6036" s="2"/>
-      <c r="C6036" s="6"/>
+      <c r="A6036" s="11">
+        <v>46231.0</v>
+      </c>
+      <c r="B6036" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6036" s="12">
+        <v>176.066855</v>
+      </c>
     </row>
     <row r="6037">
-      <c r="A6037" s="13"/>
-      <c r="B6037" s="2"/>
-      <c r="C6037" s="6"/>
+      <c r="A6037" s="11">
+        <v>46232.0</v>
+      </c>
+      <c r="B6037" s="8">
+        <v>2026.0</v>
+      </c>
+      <c r="C6037" s="12">
+        <v>177.132011</v>
+      </c>
     </row>
     <row r="6038">
       <c r="A6038" s="13"/>
